--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -2662,7 +2662,7 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。四色が並ぶ　［17-20秒］</t>
+          <t>真俯瞰。四色が並ぶ。この画のまま、ナレーション「毎日をカラフルに」が一言だけ入る　［17-20秒］</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr"/>
@@ -2682,7 +2682,7 @@
       <c r="E102" s="7" t="inlineStr"/>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>ナレーション「毎日をカラフルに」が一言だけ入る　［17-20秒］</t>
+          <t>そのままロゴ。テロップは出さない　［17-20秒］</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr"/>
@@ -2702,7 +2702,7 @@
       <c r="E103" s="7" t="inlineStr"/>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>テロップ 1.5秒 → ロゴ 0.5秒　［17-20秒］</t>
+          <t>―　［17-20秒］</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -2662,7 +2662,7 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。四色が並ぶ。この画のまま、ナレーション「毎日をカラフルに」が一言だけ入る　［17-20秒］</t>
+          <t>真俯瞰。四色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る　［17-20秒］</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr"/>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>白い壁の前。正面。壁に英語一文を重ねる　［27-30秒］</t>
+          <t>最初と同じフェンスの画角に戻る　［27-30秒］</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr"/>
@@ -3534,7 +3534,7 @@
       <c r="E141" s="7" t="inlineStr"/>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>一文が消える　［27-30秒］</t>
+          <t>背景の街だけが動いている　［27-30秒］</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr"/>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>店のガラスの反射に映る（引き）　［0-6秒］</t>
+          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr"/>
@@ -3730,7 +3730,7 @@
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>街を歩く。横移動で追う　［0-6秒］</t>
+          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr"/>
@@ -3750,7 +3750,7 @@
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>信号待ち。手元の鞄だけに寄る　［0-6秒］</t>
+          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr"/>
@@ -3770,7 +3770,7 @@
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>電車が通り過ぎる（ブレ＝トランジション）　［6-11秒］</t>
+          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>抜けたら、別の場所を歩いている　［6-11秒］</t>
+          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr"/>
@@ -3810,7 +3810,7 @@
       <c r="E154" s="7" t="inlineStr"/>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>看板・柱がフレームを横切る（二度目のつなぎ）　［6-11秒］</t>
+          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr"/>
@@ -3830,7 +3830,7 @@
       <c r="E155" s="7" t="inlineStr"/>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>手すりに置き、真俯瞰でA4とノートPCを入れる　［11-18秒］</t>
+          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr"/>
@@ -3850,7 +3850,7 @@
       <c r="E156" s="7" t="inlineStr"/>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>寄り。内ポケットに名刺入れ・鍵・携帯　［11-18秒］</t>
+          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr"/>
@@ -3870,7 +3870,7 @@
       <c r="E157" s="7" t="inlineStr"/>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>財布に何かを差し込む超マクロ　［11-18秒］</t>
+          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr"/>
@@ -3890,7 +3890,7 @@
       <c r="E158" s="7" t="inlineStr"/>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>カフェの窓際。自然光・浅い被写界深度　［18-23秒］</t>
+          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr"/>
@@ -3910,7 +3910,7 @@
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>金具のロゴに超マクロ　［18-23秒］</t>
+          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr"/>
@@ -3930,7 +3930,7 @@
       <c r="E160" s="7" t="inlineStr"/>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>珈琲を置く手と鞄が、同じ画面に入る　［18-23秒］</t>
+          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
         </is>
       </c>
       <c r="G160" s="11" t="inlineStr"/>
@@ -3950,7 +3950,7 @@
       <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>高い場所に立つ（引き・映画的）　［23-27秒］</t>
+          <t>手すりの前で立ち止まる　［24-27秒］</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr"/>
@@ -3970,7 +3970,7 @@
       <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>街に置く。背景をボカして流す　［23-27秒］</t>
+          <t>白い服の寄り。革の色との対比　［24-27秒］</t>
         </is>
       </c>
       <c r="G162" s="11" t="inlineStr"/>
@@ -3990,7 +3990,7 @@
       <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>夕方の斜光。歩く後ろ姿（引き）　［23-27秒］</t>
+          <t>真俯瞰。保存袋・靴・小物まで並べる　［24-27秒］</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ショットリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>永尾社長が画に映る。役職テロップはこの画角で出す　［18-28秒］</t>
+          <t>永尾社長が画に映る。革を背景にしたバストショット。役職テロップはこの画角で出す　［18-28秒］</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>座って正面。名前は出さず「使っている人」として自己紹介　［秒数未定］</t>
+          <t>バストショット。窓を背にして、手前に植物を置いてボカす。名前は出さず「使っている人」として自己紹介　［8-18秒］</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr"/>
@@ -870,7 +870,7 @@
       <c r="E21" s="7" t="inlineStr"/>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>手元の BROOKLYN MUSEUM の鞄が画面に入る　［秒数未定］</t>
+          <t>同じ画角。カメラは一度も動かさない　［8-18秒］</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr"/>
@@ -890,7 +890,7 @@
       <c r="E22" s="7" t="inlineStr"/>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>「なぜこれを選んだか」を聞く　［秒数未定］</t>
+          <t>話した言葉をそのままテロップで出す（この参考動画の出し方をそのまま真似る）　［8-18秒］</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr"/>
@@ -910,7 +910,7 @@
       <c r="E23" s="7" t="inlineStr"/>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>購入前に迷っていた話　［秒数未定］</t>
+          <t>外に出る。空を入れて気分を変える　［42-52秒］</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr"/>
@@ -930,7 +930,7 @@
       <c r="E24" s="7" t="inlineStr"/>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>買ってから変わったことを一言で　［秒数未定］</t>
+          <t>引きの画に人が入る。買ってから変わったことを語る　［42-52秒］</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr"/>
@@ -950,7 +950,7 @@
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>表情のアップ。台本にない一言を拾う　［秒数未定］</t>
+          <t>インタビューの画に戻る。表情のアップ　［42-52秒］</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       <c r="E27" s="7" t="inlineStr"/>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>高度を下げ、建物に寄る（ハイアングル）　［0-6秒］</t>
+          <t>高度を下げ、建物に寄る　［0-6秒］</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       <c r="E30" s="7" t="inlineStr"/>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>高度を下げ、外観と看板へ（ローアングルに切り替え）。街の音　［0-10秒］</t>
+          <t>高度を下げ、建物の全景へ。街の音　［0-10秒］</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>工房の全景（ハイアングル）。規模が分かる画角　［10-25秒］</t>
+          <t>工房の全景（引き）。規模が分かる画角　［10-25秒］</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>機械と人が同じ画面に入る引き。台数と人数が分かる　［10-25秒］</t>
+          <t>機械と人が同じ画面に入る。台数と人数が分かる　［10-25秒］</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>作業台に原反が広がる（真俯瞰）。扱える革の大きさを示す　［25-42秒］</t>
+          <t>原反が積まれている。扱える革の量を示す　［25-42秒］</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr"/>
@@ -1278,7 +1278,7 @@
       <c r="E39" s="7" t="inlineStr"/>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>刃が進み、革の繊維が開いていく（超マクロ・同じ画角のまま）　［0-3秒］</t>
+          <t>刃が進み、革の繊維が開いていく（同じ画角のまま）　［0-3秒］</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
       <c r="E42" s="7" t="inlineStr"/>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>四十五度。角を丸く回して切る　［3-11秒］</t>
+          <t>角を回して切る（横）　［3-11秒］</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr"/>
@@ -1358,7 +1358,7 @@
       <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>切り落とした端材が台に落ちる（寄り）　［3-11秒］</t>
+          <t>切り終わり。断面がまだ生成りのまま残っている　［3-11秒］</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
       <c r="E45" s="7" t="inlineStr"/>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。等間隔に並んだ穴だけが画面に残る　［11-17秒］</t>
+          <t>等間隔に並んだ穴だけが画面に残る　［11-17秒］</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       <c r="E46" s="7" t="inlineStr"/>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。作業台と職人の手全体（引き）。ここで一度引く　［11-17秒］</t>
+          <t>目打ちの超マクロ。革の断面と穴が同じ画面に入る　［11-17秒］</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       <c r="E49" s="7" t="inlineStr"/>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>裁ち上がったパーツが並ぶ（真俯瞰）。量産も少量も同じ場所でできる　［42-62秒］</t>
+          <t>裁ち上がったパーツが並ぶ。量産も少量も同じ場所でできる　［42-62秒］</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。針が革を抜ける　［17-24秒］</t>
+          <t>針が革を抜ける（寄り）　［17-24秒］</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr"/>
@@ -1698,7 +1698,7 @@
       <c r="E58" s="7" t="inlineStr"/>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>横から。目だけのアップ。顔全体は入れない　［17-24秒］</t>
+          <t>縫い目に沿って仕上げる。手の動きだけを見せる　［17-24秒］</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr"/>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>塗る直前。断面はまだ生成りのまま（超マクロ）　［24-33秒］</t>
+          <t>塗り始め。道具の先が断面に触れる（超マクロ）　［24-33秒］</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr"/>
@@ -1810,7 +1810,7 @@
       <c r="E63" s="7" t="inlineStr"/>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>手が止まる。職人の声が一言だけ入る（台本なし）　［33-40秒］</t>
+          <t>使われている場所に置かれる → テロップ → ロゴ　［33-40秒］</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr"/>
@@ -1830,7 +1830,7 @@
       <c r="E64" s="7" t="inlineStr"/>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>使われている場所に置かれる → テロップ → ロゴ　［33-40秒］</t>
+          <t>―　［33-40秒］</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr"/>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>原反が広げられる（真俯瞰）　［45-55秒］</t>
+          <t>原反が積まれている（引き）　［45-55秒］</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr"/>
@@ -1902,7 +1902,7 @@
       <c r="E67" s="7" t="inlineStr"/>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>検品。詳しい工程は6本目（OEM案内）で見せる　［45-55秒］</t>
+          <t>設備で仕上げる。詳しい工程は6本目（OEM案内）で見せる　［45-55秒］</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr"/>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>縫い目と断面を目で確かめる（寄り）。作業音が消える　［102-122秒］</t>
+          <t>一点を手に取り、光にかざす。作業音が消える　［102-122秒］</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr"/>
@@ -1954,7 +1954,7 @@
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>一点を手に取り、光にかざす　［102-122秒］</t>
+          <t>寸法と縫い目を目で確かめる（寄り）　［102-122秒］</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr"/>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>画面上で型紙を引く（CAD）　［37-45秒］</t>
+          <t>手が図面をなぞる（寄り）　［37-45秒］</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
       <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>型紙を革に当て、取り都合を決める　［37-45秒］</t>
+          <t>型紙・図面の俯瞰　［37-45秒］</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr"/>
@@ -2118,7 +2118,7 @@
       <c r="E76" s="7" t="inlineStr"/>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>数値を入れる。設計はここで終わり、手に渡る　［37-45秒］</t>
+          <t>机で数値を決める。設計はここで終わり、手に渡る　［37-45秒］</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>企画中の新作サンプルとスケッチが並ぶ（引き）　［28-37秒］</t>
+          <t>革が色ごとに並ぶ。扱える色数がそのまま伝わる　［28-37秒］</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
       <c r="E78" s="7" t="inlineStr"/>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>図面の束をめくる（俯瞰）　［28-37秒］</t>
+          <t>色を選ぶ（寄り）　［28-37秒］</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>手が図面をなぞる（寄り）　［28-37秒］</t>
+          <t>工房に革が吊るされている（引き）　［28-37秒］</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>コラボの実績から始める。年号テロップを重ねる（1980 SHIPS〜）　［6-18秒］</t>
+          <t>コラボの実績から始める。年号テロップを重ねる（1980 SHIPS〜）※現物の資料を複写して使う　［6-18秒］</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
       <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>昔の店舗の写真・当時のカタログを複写して差し込む（撮影して差し替え）　［6-18秒］</t>
+          <t>昔の店舗の写真・当時のカタログを複写して差し込む　［6-18秒］</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>真っ黒。細い光の帯が、革の断面だけを照らす　［0-4秒］</t>
+          <t>真っ黒。細い光の帯が一本だけ立つ　［0-4秒］</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr"/>
@@ -2310,7 +2310,7 @@
       <c r="E84" s="7" t="inlineStr"/>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>光の帯がゆっくり動き、革の表情だけが変わる　［0-4秒］</t>
+          <t>光の帯がゆっくり動く。無音から低いBGMが立ち上がる　［0-4秒］</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr"/>
@@ -2330,7 +2330,7 @@
       <c r="E85" s="7" t="inlineStr"/>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>無音から、低いBGMが立ち上がる　［0-4秒］</t>
+          <t>―　［0-4秒］</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr"/>
@@ -2350,7 +2350,7 @@
       <c r="E86" s="7" t="inlineStr"/>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>黒の上に道具だけが並ぶ（真俯瞰）　［4-8秒］</t>
+          <t>道具と染料が並ぶ。手がその前に入る　［4-8秒］</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr"/>
@@ -2370,7 +2370,7 @@
       <c r="E87" s="7" t="inlineStr"/>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>一本を手に取る（超マクロ）。金属の音だけ　［4-8秒］</t>
+          <t>革を持ち上げる。腕時計・指輪は外す　［4-8秒］</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       <c r="E89" s="7" t="inlineStr"/>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>手だけ。革を折り、角を作る。腕時計・指輪は外す　［8-15秒］</t>
+          <t>手だけ。革を折る　［8-15秒］</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr"/>
@@ -2430,7 +2430,7 @@
       <c r="E90" s="7" t="inlineStr"/>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>角が立ち上がる（超マクロ）　［8-15秒］</t>
+          <t>縁を押さえる（超マクロ）　［8-15秒］</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr"/>
@@ -2450,7 +2450,7 @@
       <c r="E91" s="7" t="inlineStr"/>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>手が革を押さえ直す。顔と工房は一切映さない　［8-15秒］</t>
+          <t>角が立ち上がる。顔と工房は一切映さない　［8-15秒］</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr"/>
@@ -2470,7 +2470,7 @@
       <c r="E92" s="7" t="inlineStr"/>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>白手袋で金具を持ち、取り付ける。金属が触れる音　［15-19秒］</t>
+          <t>白手袋で金具を持つ。金属が触れる音　［15-19秒］</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr"/>
@@ -2490,7 +2490,7 @@
       <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>金具が座る瞬間（超マクロ）。カチリと一音　［15-19秒］</t>
+          <t>金具を取り付ける（超マクロ）。カチリと一音　［15-19秒］</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr"/>
@@ -2530,7 +2530,7 @@
       <c r="E95" s="7" t="inlineStr"/>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>コバに染料を入れる（超マクロ）　［19-25秒］</t>
+          <t>コバに染料を入れる（超マクロ）　※参考動画にこの工程は映っていない。2本目の参考動画（コバ塗り）を見て画角を決める　［19-25秒］</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr"/>
@@ -2550,7 +2550,7 @@
       <c r="E96" s="7" t="inlineStr"/>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>磨く。光が断面に反射する角度を探す　［19-25秒］</t>
+          <t>磨く。光が断面に反射する角度を探す（超マクロ）　［19-25秒］</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr"/>
@@ -2590,7 +2590,7 @@
       <c r="E98" s="7" t="inlineStr"/>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>完成品が黒の中に浮かぶ。上から一灯だけ　［25-28秒］</t>
+          <t>完成品を持ち上げる　［25-28秒］</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr"/>
@@ -2610,7 +2610,7 @@
       <c r="E99" s="7" t="inlineStr"/>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>BGMが止まる。画面が黒に戻る　［25-28秒］</t>
+          <t>道具の前に置く。上から一灯だけ　［25-28秒］</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr"/>
@@ -2630,7 +2630,7 @@
       <c r="E100" s="7" t="inlineStr"/>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>ロゴのみ。テロップは出さない　［25-28秒］</t>
+          <t>金具のマクロ → BGMが止まる → ロゴのみ。テロップは出さない　［25-28秒］</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。四色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る　［17-20秒］</t>
+          <t>四色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る　［17-20秒］</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr"/>
@@ -2682,7 +2682,7 @@
       <c r="E102" s="7" t="inlineStr"/>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>そのままロゴ。テロップは出さない　［17-20秒］</t>
+          <t>そのままロゴ。締めのテロップは出さない　［17-20秒］</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr"/>
@@ -2750,7 +2750,7 @@
       <c r="E105" s="7" t="inlineStr"/>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>型押しのロゴ、ハンドルの付け根　［0-4秒］</t>
+          <t>ストラップと縫い目（モノクロのまま）　［0-4秒］</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
       <c r="E106" s="7" t="inlineStr"/>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>縫い目を横になぞる（モノクロのまま）　［0-4秒］</t>
+          <t>金具の質感（モノクロのまま）　［0-4秒］</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
       <c r="E109" s="7" t="inlineStr"/>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>ファスナーを開ける。中は空　［4-7秒］</t>
+          <t>鞄を開ける。中は空　［4-7秒］</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr"/>
@@ -2950,7 +2950,7 @@
       <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>ファスナーを閉じる。一音　［13-17秒］</t>
+          <t>最後の一つを入れる。ここで手が止まる　［13-17秒］</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr"/>
@@ -3050,7 +3050,7 @@
       <c r="E120" s="7" t="inlineStr"/>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>テロップ　［21-25秒］</t>
+          <t>テロップ「急がば、定位置。」　［21-25秒］</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr"/>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>BROOKLYN MUSEUM 店舗の外観（撮影して差し替え）　［55-66秒］</t>
+          <t>BROOKLYN MUSEUM 店舗の外観　［55-66秒］</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr"/>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>買った日の再現。リボンをほどく　［秒数未定］</t>
+          <t>商品の真俯瞰。声は続いたまま　［30-42秒］</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr"/>
@@ -3194,7 +3194,7 @@
       <c r="E126" s="7" t="inlineStr"/>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>開けた瞬間の表情　［秒数未定］</t>
+          <t>売り場・棚の引き　［30-42秒］</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>光にかざして見る　［秒数未定］</t>
+          <t>ディテールの寄り。良かった点を語っている場所に重ねる　［30-42秒］</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>実際に使っているシーン（移動中）　［秒数未定］</t>
+          <t>ここから画はBロールに変わるが、声はそのまま流し続ける　［18-30秒］</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr"/>
@@ -3266,7 +3266,7 @@
       <c r="E129" s="7" t="inlineStr"/>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>声だけ流しながら、日常の画を重ねる　［秒数未定］</t>
+          <t>同じ場所を別の角度で。声に合わせて切り替える　［18-30秒］</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr"/>
@@ -3286,7 +3286,7 @@
       <c r="E130" s="7" t="inlineStr"/>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>良かった点を具体的なエピソードで語ってもらう　［秒数未定］</t>
+          <t>落ち着いた場所での一枚。間を作る　［18-30秒］</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr"/>
@@ -3374,7 +3374,7 @@
       <c r="E134" s="7" t="inlineStr"/>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>店を出る／使っている場所で迎える（引き）　［秒数未定］</t>
+          <t>外観のロー。空を入れて見上げる。まだ人は出さない　［0-8秒］</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr"/>
@@ -3394,7 +3394,7 @@
       <c r="E135" s="7" t="inlineStr"/>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>袋を持って歩く後ろ姿　［秒数未定］</t>
+          <t>店舗／工房の全景（引き）。人が出入りする　［0-8秒］</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr"/>
@@ -3414,7 +3414,7 @@
       <c r="E136" s="7" t="inlineStr"/>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>手元の袋・鞄に寄る　［秒数未定］</t>
+          <t>窓辺と光。商品が置いてある（寄り）　［0-8秒］</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr"/>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>鞄を持って歩き出す後ろ姿　［秒数未定］</t>
+          <t>最後の一言。台本にない言葉を拾う　［52-60秒］</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr"/>
@@ -3462,7 +3462,7 @@
       <c r="E138" s="7" t="inlineStr"/>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>テロップ　［秒数未定］</t>
+          <t>テロップ　［52-60秒］</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr"/>
@@ -3482,7 +3482,7 @@
       <c r="E139" s="7" t="inlineStr"/>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>ロゴ　［秒数未定］</t>
+          <t>ロゴ　［52-60秒］</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr"/>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>白い壁の前（④の締め）</t>
+          <t>自宅の玄関まわり（①）</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>④ S6-1</t>
+          <t>① S1-1</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>最初と同じフェンスの画角に戻る　［27-30秒］</t>
+          <t>玄関。財布をポケットに入れる（寄り）　［0-3秒］</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr"/>
@@ -3528,13 +3528,13 @@
       <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>④ S6-2</t>
+          <t>① S1-2</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr"/>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>背景の街だけが動いている　［27-30秒］</t>
+          <t>鍵を取る手元（超寄り）。ここではまだ色を見せない　［0-3秒］</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr"/>
@@ -3548,13 +3548,13 @@
       <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>④ S6-3</t>
+          <t>① S1-3</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr"/>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>ロゴのみ。テロップは出さない　［27-30秒］</t>
+          <t>ドアノブに手がかかる（超寄り）　［0-3秒］</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr"/>
@@ -3565,24 +3565,16 @@
         <v>132</v>
       </c>
       <c r="B143" s="7" t="inlineStr"/>
-      <c r="C143" s="9" t="inlineStr">
-        <is>
-          <t>自宅の玄関まわり（①）</t>
-        </is>
-      </c>
+      <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>① S1-1</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>① S2-1</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>玄関。財布をポケットに入れる（寄り）　［0-3秒］</t>
+          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［3-6秒］</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr"/>
@@ -3596,13 +3588,13 @@
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>① S1-2</t>
+          <t>① S2-2</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>鍵を取る手元（超寄り）。ここではまだ色を見せない　［0-3秒］</t>
+          <t>同じ画角。車が手前を横切る（トランジション）　［3-6秒］</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr"/>
@@ -3616,13 +3608,13 @@
       <c r="C145" s="7" t="inlineStr"/>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>① S1-3</t>
+          <t>① S2-3</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr"/>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>ドアノブに手がかかる（超寄り）　［0-3秒］</t>
+          <t>手元の革小物だけに寄る（超寄り・一色目）※この寄りは参考動画にはない　［3-6秒］</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr"/>
@@ -3633,16 +3625,24 @@
         <v>135</v>
       </c>
       <c r="B146" s="7" t="inlineStr"/>
-      <c r="C146" s="7" t="inlineStr"/>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>街歩き・夕方の斜光（④）</t>
+        </is>
+      </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>① S2-1</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr"/>
+          <t>④ S1-1</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>ドアが開き、外へ出る（引き・逆光）　［3-6秒］</t>
+          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr"/>
@@ -3656,13 +3656,13 @@
       <c r="C147" s="7" t="inlineStr"/>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>① S2-2</t>
+          <t>④ S1-2</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr"/>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>歩き出す足元（ロー）。手元の小物が一瞬だけ入る　［3-6秒］</t>
+          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr"/>
@@ -3676,13 +3676,13 @@
       <c r="C148" s="7" t="inlineStr"/>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>① S2-3</t>
+          <t>④ S1-3</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr"/>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>引きの全身。この画角を最後まで使い回す（基準カット）　［3-6秒］</t>
+          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr"/>
@@ -3693,24 +3693,16 @@
         <v>138</v>
       </c>
       <c r="B149" s="7" t="inlineStr"/>
-      <c r="C149" s="9" t="inlineStr">
-        <is>
-          <t>街歩き・夕方の斜光（④）</t>
-        </is>
-      </c>
+      <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>④ S1-1</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>④ S2-1</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
+          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr"/>
@@ -3724,13 +3716,13 @@
       <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>④ S1-2</t>
+          <t>④ S2-2</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
+          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr"/>
@@ -3744,13 +3736,13 @@
       <c r="C151" s="7" t="inlineStr"/>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>④ S1-3</t>
+          <t>④ S2-3</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
+          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr"/>
@@ -3764,13 +3756,13 @@
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>④ S2-1</t>
+          <t>④ S3-1</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
+          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr"/>
@@ -3784,13 +3776,13 @@
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>④ S2-2</t>
+          <t>④ S3-2</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
+          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr"/>
@@ -3804,13 +3796,13 @@
       <c r="C154" s="7" t="inlineStr"/>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>④ S2-3</t>
+          <t>④ S3-3</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr"/>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
+          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr"/>
@@ -3824,13 +3816,13 @@
       <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>④ S3-1</t>
+          <t>④ S4-1</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr"/>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
+          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr"/>
@@ -3844,13 +3836,13 @@
       <c r="C156" s="7" t="inlineStr"/>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>④ S3-2</t>
+          <t>④ S4-2</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr"/>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
+          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr"/>
@@ -3864,13 +3856,13 @@
       <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>④ S3-3</t>
+          <t>④ S4-3</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr"/>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
+          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr"/>
@@ -3884,13 +3876,13 @@
       <c r="C158" s="7" t="inlineStr"/>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>④ S4-1</t>
+          <t>④ S5-1</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr"/>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
+          <t>手すりの前で立ち止まる　［24-30秒］</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr"/>
@@ -3904,13 +3896,13 @@
       <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>④ S4-2</t>
+          <t>④ S5-2</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
+          <t>真俯瞰。保存袋・小物まで並べる　［24-30秒］</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr"/>
@@ -3924,13 +3916,13 @@
       <c r="C160" s="7" t="inlineStr"/>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>④ S4-3</t>
+          <t>④ S5-3</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr"/>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
+          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
         </is>
       </c>
       <c r="G160" s="11" t="inlineStr"/>
@@ -3941,16 +3933,24 @@
         <v>150</v>
       </c>
       <c r="B161" s="7" t="inlineStr"/>
-      <c r="C161" s="7" t="inlineStr"/>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
+        </is>
+      </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>④ S5-1</t>
-        </is>
-      </c>
-      <c r="E161" s="7" t="inlineStr"/>
+          <t>① S3-1</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>手すりの前で立ち止まる　［24-27秒］</t>
+          <t>同じ画角のまま服が変わっている。小物の色も変わる　［6-10秒］</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr"/>
@@ -3964,13 +3964,13 @@
       <c r="C162" s="7" t="inlineStr"/>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>④ S5-2</t>
+          <t>① S3-2</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>白い服の寄り。革の色との対比　［24-27秒］</t>
+          <t>同じ道。二色目（キャメル）　［6-10秒］</t>
         </is>
       </c>
       <c r="G162" s="11" t="inlineStr"/>
@@ -3984,13 +3984,13 @@
       <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>④ S5-3</t>
+          <t>① S3-3</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。保存袋・靴・小物まで並べる　［24-27秒］</t>
+          <t>同じ道。三色目　［6-10秒］</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr"/>
@@ -4001,24 +4001,16 @@
         <v>153</v>
       </c>
       <c r="B164" s="7" t="inlineStr"/>
-      <c r="C164" s="9" t="inlineStr">
-        <is>
-          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
-        </is>
-      </c>
+      <c r="C164" s="7" t="inlineStr"/>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>① S3-1</t>
-        </is>
-      </c>
-      <c r="E164" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>① S4-1</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr"/>
       <c r="F164" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま服が変わっている。小物の色も変わる　［6-10秒］</t>
+          <t>場所が変わる。乗り場（引き）　［10-14秒］</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr"/>
@@ -4032,13 +4024,13 @@
       <c r="C165" s="7" t="inlineStr"/>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>① S3-2</t>
+          <t>① S4-2</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr"/>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>車が横切る → 抜けたら別の服・別の色　［6-10秒］</t>
+          <t>構内を歩く。同じ人・違う色　［10-14秒］</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr"/>
@@ -4052,13 +4044,13 @@
       <c r="C166" s="7" t="inlineStr"/>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>① S3-3</t>
+          <t>① S4-3</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr"/>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>手元の小物だけに寄る（キャメル）　［6-10秒］</t>
+          <t>四色目。ここまでで四色そろう　［10-14秒］</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr"/>
@@ -4072,13 +4064,13 @@
       <c r="C167" s="7" t="inlineStr"/>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>① S4-1</t>
+          <t>① S5-1</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr"/>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>電車が通り過ぎる → 抜けたら変わっている　［10-14秒］</t>
+          <t>会社の入口に着く　［14-17秒］</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr"/>
@@ -4092,13 +4084,13 @@
       <c r="C168" s="7" t="inlineStr"/>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>① S4-2</t>
+          <t>① S5-2</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>ホームの柱がフレームを横切る → 三色目へ　［10-14秒］</t>
+          <t>ロビーを歩く（引き）　［14-17秒］</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr"/>
@@ -4112,13 +4104,13 @@
       <c r="C169" s="7" t="inlineStr"/>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>① S4-3</t>
+          <t>① S5-3</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr"/>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>歩く足元（ロー）。手元の色だけが見える　［10-14秒］</t>
+          <t>立ち止まる。ここが到着点　［14-17秒］</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr"/>
@@ -4128,17 +4120,29 @@
       <c r="A170" s="7" t="n">
         <v>159</v>
       </c>
-      <c r="B170" s="7" t="inlineStr"/>
-      <c r="C170" s="7" t="inlineStr"/>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>締めカード</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。文字を組んで作る</t>
+        </is>
+      </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>① S5-1</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr"/>
+          <t>⑥ S9-1</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>エスカレーターを上がりきると変わっている　［14-17秒］</t>
+          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr"/>
@@ -4152,13 +4156,13 @@
       <c r="C171" s="7" t="inlineStr"/>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>① S5-2</t>
+          <t>⑥ S9-2</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>自動ドアのガラスに映る全身（四色目）　［14-17秒］</t>
+          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr"/>
@@ -4172,92 +4176,20 @@
       <c r="C172" s="7" t="inlineStr"/>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>① S5-3</t>
+          <t>⑥ S9-3</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="10" t="inlineStr">
         <is>
-          <t>会社のエントランス。ここが到着点　［14-17秒］</t>
+          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr"/>
       <c r="H172" s="11" t="inlineStr"/>
     </row>
-    <row r="173" ht="32" customHeight="1">
-      <c r="A173" s="7" t="n">
-        <v>162</v>
-      </c>
-      <c r="B173" s="8" t="inlineStr">
-        <is>
-          <t>締めカード</t>
-        </is>
-      </c>
-      <c r="C173" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。文字を組んで作る</t>
-        </is>
-      </c>
-      <c r="D173" s="7" t="inlineStr">
-        <is>
-          <t>⑥ S9-1</t>
-        </is>
-      </c>
-      <c r="E173" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
-      <c r="F173" s="10" t="inlineStr">
-        <is>
-          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
-        </is>
-      </c>
-      <c r="G173" s="11" t="inlineStr"/>
-      <c r="H173" s="11" t="inlineStr"/>
-    </row>
-    <row r="174" ht="32" customHeight="1">
-      <c r="A174" s="7" t="n">
-        <v>163</v>
-      </c>
-      <c r="B174" s="7" t="inlineStr"/>
-      <c r="C174" s="7" t="inlineStr"/>
-      <c r="D174" s="7" t="inlineStr">
-        <is>
-          <t>⑥ S9-2</t>
-        </is>
-      </c>
-      <c r="E174" s="7" t="inlineStr"/>
-      <c r="F174" s="10" t="inlineStr">
-        <is>
-          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
-        </is>
-      </c>
-      <c r="G174" s="11" t="inlineStr"/>
-      <c r="H174" s="11" t="inlineStr"/>
-    </row>
-    <row r="175" ht="32" customHeight="1">
-      <c r="A175" s="7" t="n">
-        <v>164</v>
-      </c>
-      <c r="B175" s="7" t="inlineStr"/>
-      <c r="C175" s="7" t="inlineStr"/>
-      <c r="D175" s="7" t="inlineStr">
-        <is>
-          <t>⑥ S9-3</t>
-        </is>
-      </c>
-      <c r="E175" s="7" t="inlineStr"/>
-      <c r="F175" s="10" t="inlineStr">
-        <is>
-          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
-        </is>
-      </c>
-      <c r="G175" s="11" t="inlineStr"/>
-      <c r="H175" s="11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A11:H175"/>
+  <autoFilter ref="A11:H172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ショットリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -679,12 +679,12 @@
       <c r="B13" s="7" t="inlineStr"/>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>佐藤さん（②に出演・声と手元）</t>
+          <t>三人共通の撮り方</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>②⑤⑥</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>この仕事を20年続けている理由を聞く。②S6で一言だけ使う（台本なし）</t>
+          <t>画角を三つ撮る：①バストショット（人物を左右に寄せ、空いた側にテロップ）②引き（背景に社名ロゴの壁）③横顔</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr"/>
@@ -708,13 +708,13 @@
       <c r="C14" s="7" t="inlineStr"/>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>②⑤⑥</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>作業音は別録りが必要なので、インタビューと手元カットは別のセッションにする</t>
+          <t>背景は必ず大きくボカす。明るい室内・窓・緑を背にする。役職テロップは日英二行</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr"/>
@@ -727,12 +727,12 @@
       <c r="B15" s="7" t="inlineStr"/>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>永尾社長（⑤・画に映る／以降は声だけ流す）</t>
+          <t>佐藤さん（②に出演・声と手元）</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>⑤ S3-1</t>
+          <t>②</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>永尾社長が画に映る。革を背景にしたバストショット。役職テロップはこの画角で出す　［18-28秒］</t>
+          <t>この仕事を20年続けている理由を聞く。②S6で一言だけ使う（台本なし）</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr"/>
@@ -756,13 +756,13 @@
       <c r="C16" s="7" t="inlineStr"/>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>⑤ S3-2</t>
+          <t>②</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>少し寄る。話しながら動く手も入れる　［18-28秒］</t>
+          <t>作業音は別録りが必要なので、インタビューと手元カットは別のセッションにする</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr"/>
@@ -773,16 +773,24 @@
         <v>6</v>
       </c>
       <c r="B17" s="7" t="inlineStr"/>
-      <c r="C17" s="7" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>永尾社長（⑤・画に映る／以降は声だけ流す）</t>
+        </is>
+      </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>⑤ S3-3</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr"/>
+          <t>⑤ S3-1</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
+        </is>
+      </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>ここから画は変わるが、音声はそのまま流し続ける（以降ずっと社長の声）　［18-28秒］</t>
+          <t>永尾社長が画に映る。バストショット。人物は画面の左右どちらかに寄せ、空いた側に役職テロップを置く。背景は工房を大きくボカす　［18-28秒］</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr"/>
@@ -796,13 +804,13 @@
       <c r="C18" s="7" t="inlineStr"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>⑤ S3-2</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>30分収録して、経営方針の本音を拾う。台本の読み上げにしない</t>
+          <t>引きに変える。背景に社名のロゴが入る位置を選ぶ。話しながら動く手も入れる　［18-28秒］</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr"/>
@@ -816,13 +824,13 @@
       <c r="C19" s="7" t="inlineStr"/>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>⑤ S3-3</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>創業から今までの変遷。⑤の全編に流し続けるナレーション素材になる</t>
+          <t>横顔の三つ目の画角。ここから画は変わるが、音声はそのまま流し続ける（以降ずっと社長の声）　［18-28秒］</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr"/>
@@ -833,24 +841,16 @@
         <v>9</v>
       </c>
       <c r="B20" s="7" t="inlineStr"/>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>購入者（⑧）</t>
-        </is>
-      </c>
+      <c r="C20" s="7" t="inlineStr"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-1</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
-        </is>
-      </c>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr"/>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>バストショット。窓を背にして、手前に植物を置いてボカす。名前は出さず「使っている人」として自己紹介　［8-18秒］</t>
+          <t>30分収録して、経営方針の本音を拾う。台本の読み上げにしない</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr"/>
@@ -864,13 +864,13 @@
       <c r="C21" s="7" t="inlineStr"/>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-2</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr"/>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>同じ画角。カメラは一度も動かさない　［8-18秒］</t>
+          <t>創業から今までの変遷。⑤の全編に流し続けるナレーション素材になる</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr"/>
@@ -881,16 +881,24 @@
         <v>11</v>
       </c>
       <c r="B22" s="7" t="inlineStr"/>
-      <c r="C22" s="7" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>購入者（⑧）</t>
+        </is>
+      </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-3</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr"/>
+          <t>⑧ S2-1</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
+        </is>
+      </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>話した言葉をそのままテロップで出す（この参考動画の出し方をそのまま真似る）　［8-18秒］</t>
+          <t>バストショット。窓を背にして、手前に植物を置いてボカす。名前は出さず「使っている人」として自己紹介　［8-18秒］</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr"/>
@@ -904,13 +912,13 @@
       <c r="C23" s="7" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-1</t>
+          <t>⑧ S2-2</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr"/>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>外に出る。空を入れて気分を変える　［42-52秒］</t>
+          <t>同じ画角。カメラは一度も動かさない　［8-18秒］</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr"/>
@@ -924,13 +932,13 @@
       <c r="C24" s="7" t="inlineStr"/>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-2</t>
+          <t>⑧ S2-3</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr"/>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>引きの画に人が入る。買ってから変わったことを語る　［42-52秒］</t>
+          <t>話した言葉をそのままテロップで出す（この参考動画の出し方をそのまま真似る）　［8-18秒］</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr"/>
@@ -944,13 +952,13 @@
       <c r="C25" s="7" t="inlineStr"/>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-3</t>
+          <t>⑧ S5-1</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>インタビューの画に戻る。表情のアップ　［42-52秒］</t>
+          <t>外に出る。空を入れて気分を変える　［42-52秒］</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr"/>
@@ -960,29 +968,17 @@
       <c r="A26" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>空撮・外観</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>工房の上空と外観（⑤⑥共通・晴天の午前）</t>
-        </is>
-      </c>
+      <c r="B26" s="7" t="inlineStr"/>
+      <c r="C26" s="7" t="inlineStr"/>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>⑤ S1-1</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>ドローンまたは高所／カメラ</t>
-        </is>
-      </c>
+          <t>⑧ S5-2</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr"/>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>バードアイショット。東京の空から降り、向島の街と工房を見つける　［0-6秒］</t>
+          <t>引きの画に人が入る。買ってから変わったことを語る　［42-52秒］</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr"/>
@@ -996,13 +992,13 @@
       <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>⑤ S1-2</t>
+          <t>⑧ S5-3</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr"/>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>高度を下げ、建物に寄る　［0-6秒］</t>
+          <t>インタビューの画に戻る。表情のアップ　［42-52秒］</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr"/>
@@ -1012,17 +1008,29 @@
       <c r="A28" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B28" s="7" t="inlineStr"/>
-      <c r="C28" s="7" t="inlineStr"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>空撮・外観</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>工房の上空と外観（⑤⑥共通・晴天の午前）</t>
+        </is>
+      </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>⑤ S1-3</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr"/>
+          <t>⑤ S1-1</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>ドローンまたは高所／カメラ</t>
+        </is>
+      </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>中へ入る。工房の全景。ここまでBGMだけ　［0-6秒］</t>
+          <t>バードアイショット。東京の空から降り、向島の街と工房を見つける　［0-6秒］</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr"/>
@@ -1036,13 +1044,13 @@
       <c r="C29" s="7" t="inlineStr"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>⑥ S1-1</t>
+          <t>⑤ S1-2</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr"/>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>バードアイショット。上から降りて、向島の工房を見つける　［0-10秒］</t>
+          <t>高度を下げ、建物に寄る　［0-6秒］</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr"/>
@@ -1056,13 +1064,13 @@
       <c r="C30" s="7" t="inlineStr"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>⑥ S1-2</t>
+          <t>⑤ S1-3</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr"/>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>高度を下げ、建物の全景へ。街の音　［0-10秒］</t>
+          <t>中へ入る。工房の全景。ここまでBGMだけ　［0-6秒］</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr"/>
@@ -1076,13 +1084,13 @@
       <c r="C31" s="7" t="inlineStr"/>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>⑥ S1-3</t>
+          <t>⑥ S1-1</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr"/>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>入口を抜けて中へ。ここから一続きで進む　［0-10秒］</t>
+          <t>バードアイショット。上から降りて、向島の工房を見つける　［0-10秒］</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr"/>
@@ -1092,29 +1100,17 @@
       <c r="A32" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>工房・全体</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>工房の全景と通路（⑥）</t>
-        </is>
-      </c>
+      <c r="B32" s="7" t="inlineStr"/>
+      <c r="C32" s="7" t="inlineStr"/>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>⑥ S2-1</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／広角</t>
-        </is>
-      </c>
+          <t>⑥ S1-2</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>工房の全景（引き）。規模が分かる画角　［10-25秒］</t>
+          <t>高度を下げ、建物の全景へ。街の音　［0-10秒］</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr"/>
@@ -1128,13 +1124,13 @@
       <c r="C33" s="7" t="inlineStr"/>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>⑥ S2-2</t>
+          <t>⑥ S1-3</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>機械と人が同じ画面に入る。台数と人数が分かる　［10-25秒］</t>
+          <t>入口を抜けて中へ。ここから一続きで進む　［0-10秒］</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr"/>
@@ -1144,17 +1140,29 @@
       <c r="A34" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B34" s="7" t="inlineStr"/>
-      <c r="C34" s="7" t="inlineStr"/>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>工房・全体</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>工房の全景と通路（⑥）</t>
+        </is>
+      </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>⑥ S2-3</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr"/>
+          <t>⑥ S2-1</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／広角</t>
+        </is>
+      </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の顔。手を止めずに作業している横顔（寄り）　［10-25秒］</t>
+          <t>工房の全景（引き）。規模が分かる画角　［10-25秒］</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr"/>
@@ -1164,29 +1172,17 @@
       <c r="A35" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>工房・材料</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>原反と金型・型紙（⑥）</t>
-        </is>
-      </c>
+      <c r="B35" s="7" t="inlineStr"/>
+      <c r="C35" s="7" t="inlineStr"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>⑥ S3-1</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑥ S2-2</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr"/>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>原反が積まれている。扱える革の量を示す　［25-42秒］</t>
+          <t>機械と人が同じ画面に入る。台数と人数が分かる　［10-25秒］</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr"/>
@@ -1200,13 +1196,13 @@
       <c r="C36" s="7" t="inlineStr"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>⑥ S3-2</t>
+          <t>⑥ S2-3</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr"/>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>金型・型紙が品番ごとに並ぶ。手が一つを抜き出す　［25-42秒］</t>
+          <t>Bロール：職人の顔。手を止めずに作業している横顔（寄り）　［10-25秒］</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr"/>
@@ -1216,17 +1212,29 @@
       <c r="A37" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B37" s="7" t="inlineStr"/>
-      <c r="C37" s="7" t="inlineStr"/>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>工房・材料</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>原反と金型・型紙（⑥）</t>
+        </is>
+      </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>⑥ S3-3</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr"/>
+          <t>⑥ S3-1</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>革の上に型紙を置き、取り都合を決める（寄り）　［25-42秒］</t>
+          <t>原反が積まれている。扱える革の量を示す　［25-42秒］</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr"/>
@@ -1236,29 +1244,17 @@
       <c r="A38" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>工房・裁つ</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>作業台・真俯瞰と横（②）</t>
-        </is>
-      </c>
+      <c r="B38" s="7" t="inlineStr"/>
+      <c r="C38" s="7" t="inlineStr"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>② S1-1</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
-        </is>
-      </c>
+          <t>⑥ S3-2</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr"/>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>超マクロ。刃が革に入る瞬間。何を見ているか分からない距離　［0-3秒］</t>
+          <t>金型・型紙が品番ごとに並ぶ。手が一つを抜き出す　［25-42秒］</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr"/>
@@ -1272,13 +1268,13 @@
       <c r="C39" s="7" t="inlineStr"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>② S1-2</t>
+          <t>⑥ S3-3</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr"/>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>刃が進み、革の繊維が開いていく（同じ画角のまま）　［0-3秒］</t>
+          <t>革の上に型紙を置き、取り都合を決める（寄り）　［25-42秒］</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr"/>
@@ -1288,17 +1284,29 @@
       <c r="A40" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B40" s="7" t="inlineStr"/>
-      <c r="C40" s="7" t="inlineStr"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>工房・裁つ</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>作業台・真俯瞰と横（②）</t>
+        </is>
+      </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>② S1-3</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr"/>
+          <t>② S1-1</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+        </is>
+      </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>「スッ」と抜ける一音だけ。BGMは鳴らさない　［0-3秒］</t>
+          <t>超マクロ。刃が革に入る瞬間。何を見ているか分からない距離　［0-3秒］</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr"/>
@@ -1312,13 +1320,13 @@
       <c r="C41" s="7" t="inlineStr"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>② S2-1</t>
+          <t>② S1-2</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr"/>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。金属定規を当てて直線を一気に引く　［3-11秒］</t>
+          <t>刃が進み、革の繊維が開いていく（同じ画角のまま）　［0-3秒］</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr"/>
@@ -1332,13 +1340,13 @@
       <c r="C42" s="7" t="inlineStr"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>② S2-2</t>
+          <t>② S1-3</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr"/>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>角を回して切る（横）　［3-11秒］</t>
+          <t>「スッ」と抜ける一音だけ。BGMは鳴らさない　［0-3秒］</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr"/>
@@ -1352,13 +1360,13 @@
       <c r="C43" s="7" t="inlineStr"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>② S2-3</t>
+          <t>② S2-1</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>切り終わり。断面がまだ生成りのまま残っている　［3-11秒］</t>
+          <t>真俯瞰。金属定規を当てて直線を一気に引く　［3-11秒］</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr"/>
@@ -1372,13 +1380,13 @@
       <c r="C44" s="7" t="inlineStr"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>② S3-1</t>
+          <t>② S2-2</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr"/>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>菱目打ちを槌で打つ。同じ音が三回続く（横）　［11-17秒］</t>
+          <t>角を回して切る（横）　［3-11秒］</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr"/>
@@ -1392,13 +1400,13 @@
       <c r="C45" s="7" t="inlineStr"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>② S3-2</t>
+          <t>② S2-3</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr"/>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>等間隔に並んだ穴だけが画面に残る　［11-17秒］</t>
+          <t>切り終わり。断面がまだ生成りのまま残っている　［3-11秒］</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr"/>
@@ -1412,13 +1420,13 @@
       <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>② S3-3</t>
+          <t>② S3-1</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr"/>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>目打ちの超マクロ。革の断面と穴が同じ画面に入る　［11-17秒］</t>
+          <t>菱目打ちを槌で打つ。同じ音が三回続く（横）　［11-17秒］</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr"/>
@@ -1429,24 +1437,16 @@
         <v>36</v>
       </c>
       <c r="B47" s="7" t="inlineStr"/>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>裁断機と革包丁（⑥）</t>
-        </is>
-      </c>
+      <c r="C47" s="7" t="inlineStr"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>⑥ S4-1</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>② S3-2</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr"/>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>金型が置かれ、裁断機が下りる。テロップ「金型裁断 Die Cutting」　［42-62秒］</t>
+          <t>等間隔に並んだ穴だけが画面に残る　［11-17秒］</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr"/>
@@ -1460,13 +1460,13 @@
       <c r="C48" s="7" t="inlineStr"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>⑥ S4-2</t>
+          <t>② S3-3</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr"/>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>革包丁で細部を切る。テロップ「手裁断 Hand Cutting」　［42-62秒］</t>
+          <t>目打ちの超マクロ。革の断面と穴が同じ画面に入る　［11-17秒］</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr"/>
@@ -1477,16 +1477,24 @@
         <v>38</v>
       </c>
       <c r="B49" s="7" t="inlineStr"/>
-      <c r="C49" s="7" t="inlineStr"/>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>裁断機と革包丁（⑥）</t>
+        </is>
+      </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>⑥ S4-3</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr"/>
+          <t>⑥ S4-1</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>裁ち上がったパーツが並ぶ。量産も少量も同じ場所でできる　［42-62秒］</t>
+          <t>金型が置かれ、裁断機が下りる。テロップ「金型裁断 Die Cutting」　［42-62秒］</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr"/>
@@ -1496,29 +1504,17 @@
       <c r="A50" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>工房・下仕事</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>漉き・目打ち（⑥）</t>
-        </is>
-      </c>
+      <c r="B50" s="7" t="inlineStr"/>
+      <c r="C50" s="7" t="inlineStr"/>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>⑥ S5-1</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑥ S4-2</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>革を漉いて厚みを揃える（寄り）。テロップ「漉き Skiving」　［62-82秒］</t>
+          <t>革包丁で細部を切る。テロップ「手裁断 Hand Cutting」　［42-62秒］</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr"/>
@@ -1532,13 +1528,13 @@
       <c r="C51" s="7" t="inlineStr"/>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>⑥ S5-2</t>
+          <t>⑥ S4-3</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>目打ち・接着。縫う前の下ごしらえ（マクロ）　［62-82秒］</t>
+          <t>裁ち上がったパーツが並ぶ。量産も少量も同じ場所でできる　［42-62秒］</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr"/>
@@ -1548,17 +1544,29 @@
       <c r="A52" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="B52" s="7" t="inlineStr"/>
-      <c r="C52" s="7" t="inlineStr"/>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>工房・下仕事</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>漉き・目打ち（⑥）</t>
+        </is>
+      </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>⑥ S5-3</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr"/>
+          <t>⑥ S5-1</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の顔。手元から顔へパンし、目線だけを見せる　［62-82秒］</t>
+          <t>革を漉いて厚みを揃える（寄り）。テロップ「漉き Skiving」　［62-82秒］</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr"/>
@@ -1568,29 +1576,17 @@
       <c r="A53" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>工房・縫う</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>ミシンと手縫い（⑥）</t>
-        </is>
-      </c>
+      <c r="B53" s="7" t="inlineStr"/>
+      <c r="C53" s="7" t="inlineStr"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>⑥ S6-1</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑥ S5-2</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>ミシンで縫う（横）。テロップ「機械縫製 Machine Stitching」　［82-102秒］</t>
+          <t>目打ち・接着。縫う前の下ごしらえ（マクロ）　［62-82秒］</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr"/>
@@ -1604,13 +1600,13 @@
       <c r="C54" s="7" t="inlineStr"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>⑥ S6-2</t>
+          <t>⑥ S5-3</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr"/>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>手縫い。二本の針が交差する（マクロ）。テロップ「手縫い Hand Stitching」　［82-102秒］</t>
+          <t>Bロール：職人の顔。手元から顔へパンし、目線だけを見せる　［62-82秒］</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr"/>
@@ -1620,17 +1616,29 @@
       <c r="A55" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B55" s="7" t="inlineStr"/>
-      <c r="C55" s="7" t="inlineStr"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>工房・縫う</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>ミシンと手縫い（⑥）</t>
+        </is>
+      </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>⑥ S6-3</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr"/>
+          <t>⑥ S6-1</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>目止め → コバ磨き（超マクロ）。ここが全工程の四割　［82-102秒］</t>
+          <t>ミシンで縫う（横）。テロップ「機械縫製 Machine Stitching」　［82-102秒］</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr"/>
@@ -1641,24 +1649,16 @@
         <v>45</v>
       </c>
       <c r="B56" s="7" t="inlineStr"/>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>作業台・真俯瞰と横（②）</t>
-        </is>
-      </c>
+      <c r="C56" s="7" t="inlineStr"/>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>② S4-1</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
-        </is>
-      </c>
+          <t>⑥ S6-2</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr"/>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>針が革を抜ける（寄り）　［17-24秒］</t>
+          <t>手縫い。二本の針が交差する（マクロ）。テロップ「手縫い Hand Stitching」　［82-102秒］</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr"/>
@@ -1672,13 +1672,13 @@
       <c r="C57" s="7" t="inlineStr"/>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>② S4-2</t>
+          <t>⑥ S6-3</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>二本の糸が交差して締まる（超マクロ）　［17-24秒］</t>
+          <t>目止め → コバ磨き（超マクロ）。ここが全工程の四割　［82-102秒］</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr"/>
@@ -1689,16 +1689,24 @@
         <v>47</v>
       </c>
       <c r="B58" s="7" t="inlineStr"/>
-      <c r="C58" s="7" t="inlineStr"/>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>作業台・真俯瞰と横（②）</t>
+        </is>
+      </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>② S4-3</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr"/>
+          <t>② S4-1</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+        </is>
+      </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>縫い目に沿って仕上げる。手の動きだけを見せる　［17-24秒］</t>
+          <t>針が革を抜ける（寄り）　［17-24秒］</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr"/>
@@ -1708,29 +1716,17 @@
       <c r="A59" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>工房・コバ</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>作業台・超マクロ（②の核）</t>
-        </is>
-      </c>
+      <c r="B59" s="7" t="inlineStr"/>
+      <c r="C59" s="7" t="inlineStr"/>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>② S5-1</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
-        </is>
-      </c>
+          <t>② S4-2</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr"/>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>塗り始め。道具の先が断面に触れる（超マクロ）　［24-33秒］</t>
+          <t>二本の糸が交差して締まる（超マクロ）　［17-24秒］</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr"/>
@@ -1744,13 +1740,13 @@
       <c r="C60" s="7" t="inlineStr"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>② S5-2</t>
+          <t>② S4-3</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr"/>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>コバ塗り ★核。塗った側と塗っていない側が同じ画面に入る。長回し・カットを割らない　［24-33秒］</t>
+          <t>縫い目に沿って仕上げる。手の動きだけを見せる　［17-24秒］</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr"/>
@@ -1760,17 +1756,29 @@
       <c r="A61" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B61" s="7" t="inlineStr"/>
-      <c r="C61" s="7" t="inlineStr"/>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>工房・コバ</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>作業台・超マクロ（②の核）</t>
+        </is>
+      </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>② S5-3</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr"/>
+          <t>② S5-1</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+        </is>
+      </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>塗り終わり。同じ画角のまま断面の色が変わりきっている　［24-33秒］</t>
+          <t>塗り始め。道具の先が断面に触れる（超マクロ）　［24-33秒］</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr"/>
@@ -1784,13 +1792,13 @@
       <c r="C62" s="7" t="inlineStr"/>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>② S6-1</t>
+          <t>② S5-2</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr"/>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>超マクロ。コバを磨く。摩擦音　［33-40秒］</t>
+          <t>コバ塗り ★核。塗った側と塗っていない側が同じ画面に入る。長回し・カットを割らない　［24-33秒］</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr"/>
@@ -1804,13 +1812,13 @@
       <c r="C63" s="7" t="inlineStr"/>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>② S6-2</t>
+          <t>② S5-3</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr"/>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>使われている場所に置かれる → テロップ → ロゴ　［33-40秒］</t>
+          <t>塗り終わり。同じ画角のまま断面の色が変わりきっている　［24-33秒］</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr"/>
@@ -1824,13 +1832,13 @@
       <c r="C64" s="7" t="inlineStr"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>② S6-3</t>
+          <t>② S6-1</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr"/>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>―　［33-40秒］</t>
+          <t>超マクロ。コバを磨く。摩擦音　［33-40秒］</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr"/>
@@ -1840,29 +1848,17 @@
       <c r="A65" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>工房・全工程</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>一工程一カットで流す（⑤は簡潔に）</t>
-        </is>
-      </c>
+      <c r="B65" s="7" t="inlineStr"/>
+      <c r="C65" s="7" t="inlineStr"/>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>⑤ S6-1</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>② S6-2</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr"/>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>原反が積まれている（引き）　［45-55秒］</t>
+          <t>使われている場所に置かれる → テロップ → ロゴ　［33-40秒］</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr"/>
@@ -1876,13 +1872,13 @@
       <c r="C66" s="7" t="inlineStr"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>⑤ S6-2</t>
+          <t>② S6-3</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr"/>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>裁つ・縫う・磨く。一工程一カット。説明はしない　［45-55秒］</t>
+          <t>―　［33-40秒］</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr"/>
@@ -1892,17 +1888,29 @@
       <c r="A67" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B67" s="7" t="inlineStr"/>
-      <c r="C67" s="7" t="inlineStr"/>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>工房・全工程</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>一工程一カットで流す（⑤は簡潔に）</t>
+        </is>
+      </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>⑤ S6-3</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr"/>
+          <t>⑤ S6-1</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>設備で仕上げる。詳しい工程は6本目（OEM案内）で見せる　［45-55秒］</t>
+          <t>原反が積まれている（引き）　［45-55秒］</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr"/>
@@ -1912,29 +1920,17 @@
       <c r="A68" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>工房・検品</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>検品台（⑥・最重要）</t>
-        </is>
-      </c>
+      <c r="B68" s="7" t="inlineStr"/>
+      <c r="C68" s="7" t="inlineStr"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>⑥ S7-1</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑤ S6-2</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr"/>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>一点を手に取り、光にかざす。作業音が消える　［102-122秒］</t>
+          <t>裁つ・縫う・磨く。一工程一カット。説明はしない　［45-55秒］</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr"/>
@@ -1948,13 +1944,13 @@
       <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>⑥ S7-2</t>
+          <t>⑤ S6-3</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>寸法と縫い目を目で確かめる（寄り）　［102-122秒］</t>
+          <t>設備で仕上げる。詳しい工程は6本目（OEM案内）で見せる　［45-55秒］</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr"/>
@@ -1964,17 +1960,29 @@
       <c r="A70" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="B70" s="7" t="inlineStr"/>
-      <c r="C70" s="7" t="inlineStr"/>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>工房・検品</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>検品台（⑥・最重要）</t>
+        </is>
+      </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>⑥ S7-3</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr"/>
+          <t>⑥ S7-1</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の顔。確かめ終えて顔を上げる一瞬。テロップ「検品 Inspection」　［102-122秒］</t>
+          <t>一点を手に取り、光にかざす。作業音が消える　［102-122秒］</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr"/>
@@ -1984,29 +1992,17 @@
       <c r="A71" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>梱包</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>梱包場（⑥）</t>
-        </is>
-      </c>
+      <c r="B71" s="7" t="inlineStr"/>
+      <c r="C71" s="7" t="inlineStr"/>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>⑥ S8-1</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑥ S7-2</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr"/>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>不織布で包み、角を折る（真俯瞰）。紙の音　［122-133秒］</t>
+          <t>寸法と縫い目を目で確かめる（寄り）　［102-122秒］</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr"/>
@@ -2020,13 +2016,13 @@
       <c r="C72" s="7" t="inlineStr"/>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>⑥ S8-2</t>
+          <t>⑥ S7-3</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr"/>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>箱に納め、テープで閉じる。テロップ「梱包 Packing」　［122-133秒］</t>
+          <t>Bロール：職人の顔。確かめ終えて顔を上げる一瞬。テロップ「検品 Inspection」　［102-122秒］</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr"/>
@@ -2036,17 +2032,29 @@
       <c r="A73" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B73" s="7" t="inlineStr"/>
-      <c r="C73" s="7" t="inlineStr"/>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>梱包</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>梱包場（⑥）</t>
+        </is>
+      </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>⑥ S8-3</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr"/>
+          <t>⑥ S8-1</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>出荷を待つ箱が積まれている。ここまで見せる　［122-133秒］</t>
+          <t>不織布で包み、角を折る（真俯瞰）。紙の音　［122-133秒］</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr"/>
@@ -2056,29 +2064,17 @@
       <c r="A74" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>企画・設計</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>机まわり・CADと数値（⑤⑥共通）</t>
-        </is>
-      </c>
+      <c r="B74" s="7" t="inlineStr"/>
+      <c r="C74" s="7" t="inlineStr"/>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>⑤ S5-1</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑥ S8-2</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr"/>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>手が図面をなぞる（寄り）　［37-45秒］</t>
+          <t>箱に納め、テープで閉じる。テロップ「梱包 Packing」　［122-133秒］</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr"/>
@@ -2092,13 +2088,13 @@
       <c r="C75" s="7" t="inlineStr"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>⑤ S5-2</t>
+          <t>⑥ S8-3</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>型紙・図面の俯瞰　［37-45秒］</t>
+          <t>出荷を待つ箱が積まれている。ここまで見せる　［122-133秒］</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr"/>
@@ -2108,17 +2104,29 @@
       <c r="A76" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="B76" s="7" t="inlineStr"/>
-      <c r="C76" s="7" t="inlineStr"/>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>企画・設計</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>机まわり・CADと数値（⑤⑥共通）</t>
+        </is>
+      </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>⑤ S5-3</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr"/>
+          <t>⑤ S5-1</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>机で数値を決める。設計はここで終わり、手に渡る　［37-45秒］</t>
+          <t>手が図面をなぞる（寄り）　［37-45秒］</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr"/>
@@ -2129,24 +2137,16 @@
         <v>66</v>
       </c>
       <c r="B77" s="7" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>机まわり・サンプルと図面（⑤⑥共通）</t>
-        </is>
-      </c>
+      <c r="C77" s="7" t="inlineStr"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>⑤ S4-1</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑤ S5-2</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>革が色ごとに並ぶ。扱える色数がそのまま伝わる　［28-37秒］</t>
+          <t>型紙・図面の俯瞰　［37-45秒］</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr"/>
@@ -2160,13 +2160,13 @@
       <c r="C78" s="7" t="inlineStr"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>⑤ S4-2</t>
+          <t>⑤ S5-3</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr"/>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>色を選ぶ（寄り）　［28-37秒］</t>
+          <t>机で数値を決める。設計はここで終わり、手に渡る　［37-45秒］</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr"/>
@@ -2177,16 +2177,24 @@
         <v>68</v>
       </c>
       <c r="B79" s="7" t="inlineStr"/>
-      <c r="C79" s="7" t="inlineStr"/>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>机まわり・サンプルと図面（⑤⑥共通）</t>
+        </is>
+      </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>⑤ S4-3</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr"/>
+          <t>⑤ S4-1</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>工房に革が吊るされている（引き）　［28-37秒］</t>
+          <t>革が色ごとに並ぶ。扱える色数がそのまま伝わる　［28-37秒］</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr"/>
@@ -2196,29 +2204,17 @@
       <c r="A80" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>複写・資料</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>昔の写真・カタログの複写（⑤）</t>
-        </is>
-      </c>
+      <c r="B80" s="7" t="inlineStr"/>
+      <c r="C80" s="7" t="inlineStr"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>⑤ S2-1</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／自然光</t>
-        </is>
-      </c>
+          <t>⑤ S4-2</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr"/>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>コラボの実績から始める。年号テロップを重ねる（1980 SHIPS〜）※現物の資料を複写して使う　［6-18秒］</t>
+          <t>色を選ぶ（寄り）　［28-37秒］</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr"/>
@@ -2232,13 +2228,13 @@
       <c r="C81" s="7" t="inlineStr"/>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>⑤ S2-2</t>
+          <t>⑤ S4-3</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>昔の店舗の写真・当時のカタログを複写して差し込む　［6-18秒］</t>
+          <t>工房に革が吊るされている（引き）　［28-37秒］</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr"/>
@@ -2248,17 +2244,29 @@
       <c r="A82" s="7" t="n">
         <v>71</v>
       </c>
-      <c r="B82" s="7" t="inlineStr"/>
-      <c r="C82" s="7" t="inlineStr"/>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>複写・資料</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>昔の写真・カタログの複写（⑤）</t>
+        </is>
+      </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>⑤ S2-3</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr"/>
+          <t>⑤ S2-1</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／自然光</t>
+        </is>
+      </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>同じ構図のまま今の BROOKLYN MUSEUM 店舗へ。変化が見えるようにつなぐ　［6-18秒］</t>
+          <t>コラボの実績から始める。年号テロップを重ねる（1980 SHIPS〜）※現物の資料を複写して使う　［6-18秒］</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr"/>
@@ -2268,29 +2276,17 @@
       <c r="A83" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>黒バック撮影</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>黒スチレンボード＋一灯（③専用・別日）</t>
-        </is>
-      </c>
+      <c r="B83" s="7" t="inlineStr"/>
+      <c r="C83" s="7" t="inlineStr"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>③ S1-1</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／黒スチレンボード／アクリル板／白手袋</t>
-        </is>
-      </c>
+          <t>⑤ S2-2</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>真っ黒。細い光の帯が一本だけ立つ　［0-4秒］</t>
+          <t>昔の店舗の写真・当時のカタログを複写して差し込む　［6-18秒］</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr"/>
@@ -2304,13 +2300,13 @@
       <c r="C84" s="7" t="inlineStr"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>③ S1-2</t>
+          <t>⑤ S2-3</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr"/>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>光の帯がゆっくり動く。無音から低いBGMが立ち上がる　［0-4秒］</t>
+          <t>同じ構図のまま今の BROOKLYN MUSEUM 店舗へ。変化が見えるようにつなぐ　［6-18秒］</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr"/>
@@ -2320,17 +2316,29 @@
       <c r="A85" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="B85" s="7" t="inlineStr"/>
-      <c r="C85" s="7" t="inlineStr"/>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>黒バック撮影</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>黒スチレンボード＋一灯（③専用・別日）</t>
+        </is>
+      </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>③ S1-3</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr"/>
+          <t>③ S1-1</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／黒スチレンボード／アクリル板／白手袋</t>
+        </is>
+      </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>―　［0-4秒］</t>
+          <t>真っ黒。細い光の帯が一本だけ立つ　［0-4秒］</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr"/>
@@ -2344,13 +2352,13 @@
       <c r="C86" s="7" t="inlineStr"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>③ S2-1</t>
+          <t>③ S1-2</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr"/>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>道具と染料が並ぶ。手がその前に入る　［4-8秒］</t>
+          <t>光の帯がゆっくり動く。無音から低いBGMが立ち上がる　［0-4秒］</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr"/>
@@ -2364,13 +2372,13 @@
       <c r="C87" s="7" t="inlineStr"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>③ S2-2</t>
+          <t>③ S1-3</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr"/>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>革を持ち上げる。腕時計・指輪は外す　［4-8秒］</t>
+          <t>―　［0-4秒］</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr"/>
@@ -2384,13 +2392,13 @@
       <c r="C88" s="7" t="inlineStr"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>③ S2-3</t>
+          <t>③ S2-1</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr"/>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>革を黒の上に置く。ここから作りはじめる　［4-8秒］</t>
+          <t>道具と染料が並ぶ。手がその前に入る　［4-8秒］</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr"/>
@@ -2404,13 +2412,13 @@
       <c r="C89" s="7" t="inlineStr"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>③ S3-1</t>
+          <t>③ S2-2</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr"/>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>手だけ。革を折る　［8-15秒］</t>
+          <t>革を持ち上げる。腕時計・指輪は外す　［4-8秒］</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr"/>
@@ -2424,13 +2432,13 @@
       <c r="C90" s="7" t="inlineStr"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>③ S3-2</t>
+          <t>③ S2-3</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr"/>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>縁を押さえる（超マクロ）　［8-15秒］</t>
+          <t>革を黒の上に置く。ここから作りはじめる　［4-8秒］</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr"/>
@@ -2444,13 +2452,13 @@
       <c r="C91" s="7" t="inlineStr"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>③ S3-3</t>
+          <t>③ S3-1</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr"/>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>角が立ち上がる。顔と工房は一切映さない　［8-15秒］</t>
+          <t>手だけ。革を折る　［8-15秒］</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr"/>
@@ -2464,13 +2472,13 @@
       <c r="C92" s="7" t="inlineStr"/>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>③ S4-1</t>
+          <t>③ S3-2</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr"/>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>白手袋で金具を持つ。金属が触れる音　［15-19秒］</t>
+          <t>縁を押さえる（超マクロ）　［8-15秒］</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr"/>
@@ -2484,13 +2492,13 @@
       <c r="C93" s="7" t="inlineStr"/>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>③ S4-2</t>
+          <t>③ S3-3</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>金具を取り付ける（超マクロ）。カチリと一音　［15-19秒］</t>
+          <t>角が立ち上がる。顔と工房は一切映さない　［8-15秒］</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr"/>
@@ -2504,13 +2512,13 @@
       <c r="C94" s="7" t="inlineStr"/>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>③ S4-3</t>
+          <t>③ S4-1</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr"/>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>指が金具の縁をなぞる　［15-19秒］</t>
+          <t>白手袋で金具を持つ。金属が触れる音　［15-19秒］</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr"/>
@@ -2524,13 +2532,13 @@
       <c r="C95" s="7" t="inlineStr"/>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>③ S5-1</t>
+          <t>③ S4-2</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr"/>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>コバに染料を入れる（超マクロ）　※参考動画にこの工程は映っていない。2本目の参考動画（コバ塗り）を見て画角を決める　［19-25秒］</t>
+          <t>金具を取り付ける（超マクロ）。カチリと一音　［15-19秒］</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr"/>
@@ -2544,13 +2552,13 @@
       <c r="C96" s="7" t="inlineStr"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>③ S5-2</t>
+          <t>③ S4-3</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr"/>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>磨く。光が断面に反射する角度を探す（超マクロ）　［19-25秒］</t>
+          <t>指が金具の縁をなぞる　［15-19秒］</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr"/>
@@ -2564,13 +2572,13 @@
       <c r="C97" s="7" t="inlineStr"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>③ S5-3</t>
+          <t>③ S5-1</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr"/>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>磨き終わった断面に、光が一本だけ走る　［19-25秒］</t>
+          <t>コバに染料を入れる（超マクロ）　※参考動画にこの工程は映っていない。2本目の参考動画（コバ塗り）を見て画角を決める　［19-25秒］</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr"/>
@@ -2584,13 +2592,13 @@
       <c r="C98" s="7" t="inlineStr"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>③ S6-1</t>
+          <t>③ S5-2</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr"/>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>完成品を持ち上げる　［25-28秒］</t>
+          <t>磨く。光が断面に反射する角度を探す（超マクロ）　［19-25秒］</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr"/>
@@ -2604,13 +2612,13 @@
       <c r="C99" s="7" t="inlineStr"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>③ S6-2</t>
+          <t>③ S5-3</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr"/>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>道具の前に置く。上から一灯だけ　［25-28秒］</t>
+          <t>磨き終わった断面に、光が一本だけ走る　［19-25秒］</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr"/>
@@ -2624,13 +2632,13 @@
       <c r="C100" s="7" t="inlineStr"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>③ S6-3</t>
+          <t>③ S6-1</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr"/>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>金具のマクロ → BGMが止まる → ロゴのみ。テロップは出さない　［25-28秒］</t>
+          <t>完成品を持ち上げる　［25-28秒］</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr"/>
@@ -2640,29 +2648,17 @@
       <c r="A101" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>白台・物撮り</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="inlineStr">
-        <is>
-          <t>四色を並べる（①の締め）</t>
-        </is>
-      </c>
+      <c r="B101" s="7" t="inlineStr"/>
+      <c r="C101" s="7" t="inlineStr"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>① S6-1</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯／白台</t>
-        </is>
-      </c>
+          <t>③ S6-2</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr"/>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>四色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る　［17-20秒］</t>
+          <t>道具の前に置く。上から一灯だけ　［25-28秒］</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr"/>
@@ -2676,13 +2672,13 @@
       <c r="C102" s="7" t="inlineStr"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>① S6-2</t>
+          <t>③ S6-3</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr"/>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>そのままロゴ。締めのテロップは出さない　［17-20秒］</t>
+          <t>金具のマクロ → BGMが止まる → ロゴのみ。テロップは出さない　［25-28秒］</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr"/>
@@ -2692,17 +2688,29 @@
       <c r="A103" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="B103" s="7" t="inlineStr"/>
-      <c r="C103" s="7" t="inlineStr"/>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>白台・物撮り</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>四色を並べる（①の締め）</t>
+        </is>
+      </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>① S6-3</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr"/>
+          <t>① S6-1</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯／白台</t>
+        </is>
+      </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>―　［17-20秒］</t>
+          <t>四色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る　［17-20秒］</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr"/>
@@ -2713,24 +2721,16 @@
         <v>93</v>
       </c>
       <c r="B104" s="7" t="inlineStr"/>
-      <c r="C104" s="9" t="inlineStr">
-        <is>
-          <t>白い台・正面固定（⑦専用・三品番を同じ画角で）</t>
-        </is>
-      </c>
+      <c r="C104" s="7" t="inlineStr"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>⑦ S1-1</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／マクロレンズ／照明1灯／白台／レフ板</t>
-        </is>
-      </c>
+          <t>① S6-2</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr"/>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>超マクロ・モノクロ。ファスナーの歯　［0-4秒］</t>
+          <t>そのままロゴ。締めのテロップは出さない　［17-20秒］</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr"/>
@@ -2744,13 +2744,13 @@
       <c r="C105" s="7" t="inlineStr"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>⑦ S1-2</t>
+          <t>① S6-3</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr"/>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>ストラップと縫い目（モノクロのまま）　［0-4秒］</t>
+          <t>―　［17-20秒］</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr"/>
@@ -2761,16 +2761,24 @@
         <v>95</v>
       </c>
       <c r="B106" s="7" t="inlineStr"/>
-      <c r="C106" s="7" t="inlineStr"/>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>白い台・正面固定（⑦専用・三品番を同じ画角で）</t>
+        </is>
+      </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>⑦ S1-3</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr"/>
+          <t>⑦ S1-1</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／マクロレンズ／照明1灯／白台／レフ板</t>
+        </is>
+      </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>金具の質感（モノクロのまま）　［0-4秒］</t>
+          <t>超マクロ・モノクロ。ファスナーの歯　［0-4秒］</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr"/>
@@ -2784,13 +2792,13 @@
       <c r="C107" s="7" t="inlineStr"/>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>⑦ S2-1</t>
+          <t>⑦ S1-2</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr"/>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>引く。カラーに変わる。白い台に鞄が一つ　［4-7秒］</t>
+          <t>ストラップと縫い目（モノクロのまま）　［0-4秒］</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr"/>
@@ -2804,13 +2812,13 @@
       <c r="C108" s="7" t="inlineStr"/>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>⑦ S2-2</t>
+          <t>⑦ S1-3</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr"/>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>正面固定。ここから最後までこの画角のまま　［4-7秒］</t>
+          <t>金具の質感（モノクロのまま）　［0-4秒］</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr"/>
@@ -2824,13 +2832,13 @@
       <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>⑦ S2-3</t>
+          <t>⑦ S2-1</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr"/>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>鞄を開ける。中は空　［4-7秒］</t>
+          <t>引く。カラーに変わる。白い台に鞄が一つ　［4-7秒］</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr"/>
@@ -2844,13 +2852,13 @@
       <c r="C110" s="7" t="inlineStr"/>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>⑦ S3-1</t>
+          <t>⑦ S2-2</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr"/>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>A4書類とノートPCを入れる　［7-13秒］</t>
+          <t>正面固定。ここから最後までこの画角のまま　［4-7秒］</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr"/>
@@ -2864,13 +2872,13 @@
       <c r="C111" s="7" t="inlineStr"/>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>⑦ S3-2</t>
+          <t>⑦ S2-3</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr"/>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>入りきる。上端にまだ余りがあるのを見せる　［7-13秒］</t>
+          <t>鞄を開ける。中は空　［4-7秒］</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr"/>
@@ -2884,13 +2892,13 @@
       <c r="C112" s="7" t="inlineStr"/>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>⑦ S3-3</t>
+          <t>⑦ S3-1</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr"/>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>手帳・鍵・サングラス。顔は入れない　［7-13秒］</t>
+          <t>A4書類とノートPCを入れる　［7-13秒］</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr"/>
@@ -2904,13 +2912,13 @@
       <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>⑦ S4-1</t>
+          <t>⑦ S3-2</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>ペン・小物。入れる音を一つずつ拾う　［13-17秒］</t>
+          <t>入りきる。上端にまだ余りがあるのを見せる　［7-13秒］</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr"/>
@@ -2924,13 +2932,13 @@
       <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>⑦ S4-2</t>
+          <t>⑦ S3-3</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr"/>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>傘・水筒まで入れる。それでもまだ閉まる　［13-17秒］</t>
+          <t>手帳・鍵・サングラス。顔は入れない　［7-13秒］</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr"/>
@@ -2944,13 +2952,13 @@
       <c r="C115" s="7" t="inlineStr"/>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>⑦ S4-3</t>
+          <t>⑦ S4-1</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>最後の一つを入れる。ここで手が止まる　［13-17秒］</t>
+          <t>ペン・小物。入れる音を一つずつ拾う　［13-17秒］</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr"/>
@@ -2964,13 +2972,13 @@
       <c r="C116" s="7" t="inlineStr"/>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>⑦ S5-1</t>
+          <t>⑦ S4-2</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr"/>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>片手で持ち上げる。軽さを動作で見せる　［17-21秒］</t>
+          <t>傘・水筒まで入れる。それでもまだ閉まる　［13-17秒］</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr"/>
@@ -2984,13 +2992,13 @@
       <c r="C117" s="7" t="inlineStr"/>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>⑦ S5-2</t>
+          <t>⑦ S4-3</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr"/>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>肩にかける。台は動かさない　［17-21秒］</t>
+          <t>最後の一つを入れる。ここで手が止まる　［13-17秒］</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr"/>
@@ -3004,13 +3012,13 @@
       <c r="C118" s="7" t="inlineStr"/>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>⑦ S5-3</t>
+          <t>⑦ S5-1</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr"/>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>数字を小さくテロップで添える（千百六十グラム）　［17-21秒］</t>
+          <t>片手で持ち上げる。軽さを動作で見せる　［17-21秒］</t>
         </is>
       </c>
       <c r="G118" s="11" t="inlineStr"/>
@@ -3024,13 +3032,13 @@
       <c r="C119" s="7" t="inlineStr"/>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>⑦ S6-1</t>
+          <t>⑦ S5-2</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr"/>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>人がフレームから出る。鞄だけが残る　［21-25秒］</t>
+          <t>肩にかける。台は動かさない　［17-21秒］</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr"/>
@@ -3044,13 +3052,13 @@
       <c r="C120" s="7" t="inlineStr"/>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>⑦ S6-2</t>
+          <t>⑦ S5-3</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr"/>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>テロップ「急がば、定位置。」　［21-25秒］</t>
+          <t>数字を小さくテロップで添える（千百六十グラム）　［17-21秒］</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr"/>
@@ -3064,13 +3072,13 @@
       <c r="C121" s="7" t="inlineStr"/>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>⑦ S6-3</t>
+          <t>⑦ S6-1</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr"/>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>ロゴ。三品番とも同じ終わり方にする　［21-25秒］</t>
+          <t>人がフレームから出る。鞄だけが残る　［21-25秒］</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr"/>
@@ -3080,29 +3088,17 @@
       <c r="A122" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="B122" s="8" t="inlineStr">
-        <is>
-          <t>店舗</t>
-        </is>
-      </c>
-      <c r="C122" s="9" t="inlineStr">
-        <is>
-          <t>BROOKLYN MUSEUM 店舗（⑤⑧共通）</t>
-        </is>
-      </c>
+      <c r="B122" s="7" t="inlineStr"/>
+      <c r="C122" s="7" t="inlineStr"/>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-1</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／ガンマイク</t>
-        </is>
-      </c>
+          <t>⑦ S6-2</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr"/>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>BROOKLYN MUSEUM 店舗の外観　［55-66秒］</t>
+          <t>テロップ「急がば、定位置。」　［21-25秒］</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr"/>
@@ -3116,13 +3112,13 @@
       <c r="C123" s="7" t="inlineStr"/>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-2</t>
+          <t>⑦ S6-3</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr"/>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>店内。棚に並ぶ商品を、お客様が手に取る　［55-66秒］</t>
+          <t>ロゴ。三品番とも同じ終わり方にする　［21-25秒］</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr"/>
@@ -3132,17 +3128,29 @@
       <c r="A124" s="7" t="n">
         <v>113</v>
       </c>
-      <c r="B124" s="7" t="inlineStr"/>
-      <c r="C124" s="7" t="inlineStr"/>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>店舗</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>BROOKLYN MUSEUM 店舗（⑤⑧共通）</t>
+        </is>
+      </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-3</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr"/>
+          <t>⑤ S7-1</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／ガンマイク</t>
+        </is>
+      </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>会計。店員から手渡される瞬間　［55-66秒］</t>
+          <t>BROOKLYN MUSEUM 店舗の外観　［55-66秒］</t>
         </is>
       </c>
       <c r="G124" s="11" t="inlineStr"/>
@@ -3152,29 +3160,17 @@
       <c r="A125" s="7" t="n">
         <v>114</v>
       </c>
-      <c r="B125" s="8" t="inlineStr">
-        <is>
-          <t>お客様・開封</t>
-        </is>
-      </c>
-      <c r="C125" s="9" t="inlineStr">
-        <is>
-          <t>買った日の再現（⑧）</t>
-        </is>
-      </c>
+      <c r="B125" s="7" t="inlineStr"/>
+      <c r="C125" s="7" t="inlineStr"/>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-1</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑤ S7-2</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr"/>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>商品の真俯瞰。声は続いたまま　［30-42秒］</t>
+          <t>店内。棚に並ぶ商品を、お客様が手に取る　［55-66秒］</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr"/>
@@ -3188,13 +3184,13 @@
       <c r="C126" s="7" t="inlineStr"/>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-2</t>
+          <t>⑤ S7-3</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr"/>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>売り場・棚の引き　［30-42秒］</t>
+          <t>会計。店員から手渡される瞬間　［55-66秒］</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr"/>
@@ -3204,17 +3200,29 @@
       <c r="A127" s="7" t="n">
         <v>116</v>
       </c>
-      <c r="B127" s="7" t="inlineStr"/>
-      <c r="C127" s="7" t="inlineStr"/>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>お客様・開封</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>買った日の再現（⑧）</t>
+        </is>
+      </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-3</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="inlineStr"/>
+          <t>⑧ S4-1</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>ディテールの寄り。良かった点を語っている場所に重ねる　［30-42秒］</t>
+          <t>商品の真俯瞰。声は続いたまま　［30-42秒］</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr"/>
@@ -3224,29 +3232,17 @@
       <c r="A128" s="7" t="n">
         <v>117</v>
       </c>
-      <c r="B128" s="8" t="inlineStr">
-        <is>
-          <t>お客様・街</t>
-        </is>
-      </c>
-      <c r="C128" s="9" t="inlineStr">
-        <is>
-          <t>使用シーン（⑧）</t>
-        </is>
-      </c>
+      <c r="B128" s="7" t="inlineStr"/>
+      <c r="C128" s="7" t="inlineStr"/>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-1</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S4-2</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr"/>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>ここから画はBロールに変わるが、声はそのまま流し続ける　［18-30秒］</t>
+          <t>売り場・棚の引き　［30-42秒］</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr"/>
@@ -3260,13 +3256,13 @@
       <c r="C129" s="7" t="inlineStr"/>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-2</t>
+          <t>⑧ S4-3</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr"/>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>同じ場所を別の角度で。声に合わせて切り替える　［18-30秒］</t>
+          <t>ディテールの寄り。良かった点を語っている場所に重ねる　［30-42秒］</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr"/>
@@ -3276,17 +3272,29 @@
       <c r="A130" s="7" t="n">
         <v>119</v>
       </c>
-      <c r="B130" s="7" t="inlineStr"/>
-      <c r="C130" s="7" t="inlineStr"/>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>お客様・街</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>使用シーン（⑧）</t>
+        </is>
+      </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-3</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="inlineStr"/>
+          <t>⑧ S3-1</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>落ち着いた場所での一枚。間を作る　［18-30秒］</t>
+          <t>ここから画はBロールに変わるが、声はそのまま流し続ける　［18-30秒］</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr"/>
@@ -3297,24 +3305,16 @@
         <v>120</v>
       </c>
       <c r="B131" s="7" t="inlineStr"/>
-      <c r="C131" s="9" t="inlineStr">
-        <is>
-          <t>受け取りと使用（⑤⑧共通）</t>
-        </is>
-      </c>
+      <c r="C131" s="7" t="inlineStr"/>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-1</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S3-2</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr"/>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>受け取った人の笑顔（寄り）　［66-75秒］</t>
+          <t>同じ場所を別の角度で。声に合わせて切り替える　［18-30秒］</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr"/>
@@ -3328,13 +3328,13 @@
       <c r="C132" s="7" t="inlineStr"/>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-2</t>
+          <t>⑧ S3-3</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr"/>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>街で実際に使われている手元 社長の声はここで終わる　［66-75秒］</t>
+          <t>落ち着いた場所での一枚。間を作る　［18-30秒］</t>
         </is>
       </c>
       <c r="G132" s="11" t="inlineStr"/>
@@ -3345,16 +3345,24 @@
         <v>122</v>
       </c>
       <c r="B133" s="7" t="inlineStr"/>
-      <c r="C133" s="7" t="inlineStr"/>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>受け取りと使用（⑤⑧共通）</t>
+        </is>
+      </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-3</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="inlineStr"/>
+          <t>⑤ S8-1</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>音が引き、ロゴだけ。テロップは出さない　［66-75秒］</t>
+          <t>受け取った人の笑顔（寄り）　［66-75秒］</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr"/>
@@ -3368,13 +3376,13 @@
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-1</t>
+          <t>⑤ S8-2</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr"/>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>外観のロー。空を入れて見上げる。まだ人は出さない　［0-8秒］</t>
+          <t>街で実際に使われている手元 社長の声はここで終わる　［66-75秒］</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr"/>
@@ -3388,13 +3396,13 @@
       <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-2</t>
+          <t>⑤ S8-3</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr"/>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>店舗／工房の全景（引き）。人が出入りする　［0-8秒］</t>
+          <t>音が引き、ロゴだけ。テロップは出さない　［66-75秒］</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr"/>
@@ -3408,13 +3416,13 @@
       <c r="C136" s="7" t="inlineStr"/>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-3</t>
+          <t>⑧ S1-1</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr"/>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>窓辺と光。商品が置いてある（寄り）　［0-8秒］</t>
+          <t>外観のロー。空を入れて見上げる。まだ人は出さない　［0-8秒］</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr"/>
@@ -3425,24 +3433,16 @@
         <v>126</v>
       </c>
       <c r="B137" s="7" t="inlineStr"/>
-      <c r="C137" s="9" t="inlineStr">
-        <is>
-          <t>締め（⑧）</t>
-        </is>
-      </c>
+      <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-1</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S1-2</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr"/>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>最後の一言。台本にない言葉を拾う　［52-60秒］</t>
+          <t>店舗／工房の全景（引き）。人が出入りする　［0-8秒］</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr"/>
@@ -3456,13 +3456,13 @@
       <c r="C138" s="7" t="inlineStr"/>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-2</t>
+          <t>⑧ S1-3</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr"/>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>テロップ　［52-60秒］</t>
+          <t>窓辺と光。商品が置いてある（寄り）　［0-8秒］</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr"/>
@@ -3473,16 +3473,24 @@
         <v>128</v>
       </c>
       <c r="B139" s="7" t="inlineStr"/>
-      <c r="C139" s="7" t="inlineStr"/>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>締め（⑧）</t>
+        </is>
+      </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-3</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="inlineStr"/>
+          <t>⑧ S6-1</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>ロゴ　［52-60秒］</t>
+          <t>最後の一言。台本にない言葉を拾う　［52-60秒］</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr"/>
@@ -3492,29 +3500,17 @@
       <c r="A140" s="7" t="n">
         <v>129</v>
       </c>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>屋外・街</t>
-        </is>
-      </c>
-      <c r="C140" s="9" t="inlineStr">
-        <is>
-          <t>自宅の玄関まわり（①）</t>
-        </is>
-      </c>
+      <c r="B140" s="7" t="inlineStr"/>
+      <c r="C140" s="7" t="inlineStr"/>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>① S1-1</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>⑧ S6-2</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr"/>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>玄関。財布をポケットに入れる（寄り）　［0-3秒］</t>
+          <t>テロップ　［52-60秒］</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr"/>
@@ -3528,13 +3524,13 @@
       <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>① S1-2</t>
+          <t>⑧ S6-3</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr"/>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>鍵を取る手元（超寄り）。ここではまだ色を見せない　［0-3秒］</t>
+          <t>ロゴ　［52-60秒］</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr"/>
@@ -3544,17 +3540,29 @@
       <c r="A142" s="7" t="n">
         <v>131</v>
       </c>
-      <c r="B142" s="7" t="inlineStr"/>
-      <c r="C142" s="7" t="inlineStr"/>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>屋外・街</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>自宅の玄関まわり（①）</t>
+        </is>
+      </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>① S1-3</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr"/>
+          <t>① S1-1</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>ドアノブに手がかかる（超寄り）　［0-3秒］</t>
+          <t>玄関。財布をポケットに入れる（寄り）　［0-3秒］</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr"/>
@@ -3568,13 +3576,13 @@
       <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>① S2-1</t>
+          <t>① S1-2</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［3-6秒］</t>
+          <t>鍵を取る手元（超寄り）。ここではまだ色を見せない　［0-3秒］</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr"/>
@@ -3588,13 +3596,13 @@
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>① S2-2</t>
+          <t>① S1-3</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>同じ画角。車が手前を横切る（トランジション）　［3-6秒］</t>
+          <t>ドアノブに手がかかる（超寄り）　［0-3秒］</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr"/>
@@ -3608,13 +3616,13 @@
       <c r="C145" s="7" t="inlineStr"/>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>① S2-3</t>
+          <t>① S2-1</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr"/>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>手元の革小物だけに寄る（超寄り・一色目）※この寄りは参考動画にはない　［3-6秒］</t>
+          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［3-6秒］</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr"/>
@@ -3625,24 +3633,16 @@
         <v>135</v>
       </c>
       <c r="B146" s="7" t="inlineStr"/>
-      <c r="C146" s="9" t="inlineStr">
-        <is>
-          <t>街歩き・夕方の斜光（④）</t>
-        </is>
-      </c>
+      <c r="C146" s="7" t="inlineStr"/>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>④ S1-1</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>① S2-2</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr"/>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
+          <t>同じ画角。車が手前を横切る（トランジション）　［3-6秒］</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr"/>
@@ -3656,13 +3656,13 @@
       <c r="C147" s="7" t="inlineStr"/>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>④ S1-2</t>
+          <t>① S2-3</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr"/>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
+          <t>手元の革小物だけに寄る（超寄り・一色目）※この寄りは参考動画にはない　［3-6秒］</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr"/>
@@ -3673,16 +3673,24 @@
         <v>137</v>
       </c>
       <c r="B148" s="7" t="inlineStr"/>
-      <c r="C148" s="7" t="inlineStr"/>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>街歩き・夕方の斜光（④）</t>
+        </is>
+      </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>④ S1-3</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="inlineStr"/>
+          <t>④ S1-1</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
+          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr"/>
@@ -3696,13 +3704,13 @@
       <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>④ S2-1</t>
+          <t>④ S1-2</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
+          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr"/>
@@ -3716,13 +3724,13 @@
       <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>④ S2-2</t>
+          <t>④ S1-3</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
+          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr"/>
@@ -3736,13 +3744,13 @@
       <c r="C151" s="7" t="inlineStr"/>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>④ S2-3</t>
+          <t>④ S2-1</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
+          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr"/>
@@ -3756,13 +3764,13 @@
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>④ S3-1</t>
+          <t>④ S2-2</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
+          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr"/>
@@ -3776,13 +3784,13 @@
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>④ S3-2</t>
+          <t>④ S2-3</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
+          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr"/>
@@ -3796,13 +3804,13 @@
       <c r="C154" s="7" t="inlineStr"/>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>④ S3-3</t>
+          <t>④ S3-1</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr"/>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
+          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr"/>
@@ -3816,13 +3824,13 @@
       <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>④ S4-1</t>
+          <t>④ S3-2</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr"/>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
+          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr"/>
@@ -3836,13 +3844,13 @@
       <c r="C156" s="7" t="inlineStr"/>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>④ S4-2</t>
+          <t>④ S3-3</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr"/>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
+          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr"/>
@@ -3856,13 +3864,13 @@
       <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>④ S4-3</t>
+          <t>④ S4-1</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr"/>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
+          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr"/>
@@ -3876,13 +3884,13 @@
       <c r="C158" s="7" t="inlineStr"/>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>④ S5-1</t>
+          <t>④ S4-2</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr"/>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>手すりの前で立ち止まる　［24-30秒］</t>
+          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr"/>
@@ -3896,13 +3904,13 @@
       <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>④ S5-2</t>
+          <t>④ S4-3</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。保存袋・小物まで並べる　［24-30秒］</t>
+          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr"/>
@@ -3916,13 +3924,13 @@
       <c r="C160" s="7" t="inlineStr"/>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>④ S5-3</t>
+          <t>④ S5-1</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr"/>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
+          <t>手すりの前で立ち止まる　［24-30秒］</t>
         </is>
       </c>
       <c r="G160" s="11" t="inlineStr"/>
@@ -3933,24 +3941,16 @@
         <v>150</v>
       </c>
       <c r="B161" s="7" t="inlineStr"/>
-      <c r="C161" s="9" t="inlineStr">
-        <is>
-          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
-        </is>
-      </c>
+      <c r="C161" s="7" t="inlineStr"/>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>① S3-1</t>
-        </is>
-      </c>
-      <c r="E161" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>④ S5-2</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま服が変わっている。小物の色も変わる　［6-10秒］</t>
+          <t>真俯瞰。保存袋・小物まで並べる　［24-30秒］</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr"/>
@@ -3964,13 +3964,13 @@
       <c r="C162" s="7" t="inlineStr"/>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>① S3-2</t>
+          <t>④ S5-3</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>同じ道。二色目（キャメル）　［6-10秒］</t>
+          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
         </is>
       </c>
       <c r="G162" s="11" t="inlineStr"/>
@@ -3981,16 +3981,24 @@
         <v>152</v>
       </c>
       <c r="B163" s="7" t="inlineStr"/>
-      <c r="C163" s="7" t="inlineStr"/>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
+        </is>
+      </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>① S3-3</t>
-        </is>
-      </c>
-      <c r="E163" s="7" t="inlineStr"/>
+          <t>① S3-1</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>同じ道。三色目　［6-10秒］</t>
+          <t>同じ画角のまま服が変わっている。小物の色も変わる　［6-10秒］</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr"/>
@@ -4004,13 +4012,13 @@
       <c r="C164" s="7" t="inlineStr"/>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>① S4-1</t>
+          <t>① S3-2</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr"/>
       <c r="F164" s="10" t="inlineStr">
         <is>
-          <t>場所が変わる。乗り場（引き）　［10-14秒］</t>
+          <t>同じ道。二色目（キャメル）　［6-10秒］</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr"/>
@@ -4024,13 +4032,13 @@
       <c r="C165" s="7" t="inlineStr"/>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>① S4-2</t>
+          <t>① S3-3</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr"/>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>構内を歩く。同じ人・違う色　［10-14秒］</t>
+          <t>同じ道。三色目　［6-10秒］</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr"/>
@@ -4044,13 +4052,13 @@
       <c r="C166" s="7" t="inlineStr"/>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>① S4-3</t>
+          <t>① S4-1</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr"/>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>四色目。ここまでで四色そろう　［10-14秒］</t>
+          <t>場所が変わる。乗り場（引き）　［10-14秒］</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr"/>
@@ -4064,13 +4072,13 @@
       <c r="C167" s="7" t="inlineStr"/>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>① S5-1</t>
+          <t>① S4-2</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr"/>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>会社の入口に着く　［14-17秒］</t>
+          <t>構内を歩く。同じ人・違う色　［10-14秒］</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr"/>
@@ -4084,13 +4092,13 @@
       <c r="C168" s="7" t="inlineStr"/>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>① S5-2</t>
+          <t>① S4-3</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>ロビーを歩く（引き）　［14-17秒］</t>
+          <t>四色目。ここまでで四色そろう　［10-14秒］</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr"/>
@@ -4104,13 +4112,13 @@
       <c r="C169" s="7" t="inlineStr"/>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>① S5-3</t>
+          <t>① S5-1</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr"/>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>立ち止まる。ここが到着点　［14-17秒］</t>
+          <t>会社の入口に着く　［14-17秒］</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr"/>
@@ -4120,29 +4128,17 @@
       <c r="A170" s="7" t="n">
         <v>159</v>
       </c>
-      <c r="B170" s="8" t="inlineStr">
-        <is>
-          <t>締めカード</t>
-        </is>
-      </c>
-      <c r="C170" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。文字を組んで作る</t>
-        </is>
-      </c>
+      <c r="B170" s="7" t="inlineStr"/>
+      <c r="C170" s="7" t="inlineStr"/>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-1</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
+          <t>① S5-2</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
+          <t>ロビーを歩く（引き）　［14-17秒］</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr"/>
@@ -4156,13 +4152,13 @@
       <c r="C171" s="7" t="inlineStr"/>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-2</t>
+          <t>① S5-3</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
+          <t>立ち止まる。ここが到着点　［14-17秒］</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr"/>
@@ -4172,24 +4168,76 @@
       <c r="A172" s="7" t="n">
         <v>161</v>
       </c>
-      <c r="B172" s="7" t="inlineStr"/>
-      <c r="C172" s="7" t="inlineStr"/>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>締めカード</t>
+        </is>
+      </c>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。文字を組んで作る</t>
+        </is>
+      </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-3</t>
-        </is>
-      </c>
-      <c r="E172" s="7" t="inlineStr"/>
+          <t>⑥ S9-1</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
       <c r="F172" s="10" t="inlineStr">
         <is>
-          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
+          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr"/>
       <c r="H172" s="11" t="inlineStr"/>
     </row>
+    <row r="173" ht="32" customHeight="1">
+      <c r="A173" s="7" t="n">
+        <v>162</v>
+      </c>
+      <c r="B173" s="7" t="inlineStr"/>
+      <c r="C173" s="7" t="inlineStr"/>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-2</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr"/>
+      <c r="F173" s="10" t="inlineStr">
+        <is>
+          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G173" s="11" t="inlineStr"/>
+      <c r="H173" s="11" t="inlineStr"/>
+    </row>
+    <row r="174" ht="32" customHeight="1">
+      <c r="A174" s="7" t="n">
+        <v>163</v>
+      </c>
+      <c r="B174" s="7" t="inlineStr"/>
+      <c r="C174" s="7" t="inlineStr"/>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-3</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr"/>
+      <c r="F174" s="10" t="inlineStr">
+        <is>
+          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G174" s="11" t="inlineStr"/>
+      <c r="H174" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A11:H172"/>
+  <autoFilter ref="A11:H174"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ショットリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$177</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>① S6-1</t>
+          <t>① S7-1</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>四色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る　［17-20秒］</t>
+          <t>人がフレームから出る。置かれた小物だけが残る　［27-30秒］</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr"/>
@@ -2724,13 +2724,13 @@
       <c r="C104" s="7" t="inlineStr"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>① S6-2</t>
+          <t>① S7-2</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr"/>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>そのままロゴ。締めのテロップは出さない　［17-20秒］</t>
+          <t>四色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る　［27-30秒］</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr"/>
@@ -2744,13 +2744,13 @@
       <c r="C105" s="7" t="inlineStr"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>① S6-3</t>
+          <t>① S7-3</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr"/>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>―　［17-20秒］</t>
+          <t>そのままロゴ。締めのテロップは出さない　［27-30秒］</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr"/>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>玄関。財布をポケットに入れる（寄り）　［0-3秒］</t>
+          <t>玄関。財布をポケットに入れる（寄り）　［0-4秒］</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr"/>
@@ -3582,7 +3582,7 @@
       <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>鍵を取る手元（超寄り）。ここではまだ色を見せない　［0-3秒］</t>
+          <t>鍵を取る手元（超寄り）。ここではまだ色を見せない　［0-4秒］</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
       <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>ドアノブに手がかかる（超寄り）　［0-3秒］</t>
+          <t>ドアノブに手がかかる（超寄り）　［0-4秒］</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr"/>
@@ -3622,7 +3622,7 @@
       <c r="E145" s="7" t="inlineStr"/>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［3-6秒］</t>
+          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［4-9秒］</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr"/>
@@ -3642,7 +3642,7 @@
       <c r="E146" s="7" t="inlineStr"/>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>同じ画角。車が手前を横切る（トランジション）　［3-6秒］</t>
+          <t>同じ画角。歩いてくる全身（一色目）　［4-9秒］</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr"/>
@@ -3662,7 +3662,7 @@
       <c r="E147" s="7" t="inlineStr"/>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>手元の革小物だけに寄る（超寄り・一色目）※この寄りは参考動画にはない　［3-6秒］</t>
+          <t>手元の革小物だけに寄る（超寄り）※この寄りは参考動画にはない　［4-9秒］</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま服が変わっている。小物の色も変わる　［6-10秒］</t>
+          <t>同じ画角のまま服が変わっている。小物の色も変わる（二色目）　［9-14秒］</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr"/>
@@ -4018,7 +4018,7 @@
       <c r="E164" s="7" t="inlineStr"/>
       <c r="F164" s="10" t="inlineStr">
         <is>
-          <t>同じ道。二色目（キャメル）　［6-10秒］</t>
+          <t>同じ道。三色目　［9-14秒］</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr"/>
@@ -4038,7 +4038,7 @@
       <c r="E165" s="7" t="inlineStr"/>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>同じ道。三色目　［6-10秒］</t>
+          <t>立ち止まって振り返る。手元の色が見える　［9-14秒］</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr"/>
@@ -4058,7 +4058,7 @@
       <c r="E166" s="7" t="inlineStr"/>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>場所が変わる。乗り場（引き）　［10-14秒］</t>
+          <t>手前を木の幹が横切る（前ボケ＝トランジション）　［14-18秒］</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr"/>
@@ -4078,7 +4078,7 @@
       <c r="E167" s="7" t="inlineStr"/>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>構内を歩く。同じ人・違う色　［10-14秒］</t>
+          <t>抜けたら別の服・別の色になっている（四色目）　［14-18秒］</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr"/>
@@ -4098,7 +4098,7 @@
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>四色目。ここまでで四色そろう　［10-14秒］</t>
+          <t>場所が変わる。駅の構内（引き）　［14-18秒］</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr"/>
@@ -4118,7 +4118,7 @@
       <c r="E169" s="7" t="inlineStr"/>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>会社の入口に着く　［14-17秒］</t>
+          <t>乗り場（引き）。同じ人・違う色　［18-22秒］</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr"/>
@@ -4138,7 +4138,7 @@
       <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>ロビーを歩く（引き）　［14-17秒］</t>
+          <t>通路を歩く。横移動で追う　［18-22秒］</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr"/>
@@ -4158,7 +4158,7 @@
       <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>立ち止まる。ここが到着点　［14-17秒］</t>
+          <t>会社の入口に着く　［18-22秒］</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr"/>
@@ -4168,29 +4168,17 @@
       <c r="A172" s="7" t="n">
         <v>161</v>
       </c>
-      <c r="B172" s="8" t="inlineStr">
-        <is>
-          <t>締めカード</t>
-        </is>
-      </c>
-      <c r="C172" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。文字を組んで作る</t>
-        </is>
-      </c>
+      <c r="B172" s="7" t="inlineStr"/>
+      <c r="C172" s="7" t="inlineStr"/>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-1</t>
-        </is>
-      </c>
-      <c r="E172" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
+          <t>① S6-1</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="10" t="inlineStr">
         <is>
-          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
+          <t>ロビーに入る　［22-27秒］</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr"/>
@@ -4204,13 +4192,13 @@
       <c r="C173" s="7" t="inlineStr"/>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-2</t>
+          <t>① S6-2</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr"/>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
+          <t>ロビーを歩く（引き）　［22-27秒］</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr"/>
@@ -4224,20 +4212,92 @@
       <c r="C174" s="7" t="inlineStr"/>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-3</t>
+          <t>① S6-3</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr"/>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
+          <t>立ち止まる。ここが到着点　［22-27秒］</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr"/>
       <c r="H174" s="11" t="inlineStr"/>
     </row>
+    <row r="175" ht="32" customHeight="1">
+      <c r="A175" s="7" t="n">
+        <v>164</v>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
+        <is>
+          <t>締めカード</t>
+        </is>
+      </c>
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。文字を組んで作る</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-1</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
+      <c r="F175" s="10" t="inlineStr">
+        <is>
+          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G175" s="11" t="inlineStr"/>
+      <c r="H175" s="11" t="inlineStr"/>
+    </row>
+    <row r="176" ht="32" customHeight="1">
+      <c r="A176" s="7" t="n">
+        <v>165</v>
+      </c>
+      <c r="B176" s="7" t="inlineStr"/>
+      <c r="C176" s="7" t="inlineStr"/>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-2</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr"/>
+      <c r="F176" s="10" t="inlineStr">
+        <is>
+          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G176" s="11" t="inlineStr"/>
+      <c r="H176" s="11" t="inlineStr"/>
+    </row>
+    <row r="177" ht="32" customHeight="1">
+      <c r="A177" s="7" t="n">
+        <v>166</v>
+      </c>
+      <c r="B177" s="7" t="inlineStr"/>
+      <c r="C177" s="7" t="inlineStr"/>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-3</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr"/>
+      <c r="F177" s="10" t="inlineStr">
+        <is>
+          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G177" s="11" t="inlineStr"/>
+      <c r="H177" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A11:H174"/>
+  <autoFilter ref="A11:H177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>永尾社長が画に映る。バストショット。人物は画面の左右どちらかに寄せ、空いた側に役職テロップを置く。背景は工房を大きくボカす　［18-28秒］</t>
+          <t>①バストショット。人物は中央よりやや右。顔の下に役職テロップ（日英二行）。背景の窓と柱は大きくボカす　［18-28秒］</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr"/>
@@ -810,7 +810,7 @@
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>引きに変える。背景に社名のロゴが入る位置を選ぶ。話しながら動く手も入れる　［18-28秒］</t>
+          <t>②引き。人物を左に寄せ、背景に社名ロゴの壁を入れる。話しながら動く手も入る　［18-28秒］</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr"/>
@@ -830,7 +830,7 @@
       <c r="E19" s="7" t="inlineStr"/>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>横顔の三つ目の画角。ここから画は変わるが、音声はそのまま流し続ける（以降ずっと社長の声）　［18-28秒］</t>
+          <t>③横顔。空いた右側に見出しテロップ（例：創業の背景）。ここから画は変わるが音声はそのまま流し続ける　［18-28秒］</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ショットリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>①バストショット。人物は中央よりやや右。顔の下に役職テロップ（日英二行）。背景の窓と柱は大きくボカす　［18-28秒］</t>
+          <t>革が色ごとに並ぶ。扱える色数がそのまま伝わる　［20-29秒］</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr"/>
@@ -810,7 +810,7 @@
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>②引き。人物を左に寄せ、背景に社名ロゴの壁を入れる。話しながら動く手も入る　［18-28秒］</t>
+          <t>色を選ぶ（寄り）　［20-29秒］</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr"/>
@@ -830,7 +830,7 @@
       <c r="E19" s="7" t="inlineStr"/>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>③横顔。空いた右側に見出しテロップ（例：創業の背景）。ここから画は変わるが音声はそのまま流し続ける　［18-28秒］</t>
+          <t>工房に革が吊るされている（引き）　［20-29秒］</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr"/>
@@ -1050,7 +1050,7 @@
       <c r="E29" s="7" t="inlineStr"/>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>高度を下げ、建物に寄る　［0-6秒］</t>
+          <t>高度を下げ、建物に寄る。ここで永尾社長の声が先に入りはじめる（Jカット）　［0-6秒］</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr"/>
@@ -1070,7 +1070,7 @@
       <c r="E30" s="7" t="inlineStr"/>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>中へ入る。工房の全景。ここまでBGMだけ　［0-6秒］</t>
+          <t>永尾社長。この一カットだけ画に映る。バストショット、顔の下に役職テロップ。声は次のシーンにかぶったまま続く　［0-6秒］</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>原反が積まれている（引き）　［45-55秒］</t>
+          <t>くさがやさん。この一カットだけ画に映る。横顔、空いた側に見出しテロップ。声は次のカットにかぶったまま続く　［52-63秒］</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr"/>
@@ -1930,7 +1930,7 @@
       <c r="E68" s="7" t="inlineStr"/>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>裁つ・縫う・磨く。一工程一カット。説明はしない　［45-55秒］</t>
+          <t>BROOKLYN MUSEUM 店舗の外観　［52-63秒］</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>設備で仕上げる。詳しい工程は6本目（OEM案内）で見せる　［45-55秒］</t>
+          <t>店内。棚に並ぶ商品を、お客様が手に取る　［52-63秒］</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr"/>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>手が図面をなぞる（寄り）　［37-45秒］</t>
+          <t>佐藤さん。この一カットだけ画に映る。引き、背景に工房。声は次のカットにかぶったまま続く　［38-52秒］</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
       <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>型紙・図面の俯瞰　［37-45秒］</t>
+          <t>原反が積まれている（引き）　［38-52秒］</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
       <c r="E78" s="7" t="inlineStr"/>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>机で数値を決める。設計はここで終わり、手に渡る　［37-45秒］</t>
+          <t>裁つ・縫う・磨く。一工程一カット。説明はしない。ここでくさがやさんの声が先に入りはじめる（Jカット）　［38-52秒］</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr"/>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>革が色ごとに並ぶ。扱える色数がそのまま伝わる　［28-37秒］</t>
+          <t>手が図面をなぞる（寄り）　［29-38秒］</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr"/>
@@ -2214,7 +2214,7 @@
       <c r="E80" s="7" t="inlineStr"/>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>色を選ぶ（寄り）　［28-37秒］</t>
+          <t>型紙・図面の俯瞰　［29-38秒］</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr"/>
@@ -2234,7 +2234,7 @@
       <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>工房に革が吊るされている（引き）　［28-37秒］</t>
+          <t>机で数値を決める。ここで佐藤さんの声が先に入りはじめる（Jカット）　［29-38秒］</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr"/>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>コラボの実績から始める。年号テロップを重ねる（1980 SHIPS〜）※現物の資料を複写して使う　［6-18秒］</t>
+          <t>1979年の創業。会社のヒストリーページの一枚目（BROOKLYN MUSEUM の看板が写った白黒写真）を複写して使う。年号テロップ「1979 東京千駄ヶ谷にて創業」を重ねる　［6-20秒］</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr"/>
@@ -2286,7 +2286,7 @@
       <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>昔の店舗の写真・当時のカタログを複写して差し込む　［6-18秒］</t>
+          <t>1984 To Boot New York の白黒写真を複写。年号テロップを続けて重ねる（1980 SHIPS ／ 1982 BEAMS ／ 1984 To Boot New York）　［6-20秒］</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr"/>
@@ -2306,7 +2306,7 @@
       <c r="E84" s="7" t="inlineStr"/>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>同じ構図のまま今の BROOKLYN MUSEUM 店舗へ。変化が見えるようにつなぐ　［6-18秒］</t>
+          <t>同じ構図のまま今の BROOKLYN MUSEUM 店舗へ。白黒からカラーに変わる　［6-20秒］</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr"/>
@@ -2438,7 +2438,7 @@
       <c r="E90" s="7" t="inlineStr"/>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>革を黒の上に置く。ここから作りはじめる　［4-8秒］</t>
+          <t>暗がりで革を手に取る。ここから作りはじめる　［4-8秒］</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr"/>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>BROOKLYN MUSEUM 店舗の外観　［55-66秒］</t>
+          <t>会計。店員から手渡される瞬間　［63-75秒］</t>
         </is>
       </c>
       <c r="G124" s="11" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
       <c r="E125" s="7" t="inlineStr"/>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>店内。棚に並ぶ商品を、お客様が手に取る　［55-66秒］</t>
+          <t>受け取った人の笑顔 → 街で実際に使われている手元 三人の声はここで終わる　［63-75秒］</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr"/>
@@ -3190,7 +3190,7 @@
       <c r="E126" s="7" t="inlineStr"/>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>会計。店員から手渡される瞬間　［55-66秒］</t>
+          <t>音が引き、ロゴだけ。テロップは出さない　［63-75秒］</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr"/>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-1</t>
+          <t>⑧ S1-1</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>受け取った人の笑顔（寄り）　［66-75秒］</t>
+          <t>外観のロー。空を入れて見上げる。まだ人は出さない　［0-8秒］</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr"/>
@@ -3376,13 +3376,13 @@
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-2</t>
+          <t>⑧ S1-2</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr"/>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>街で実際に使われている手元 社長の声はここで終わる　［66-75秒］</t>
+          <t>店舗／工房の全景（引き）。人が出入りする　［0-8秒］</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr"/>
@@ -3396,13 +3396,13 @@
       <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-3</t>
+          <t>⑧ S1-3</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr"/>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>音が引き、ロゴだけ。テロップは出さない　［66-75秒］</t>
+          <t>窓辺と光。商品が置いてある（寄り）　［0-8秒］</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr"/>
@@ -3413,16 +3413,24 @@
         <v>125</v>
       </c>
       <c r="B136" s="7" t="inlineStr"/>
-      <c r="C136" s="7" t="inlineStr"/>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>締め（⑧）</t>
+        </is>
+      </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-1</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr"/>
+          <t>⑧ S6-1</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>外観のロー。空を入れて見上げる。まだ人は出さない　［0-8秒］</t>
+          <t>最後の一言。台本にない言葉を拾う　［52-60秒］</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr"/>
@@ -3436,13 +3444,13 @@
       <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-2</t>
+          <t>⑧ S6-2</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr"/>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>店舗／工房の全景（引き）。人が出入りする　［0-8秒］</t>
+          <t>テロップ　［52-60秒］</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr"/>
@@ -3456,13 +3464,13 @@
       <c r="C138" s="7" t="inlineStr"/>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-3</t>
+          <t>⑧ S6-3</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr"/>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>窓辺と光。商品が置いてある（寄り）　［0-8秒］</t>
+          <t>ロゴ　［52-60秒］</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr"/>
@@ -3472,25 +3480,29 @@
       <c r="A139" s="7" t="n">
         <v>128</v>
       </c>
-      <c r="B139" s="7" t="inlineStr"/>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>屋外・街</t>
+        </is>
+      </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>締め（⑧）</t>
+          <t>自宅の玄関まわり（①）</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-1</t>
+          <t>① S1-1</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>カメラ／三脚</t>
+          <t>カメラ／三脚／レフ板</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>最後の一言。台本にない言葉を拾う　［52-60秒］</t>
+          <t>玄関。財布をポケットに入れる（寄り）　［0-4秒］</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr"/>
@@ -3504,13 +3516,13 @@
       <c r="C140" s="7" t="inlineStr"/>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-2</t>
+          <t>① S1-2</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr"/>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>テロップ　［52-60秒］</t>
+          <t>鍵を取る手元（超寄り）。ここではまだ色を見せない　［0-4秒］</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr"/>
@@ -3524,13 +3536,13 @@
       <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-3</t>
+          <t>① S1-3</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr"/>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>ロゴ　［52-60秒］</t>
+          <t>ドアノブに手がかかる（超寄り）　［0-4秒］</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr"/>
@@ -3540,29 +3552,17 @@
       <c r="A142" s="7" t="n">
         <v>131</v>
       </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>屋外・街</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="inlineStr">
-        <is>
-          <t>自宅の玄関まわり（①）</t>
-        </is>
-      </c>
+      <c r="B142" s="7" t="inlineStr"/>
+      <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>① S1-1</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>① S2-1</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr"/>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>玄関。財布をポケットに入れる（寄り）　［0-4秒］</t>
+          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［4-9秒］</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr"/>
@@ -3576,13 +3576,13 @@
       <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>① S1-2</t>
+          <t>① S2-2</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>鍵を取る手元（超寄り）。ここではまだ色を見せない　［0-4秒］</t>
+          <t>同じ画角。歩いてくる全身（一色目）　［4-9秒］</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr"/>
@@ -3596,13 +3596,13 @@
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>① S1-3</t>
+          <t>① S2-3</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>ドアノブに手がかかる（超寄り）　［0-4秒］</t>
+          <t>手元の革小物だけに寄る（超寄り）※この寄りは参考動画にはない　［4-9秒］</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr"/>
@@ -3613,16 +3613,24 @@
         <v>134</v>
       </c>
       <c r="B145" s="7" t="inlineStr"/>
-      <c r="C145" s="7" t="inlineStr"/>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>街歩き・夕方の斜光（④）</t>
+        </is>
+      </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>① S2-1</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr"/>
+          <t>④ S1-1</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［4-9秒］</t>
+          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr"/>
@@ -3636,13 +3644,13 @@
       <c r="C146" s="7" t="inlineStr"/>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>① S2-2</t>
+          <t>④ S1-2</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr"/>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>同じ画角。歩いてくる全身（一色目）　［4-9秒］</t>
+          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr"/>
@@ -3656,13 +3664,13 @@
       <c r="C147" s="7" t="inlineStr"/>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>① S2-3</t>
+          <t>④ S1-3</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr"/>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>手元の革小物だけに寄る（超寄り）※この寄りは参考動画にはない　［4-9秒］</t>
+          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr"/>
@@ -3673,24 +3681,16 @@
         <v>137</v>
       </c>
       <c r="B148" s="7" t="inlineStr"/>
-      <c r="C148" s="9" t="inlineStr">
-        <is>
-          <t>街歩き・夕方の斜光（④）</t>
-        </is>
-      </c>
+      <c r="C148" s="7" t="inlineStr"/>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>④ S1-1</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>④ S2-1</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr"/>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
+          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr"/>
@@ -3704,13 +3704,13 @@
       <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>④ S1-2</t>
+          <t>④ S2-2</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
+          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr"/>
@@ -3724,13 +3724,13 @@
       <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>④ S1-3</t>
+          <t>④ S2-3</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
+          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr"/>
@@ -3744,13 +3744,13 @@
       <c r="C151" s="7" t="inlineStr"/>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>④ S2-1</t>
+          <t>④ S3-1</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
+          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr"/>
@@ -3764,13 +3764,13 @@
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>④ S2-2</t>
+          <t>④ S3-2</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
+          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr"/>
@@ -3784,13 +3784,13 @@
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>④ S2-3</t>
+          <t>④ S3-3</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
+          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr"/>
@@ -3804,13 +3804,13 @@
       <c r="C154" s="7" t="inlineStr"/>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>④ S3-1</t>
+          <t>④ S4-1</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr"/>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
+          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr"/>
@@ -3824,13 +3824,13 @@
       <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>④ S3-2</t>
+          <t>④ S4-2</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr"/>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
+          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr"/>
@@ -3844,13 +3844,13 @@
       <c r="C156" s="7" t="inlineStr"/>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>④ S3-3</t>
+          <t>④ S4-3</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr"/>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
+          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr"/>
@@ -3864,13 +3864,13 @@
       <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>④ S4-1</t>
+          <t>④ S5-1</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr"/>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
+          <t>手すりの前で立ち止まる　［24-30秒］</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr"/>
@@ -3884,13 +3884,13 @@
       <c r="C158" s="7" t="inlineStr"/>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>④ S4-2</t>
+          <t>④ S5-2</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr"/>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
+          <t>真俯瞰。保存袋・小物まで並べる　［24-30秒］</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr"/>
@@ -3904,13 +3904,13 @@
       <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>④ S4-3</t>
+          <t>④ S5-3</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
+          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr"/>
@@ -3921,16 +3921,24 @@
         <v>149</v>
       </c>
       <c r="B160" s="7" t="inlineStr"/>
-      <c r="C160" s="7" t="inlineStr"/>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
+        </is>
+      </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>④ S5-1</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr"/>
+          <t>① S3-1</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>手すりの前で立ち止まる　［24-30秒］</t>
+          <t>同じ画角のまま服が変わっている。小物の色も変わる（二色目）　［9-14秒］</t>
         </is>
       </c>
       <c r="G160" s="11" t="inlineStr"/>
@@ -3944,13 +3952,13 @@
       <c r="C161" s="7" t="inlineStr"/>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>④ S5-2</t>
+          <t>① S3-2</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。保存袋・小物まで並べる　［24-30秒］</t>
+          <t>同じ道。三色目　［9-14秒］</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr"/>
@@ -3964,13 +3972,13 @@
       <c r="C162" s="7" t="inlineStr"/>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>④ S5-3</t>
+          <t>① S3-3</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
+          <t>立ち止まって振り返る。手元の色が見える　［9-14秒］</t>
         </is>
       </c>
       <c r="G162" s="11" t="inlineStr"/>
@@ -3981,24 +3989,16 @@
         <v>152</v>
       </c>
       <c r="B163" s="7" t="inlineStr"/>
-      <c r="C163" s="9" t="inlineStr">
-        <is>
-          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
-        </is>
-      </c>
+      <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>① S3-1</t>
-        </is>
-      </c>
-      <c r="E163" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>① S4-1</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま服が変わっている。小物の色も変わる（二色目）　［9-14秒］</t>
+          <t>手前を木の幹が横切る（前ボケ＝トランジション）　［14-18秒］</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr"/>
@@ -4012,13 +4012,13 @@
       <c r="C164" s="7" t="inlineStr"/>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>① S3-2</t>
+          <t>① S4-2</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr"/>
       <c r="F164" s="10" t="inlineStr">
         <is>
-          <t>同じ道。三色目　［9-14秒］</t>
+          <t>抜けたら別の服・別の色になっている（四色目）　［14-18秒］</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr"/>
@@ -4032,13 +4032,13 @@
       <c r="C165" s="7" t="inlineStr"/>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>① S3-3</t>
+          <t>① S4-3</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr"/>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>立ち止まって振り返る。手元の色が見える　［9-14秒］</t>
+          <t>場所が変わる。駅の構内（引き）　［14-18秒］</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr"/>
@@ -4052,13 +4052,13 @@
       <c r="C166" s="7" t="inlineStr"/>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>① S4-1</t>
+          <t>① S5-1</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr"/>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>手前を木の幹が横切る（前ボケ＝トランジション）　［14-18秒］</t>
+          <t>乗り場（引き）。同じ人・違う色　［18-22秒］</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr"/>
@@ -4072,13 +4072,13 @@
       <c r="C167" s="7" t="inlineStr"/>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>① S4-2</t>
+          <t>① S5-2</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr"/>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>抜けたら別の服・別の色になっている（四色目）　［14-18秒］</t>
+          <t>通路を歩く。横移動で追う　［18-22秒］</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr"/>
@@ -4092,13 +4092,13 @@
       <c r="C168" s="7" t="inlineStr"/>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>① S4-3</t>
+          <t>① S5-3</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>場所が変わる。駅の構内（引き）　［14-18秒］</t>
+          <t>会社の入口に着く　［18-22秒］</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr"/>
@@ -4112,13 +4112,13 @@
       <c r="C169" s="7" t="inlineStr"/>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>① S5-1</t>
+          <t>① S6-1</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr"/>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>乗り場（引き）。同じ人・違う色　［18-22秒］</t>
+          <t>ロビーに入る　［22-27秒］</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr"/>
@@ -4132,13 +4132,13 @@
       <c r="C170" s="7" t="inlineStr"/>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>① S5-2</t>
+          <t>① S6-2</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>通路を歩く。横移動で追う　［18-22秒］</t>
+          <t>ロビーを歩く（引き）　［22-27秒］</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr"/>
@@ -4152,13 +4152,13 @@
       <c r="C171" s="7" t="inlineStr"/>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>① S5-3</t>
+          <t>① S6-3</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>会社の入口に着く　［18-22秒］</t>
+          <t>立ち止まる。ここが到着点　［22-27秒］</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr"/>
@@ -4168,17 +4168,29 @@
       <c r="A172" s="7" t="n">
         <v>161</v>
       </c>
-      <c r="B172" s="7" t="inlineStr"/>
-      <c r="C172" s="7" t="inlineStr"/>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>締めカード</t>
+        </is>
+      </c>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。文字を組んで作る</t>
+        </is>
+      </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>① S6-1</t>
-        </is>
-      </c>
-      <c r="E172" s="7" t="inlineStr"/>
+          <t>⑥ S9-1</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
       <c r="F172" s="10" t="inlineStr">
         <is>
-          <t>ロビーに入る　［22-27秒］</t>
+          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr"/>
@@ -4192,13 +4204,13 @@
       <c r="C173" s="7" t="inlineStr"/>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>① S6-2</t>
+          <t>⑥ S9-2</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr"/>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>ロビーを歩く（引き）　［22-27秒］</t>
+          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr"/>
@@ -4212,92 +4224,20 @@
       <c r="C174" s="7" t="inlineStr"/>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>① S6-3</t>
+          <t>⑥ S9-3</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr"/>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>立ち止まる。ここが到着点　［22-27秒］</t>
+          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr"/>
       <c r="H174" s="11" t="inlineStr"/>
     </row>
-    <row r="175" ht="32" customHeight="1">
-      <c r="A175" s="7" t="n">
-        <v>164</v>
-      </c>
-      <c r="B175" s="8" t="inlineStr">
-        <is>
-          <t>締めカード</t>
-        </is>
-      </c>
-      <c r="C175" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。文字を組んで作る</t>
-        </is>
-      </c>
-      <c r="D175" s="7" t="inlineStr">
-        <is>
-          <t>⑥ S9-1</t>
-        </is>
-      </c>
-      <c r="E175" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
-      <c r="F175" s="10" t="inlineStr">
-        <is>
-          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
-        </is>
-      </c>
-      <c r="G175" s="11" t="inlineStr"/>
-      <c r="H175" s="11" t="inlineStr"/>
-    </row>
-    <row r="176" ht="32" customHeight="1">
-      <c r="A176" s="7" t="n">
-        <v>165</v>
-      </c>
-      <c r="B176" s="7" t="inlineStr"/>
-      <c r="C176" s="7" t="inlineStr"/>
-      <c r="D176" s="7" t="inlineStr">
-        <is>
-          <t>⑥ S9-2</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr"/>
-      <c r="F176" s="10" t="inlineStr">
-        <is>
-          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
-        </is>
-      </c>
-      <c r="G176" s="11" t="inlineStr"/>
-      <c r="H176" s="11" t="inlineStr"/>
-    </row>
-    <row r="177" ht="32" customHeight="1">
-      <c r="A177" s="7" t="n">
-        <v>166</v>
-      </c>
-      <c r="B177" s="7" t="inlineStr"/>
-      <c r="C177" s="7" t="inlineStr"/>
-      <c r="D177" s="7" t="inlineStr">
-        <is>
-          <t>⑥ S9-3</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="inlineStr"/>
-      <c r="F177" s="10" t="inlineStr">
-        <is>
-          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
-        </is>
-      </c>
-      <c r="G177" s="11" t="inlineStr"/>
-      <c r="H177" s="11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A11:H177"/>
+  <autoFilter ref="A11:H174"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -3502,7 +3502,7 @@
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>玄関。財布をポケットに入れる（寄り）　［0-4秒］</t>
+          <t>玄関の中。全身が入る引き。出かける支度をしている　［0-5秒］</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr"/>
@@ -3522,7 +3522,7 @@
       <c r="E140" s="7" t="inlineStr"/>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>鍵を取る手元（超寄り）。ここではまだ色を見せない　［0-4秒］</t>
+          <t>ドアの前に立つ（引き）。同じ画角に固定する　［0-5秒］</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr"/>
@@ -3542,7 +3542,7 @@
       <c r="E141" s="7" t="inlineStr"/>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>ドアノブに手がかかる（超寄り）　［0-4秒］</t>
+          <t>ドアが開く。開いた瞬間、服も鞄も変わっている。同じ画角のまま。この一本の決まりごとを、いちばん最初に見せてしまう　［0-5秒］</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr"/>
@@ -3562,7 +3562,7 @@
       <c r="E142" s="7" t="inlineStr"/>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［4-9秒］</t>
+          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［5-9秒］</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr"/>
@@ -3582,7 +3582,7 @@
       <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>同じ画角。歩いてくる全身（一色目）　［4-9秒］</t>
+          <t>同じ画角。歩いてくる全身（一色目）　［5-9秒］</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
       <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>手元の革小物だけに寄る（超寄り）※この寄りは参考動画にはない　［4-9秒］</t>
+          <t>歩き出す全身（引き・ロー）。鞄が体の横で揺れる　［5-9秒］</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -2266,7 +2266,7 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>1979年の創業。会社のヒストリーページの一枚目（BROOKLYN MUSEUM の看板が写った白黒写真）を複写して使う。年号テロップ「1979 東京千駄ヶ谷にて創業」を重ねる　［6-20秒］</t>
+          <t>1979年の創業。ヒストリーページの一枚目。年号テロップ「1979　東京千駄ヶ谷にて創業」を重ねる（画面上部の英字はサイト側の見出し。実際は年号テロップだけを載せる）　［6-20秒］</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr"/>
@@ -2286,7 +2286,7 @@
       <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>1984 To Boot New York の白黒写真を複写。年号テロップを続けて重ねる（1980 SHIPS ／ 1982 BEAMS ／ 1984 To Boot New York）　［6-20秒］</t>
+          <t>1984 To Boot New York。年号テロップを続けて重ねる（1980 SHIPS ／ 1982 BEAMS ／ 1984 To Boot New York）　［6-20秒］</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ショットリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -656,7 +656,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>⑤⑥</t>
+          <t>⑤ S6-1</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>漉き・仕上げの仕事について一言。顔出しが難しければ手元だけのバージョンも撮る</t>
+          <t>くさがやさん。この一カットだけ画に映る。横顔、空いた側に見出しテロップ。声は次のカットにかぶったまま続く　［52-63秒］</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr"/>
@@ -677,24 +677,16 @@
         <v>2</v>
       </c>
       <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>三人共通の撮り方</t>
-        </is>
-      </c>
+      <c r="C13" s="7" t="inlineStr"/>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>②⑤⑥</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
-        </is>
-      </c>
+          <t>⑤⑥</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>画角を三つ撮る：①バストショット（人物を左右に寄せ、空いた側にテロップ）②引き（背景に社名ロゴの壁）③横顔</t>
+          <t>漉き・仕上げの仕事について一言。顔出しが難しければ手元だけのバージョンも撮る</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr"/>
@@ -705,16 +697,24 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="inlineStr"/>
-      <c r="C14" s="7" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>三人共通の撮り方</t>
+        </is>
+      </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
           <t>②⑤⑥</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
+        </is>
+      </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>背景は必ず大きくボカす。明るい室内・窓・緑を背にする。役職テロップは日英二行</t>
+          <t>画角を三つ撮る：①バストショット（人物を左右に寄せ、空いた側にテロップ）②引き（背景に社名ロゴの壁）③横顔</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr"/>
@@ -725,24 +725,16 @@
         <v>4</v>
       </c>
       <c r="B15" s="7" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>佐藤さん（②に出演・声と手元）</t>
-        </is>
-      </c>
+      <c r="C15" s="7" t="inlineStr"/>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
-        </is>
-      </c>
+          <t>②⑤⑥</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>この仕事を20年続けている理由を聞く。②S6で一言だけ使う（台本なし）</t>
+          <t>背景は必ず大きくボカす。明るい室内・窓・緑を背にする。役職テロップは日英二行</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr"/>
@@ -753,16 +745,24 @@
         <v>5</v>
       </c>
       <c r="B16" s="7" t="inlineStr"/>
-      <c r="C16" s="7" t="inlineStr"/>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>佐藤さん（②に出演・声と手元）</t>
+        </is>
+      </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr"/>
+          <t>⑤ S5-1</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
+        </is>
+      </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>作業音は別録りが必要なので、インタビューと手元カットは別のセッションにする</t>
+          <t>佐藤さん。この一カットだけ画に映る。引き、背景に工房。声は次のカットにかぶったまま続く　［38-52秒］</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr"/>
@@ -773,24 +773,16 @@
         <v>6</v>
       </c>
       <c r="B17" s="7" t="inlineStr"/>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>永尾社長（⑤・画に映る／以降は声だけ流す）</t>
-        </is>
-      </c>
+      <c r="C17" s="7" t="inlineStr"/>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>⑤ S3-1</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
-        </is>
-      </c>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>革が色ごとに並ぶ。扱える色数がそのまま伝わる　［20-29秒］</t>
+          <t>この仕事を20年続けている理由を聞く。②S6で一言だけ使う（台本なし）</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr"/>
@@ -804,13 +796,13 @@
       <c r="C18" s="7" t="inlineStr"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>⑤ S3-2</t>
+          <t>②</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>色を選ぶ（寄り）　［20-29秒］</t>
+          <t>作業音は別録りが必要なので、インタビューと手元カットは別のセッションにする</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr"/>
@@ -821,16 +813,24 @@
         <v>8</v>
       </c>
       <c r="B19" s="7" t="inlineStr"/>
-      <c r="C19" s="7" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>永尾社長（⑤・冒頭と締めの二カット）</t>
+        </is>
+      </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>⑤ S3-3</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr"/>
+          <t>⑤ S1-3</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
+        </is>
+      </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>工房に革が吊るされている（引き）　［20-29秒］</t>
+          <t>永尾社長。この一カットだけ画に映る。バストショット、顔の下に役職テロップ。声は次のシーンにかぶったまま続く　［0-6秒］</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr"/>
@@ -844,13 +844,13 @@
       <c r="C20" s="7" t="inlineStr"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>⑤ S8-1</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>30分収録して、経営方針の本音を拾う。台本の読み上げにしない</t>
+          <t>永尾社長。締めの一言。冒頭と同じ画角に戻し、頭と終わりで挟む。この一本で言いたいことを、本人の言葉で置く　［70-75秒］</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr"/>
@@ -870,7 +870,7 @@
       <c r="E21" s="7" t="inlineStr"/>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>創業から今までの変遷。⑤の全編に流し続けるナレーション素材になる</t>
+          <t>30分収録して、経営方針の本音を拾う。台本の読み上げにしない</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr"/>
@@ -881,24 +881,16 @@
         <v>11</v>
       </c>
       <c r="B22" s="7" t="inlineStr"/>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>購入者（⑧）</t>
-        </is>
-      </c>
+      <c r="C22" s="7" t="inlineStr"/>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-1</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
-        </is>
-      </c>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr"/>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>バストショット。窓を背にして、手前に植物を置いてボカす。名前は出さず「使っている人」として自己紹介　［8-18秒］</t>
+          <t>創業から今までの変遷。⑤の全編に流し続けるナレーション素材になる</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr"/>
@@ -912,13 +904,13 @@
       <c r="C23" s="7" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-2</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr"/>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>同じ画角。カメラは一度も動かさない　［8-18秒］</t>
+          <t>締めの一言を、収録の最後に一本言い切ってもらう（三十分の収録から抜くのではなく、締め用に撮る）</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr"/>
@@ -929,16 +921,24 @@
         <v>13</v>
       </c>
       <c r="B24" s="7" t="inlineStr"/>
-      <c r="C24" s="7" t="inlineStr"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>購入者（⑧）</t>
+        </is>
+      </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-3</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr"/>
+          <t>⑧ S2-1</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
+        </is>
+      </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>話した言葉をそのままテロップで出す（この参考動画の出し方をそのまま真似る）　［8-18秒］</t>
+          <t>バストショット。窓を背にして、手前に植物を置いてボカす。名前は出さず「使っている人」として自己紹介　［8-18秒］</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr"/>
@@ -952,13 +952,13 @@
       <c r="C25" s="7" t="inlineStr"/>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-1</t>
+          <t>⑧ S2-2</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>外に出る。空を入れて気分を変える　［42-52秒］</t>
+          <t>同じ画角。カメラは一度も動かさない　［8-18秒］</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr"/>
@@ -972,13 +972,13 @@
       <c r="C26" s="7" t="inlineStr"/>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-2</t>
+          <t>⑧ S2-3</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr"/>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>引きの画に人が入る。買ってから変わったことを語る　［42-52秒］</t>
+          <t>話した言葉をそのままテロップで出す（この参考動画の出し方をそのまま真似る）　［8-18秒］</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr"/>
@@ -992,13 +992,13 @@
       <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-3</t>
+          <t>⑧ S5-1</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr"/>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>インタビューの画に戻る。表情のアップ　［42-52秒］</t>
+          <t>外に出る。空を入れて気分を変える　［42-52秒］</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr"/>
@@ -1008,29 +1008,17 @@
       <c r="A28" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>空撮・外観</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>工房の上空と外観（⑤⑥共通・晴天の午前）</t>
-        </is>
-      </c>
+      <c r="B28" s="7" t="inlineStr"/>
+      <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>⑤ S1-1</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>ドローンまたは高所／カメラ</t>
-        </is>
-      </c>
+          <t>⑧ S5-2</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr"/>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>バードアイショット。東京の空から降り、向島の街と工房を見つける　［0-6秒］</t>
+          <t>引きの画に人が入る。買ってから変わったことを語る　［42-52秒］</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr"/>
@@ -1044,13 +1032,13 @@
       <c r="C29" s="7" t="inlineStr"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>⑤ S1-2</t>
+          <t>⑧ S5-3</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr"/>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>高度を下げ、建物に寄る。ここで永尾社長の声が先に入りはじめる（Jカット）　［0-6秒］</t>
+          <t>インタビューの画に戻る。表情のアップ　［42-52秒］</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr"/>
@@ -1060,17 +1048,29 @@
       <c r="A30" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B30" s="7" t="inlineStr"/>
-      <c r="C30" s="7" t="inlineStr"/>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>空撮・外観</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>工房の上空と外観（⑤⑥共通・晴天の午前）</t>
+        </is>
+      </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>⑤ S1-3</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr"/>
+          <t>⑤ S1-1</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>ドローンまたは高所／カメラ</t>
+        </is>
+      </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>永尾社長。この一カットだけ画に映る。バストショット、顔の下に役職テロップ。声は次のシーンにかぶったまま続く　［0-6秒］</t>
+          <t>バードアイショット。東京の空から降り、向島の街と工房を見つける　［0-6秒］</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr"/>
@@ -1084,13 +1084,13 @@
       <c r="C31" s="7" t="inlineStr"/>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>⑥ S1-1</t>
+          <t>⑤ S1-2</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr"/>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>バードアイショット。上から降りて、向島の工房を見つける　［0-10秒］</t>
+          <t>高度を下げ、建物に寄る。ここで永尾社長の声が先に入りはじめる（Jカット）　［0-6秒］</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr"/>
@@ -1104,13 +1104,13 @@
       <c r="C32" s="7" t="inlineStr"/>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>⑥ S1-2</t>
+          <t>⑥ S1-1</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>高度を下げ、建物の全景へ。街の音　［0-10秒］</t>
+          <t>バードアイショット。上から降りて、向島の工房を見つける　［0-10秒］</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr"/>
@@ -1124,13 +1124,13 @@
       <c r="C33" s="7" t="inlineStr"/>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>⑥ S1-3</t>
+          <t>⑥ S1-2</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>入口を抜けて中へ。ここから一続きで進む　［0-10秒］</t>
+          <t>高度を下げ、建物の全景へ。街の音　［0-10秒］</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr"/>
@@ -1140,29 +1140,17 @@
       <c r="A34" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>工房・全体</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>工房の全景と通路（⑥）</t>
-        </is>
-      </c>
+      <c r="B34" s="7" t="inlineStr"/>
+      <c r="C34" s="7" t="inlineStr"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>⑥ S2-1</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／広角</t>
-        </is>
-      </c>
+          <t>⑥ S1-3</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr"/>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>工房の全景（引き）。規模が分かる画角　［10-25秒］</t>
+          <t>入口を抜けて中へ。ここから一続きで進む　［0-10秒］</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr"/>
@@ -1172,17 +1160,29 @@
       <c r="A35" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B35" s="7" t="inlineStr"/>
-      <c r="C35" s="7" t="inlineStr"/>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>工房・全体</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>工房の全景と通路（⑥）</t>
+        </is>
+      </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>⑥ S2-2</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr"/>
+          <t>⑥ S2-1</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／広角</t>
+        </is>
+      </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>機械と人が同じ画面に入る。台数と人数が分かる　［10-25秒］</t>
+          <t>工房の全景（引き）。規模が分かる画角　［10-25秒］</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr"/>
@@ -1196,13 +1196,13 @@
       <c r="C36" s="7" t="inlineStr"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>⑥ S2-3</t>
+          <t>⑥ S2-2</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr"/>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の顔。手を止めずに作業している横顔（寄り）　［10-25秒］</t>
+          <t>機械と人が同じ画面に入る。台数と人数が分かる　［10-25秒］</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr"/>
@@ -1212,29 +1212,17 @@
       <c r="A37" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>工房・材料</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>原反と金型・型紙（⑥）</t>
-        </is>
-      </c>
+      <c r="B37" s="7" t="inlineStr"/>
+      <c r="C37" s="7" t="inlineStr"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>⑥ S3-1</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑥ S2-3</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr"/>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>原反が積まれている。扱える革の量を示す　［25-42秒］</t>
+          <t>Bロール：職人の顔。手を止めずに作業している横顔（寄り）　［10-25秒］</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr"/>
@@ -1244,17 +1232,29 @@
       <c r="A38" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B38" s="7" t="inlineStr"/>
-      <c r="C38" s="7" t="inlineStr"/>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>工房・材料</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>原反と金型・型紙（⑥）</t>
+        </is>
+      </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>⑥ S3-2</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr"/>
+          <t>⑥ S3-1</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>金型・型紙が品番ごとに並ぶ。手が一つを抜き出す　［25-42秒］</t>
+          <t>原反が積まれている。扱える革の量を示す　［25-42秒］</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr"/>
@@ -1268,13 +1268,13 @@
       <c r="C39" s="7" t="inlineStr"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>⑥ S3-3</t>
+          <t>⑥ S3-2</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr"/>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>革の上に型紙を置き、取り都合を決める（寄り）　［25-42秒］</t>
+          <t>金型・型紙が品番ごとに並ぶ。手が一つを抜き出す　［25-42秒］</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr"/>
@@ -1284,29 +1284,17 @@
       <c r="A40" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>工房・裁つ</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>作業台・真俯瞰と横（②）</t>
-        </is>
-      </c>
+      <c r="B40" s="7" t="inlineStr"/>
+      <c r="C40" s="7" t="inlineStr"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>② S1-1</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
-        </is>
-      </c>
+          <t>⑥ S3-3</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr"/>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>超マクロ。刃が革に入る瞬間。何を見ているか分からない距離　［0-3秒］</t>
+          <t>革の上に型紙を置き、取り都合を決める（寄り）　［25-42秒］</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr"/>
@@ -1316,17 +1304,29 @@
       <c r="A41" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B41" s="7" t="inlineStr"/>
-      <c r="C41" s="7" t="inlineStr"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>工房・裁つ</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>作業台・真俯瞰と横（②）</t>
+        </is>
+      </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>② S1-2</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr"/>
+          <t>② S1-1</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+        </is>
+      </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>刃が進み、革の繊維が開いていく（同じ画角のまま）　［0-3秒］</t>
+          <t>超マクロ。刃が革に入る瞬間。何を見ているか分からない距離　［0-3秒］</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr"/>
@@ -1340,13 +1340,13 @@
       <c r="C42" s="7" t="inlineStr"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>② S1-3</t>
+          <t>② S1-2</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr"/>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>「スッ」と抜ける一音だけ。BGMは鳴らさない　［0-3秒］</t>
+          <t>刃が進み、革の繊維が開いていく（同じ画角のまま）　［0-3秒］</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr"/>
@@ -1360,13 +1360,13 @@
       <c r="C43" s="7" t="inlineStr"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>② S2-1</t>
+          <t>② S1-3</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。金属定規を当てて直線を一気に引く　［3-11秒］</t>
+          <t>「スッ」と抜ける一音だけ。BGMは鳴らさない　［0-3秒］</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr"/>
@@ -1380,13 +1380,13 @@
       <c r="C44" s="7" t="inlineStr"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>② S2-2</t>
+          <t>② S2-1</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr"/>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>角を回して切る（横）　［3-11秒］</t>
+          <t>真俯瞰。金属定規を当てて直線を一気に引く　［3-11秒］</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr"/>
@@ -1400,13 +1400,13 @@
       <c r="C45" s="7" t="inlineStr"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>② S2-3</t>
+          <t>② S2-2</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr"/>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>切り終わり。断面がまだ生成りのまま残っている　［3-11秒］</t>
+          <t>角を回して切る（横）　［3-11秒］</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr"/>
@@ -1420,13 +1420,13 @@
       <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>② S3-1</t>
+          <t>② S2-3</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr"/>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>菱目打ちを槌で打つ。同じ音が三回続く（横）　［11-17秒］</t>
+          <t>切り終わり。断面がまだ生成りのまま残っている　［3-11秒］</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr"/>
@@ -1440,13 +1440,13 @@
       <c r="C47" s="7" t="inlineStr"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>② S3-2</t>
+          <t>② S3-1</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr"/>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>等間隔に並んだ穴だけが画面に残る　［11-17秒］</t>
+          <t>菱目打ちを槌で打つ。同じ音が三回続く（横）　［11-17秒］</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr"/>
@@ -1460,13 +1460,13 @@
       <c r="C48" s="7" t="inlineStr"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>② S3-3</t>
+          <t>② S3-2</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr"/>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>目打ちの超マクロ。革の断面と穴が同じ画面に入る　［11-17秒］</t>
+          <t>等間隔に並んだ穴だけが画面に残る　［11-17秒］</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr"/>
@@ -1477,24 +1477,16 @@
         <v>38</v>
       </c>
       <c r="B49" s="7" t="inlineStr"/>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>裁断機と革包丁（⑥）</t>
-        </is>
-      </c>
+      <c r="C49" s="7" t="inlineStr"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>⑥ S4-1</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>② S3-3</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr"/>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>金型が置かれ、裁断機が下りる。テロップ「金型裁断 Die Cutting」　［42-62秒］</t>
+          <t>目打ちの超マクロ。革の断面と穴が同じ画面に入る　［11-17秒］</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr"/>
@@ -1505,16 +1497,24 @@
         <v>39</v>
       </c>
       <c r="B50" s="7" t="inlineStr"/>
-      <c r="C50" s="7" t="inlineStr"/>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>裁断機と革包丁（⑥）</t>
+        </is>
+      </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>⑥ S4-2</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr"/>
+          <t>⑥ S4-1</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>革包丁で細部を切る。テロップ「手裁断 Hand Cutting」　［42-62秒］</t>
+          <t>金型が置かれ、裁断機が下りる。テロップ「金型裁断 Die Cutting」　［42-62秒］</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr"/>
@@ -1528,13 +1528,13 @@
       <c r="C51" s="7" t="inlineStr"/>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>⑥ S4-3</t>
+          <t>⑥ S4-2</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>裁ち上がったパーツが並ぶ。量産も少量も同じ場所でできる　［42-62秒］</t>
+          <t>革包丁で細部を切る。テロップ「手裁断 Hand Cutting」　［42-62秒］</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr"/>
@@ -1544,29 +1544,17 @@
       <c r="A52" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>工房・下仕事</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>漉き・目打ち（⑥）</t>
-        </is>
-      </c>
+      <c r="B52" s="7" t="inlineStr"/>
+      <c r="C52" s="7" t="inlineStr"/>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>⑥ S5-1</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑥ S4-3</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>革を漉いて厚みを揃える（寄り）。テロップ「漉き Skiving」　［62-82秒］</t>
+          <t>裁ち上がったパーツが並ぶ。量産も少量も同じ場所でできる　［42-62秒］</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr"/>
@@ -1576,17 +1564,29 @@
       <c r="A53" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B53" s="7" t="inlineStr"/>
-      <c r="C53" s="7" t="inlineStr"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>工房・下仕事</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>漉き・目打ち（⑥）</t>
+        </is>
+      </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>⑥ S5-2</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr"/>
+          <t>⑥ S5-1</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>目打ち・接着。縫う前の下ごしらえ（マクロ）　［62-82秒］</t>
+          <t>革を漉いて厚みを揃える（寄り）。テロップ「漉き Skiving」　［62-82秒］</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr"/>
@@ -1600,13 +1600,13 @@
       <c r="C54" s="7" t="inlineStr"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>⑥ S5-3</t>
+          <t>⑥ S5-2</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr"/>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の顔。手元から顔へパンし、目線だけを見せる　［62-82秒］</t>
+          <t>目打ち・接着。縫う前の下ごしらえ（マクロ）　［62-82秒］</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr"/>
@@ -1616,29 +1616,17 @@
       <c r="A55" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>工房・縫う</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>ミシンと手縫い（⑥）</t>
-        </is>
-      </c>
+      <c r="B55" s="7" t="inlineStr"/>
+      <c r="C55" s="7" t="inlineStr"/>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>⑥ S6-1</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑥ S5-3</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>ミシンで縫う（横）。テロップ「機械縫製 Machine Stitching」　［82-102秒］</t>
+          <t>Bロール：職人の顔。手元から顔へパンし、目線だけを見せる　［62-82秒］</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr"/>
@@ -1648,17 +1636,29 @@
       <c r="A56" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="B56" s="7" t="inlineStr"/>
-      <c r="C56" s="7" t="inlineStr"/>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>工房・縫う</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>ミシンと手縫い（⑥）</t>
+        </is>
+      </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>⑥ S6-2</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr"/>
+          <t>⑥ S6-1</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>手縫い。二本の針が交差する（マクロ）。テロップ「手縫い Hand Stitching」　［82-102秒］</t>
+          <t>ミシンで縫う（横）。テロップ「機械縫製 Machine Stitching」　［82-102秒］</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr"/>
@@ -1672,13 +1672,13 @@
       <c r="C57" s="7" t="inlineStr"/>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>⑥ S6-3</t>
+          <t>⑥ S6-2</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>目止め → コバ磨き（超マクロ）。ここが全工程の四割　［82-102秒］</t>
+          <t>手縫い。二本の針が交差する（マクロ）。テロップ「手縫い Hand Stitching」　［82-102秒］</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr"/>
@@ -1689,24 +1689,16 @@
         <v>47</v>
       </c>
       <c r="B58" s="7" t="inlineStr"/>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>作業台・真俯瞰と横（②）</t>
-        </is>
-      </c>
+      <c r="C58" s="7" t="inlineStr"/>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>② S4-1</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
-        </is>
-      </c>
+          <t>⑥ S6-3</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr"/>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>針が革を抜ける（寄り）　［17-24秒］</t>
+          <t>目止め → コバ磨き（超マクロ）。ここが全工程の四割　［82-102秒］</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr"/>
@@ -1717,16 +1709,24 @@
         <v>48</v>
       </c>
       <c r="B59" s="7" t="inlineStr"/>
-      <c r="C59" s="7" t="inlineStr"/>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>作業台・真俯瞰と横（②）</t>
+        </is>
+      </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>② S4-2</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr"/>
+          <t>② S4-1</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+        </is>
+      </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>二本の糸が交差して締まる（超マクロ）　［17-24秒］</t>
+          <t>針が革を抜ける（寄り）　［17-24秒］</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
       <c r="C60" s="7" t="inlineStr"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>② S4-3</t>
+          <t>② S4-2</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr"/>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>縫い目に沿って仕上げる。手の動きだけを見せる　［17-24秒］</t>
+          <t>二本の糸が交差して締まる（超マクロ）　［17-24秒］</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr"/>
@@ -1756,29 +1756,17 @@
       <c r="A61" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>工房・コバ</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>作業台・超マクロ（②の核）</t>
-        </is>
-      </c>
+      <c r="B61" s="7" t="inlineStr"/>
+      <c r="C61" s="7" t="inlineStr"/>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>② S5-1</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
-        </is>
-      </c>
+          <t>② S4-3</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr"/>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>塗り始め。道具の先が断面に触れる（超マクロ）　［24-33秒］</t>
+          <t>縫い目に沿って仕上げる。手の動きだけを見せる　［17-24秒］</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr"/>
@@ -1788,17 +1776,29 @@
       <c r="A62" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="B62" s="7" t="inlineStr"/>
-      <c r="C62" s="7" t="inlineStr"/>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>工房・コバ</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>作業台・超マクロ（②の核）</t>
+        </is>
+      </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>② S5-2</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr"/>
+          <t>② S5-1</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+        </is>
+      </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>コバ塗り ★核。塗った側と塗っていない側が同じ画面に入る。長回し・カットを割らない　［24-33秒］</t>
+          <t>塗り始め。道具の先が断面に触れる（超マクロ）　［24-33秒］</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr"/>
@@ -1812,13 +1812,13 @@
       <c r="C63" s="7" t="inlineStr"/>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>② S5-3</t>
+          <t>② S5-2</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr"/>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>塗り終わり。同じ画角のまま断面の色が変わりきっている　［24-33秒］</t>
+          <t>コバ塗り ★核。塗った側と塗っていない側が同じ画面に入る。長回し・カットを割らない　［24-33秒］</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr"/>
@@ -1832,13 +1832,13 @@
       <c r="C64" s="7" t="inlineStr"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>② S6-1</t>
+          <t>② S5-3</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr"/>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>超マクロ。コバを磨く。摩擦音　［33-40秒］</t>
+          <t>塗り終わり。同じ画角のまま断面の色が変わりきっている　［24-33秒］</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr"/>
@@ -1852,13 +1852,13 @@
       <c r="C65" s="7" t="inlineStr"/>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>② S6-2</t>
+          <t>② S6-1</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr"/>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>使われている場所に置かれる → テロップ → ロゴ　［33-40秒］</t>
+          <t>超マクロ。コバを磨く。摩擦音　［33-40秒］</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr"/>
@@ -1872,13 +1872,13 @@
       <c r="C66" s="7" t="inlineStr"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>② S6-3</t>
+          <t>② S6-2</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr"/>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>―　［33-40秒］</t>
+          <t>使われている場所に置かれる → テロップ → ロゴ　［33-40秒］</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr"/>
@@ -1888,29 +1888,17 @@
       <c r="A67" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>工房・全工程</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>一工程一カットで流す（⑤は簡潔に）</t>
-        </is>
-      </c>
+      <c r="B67" s="7" t="inlineStr"/>
+      <c r="C67" s="7" t="inlineStr"/>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>⑤ S6-1</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>② S6-3</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr"/>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>くさがやさん。この一カットだけ画に映る。横顔、空いた側に見出しテロップ。声は次のカットにかぶったまま続く　［52-63秒］</t>
+          <t>―　［33-40秒］</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr"/>
@@ -1920,17 +1908,29 @@
       <c r="A68" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="B68" s="7" t="inlineStr"/>
-      <c r="C68" s="7" t="inlineStr"/>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>工房・全工程</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>一工程一カットで流す（⑤は簡潔に）</t>
+        </is>
+      </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>⑤ S6-2</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr"/>
+          <t>⑤ S5-2</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>BROOKLYN MUSEUM 店舗の外観　［52-63秒］</t>
+          <t>原反が積まれている（引き）　［38-52秒］</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr"/>
@@ -1944,13 +1944,13 @@
       <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>⑤ S6-3</t>
+          <t>⑤ S5-3</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>店内。棚に並ぶ商品を、お客様が手に取る　［52-63秒］</t>
+          <t>裁つ・縫う・磨く。一工程一カット。説明はしない。ここでくさがやさんの声が先に入りはじめる（Jカット）　［38-52秒］</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr"/>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>机まわり・CADと数値（⑤⑥共通）</t>
+          <t>机まわり・図面と数値（⑤⑥共通）</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>⑤ S5-1</t>
+          <t>⑤ S4-1</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>佐藤さん。この一カットだけ画に映る。引き、背景に工房。声は次のカットにかぶったまま続く　［38-52秒］</t>
+          <t>手が図面をなぞる（寄り）　［29-38秒］</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr"/>
@@ -2140,13 +2140,13 @@
       <c r="C77" s="7" t="inlineStr"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>⑤ S5-2</t>
+          <t>⑤ S4-2</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>原反が積まれている（引き）　［38-52秒］</t>
+          <t>型紙・図面の俯瞰　［29-38秒］</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr"/>
@@ -2160,13 +2160,13 @@
       <c r="C78" s="7" t="inlineStr"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>⑤ S5-3</t>
+          <t>⑤ S4-3</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr"/>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>裁つ・縫う・磨く。一工程一カット。説明はしない。ここでくさがやさんの声が先に入りはじめる（Jカット）　［38-52秒］</t>
+          <t>机で数値を決める。ここで佐藤さんの声が先に入りはじめる（Jカット）　［29-38秒］</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr"/>
@@ -2179,12 +2179,12 @@
       <c r="B79" s="7" t="inlineStr"/>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>机まわり・サンプルと図面（⑤⑥共通）</t>
+          <t>革を選ぶ・色を決める（⑤）</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>⑤ S4-1</t>
+          <t>⑤ S3-1</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>手が図面をなぞる（寄り）　［29-38秒］</t>
+          <t>革が色ごとに並ぶ。扱える色数がそのまま伝わる　［20-29秒］</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr"/>
@@ -2208,13 +2208,13 @@
       <c r="C80" s="7" t="inlineStr"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>⑤ S4-2</t>
+          <t>⑤ S3-2</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr"/>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>型紙・図面の俯瞰　［29-38秒］</t>
+          <t>色を選ぶ（寄り）　［20-29秒］</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr"/>
@@ -2228,13 +2228,13 @@
       <c r="C81" s="7" t="inlineStr"/>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>⑤ S4-3</t>
+          <t>⑤ S3-3</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>机で数値を決める。ここで佐藤さんの声が先に入りはじめる（Jカット）　［29-38秒］</t>
+          <t>工房に革が吊るされている（引き）　［20-29秒］</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>昔の写真・カタログの複写（⑤）</t>
+          <t>沿革の写真を複写する（⑤）</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-1</t>
+          <t>⑤ S6-2</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>会計。店員から手渡される瞬間　［63-75秒］</t>
+          <t>BROOKLYN MUSEUM 店舗の外観　［52-63秒］</t>
         </is>
       </c>
       <c r="G124" s="11" t="inlineStr"/>
@@ -3164,13 +3164,13 @@
       <c r="C125" s="7" t="inlineStr"/>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-2</t>
+          <t>⑤ S6-3</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr"/>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>受け取った人の笑顔 → 街で実際に使われている手元 三人の声はここで終わる　［63-75秒］</t>
+          <t>店内。棚に並ぶ商品を、お客様が手に取る　［52-63秒］</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr"/>
@@ -3180,17 +3180,29 @@
       <c r="A126" s="7" t="n">
         <v>115</v>
       </c>
-      <c r="B126" s="7" t="inlineStr"/>
-      <c r="C126" s="7" t="inlineStr"/>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>お客様・開封</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>買った日の再現（⑧）</t>
+        </is>
+      </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-3</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr"/>
+          <t>⑧ S4-1</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>音が引き、ロゴだけ。テロップは出さない　［63-75秒］</t>
+          <t>商品の真俯瞰。声は続いたまま　［30-42秒］</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr"/>
@@ -3200,29 +3212,17 @@
       <c r="A127" s="7" t="n">
         <v>116</v>
       </c>
-      <c r="B127" s="8" t="inlineStr">
-        <is>
-          <t>お客様・開封</t>
-        </is>
-      </c>
-      <c r="C127" s="9" t="inlineStr">
-        <is>
-          <t>買った日の再現（⑧）</t>
-        </is>
-      </c>
+      <c r="B127" s="7" t="inlineStr"/>
+      <c r="C127" s="7" t="inlineStr"/>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-1</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑧ S4-2</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>商品の真俯瞰。声は続いたまま　［30-42秒］</t>
+          <t>売り場・棚の引き　［30-42秒］</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr"/>
@@ -3236,13 +3236,13 @@
       <c r="C128" s="7" t="inlineStr"/>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-2</t>
+          <t>⑧ S4-3</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr"/>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>売り場・棚の引き　［30-42秒］</t>
+          <t>ディテールの寄り。良かった点を語っている場所に重ねる　［30-42秒］</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr"/>
@@ -3252,17 +3252,29 @@
       <c r="A129" s="7" t="n">
         <v>118</v>
       </c>
-      <c r="B129" s="7" t="inlineStr"/>
-      <c r="C129" s="7" t="inlineStr"/>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>お客様・街</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>使用シーン（⑧）</t>
+        </is>
+      </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-3</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr"/>
+          <t>⑧ S3-1</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>ディテールの寄り。良かった点を語っている場所に重ねる　［30-42秒］</t>
+          <t>ここから画はBロールに変わるが、声はそのまま流し続ける　［18-30秒］</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr"/>
@@ -3272,29 +3284,17 @@
       <c r="A130" s="7" t="n">
         <v>119</v>
       </c>
-      <c r="B130" s="8" t="inlineStr">
-        <is>
-          <t>お客様・街</t>
-        </is>
-      </c>
-      <c r="C130" s="9" t="inlineStr">
-        <is>
-          <t>使用シーン（⑧）</t>
-        </is>
-      </c>
+      <c r="B130" s="7" t="inlineStr"/>
+      <c r="C130" s="7" t="inlineStr"/>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-1</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S3-2</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr"/>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>ここから画はBロールに変わるが、声はそのまま流し続ける　［18-30秒］</t>
+          <t>同じ場所を別の角度で。声に合わせて切り替える　［18-30秒］</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr"/>
@@ -3308,13 +3308,13 @@
       <c r="C131" s="7" t="inlineStr"/>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-2</t>
+          <t>⑧ S3-3</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr"/>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>同じ場所を別の角度で。声に合わせて切り替える　［18-30秒］</t>
+          <t>落ち着いた場所での一枚。間を作る　［18-30秒］</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr"/>
@@ -3325,16 +3325,24 @@
         <v>121</v>
       </c>
       <c r="B132" s="7" t="inlineStr"/>
-      <c r="C132" s="7" t="inlineStr"/>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>受け取りと使用（⑤⑧共通）</t>
+        </is>
+      </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-3</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr"/>
+          <t>⑤ S7-1</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>落ち着いた場所での一枚。間を作る　［18-30秒］</t>
+          <t>会計。店員から手渡される瞬間　［63-70秒］</t>
         </is>
       </c>
       <c r="G132" s="11" t="inlineStr"/>
@@ -3345,24 +3353,16 @@
         <v>122</v>
       </c>
       <c r="B133" s="7" t="inlineStr"/>
-      <c r="C133" s="9" t="inlineStr">
-        <is>
-          <t>受け取りと使用（⑤⑧共通）</t>
-        </is>
-      </c>
+      <c r="C133" s="7" t="inlineStr"/>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-1</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑤ S7-2</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr"/>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>外観のロー。空を入れて見上げる。まだ人は出さない　［0-8秒］</t>
+          <t>受け取った人の笑顔　［63-70秒］</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr"/>
@@ -3376,13 +3376,13 @@
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-2</t>
+          <t>⑤ S7-3</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr"/>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>店舗／工房の全景（引き）。人が出入りする　［0-8秒］</t>
+          <t>街で実際に使われている手元。ここで永尾社長の声がもう一度入りはじめる（Jカット）　［63-70秒］</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr"/>
@@ -3396,13 +3396,13 @@
       <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-3</t>
+          <t>⑧ S1-1</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr"/>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>窓辺と光。商品が置いてある（寄り）　［0-8秒］</t>
+          <t>外観のロー。空を入れて見上げる。まだ人は出さない　［0-8秒］</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr"/>
@@ -3413,24 +3413,16 @@
         <v>125</v>
       </c>
       <c r="B136" s="7" t="inlineStr"/>
-      <c r="C136" s="9" t="inlineStr">
-        <is>
-          <t>締め（⑧）</t>
-        </is>
-      </c>
+      <c r="C136" s="7" t="inlineStr"/>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-1</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S1-2</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr"/>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>最後の一言。台本にない言葉を拾う　［52-60秒］</t>
+          <t>店舗／工房の全景（引き）。人が出入りする　［0-8秒］</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr"/>
@@ -3444,13 +3436,13 @@
       <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-2</t>
+          <t>⑧ S1-3</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr"/>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>テロップ　［52-60秒］</t>
+          <t>窓辺と光。商品が置いてある（寄り）　［0-8秒］</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr"/>
@@ -3461,16 +3453,24 @@
         <v>127</v>
       </c>
       <c r="B138" s="7" t="inlineStr"/>
-      <c r="C138" s="7" t="inlineStr"/>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>締め（⑤）</t>
+        </is>
+      </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-3</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr"/>
+          <t>⑤ S8-2</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>ロゴ　［52-60秒］</t>
+          <t>声が終わり、音が引く。ロゴだけ。テロップは出さない　［70-75秒］</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr"/>
@@ -3480,29 +3480,17 @@
       <c r="A139" s="7" t="n">
         <v>128</v>
       </c>
-      <c r="B139" s="8" t="inlineStr">
-        <is>
-          <t>屋外・街</t>
-        </is>
-      </c>
-      <c r="C139" s="9" t="inlineStr">
-        <is>
-          <t>自宅の玄関まわり（①）</t>
-        </is>
-      </c>
+      <c r="B139" s="7" t="inlineStr"/>
+      <c r="C139" s="7" t="inlineStr"/>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>① S1-1</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>⑤ S8-3</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr"/>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>玄関の中。全身が入る引き。出かける支度をしている　［0-5秒］</t>
+          <t>―　［70-75秒］</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr"/>
@@ -3513,16 +3501,24 @@
         <v>129</v>
       </c>
       <c r="B140" s="7" t="inlineStr"/>
-      <c r="C140" s="7" t="inlineStr"/>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>締め（⑧）</t>
+        </is>
+      </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>① S1-2</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr"/>
+          <t>⑧ S6-1</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>ドアの前に立つ（引き）。同じ画角に固定する　［0-5秒］</t>
+          <t>最後の一言。台本にない言葉を拾う　［52-60秒］</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr"/>
@@ -3536,13 +3532,13 @@
       <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>① S1-3</t>
+          <t>⑧ S6-2</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr"/>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>ドアが開く。開いた瞬間、服も鞄も変わっている。同じ画角のまま。この一本の決まりごとを、いちばん最初に見せてしまう　［0-5秒］</t>
+          <t>テロップ　［52-60秒］</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr"/>
@@ -3556,13 +3552,13 @@
       <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>① S2-1</t>
+          <t>⑧ S6-3</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr"/>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［5-9秒］</t>
+          <t>ロゴ　［52-60秒］</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr"/>
@@ -3572,17 +3568,29 @@
       <c r="A143" s="7" t="n">
         <v>132</v>
       </c>
-      <c r="B143" s="7" t="inlineStr"/>
-      <c r="C143" s="7" t="inlineStr"/>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>屋外・街</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>自宅の玄関まわり（①）</t>
+        </is>
+      </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>① S2-2</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr"/>
+          <t>① S1-1</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>同じ画角。歩いてくる全身（一色目）　［5-9秒］</t>
+          <t>玄関の中。全身が入る引き。出かける支度をしている　［0-5秒］</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr"/>
@@ -3596,13 +3604,13 @@
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>① S2-3</t>
+          <t>① S1-2</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>歩き出す全身（引き・ロー）。鞄が体の横で揺れる　［5-9秒］</t>
+          <t>ドアの前に立つ（引き）。同じ画角に固定する　［0-5秒］</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr"/>
@@ -3613,24 +3621,16 @@
         <v>134</v>
       </c>
       <c r="B145" s="7" t="inlineStr"/>
-      <c r="C145" s="9" t="inlineStr">
-        <is>
-          <t>街歩き・夕方の斜光（④）</t>
-        </is>
-      </c>
+      <c r="C145" s="7" t="inlineStr"/>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>④ S1-1</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>① S1-3</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr"/>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
+          <t>ドアが開く。開いた瞬間、服も鞄も変わっている。同じ画角のまま。この一本の決まりごとを、いちばん最初に見せてしまう　［0-5秒］</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr"/>
@@ -3644,13 +3644,13 @@
       <c r="C146" s="7" t="inlineStr"/>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>④ S1-2</t>
+          <t>① S2-1</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr"/>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
+          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［5-9秒］</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr"/>
@@ -3664,13 +3664,13 @@
       <c r="C147" s="7" t="inlineStr"/>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>④ S1-3</t>
+          <t>① S2-2</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr"/>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
+          <t>同じ画角。歩いてくる全身（一色目）　［5-9秒］</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
       <c r="C148" s="7" t="inlineStr"/>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>④ S2-1</t>
+          <t>① S2-3</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr"/>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
+          <t>歩き出す全身（引き・ロー）。鞄が体の横で揺れる　［5-9秒］</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr"/>
@@ -3701,16 +3701,24 @@
         <v>138</v>
       </c>
       <c r="B149" s="7" t="inlineStr"/>
-      <c r="C149" s="7" t="inlineStr"/>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>街歩き・夕方の斜光（④）</t>
+        </is>
+      </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>④ S2-2</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr"/>
+          <t>④ S1-1</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
+          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr"/>
@@ -3724,13 +3732,13 @@
       <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>④ S2-3</t>
+          <t>④ S1-2</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
+          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr"/>
@@ -3744,13 +3752,13 @@
       <c r="C151" s="7" t="inlineStr"/>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>④ S3-1</t>
+          <t>④ S1-3</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
+          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr"/>
@@ -3764,13 +3772,13 @@
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>④ S3-2</t>
+          <t>④ S2-1</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
+          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr"/>
@@ -3784,13 +3792,13 @@
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>④ S3-3</t>
+          <t>④ S2-2</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
+          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr"/>
@@ -3804,13 +3812,13 @@
       <c r="C154" s="7" t="inlineStr"/>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>④ S4-1</t>
+          <t>④ S2-3</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr"/>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
+          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr"/>
@@ -3824,13 +3832,13 @@
       <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>④ S4-2</t>
+          <t>④ S3-1</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr"/>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
+          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr"/>
@@ -3844,13 +3852,13 @@
       <c r="C156" s="7" t="inlineStr"/>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>④ S4-3</t>
+          <t>④ S3-2</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr"/>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
+          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr"/>
@@ -3864,13 +3872,13 @@
       <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>④ S5-1</t>
+          <t>④ S3-3</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr"/>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>手すりの前で立ち止まる　［24-30秒］</t>
+          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr"/>
@@ -3884,13 +3892,13 @@
       <c r="C158" s="7" t="inlineStr"/>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>④ S5-2</t>
+          <t>④ S4-1</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr"/>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。保存袋・小物まで並べる　［24-30秒］</t>
+          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr"/>
@@ -3904,13 +3912,13 @@
       <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>④ S5-3</t>
+          <t>④ S4-2</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
+          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr"/>
@@ -3921,24 +3929,16 @@
         <v>149</v>
       </c>
       <c r="B160" s="7" t="inlineStr"/>
-      <c r="C160" s="9" t="inlineStr">
-        <is>
-          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
-        </is>
-      </c>
+      <c r="C160" s="7" t="inlineStr"/>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>① S3-1</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>④ S4-3</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr"/>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま服が変わっている。小物の色も変わる（二色目）　［9-14秒］</t>
+          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
         </is>
       </c>
       <c r="G160" s="11" t="inlineStr"/>
@@ -3952,13 +3952,13 @@
       <c r="C161" s="7" t="inlineStr"/>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>① S3-2</t>
+          <t>④ S5-1</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>同じ道。三色目　［9-14秒］</t>
+          <t>手すりの前で立ち止まる　［24-30秒］</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr"/>
@@ -3972,13 +3972,13 @@
       <c r="C162" s="7" t="inlineStr"/>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>① S3-3</t>
+          <t>④ S5-2</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>立ち止まって振り返る。手元の色が見える　［9-14秒］</t>
+          <t>真俯瞰。保存袋・小物まで並べる　［24-30秒］</t>
         </is>
       </c>
       <c r="G162" s="11" t="inlineStr"/>
@@ -3992,13 +3992,13 @@
       <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>① S4-1</t>
+          <t>④ S5-3</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>手前を木の幹が横切る（前ボケ＝トランジション）　［14-18秒］</t>
+          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr"/>
@@ -4009,16 +4009,24 @@
         <v>153</v>
       </c>
       <c r="B164" s="7" t="inlineStr"/>
-      <c r="C164" s="7" t="inlineStr"/>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
+        </is>
+      </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>① S4-2</t>
-        </is>
-      </c>
-      <c r="E164" s="7" t="inlineStr"/>
+          <t>① S3-1</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F164" s="10" t="inlineStr">
         <is>
-          <t>抜けたら別の服・別の色になっている（四色目）　［14-18秒］</t>
+          <t>同じ画角のまま服が変わっている。小物の色も変わる（二色目）　［9-14秒］</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr"/>
@@ -4032,13 +4040,13 @@
       <c r="C165" s="7" t="inlineStr"/>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>① S4-3</t>
+          <t>① S3-2</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr"/>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>場所が変わる。駅の構内（引き）　［14-18秒］</t>
+          <t>同じ道。三色目　［9-14秒］</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr"/>
@@ -4052,13 +4060,13 @@
       <c r="C166" s="7" t="inlineStr"/>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>① S5-1</t>
+          <t>① S3-3</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr"/>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>乗り場（引き）。同じ人・違う色　［18-22秒］</t>
+          <t>立ち止まって振り返る。手元の色が見える　［9-14秒］</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr"/>
@@ -4072,13 +4080,13 @@
       <c r="C167" s="7" t="inlineStr"/>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>① S5-2</t>
+          <t>① S4-1</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr"/>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>通路を歩く。横移動で追う　［18-22秒］</t>
+          <t>手前を木の幹が横切る（前ボケ＝トランジション）　［14-18秒］</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr"/>
@@ -4092,13 +4100,13 @@
       <c r="C168" s="7" t="inlineStr"/>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>① S5-3</t>
+          <t>① S4-2</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>会社の入口に着く　［18-22秒］</t>
+          <t>抜けたら別の服・別の色になっている（四色目）　［14-18秒］</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr"/>
@@ -4112,13 +4120,13 @@
       <c r="C169" s="7" t="inlineStr"/>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>① S6-1</t>
+          <t>① S4-3</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr"/>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>ロビーに入る　［22-27秒］</t>
+          <t>場所が変わる。駅の構内（引き）　［14-18秒］</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr"/>
@@ -4132,13 +4140,13 @@
       <c r="C170" s="7" t="inlineStr"/>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>① S6-2</t>
+          <t>① S5-1</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>ロビーを歩く（引き）　［22-27秒］</t>
+          <t>乗り場（引き）。同じ人・違う色　［18-22秒］</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr"/>
@@ -4152,13 +4160,13 @@
       <c r="C171" s="7" t="inlineStr"/>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>① S6-3</t>
+          <t>① S5-2</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>立ち止まる。ここが到着点　［22-27秒］</t>
+          <t>通路を歩く。横移動で追う　［18-22秒］</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr"/>
@@ -4168,29 +4176,17 @@
       <c r="A172" s="7" t="n">
         <v>161</v>
       </c>
-      <c r="B172" s="8" t="inlineStr">
-        <is>
-          <t>締めカード</t>
-        </is>
-      </c>
-      <c r="C172" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。文字を組んで作る</t>
-        </is>
-      </c>
+      <c r="B172" s="7" t="inlineStr"/>
+      <c r="C172" s="7" t="inlineStr"/>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-1</t>
-        </is>
-      </c>
-      <c r="E172" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
+          <t>① S5-3</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="10" t="inlineStr">
         <is>
-          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
+          <t>会社の入口に着く　［18-22秒］</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr"/>
@@ -4204,13 +4200,13 @@
       <c r="C173" s="7" t="inlineStr"/>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-2</t>
+          <t>① S6-1</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr"/>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
+          <t>ロビーに入る　［22-27秒］</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr"/>
@@ -4224,20 +4220,112 @@
       <c r="C174" s="7" t="inlineStr"/>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-3</t>
+          <t>① S6-2</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr"/>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
+          <t>ロビーを歩く（引き）　［22-27秒］</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr"/>
       <c r="H174" s="11" t="inlineStr"/>
     </row>
+    <row r="175" ht="32" customHeight="1">
+      <c r="A175" s="7" t="n">
+        <v>164</v>
+      </c>
+      <c r="B175" s="7" t="inlineStr"/>
+      <c r="C175" s="7" t="inlineStr"/>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>① S6-3</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr"/>
+      <c r="F175" s="10" t="inlineStr">
+        <is>
+          <t>立ち止まる。ここが到着点　［22-27秒］</t>
+        </is>
+      </c>
+      <c r="G175" s="11" t="inlineStr"/>
+      <c r="H175" s="11" t="inlineStr"/>
+    </row>
+    <row r="176" ht="32" customHeight="1">
+      <c r="A176" s="7" t="n">
+        <v>165</v>
+      </c>
+      <c r="B176" s="8" t="inlineStr">
+        <is>
+          <t>締めカード</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。文字を組んで作る</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-1</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
+      <c r="F176" s="10" t="inlineStr">
+        <is>
+          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G176" s="11" t="inlineStr"/>
+      <c r="H176" s="11" t="inlineStr"/>
+    </row>
+    <row r="177" ht="32" customHeight="1">
+      <c r="A177" s="7" t="n">
+        <v>166</v>
+      </c>
+      <c r="B177" s="7" t="inlineStr"/>
+      <c r="C177" s="7" t="inlineStr"/>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-2</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr"/>
+      <c r="F177" s="10" t="inlineStr">
+        <is>
+          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G177" s="11" t="inlineStr"/>
+      <c r="H177" s="11" t="inlineStr"/>
+    </row>
+    <row r="178" ht="32" customHeight="1">
+      <c r="A178" s="7" t="n">
+        <v>167</v>
+      </c>
+      <c r="B178" s="7" t="inlineStr"/>
+      <c r="C178" s="7" t="inlineStr"/>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-3</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr"/>
+      <c r="F178" s="10" t="inlineStr">
+        <is>
+          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G178" s="11" t="inlineStr"/>
+      <c r="H178" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A11:H174"/>
+  <autoFilter ref="A11:H178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ショットリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -815,12 +815,12 @@
       <c r="B19" s="7" t="inlineStr"/>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>永尾社長（⑤・冒頭と締めの二カット）</t>
+          <t>佐藤さん（⑥・工房案内／②にも出演）</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>⑤ S1-3</t>
+          <t>⑥ S1-3</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>永尾社長。この一カットだけ画に映る。バストショット、顔の下に役職テロップ。声は次のシーンにかぶったまま続く　［0-6秒］</t>
+          <t>佐藤さん。工房案内のはじまり。引き、背景に工房。ここから最後まで、佐藤さんの声が画の上に流れ続ける　［0-10秒］</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr"/>
@@ -844,13 +844,13 @@
       <c r="C20" s="7" t="inlineStr"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-1</t>
+          <t>⑥ S8-3</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>永尾社長。締めの一言。冒頭と同じ画角に戻し、頭と終わりで挟む。この一本で言いたいことを、本人の言葉で置く　［70-75秒］</t>
+          <t>佐藤さん。話し終わる瞬間。バストショットに寄る。言い終えて口を閉じるところまで残す　［122-133秒］</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr"/>
@@ -864,13 +864,13 @@
       <c r="C21" s="7" t="inlineStr"/>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>⑥</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr"/>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>30分収録して、経営方針の本音を拾う。台本の読み上げにしない</t>
+          <t>工房を歩きながら案内してもらう。台本は作らない。⑥の全編に流し続けるナレーション素材になる</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr"/>
@@ -884,13 +884,13 @@
       <c r="C22" s="7" t="inlineStr"/>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>⑥</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr"/>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>創業から今までの変遷。⑤の全編に流し続けるナレーション素材になる</t>
+          <t>強みを三つ話してもらう：小ロットから量産まで／自社で完結／誰が作っているか顔が見える</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr"/>
@@ -901,16 +901,24 @@
         <v>12</v>
       </c>
       <c r="B23" s="7" t="inlineStr"/>
-      <c r="C23" s="7" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>永尾社長（⑤・冒頭と締めの二カット）</t>
+        </is>
+      </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr"/>
+          <t>⑤ S1-3</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
+        </is>
+      </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>締めの一言を、収録の最後に一本言い切ってもらう（三十分の収録から抜くのではなく、締め用に撮る）</t>
+          <t>永尾社長。この一カットだけ画に映る。バストショット、顔の下に役職テロップ。声は次のシーンにかぶったまま続く　［0-6秒］</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr"/>
@@ -921,24 +929,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="7" t="inlineStr"/>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>購入者（⑧）</t>
-        </is>
-      </c>
+      <c r="C24" s="7" t="inlineStr"/>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-1</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
-        </is>
-      </c>
+          <t>⑤ S8-1</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr"/>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>バストショット。窓を背にして、手前に植物を置いてボカす。名前は出さず「使っている人」として自己紹介　［8-18秒］</t>
+          <t>永尾社長。締めの一言。冒頭と同じ画角に戻し、頭と終わりで挟む。この一本で言いたいことを、本人の言葉で置く　［70-75秒］</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr"/>
@@ -952,13 +952,13 @@
       <c r="C25" s="7" t="inlineStr"/>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-2</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>同じ画角。カメラは一度も動かさない　［8-18秒］</t>
+          <t>30分収録して、経営方針の本音を拾う。台本の読み上げにしない</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr"/>
@@ -972,13 +972,13 @@
       <c r="C26" s="7" t="inlineStr"/>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-3</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr"/>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>話した言葉をそのままテロップで出す（この参考動画の出し方をそのまま真似る）　［8-18秒］</t>
+          <t>創業から今までの変遷。⑤の全編に流し続けるナレーション素材になる</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr"/>
@@ -992,13 +992,13 @@
       <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-1</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr"/>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>外に出る。空を入れて気分を変える　［42-52秒］</t>
+          <t>締めの一言を、収録の最後に一本言い切ってもらう（三十分の収録から抜くのではなく、締め用に撮る）</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr"/>
@@ -1009,16 +1009,24 @@
         <v>17</v>
       </c>
       <c r="B28" s="7" t="inlineStr"/>
-      <c r="C28" s="7" t="inlineStr"/>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>購入者（⑧）</t>
+        </is>
+      </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-2</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr"/>
+          <t>⑧ S2-1</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯／音声レコーダー／ガンマイク</t>
+        </is>
+      </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>引きの画に人が入る。買ってから変わったことを語る　［42-52秒］</t>
+          <t>バストショット。窓を背にして、手前に植物を置いてボカす。名前は出さず「使っている人」として自己紹介　［8-18秒］</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr"/>
@@ -1032,13 +1040,13 @@
       <c r="C29" s="7" t="inlineStr"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-3</t>
+          <t>⑧ S2-2</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr"/>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>インタビューの画に戻る。表情のアップ　［42-52秒］</t>
+          <t>同じ画角。カメラは一度も動かさない　［8-18秒］</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr"/>
@@ -1048,29 +1056,17 @@
       <c r="A30" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>空撮・外観</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>工房の上空と外観（⑤⑥共通・晴天の午前）</t>
-        </is>
-      </c>
+      <c r="B30" s="7" t="inlineStr"/>
+      <c r="C30" s="7" t="inlineStr"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>⑤ S1-1</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>ドローンまたは高所／カメラ</t>
-        </is>
-      </c>
+          <t>⑧ S2-3</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr"/>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>バードアイショット。東京の空から降り、向島の街と工房を見つける　［0-6秒］</t>
+          <t>話した言葉をそのままテロップで出す（この参考動画の出し方をそのまま真似る）　［8-18秒］</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr"/>
@@ -1084,13 +1080,13 @@
       <c r="C31" s="7" t="inlineStr"/>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>⑤ S1-2</t>
+          <t>⑧ S5-1</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr"/>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>高度を下げ、建物に寄る。ここで永尾社長の声が先に入りはじめる（Jカット）　［0-6秒］</t>
+          <t>外に出る。空を入れて気分を変える　［42-52秒］</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr"/>
@@ -1104,13 +1100,13 @@
       <c r="C32" s="7" t="inlineStr"/>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>⑥ S1-1</t>
+          <t>⑧ S5-2</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>バードアイショット。上から降りて、向島の工房を見つける　［0-10秒］</t>
+          <t>引きの画に人が入る。買ってから変わったことを語る　［42-52秒］</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr"/>
@@ -1124,13 +1120,13 @@
       <c r="C33" s="7" t="inlineStr"/>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>⑥ S1-2</t>
+          <t>⑧ S5-3</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>高度を下げ、建物の全景へ。街の音　［0-10秒］</t>
+          <t>インタビューの画に戻る。表情のアップ　［42-52秒］</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr"/>
@@ -1140,17 +1136,29 @@
       <c r="A34" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B34" s="7" t="inlineStr"/>
-      <c r="C34" s="7" t="inlineStr"/>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>空撮・外観</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>工房の上空と外観（⑤⑥共通・晴天の午前）</t>
+        </is>
+      </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>⑥ S1-3</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr"/>
+          <t>⑤ S1-1</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>ドローンまたは高所／カメラ</t>
+        </is>
+      </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>入口を抜けて中へ。ここから一続きで進む　［0-10秒］</t>
+          <t>バードアイショット。東京の空から降り、向島の街と工房を見つける　［0-6秒］</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr"/>
@@ -1160,29 +1168,17 @@
       <c r="A35" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>工房・全体</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>工房の全景と通路（⑥）</t>
-        </is>
-      </c>
+      <c r="B35" s="7" t="inlineStr"/>
+      <c r="C35" s="7" t="inlineStr"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>⑥ S2-1</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／広角</t>
-        </is>
-      </c>
+          <t>⑤ S1-2</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr"/>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>工房の全景（引き）。規模が分かる画角　［10-25秒］</t>
+          <t>高度を下げ、建物に寄る。ここで永尾社長の声が先に入りはじめる（Jカット）　［0-6秒］</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr"/>
@@ -1196,13 +1192,13 @@
       <c r="C36" s="7" t="inlineStr"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>⑥ S2-2</t>
+          <t>⑥ S1-1</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr"/>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>機械と人が同じ画面に入る。台数と人数が分かる　［10-25秒］</t>
+          <t>バードアイショット。上から降りて、向島の工房を見つける　［0-10秒］</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr"/>
@@ -1216,13 +1212,13 @@
       <c r="C37" s="7" t="inlineStr"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>⑥ S2-3</t>
+          <t>⑥ S1-2</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr"/>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の顔。手を止めずに作業している横顔（寄り）　［10-25秒］</t>
+          <t>高度を下げ、建物の全景へ。街の音　［0-10秒］</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr"/>
@@ -1234,27 +1230,27 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>工房・材料</t>
+          <t>工房・全体</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>原反と金型・型紙（⑥）</t>
+          <t>工房の全景と通路（⑥）</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>⑥ S3-1</t>
+          <t>⑥ S2-1</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>カメラ／三脚</t>
+          <t>カメラ／三脚／広角</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>原反が積まれている。扱える革の量を示す　［25-42秒］</t>
+          <t>入口を抜けて中へ。工房の全景（引き）。規模が分かる画角　［10-25秒］</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr"/>
@@ -1268,13 +1264,13 @@
       <c r="C39" s="7" t="inlineStr"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>⑥ S3-2</t>
+          <t>⑥ S2-2</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr"/>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>金型・型紙が品番ごとに並ぶ。手が一つを抜き出す　［25-42秒］</t>
+          <t>機械と人が同じ画面に入る。台数と人数が分かる　［10-25秒］</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr"/>
@@ -1288,13 +1284,13 @@
       <c r="C40" s="7" t="inlineStr"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>⑥ S3-3</t>
+          <t>⑥ S2-3</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr"/>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>革の上に型紙を置き、取り都合を決める（寄り）　［25-42秒］</t>
+          <t>Bロール：職人の顔。手を止めずに作業している横顔（寄り）　［10-25秒］</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr"/>
@@ -1306,27 +1302,27 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>工房・裁つ</t>
+          <t>工房・材料</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>作業台・真俯瞰と横（②）</t>
+          <t>原反と金型・型紙（⑥）</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>② S1-1</t>
+          <t>⑥ S3-1</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+          <t>カメラ／三脚</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>超マクロ。刃が革に入る瞬間。何を見ているか分からない距離　［0-3秒］</t>
+          <t>原反が積まれている。扱える革の量を示す　［25-42秒］</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr"/>
@@ -1340,13 +1336,13 @@
       <c r="C42" s="7" t="inlineStr"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>② S1-2</t>
+          <t>⑥ S3-2</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr"/>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>刃が進み、革の繊維が開いていく（同じ画角のまま）　［0-3秒］</t>
+          <t>金型・型紙が品番ごとに並ぶ。手が一つを抜き出す　［25-42秒］</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr"/>
@@ -1360,13 +1356,13 @@
       <c r="C43" s="7" t="inlineStr"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>② S1-3</t>
+          <t>⑥ S3-3</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>「スッ」と抜ける一音だけ。BGMは鳴らさない　［0-3秒］</t>
+          <t>革の上に型紙を置き、取り都合を決める（寄り）　［25-42秒］</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr"/>
@@ -1376,17 +1372,29 @@
       <c r="A44" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B44" s="7" t="inlineStr"/>
-      <c r="C44" s="7" t="inlineStr"/>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>工房・裁つ</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>作業台・真俯瞰と横（②）</t>
+        </is>
+      </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>② S2-1</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr"/>
+          <t>② S1-1</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+        </is>
+      </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。金属定規を当てて直線を一気に引く　［3-11秒］</t>
+          <t>超マクロ。刃が革に入る瞬間。何を見ているか分からない距離　［0-3秒］</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr"/>
@@ -1400,13 +1408,13 @@
       <c r="C45" s="7" t="inlineStr"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>② S2-2</t>
+          <t>② S1-2</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr"/>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>角を回して切る（横）　［3-11秒］</t>
+          <t>刃が進み、革の繊維が開いていく（同じ画角のまま）　［0-3秒］</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr"/>
@@ -1420,13 +1428,13 @@
       <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>② S2-3</t>
+          <t>② S1-3</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr"/>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>切り終わり。断面がまだ生成りのまま残っている　［3-11秒］</t>
+          <t>「スッ」と抜ける一音だけ。BGMは鳴らさない　［0-3秒］</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr"/>
@@ -1440,13 +1448,13 @@
       <c r="C47" s="7" t="inlineStr"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>② S3-1</t>
+          <t>② S2-1</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr"/>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>菱目打ちを槌で打つ。同じ音が三回続く（横）　［11-17秒］</t>
+          <t>真俯瞰。金属定規を当てて直線を一気に引く　［3-11秒］</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr"/>
@@ -1460,13 +1468,13 @@
       <c r="C48" s="7" t="inlineStr"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>② S3-2</t>
+          <t>② S2-2</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr"/>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>等間隔に並んだ穴だけが画面に残る　［11-17秒］</t>
+          <t>角を回して切る（横）　［3-11秒］</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr"/>
@@ -1480,13 +1488,13 @@
       <c r="C49" s="7" t="inlineStr"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>② S3-3</t>
+          <t>② S2-3</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr"/>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>目打ちの超マクロ。革の断面と穴が同じ画面に入る　［11-17秒］</t>
+          <t>切り終わり。断面がまだ生成りのまま残っている　［3-11秒］</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr"/>
@@ -1497,24 +1505,16 @@
         <v>39</v>
       </c>
       <c r="B50" s="7" t="inlineStr"/>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>裁断機と革包丁（⑥）</t>
-        </is>
-      </c>
+      <c r="C50" s="7" t="inlineStr"/>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>⑥ S4-1</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>② S3-1</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>金型が置かれ、裁断機が下りる。テロップ「金型裁断 Die Cutting」　［42-62秒］</t>
+          <t>菱目打ちを槌で打つ。同じ音が三回続く（横）　［11-17秒］</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr"/>
@@ -1528,13 +1528,13 @@
       <c r="C51" s="7" t="inlineStr"/>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>⑥ S4-2</t>
+          <t>② S3-2</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>革包丁で細部を切る。テロップ「手裁断 Hand Cutting」　［42-62秒］</t>
+          <t>等間隔に並んだ穴だけが画面に残る　［11-17秒］</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr"/>
@@ -1548,13 +1548,13 @@
       <c r="C52" s="7" t="inlineStr"/>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>⑥ S4-3</t>
+          <t>② S3-3</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>裁ち上がったパーツが並ぶ。量産も少量も同じ場所でできる　［42-62秒］</t>
+          <t>目打ちの超マクロ。革の断面と穴が同じ画面に入る　［11-17秒］</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr"/>
@@ -1564,29 +1564,25 @@
       <c r="A53" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>工房・下仕事</t>
-        </is>
-      </c>
+      <c r="B53" s="7" t="inlineStr"/>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>漉き・目打ち（⑥）</t>
+          <t>裁断機と革包丁（⑥）</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>⑥ S5-1</t>
+          <t>⑥ S4-1</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯</t>
+          <t>カメラ／三脚</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>革を漉いて厚みを揃える（寄り）。テロップ「漉き Skiving」　［62-82秒］</t>
+          <t>金型が置かれ、裁断機が下りる。テロップ「金型裁断 Die Cutting」　［42-62秒］</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr"/>
@@ -1600,13 +1596,13 @@
       <c r="C54" s="7" t="inlineStr"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>⑥ S5-2</t>
+          <t>⑥ S4-2</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr"/>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>目打ち・接着。縫う前の下ごしらえ（マクロ）　［62-82秒］</t>
+          <t>革包丁で細部を切る。テロップ「手裁断 Hand Cutting」　［42-62秒］</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr"/>
@@ -1620,13 +1616,13 @@
       <c r="C55" s="7" t="inlineStr"/>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>⑥ S5-3</t>
+          <t>⑥ S4-3</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の顔。手元から顔へパンし、目線だけを見せる　［62-82秒］</t>
+          <t>裁ち上がったパーツが並ぶ。量産も少量も同じ場所でできる　［42-62秒］</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr"/>
@@ -1638,17 +1634,17 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>工房・縫う</t>
+          <t>工房・下仕事</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>ミシンと手縫い（⑥）</t>
+          <t>漉き・目打ち（⑥）</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>⑥ S6-1</t>
+          <t>⑥ S5-1</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -1658,7 +1654,7 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>ミシンで縫う（横）。テロップ「機械縫製 Machine Stitching」　［82-102秒］</t>
+          <t>革を漉いて厚みを揃える（寄り）。テロップ「漉き Skiving」　［62-82秒］</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr"/>
@@ -1672,13 +1668,13 @@
       <c r="C57" s="7" t="inlineStr"/>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>⑥ S6-2</t>
+          <t>⑥ S5-2</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>手縫い。二本の針が交差する（マクロ）。テロップ「手縫い Hand Stitching」　［82-102秒］</t>
+          <t>目打ち・接着。縫う前の下ごしらえ（マクロ）　［62-82秒］</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr"/>
@@ -1692,13 +1688,13 @@
       <c r="C58" s="7" t="inlineStr"/>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>⑥ S6-3</t>
+          <t>⑥ S5-3</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr"/>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>目止め → コバ磨き（超マクロ）。ここが全工程の四割　［82-102秒］</t>
+          <t>Bロール：職人の顔。手元から顔へパンし、目線だけを見せる　［62-82秒］</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr"/>
@@ -1708,25 +1704,29 @@
       <c r="A59" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B59" s="7" t="inlineStr"/>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>工房・縫う</t>
+        </is>
+      </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>作業台・真俯瞰と横（②）</t>
+          <t>ミシンと手縫い（⑥）</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>② S4-1</t>
+          <t>⑥ S6-1</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+          <t>カメラ／マクロレンズ／三脚／照明1灯</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>針が革を抜ける（寄り）　［17-24秒］</t>
+          <t>ミシンで縫う（横）。テロップ「機械縫製 Machine Stitching」　［82-102秒］</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
       <c r="C60" s="7" t="inlineStr"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>② S4-2</t>
+          <t>⑥ S6-2</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr"/>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>二本の糸が交差して締まる（超マクロ）　［17-24秒］</t>
+          <t>手縫い。二本の針が交差する（マクロ）。テロップ「手縫い Hand Stitching」　［82-102秒］</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr"/>
@@ -1760,13 +1760,13 @@
       <c r="C61" s="7" t="inlineStr"/>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>② S4-3</t>
+          <t>⑥ S6-3</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr"/>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>縫い目に沿って仕上げる。手の動きだけを見せる　［17-24秒］</t>
+          <t>目止め → コバ磨き（超マクロ）。ここが全工程の四割　［82-102秒］</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr"/>
@@ -1776,19 +1776,15 @@
       <c r="A62" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>工房・コバ</t>
-        </is>
-      </c>
+      <c r="B62" s="7" t="inlineStr"/>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>作業台・超マクロ（②の核）</t>
+          <t>作業台・真俯瞰と横（②）</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>② S5-1</t>
+          <t>② S4-1</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -1798,7 +1794,7 @@
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>塗り始め。道具の先が断面に触れる（超マクロ）　［24-33秒］</t>
+          <t>針が革を抜ける（寄り）　［17-24秒］</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr"/>
@@ -1812,13 +1808,13 @@
       <c r="C63" s="7" t="inlineStr"/>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>② S5-2</t>
+          <t>② S4-2</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr"/>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>コバ塗り ★核。塗った側と塗っていない側が同じ画面に入る。長回し・カットを割らない　［24-33秒］</t>
+          <t>二本の糸が交差して締まる（超マクロ）　［17-24秒］</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr"/>
@@ -1832,13 +1828,13 @@
       <c r="C64" s="7" t="inlineStr"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>② S5-3</t>
+          <t>② S4-3</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr"/>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>塗り終わり。同じ画角のまま断面の色が変わりきっている　［24-33秒］</t>
+          <t>縫い目に沿って仕上げる。手の動きだけを見せる　［17-24秒］</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr"/>
@@ -1848,17 +1844,29 @@
       <c r="A65" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B65" s="7" t="inlineStr"/>
-      <c r="C65" s="7" t="inlineStr"/>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>工房・コバ</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>作業台・超マクロ（②の核）</t>
+        </is>
+      </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>② S6-1</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr"/>
+          <t>② S5-1</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+        </is>
+      </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>超マクロ。コバを磨く。摩擦音　［33-40秒］</t>
+          <t>塗り始め。道具の先が断面に触れる（超マクロ）　［24-33秒］</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr"/>
@@ -1872,13 +1880,13 @@
       <c r="C66" s="7" t="inlineStr"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>② S6-2</t>
+          <t>② S5-2</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr"/>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>使われている場所に置かれる → テロップ → ロゴ　［33-40秒］</t>
+          <t>コバ塗り ★核。塗った側と塗っていない側が同じ画面に入る。長回し・カットを割らない　［24-33秒］</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr"/>
@@ -1892,13 +1900,13 @@
       <c r="C67" s="7" t="inlineStr"/>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>② S6-3</t>
+          <t>② S5-3</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr"/>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>―　［33-40秒］</t>
+          <t>塗り終わり。同じ画角のまま断面の色が変わりきっている　［24-33秒］</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr"/>
@@ -1908,29 +1916,17 @@
       <c r="A68" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>工房・全工程</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>一工程一カットで流す（⑤は簡潔に）</t>
-        </is>
-      </c>
+      <c r="B68" s="7" t="inlineStr"/>
+      <c r="C68" s="7" t="inlineStr"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>⑤ S5-2</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>② S6-1</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr"/>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>原反が積まれている（引き）　［38-52秒］</t>
+          <t>超マクロ。コバを磨く。摩擦音　［33-40秒］</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr"/>
@@ -1944,13 +1940,13 @@
       <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>⑤ S5-3</t>
+          <t>② S6-2</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>裁つ・縫う・磨く。一工程一カット。説明はしない。ここでくさがやさんの声が先に入りはじめる（Jカット）　［38-52秒］</t>
+          <t>使われている場所に置かれる → テロップ → ロゴ　［33-40秒］</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr"/>
@@ -1960,29 +1956,17 @@
       <c r="A70" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>工房・検品</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>検品台（⑥・最重要）</t>
-        </is>
-      </c>
+      <c r="B70" s="7" t="inlineStr"/>
+      <c r="C70" s="7" t="inlineStr"/>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>⑥ S7-1</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>② S6-3</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr"/>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>一点を手に取り、光にかざす。作業音が消える　［102-122秒］</t>
+          <t>―　［33-40秒］</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr"/>
@@ -1992,17 +1976,29 @@
       <c r="A71" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B71" s="7" t="inlineStr"/>
-      <c r="C71" s="7" t="inlineStr"/>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>工房・全工程</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>一工程一カットで流す（⑤は簡潔に）</t>
+        </is>
+      </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>⑥ S7-2</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr"/>
+          <t>⑤ S5-2</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>寸法と縫い目を目で確かめる（寄り）　［102-122秒］</t>
+          <t>原反が積まれている（引き）　［38-52秒］</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr"/>
@@ -2016,13 +2012,13 @@
       <c r="C72" s="7" t="inlineStr"/>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>⑥ S7-3</t>
+          <t>⑤ S5-3</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr"/>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の顔。確かめ終えて顔を上げる一瞬。テロップ「検品 Inspection」　［102-122秒］</t>
+          <t>裁つ・縫う・磨く。一工程一カット。説明はしない。ここでくさがやさんの声が先に入りはじめる（Jカット）　［38-52秒］</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr"/>
@@ -2034,27 +2030,27 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>工房・検品</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>梱包場（⑥）</t>
+          <t>検品台（⑥・最重要）</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>⑥ S8-1</t>
+          <t>⑥ S7-1</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>カメラ／三脚</t>
+          <t>カメラ／三脚／照明1灯</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>不織布で包み、角を折る（真俯瞰）。紙の音　［122-133秒］</t>
+          <t>一点を手に取り、光にかざす。作業音が消える　［102-122秒］</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr"/>
@@ -2068,13 +2064,13 @@
       <c r="C74" s="7" t="inlineStr"/>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>⑥ S8-2</t>
+          <t>⑥ S7-2</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr"/>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>箱に納め、テープで閉じる。テロップ「梱包 Packing」　［122-133秒］</t>
+          <t>寸法と縫い目を目で確かめる（寄り）　［102-122秒］</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr"/>
@@ -2088,13 +2084,13 @@
       <c r="C75" s="7" t="inlineStr"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>⑥ S8-3</t>
+          <t>⑥ S7-3</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>出荷を待つ箱が積まれている。ここまで見せる　［122-133秒］</t>
+          <t>Bロール：職人の顔。確かめ終えて顔を上げる一瞬。テロップ「検品 Inspection」　［102-122秒］</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr"/>
@@ -2106,27 +2102,27 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>企画・設計</t>
+          <t>梱包</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>机まわり・図面と数値（⑤⑥共通）</t>
+          <t>梱包場（⑥）</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>⑤ S4-1</t>
+          <t>⑥ S8-1</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>カメラ／三脚／照明1灯</t>
+          <t>カメラ／三脚</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>手が図面をなぞる（寄り）　［29-38秒］</t>
+          <t>不織布で包み、角を折る（真俯瞰）。紙の音　［122-133秒］</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr"/>
@@ -2140,13 +2136,13 @@
       <c r="C77" s="7" t="inlineStr"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>⑤ S4-2</t>
+          <t>⑥ S8-2</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>型紙・図面の俯瞰　［29-38秒］</t>
+          <t>箱に納め、テープで閉じる → 出荷を待つ箱が積まれている。テロップ「梱包 Packing」　［122-133秒］</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr"/>
@@ -2156,17 +2152,29 @@
       <c r="A78" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="B78" s="7" t="inlineStr"/>
-      <c r="C78" s="7" t="inlineStr"/>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>企画・設計</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>机まわり・図面と数値（⑤⑥共通）</t>
+        </is>
+      </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>⑤ S4-3</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr"/>
+          <t>⑤ S4-1</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>机で数値を決める。ここで佐藤さんの声が先に入りはじめる（Jカット）　［29-38秒］</t>
+          <t>手が図面をなぞる（寄り）　［29-38秒］</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr"/>
@@ -2177,24 +2185,16 @@
         <v>68</v>
       </c>
       <c r="B79" s="7" t="inlineStr"/>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>革を選ぶ・色を決める（⑤）</t>
-        </is>
-      </c>
+      <c r="C79" s="7" t="inlineStr"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>⑤ S3-1</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑤ S4-2</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>革が色ごとに並ぶ。扱える色数がそのまま伝わる　［20-29秒］</t>
+          <t>型紙・図面の俯瞰　［29-38秒］</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr"/>
@@ -2208,13 +2208,13 @@
       <c r="C80" s="7" t="inlineStr"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>⑤ S3-2</t>
+          <t>⑤ S4-3</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr"/>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>色を選ぶ（寄り）　［20-29秒］</t>
+          <t>机で数値を決める。ここで佐藤さんの声が先に入りはじめる（Jカット）　［29-38秒］</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr"/>
@@ -2225,16 +2225,24 @@
         <v>70</v>
       </c>
       <c r="B81" s="7" t="inlineStr"/>
-      <c r="C81" s="7" t="inlineStr"/>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>革を選ぶ・色を決める（⑤）</t>
+        </is>
+      </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>⑤ S3-3</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr"/>
+          <t>⑤ S3-1</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>工房に革が吊るされている（引き）　［20-29秒］</t>
+          <t>革が色ごとに並ぶ。扱える色数がそのまま伝わる　［20-29秒］</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr"/>
@@ -2244,29 +2252,17 @@
       <c r="A82" s="7" t="n">
         <v>71</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>複写・資料</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>沿革の写真を複写する（⑤）</t>
-        </is>
-      </c>
+      <c r="B82" s="7" t="inlineStr"/>
+      <c r="C82" s="7" t="inlineStr"/>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>⑤ S2-1</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／自然光</t>
-        </is>
-      </c>
+          <t>⑤ S3-2</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr"/>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>1979年の創業。ヒストリーページの一枚目。年号テロップ「1979　東京千駄ヶ谷にて創業」を重ねる（画面上部の英字はサイト側の見出し。実際は年号テロップだけを載せる）　［6-20秒］</t>
+          <t>色を選ぶ（寄り）　［20-29秒］</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr"/>
@@ -2280,13 +2276,13 @@
       <c r="C83" s="7" t="inlineStr"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>⑤ S2-2</t>
+          <t>⑤ S3-3</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>1984 To Boot New York。年号テロップを続けて重ねる（1980 SHIPS ／ 1982 BEAMS ／ 1984 To Boot New York）　［6-20秒］</t>
+          <t>工房に革が吊るされている（引き）　［20-29秒］</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr"/>
@@ -2296,17 +2292,29 @@
       <c r="A84" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="B84" s="7" t="inlineStr"/>
-      <c r="C84" s="7" t="inlineStr"/>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>複写・資料</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>沿革の写真を複写する（⑤）</t>
+        </is>
+      </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>⑤ S2-3</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr"/>
+          <t>⑤ S2-1</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／自然光</t>
+        </is>
+      </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>同じ構図のまま今の BROOKLYN MUSEUM 店舗へ。白黒からカラーに変わる　［6-20秒］</t>
+          <t>1979年の創業。ヒストリーページの一枚目。年号テロップ「1979　東京千駄ヶ谷にて創業」を重ねる（画面上部の英字はサイト側の見出し。実際は年号テロップだけを載せる）　［6-20秒］</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr"/>
@@ -2316,29 +2324,17 @@
       <c r="A85" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>黒バック撮影</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>黒スチレンボード＋一灯（③専用・別日）</t>
-        </is>
-      </c>
+      <c r="B85" s="7" t="inlineStr"/>
+      <c r="C85" s="7" t="inlineStr"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>③ S1-1</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／黒スチレンボード／アクリル板／白手袋</t>
-        </is>
-      </c>
+          <t>⑤ S2-2</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr"/>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>真っ黒。細い光の帯が一本だけ立つ　［0-4秒］</t>
+          <t>1984 To Boot New York。年号テロップを続けて重ねる（1980 SHIPS ／ 1982 BEAMS ／ 1984 To Boot New York）　［6-20秒］</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr"/>
@@ -2352,13 +2348,13 @@
       <c r="C86" s="7" t="inlineStr"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>③ S1-2</t>
+          <t>⑤ S2-3</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr"/>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>光の帯がゆっくり動く。無音から低いBGMが立ち上がる　［0-4秒］</t>
+          <t>同じ構図のまま今の BROOKLYN MUSEUM 店舗へ。白黒からカラーに変わる　［6-20秒］</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr"/>
@@ -2368,17 +2364,29 @@
       <c r="A87" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="B87" s="7" t="inlineStr"/>
-      <c r="C87" s="7" t="inlineStr"/>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>黒バック撮影</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>黒スチレンボード＋一灯（③専用・別日）</t>
+        </is>
+      </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>③ S1-3</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr"/>
+          <t>③ S1-1</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／黒スチレンボード／アクリル板／白手袋</t>
+        </is>
+      </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>―　［0-4秒］</t>
+          <t>真っ黒。細い光の帯が一本だけ立つ　［0-4秒］</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr"/>
@@ -2392,13 +2400,13 @@
       <c r="C88" s="7" t="inlineStr"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>③ S2-1</t>
+          <t>③ S1-2</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr"/>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>道具と染料が並ぶ。手がその前に入る　［4-8秒］</t>
+          <t>光の帯がゆっくり動く。無音から低いBGMが立ち上がる　［0-4秒］</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr"/>
@@ -2412,13 +2420,13 @@
       <c r="C89" s="7" t="inlineStr"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>③ S2-2</t>
+          <t>③ S1-3</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr"/>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>革を持ち上げる。腕時計・指輪は外す　［4-8秒］</t>
+          <t>―　［0-4秒］</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr"/>
@@ -2432,13 +2440,13 @@
       <c r="C90" s="7" t="inlineStr"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>③ S2-3</t>
+          <t>③ S2-1</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr"/>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>暗がりで革を手に取る。ここから作りはじめる　［4-8秒］</t>
+          <t>道具と染料が並ぶ。手がその前に入る　［4-8秒］</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr"/>
@@ -2452,13 +2460,13 @@
       <c r="C91" s="7" t="inlineStr"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>③ S3-1</t>
+          <t>③ S2-2</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr"/>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>手だけ。革を折る　［8-15秒］</t>
+          <t>革を持ち上げる。腕時計・指輪は外す　［4-8秒］</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr"/>
@@ -2472,13 +2480,13 @@
       <c r="C92" s="7" t="inlineStr"/>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>③ S3-2</t>
+          <t>③ S2-3</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr"/>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>縁を押さえる（超マクロ）　［8-15秒］</t>
+          <t>暗がりで革を手に取る。ここから作りはじめる　［4-8秒］</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr"/>
@@ -2492,13 +2500,13 @@
       <c r="C93" s="7" t="inlineStr"/>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>③ S3-3</t>
+          <t>③ S3-1</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>角が立ち上がる。顔と工房は一切映さない　［8-15秒］</t>
+          <t>手だけ。革を折る　［8-15秒］</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr"/>
@@ -2512,13 +2520,13 @@
       <c r="C94" s="7" t="inlineStr"/>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>③ S4-1</t>
+          <t>③ S3-2</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr"/>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>白手袋で金具を持つ。金属が触れる音　［15-19秒］</t>
+          <t>縁を押さえる（超マクロ）　［8-15秒］</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr"/>
@@ -2532,13 +2540,13 @@
       <c r="C95" s="7" t="inlineStr"/>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>③ S4-2</t>
+          <t>③ S3-3</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr"/>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>金具を取り付ける（超マクロ）。カチリと一音　［15-19秒］</t>
+          <t>角が立ち上がる。顔と工房は一切映さない　［8-15秒］</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr"/>
@@ -2552,13 +2560,13 @@
       <c r="C96" s="7" t="inlineStr"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>③ S4-3</t>
+          <t>③ S4-1</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr"/>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>指が金具の縁をなぞる　［15-19秒］</t>
+          <t>白手袋で金具を持つ。金属が触れる音　［15-19秒］</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr"/>
@@ -2572,13 +2580,13 @@
       <c r="C97" s="7" t="inlineStr"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>③ S5-1</t>
+          <t>③ S4-2</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr"/>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>コバに染料を入れる（超マクロ）　※参考動画にこの工程は映っていない。2本目の参考動画（コバ塗り）を見て画角を決める　［19-25秒］</t>
+          <t>金具を取り付ける（超マクロ）。カチリと一音　［15-19秒］</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr"/>
@@ -2592,13 +2600,13 @@
       <c r="C98" s="7" t="inlineStr"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>③ S5-2</t>
+          <t>③ S4-3</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr"/>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>磨く。光が断面に反射する角度を探す（超マクロ）　［19-25秒］</t>
+          <t>指が金具の縁をなぞる　［15-19秒］</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr"/>
@@ -2612,13 +2620,13 @@
       <c r="C99" s="7" t="inlineStr"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>③ S5-3</t>
+          <t>③ S5-1</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr"/>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>磨き終わった断面に、光が一本だけ走る　［19-25秒］</t>
+          <t>コバに染料を入れる（超マクロ）　※参考動画にこの工程は映っていない。2本目の参考動画（コバ塗り）を見て画角を決める　［19-25秒］</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr"/>
@@ -2632,13 +2640,13 @@
       <c r="C100" s="7" t="inlineStr"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>③ S6-1</t>
+          <t>③ S5-2</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr"/>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>完成品を持ち上げる　［25-28秒］</t>
+          <t>磨く。光が断面に反射する角度を探す（超マクロ）　［19-25秒］</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr"/>
@@ -2652,13 +2660,13 @@
       <c r="C101" s="7" t="inlineStr"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>③ S6-2</t>
+          <t>③ S5-3</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr"/>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>道具の前に置く。上から一灯だけ　［25-28秒］</t>
+          <t>磨き終わった断面に、光が一本だけ走る　［19-25秒］</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr"/>
@@ -2672,13 +2680,13 @@
       <c r="C102" s="7" t="inlineStr"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>③ S6-3</t>
+          <t>③ S6-1</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr"/>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>金具のマクロ → BGMが止まる → ロゴのみ。テロップは出さない　［25-28秒］</t>
+          <t>完成品を持ち上げる　［25-28秒］</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr"/>
@@ -2688,29 +2696,17 @@
       <c r="A103" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>白台・物撮り</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>四色を並べる（①の締め）</t>
-        </is>
-      </c>
+      <c r="B103" s="7" t="inlineStr"/>
+      <c r="C103" s="7" t="inlineStr"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>① S7-1</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯／白台</t>
-        </is>
-      </c>
+          <t>③ S6-2</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr"/>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>人がフレームから出る。置かれた小物だけが残る　［27-30秒］</t>
+          <t>道具の前に置く。上から一灯だけ　［25-28秒］</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr"/>
@@ -2724,13 +2720,13 @@
       <c r="C104" s="7" t="inlineStr"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>① S7-2</t>
+          <t>③ S6-3</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr"/>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>四色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る　［27-30秒］</t>
+          <t>金具のマクロ → BGMが止まる → ロゴのみ。テロップは出さない　［25-28秒］</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr"/>
@@ -2740,17 +2736,29 @@
       <c r="A105" s="7" t="n">
         <v>94</v>
       </c>
-      <c r="B105" s="7" t="inlineStr"/>
-      <c r="C105" s="7" t="inlineStr"/>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>白台・物撮り</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>四色を並べる（①の締め）</t>
+        </is>
+      </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>① S7-3</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr"/>
+          <t>① S7-1</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯／白台</t>
+        </is>
+      </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>そのままロゴ。締めのテロップは出さない　［27-30秒］</t>
+          <t>人がフレームから出る。置かれた小物だけが残る　［27-30秒］</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr"/>
@@ -2761,24 +2769,16 @@
         <v>95</v>
       </c>
       <c r="B106" s="7" t="inlineStr"/>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>白い台・正面固定（⑦専用・三品番を同じ画角で）</t>
-        </is>
-      </c>
+      <c r="C106" s="7" t="inlineStr"/>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>⑦ S1-1</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／マクロレンズ／照明1灯／白台／レフ板</t>
-        </is>
-      </c>
+          <t>① S7-2</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr"/>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>超マクロ・モノクロ。ファスナーの歯　［0-4秒］</t>
+          <t>四色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る　［27-30秒］</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr"/>
@@ -2792,13 +2792,13 @@
       <c r="C107" s="7" t="inlineStr"/>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>⑦ S1-2</t>
+          <t>① S7-3</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr"/>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>ストラップと縫い目（モノクロのまま）　［0-4秒］</t>
+          <t>そのままロゴ。締めのテロップは出さない　［27-30秒］</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr"/>
@@ -2809,16 +2809,24 @@
         <v>97</v>
       </c>
       <c r="B108" s="7" t="inlineStr"/>
-      <c r="C108" s="7" t="inlineStr"/>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>白い台・正面固定（⑦専用・三品番を同じ画角で）</t>
+        </is>
+      </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>⑦ S1-3</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="inlineStr"/>
+          <t>⑦ S1-1</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／マクロレンズ／照明1灯／白台／レフ板</t>
+        </is>
+      </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>金具の質感（モノクロのまま）　［0-4秒］</t>
+          <t>超マクロ・モノクロ。ファスナーの歯　［0-4秒］</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr"/>
@@ -2832,13 +2840,13 @@
       <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>⑦ S2-1</t>
+          <t>⑦ S1-2</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr"/>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>引く。カラーに変わる。白い台に鞄が一つ　［4-7秒］</t>
+          <t>ストラップと縫い目（モノクロのまま）　［0-4秒］</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr"/>
@@ -2852,13 +2860,13 @@
       <c r="C110" s="7" t="inlineStr"/>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>⑦ S2-2</t>
+          <t>⑦ S1-3</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr"/>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>正面固定。ここから最後までこの画角のまま　［4-7秒］</t>
+          <t>金具の質感（モノクロのまま）　［0-4秒］</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr"/>
@@ -2872,13 +2880,13 @@
       <c r="C111" s="7" t="inlineStr"/>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>⑦ S2-3</t>
+          <t>⑦ S2-1</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr"/>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>鞄を開ける。中は空　［4-7秒］</t>
+          <t>引く。カラーに変わる。白い台に鞄が一つ　［4-7秒］</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr"/>
@@ -2892,13 +2900,13 @@
       <c r="C112" s="7" t="inlineStr"/>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>⑦ S3-1</t>
+          <t>⑦ S2-2</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr"/>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>A4書類とノートPCを入れる　［7-13秒］</t>
+          <t>正面固定。ここから最後までこの画角のまま　［4-7秒］</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr"/>
@@ -2912,13 +2920,13 @@
       <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>⑦ S3-2</t>
+          <t>⑦ S2-3</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>入りきる。上端にまだ余りがあるのを見せる　［7-13秒］</t>
+          <t>鞄を開ける。中は空　［4-7秒］</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr"/>
@@ -2932,13 +2940,13 @@
       <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>⑦ S3-3</t>
+          <t>⑦ S3-1</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr"/>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>手帳・鍵・サングラス。顔は入れない　［7-13秒］</t>
+          <t>A4書類とノートPCを入れる　［7-13秒］</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr"/>
@@ -2952,13 +2960,13 @@
       <c r="C115" s="7" t="inlineStr"/>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>⑦ S4-1</t>
+          <t>⑦ S3-2</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>ペン・小物。入れる音を一つずつ拾う　［13-17秒］</t>
+          <t>入りきる。上端にまだ余りがあるのを見せる　［7-13秒］</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr"/>
@@ -2972,13 +2980,13 @@
       <c r="C116" s="7" t="inlineStr"/>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>⑦ S4-2</t>
+          <t>⑦ S3-3</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr"/>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>傘・水筒まで入れる。それでもまだ閉まる　［13-17秒］</t>
+          <t>手帳・鍵・サングラス。顔は入れない　［7-13秒］</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr"/>
@@ -2992,13 +3000,13 @@
       <c r="C117" s="7" t="inlineStr"/>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>⑦ S4-3</t>
+          <t>⑦ S4-1</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr"/>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>最後の一つを入れる。ここで手が止まる　［13-17秒］</t>
+          <t>ペン・小物。入れる音を一つずつ拾う　［13-17秒］</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr"/>
@@ -3012,13 +3020,13 @@
       <c r="C118" s="7" t="inlineStr"/>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>⑦ S5-1</t>
+          <t>⑦ S4-2</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr"/>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>片手で持ち上げる。軽さを動作で見せる　［17-21秒］</t>
+          <t>傘・水筒まで入れる。それでもまだ閉まる　［13-17秒］</t>
         </is>
       </c>
       <c r="G118" s="11" t="inlineStr"/>
@@ -3032,13 +3040,13 @@
       <c r="C119" s="7" t="inlineStr"/>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>⑦ S5-2</t>
+          <t>⑦ S4-3</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr"/>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>肩にかける。台は動かさない　［17-21秒］</t>
+          <t>最後の一つを入れる。ここで手が止まる　［13-17秒］</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr"/>
@@ -3052,13 +3060,13 @@
       <c r="C120" s="7" t="inlineStr"/>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>⑦ S5-3</t>
+          <t>⑦ S5-1</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr"/>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>数字を小さくテロップで添える（千百六十グラム）　［17-21秒］</t>
+          <t>片手で持ち上げる。軽さを動作で見せる　［17-21秒］</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr"/>
@@ -3072,13 +3080,13 @@
       <c r="C121" s="7" t="inlineStr"/>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>⑦ S6-1</t>
+          <t>⑦ S5-2</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr"/>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>人がフレームから出る。鞄だけが残る　［21-25秒］</t>
+          <t>肩にかける。台は動かさない　［17-21秒］</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr"/>
@@ -3092,13 +3100,13 @@
       <c r="C122" s="7" t="inlineStr"/>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>⑦ S6-2</t>
+          <t>⑦ S5-3</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr"/>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>テロップ「急がば、定位置。」　［21-25秒］</t>
+          <t>数字を小さくテロップで添える（千百六十グラム）　［17-21秒］</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr"/>
@@ -3112,13 +3120,13 @@
       <c r="C123" s="7" t="inlineStr"/>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>⑦ S6-3</t>
+          <t>⑦ S6-1</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr"/>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>ロゴ。三品番とも同じ終わり方にする　［21-25秒］</t>
+          <t>人がフレームから出る。鞄だけが残る　［21-25秒］</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr"/>
@@ -3128,29 +3136,17 @@
       <c r="A124" s="7" t="n">
         <v>113</v>
       </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>店舗</t>
-        </is>
-      </c>
-      <c r="C124" s="9" t="inlineStr">
-        <is>
-          <t>BROOKLYN MUSEUM 店舗（⑤⑧共通）</t>
-        </is>
-      </c>
+      <c r="B124" s="7" t="inlineStr"/>
+      <c r="C124" s="7" t="inlineStr"/>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>⑤ S6-2</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／ガンマイク</t>
-        </is>
-      </c>
+          <t>⑦ S6-2</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr"/>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>BROOKLYN MUSEUM 店舗の外観　［52-63秒］</t>
+          <t>テロップ「急がば、定位置。」　［21-25秒］</t>
         </is>
       </c>
       <c r="G124" s="11" t="inlineStr"/>
@@ -3164,13 +3160,13 @@
       <c r="C125" s="7" t="inlineStr"/>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>⑤ S6-3</t>
+          <t>⑦ S6-3</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr"/>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>店内。棚に並ぶ商品を、お客様が手に取る　［52-63秒］</t>
+          <t>ロゴ。三品番とも同じ終わり方にする　［21-25秒］</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr"/>
@@ -3182,27 +3178,27 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>お客様・開封</t>
+          <t>店舗</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>買った日の再現（⑧）</t>
+          <t>BROOKLYN MUSEUM 店舗（⑤⑧共通）</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-1</t>
+          <t>⑤ S6-2</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>カメラ／三脚／照明1灯</t>
+          <t>カメラ／三脚／ガンマイク</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>商品の真俯瞰。声は続いたまま　［30-42秒］</t>
+          <t>BROOKLYN MUSEUM 店舗の外観　［52-63秒］</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr"/>
@@ -3216,13 +3212,13 @@
       <c r="C127" s="7" t="inlineStr"/>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-2</t>
+          <t>⑤ S6-3</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>売り場・棚の引き　［30-42秒］</t>
+          <t>店内。棚に並ぶ商品を、お客様が手に取る　［52-63秒］</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr"/>
@@ -3232,17 +3228,29 @@
       <c r="A128" s="7" t="n">
         <v>117</v>
       </c>
-      <c r="B128" s="7" t="inlineStr"/>
-      <c r="C128" s="7" t="inlineStr"/>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>お客様・開封</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>買った日の再現（⑧）</t>
+        </is>
+      </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-3</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr"/>
+          <t>⑧ S4-1</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>ディテールの寄り。良かった点を語っている場所に重ねる　［30-42秒］</t>
+          <t>商品の真俯瞰。声は続いたまま　［30-42秒］</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr"/>
@@ -3252,29 +3260,17 @@
       <c r="A129" s="7" t="n">
         <v>118</v>
       </c>
-      <c r="B129" s="8" t="inlineStr">
-        <is>
-          <t>お客様・街</t>
-        </is>
-      </c>
-      <c r="C129" s="9" t="inlineStr">
-        <is>
-          <t>使用シーン（⑧）</t>
-        </is>
-      </c>
+      <c r="B129" s="7" t="inlineStr"/>
+      <c r="C129" s="7" t="inlineStr"/>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-1</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S4-2</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr"/>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>ここから画はBロールに変わるが、声はそのまま流し続ける　［18-30秒］</t>
+          <t>売り場・棚の引き　［30-42秒］</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr"/>
@@ -3288,13 +3284,13 @@
       <c r="C130" s="7" t="inlineStr"/>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-2</t>
+          <t>⑧ S4-3</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr"/>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>同じ場所を別の角度で。声に合わせて切り替える　［18-30秒］</t>
+          <t>ディテールの寄り。良かった点を語っている場所に重ねる　［30-42秒］</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr"/>
@@ -3304,17 +3300,29 @@
       <c r="A131" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="B131" s="7" t="inlineStr"/>
-      <c r="C131" s="7" t="inlineStr"/>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>お客様・街</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>使用シーン（⑧）</t>
+        </is>
+      </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-3</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr"/>
+          <t>⑧ S3-1</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>落ち着いた場所での一枚。間を作る　［18-30秒］</t>
+          <t>ここから画はBロールに変わるが、声はそのまま流し続ける　［18-30秒］</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr"/>
@@ -3325,24 +3333,16 @@
         <v>121</v>
       </c>
       <c r="B132" s="7" t="inlineStr"/>
-      <c r="C132" s="9" t="inlineStr">
-        <is>
-          <t>受け取りと使用（⑤⑧共通）</t>
-        </is>
-      </c>
+      <c r="C132" s="7" t="inlineStr"/>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-1</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S3-2</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr"/>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>会計。店員から手渡される瞬間　［63-70秒］</t>
+          <t>同じ場所を別の角度で。声に合わせて切り替える　［18-30秒］</t>
         </is>
       </c>
       <c r="G132" s="11" t="inlineStr"/>
@@ -3356,13 +3356,13 @@
       <c r="C133" s="7" t="inlineStr"/>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-2</t>
+          <t>⑧ S3-3</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr"/>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>受け取った人の笑顔　［63-70秒］</t>
+          <t>落ち着いた場所での一枚。間を作る　［18-30秒］</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr"/>
@@ -3373,16 +3373,24 @@
         <v>123</v>
       </c>
       <c r="B134" s="7" t="inlineStr"/>
-      <c r="C134" s="7" t="inlineStr"/>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>受け取りと使用（⑤⑧共通）</t>
+        </is>
+      </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-3</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr"/>
+          <t>⑤ S7-1</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>街で実際に使われている手元。ここで永尾社長の声がもう一度入りはじめる（Jカット）　［63-70秒］</t>
+          <t>会計。店員から手渡される瞬間　［63-70秒］</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr"/>
@@ -3396,13 +3404,13 @@
       <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-1</t>
+          <t>⑤ S7-2</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr"/>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>外観のロー。空を入れて見上げる。まだ人は出さない　［0-8秒］</t>
+          <t>受け取った人の笑顔　［63-70秒］</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr"/>
@@ -3416,13 +3424,13 @@
       <c r="C136" s="7" t="inlineStr"/>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-2</t>
+          <t>⑤ S7-3</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr"/>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>店舗／工房の全景（引き）。人が出入りする　［0-8秒］</t>
+          <t>街で実際に使われている手元。ここで永尾社長の声がもう一度入りはじめる（Jカット）　［63-70秒］</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr"/>
@@ -3436,13 +3444,13 @@
       <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-3</t>
+          <t>⑧ S1-1</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr"/>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>窓辺と光。商品が置いてある（寄り）　［0-8秒］</t>
+          <t>外観のロー。空を入れて見上げる。まだ人は出さない　［0-8秒］</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr"/>
@@ -3453,24 +3461,16 @@
         <v>127</v>
       </c>
       <c r="B138" s="7" t="inlineStr"/>
-      <c r="C138" s="9" t="inlineStr">
-        <is>
-          <t>締め（⑤）</t>
-        </is>
-      </c>
+      <c r="C138" s="7" t="inlineStr"/>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-2</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S1-2</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr"/>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>声が終わり、音が引く。ロゴだけ。テロップは出さない　［70-75秒］</t>
+          <t>店舗／工房の全景（引き）。人が出入りする　［0-8秒］</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr"/>
@@ -3484,13 +3484,13 @@
       <c r="C139" s="7" t="inlineStr"/>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-3</t>
+          <t>⑧ S1-3</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr"/>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>―　［70-75秒］</t>
+          <t>窓辺と光。商品が置いてある（寄り）　［0-8秒］</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr"/>
@@ -3503,12 +3503,12 @@
       <c r="B140" s="7" t="inlineStr"/>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>締め（⑧）</t>
+          <t>締め（⑤）</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-1</t>
+          <t>⑤ S8-2</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>最後の一言。台本にない言葉を拾う　［52-60秒］</t>
+          <t>声が終わり、音が引く。ロゴだけ。テロップは出さない　［70-75秒］</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr"/>
@@ -3532,13 +3532,13 @@
       <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-2</t>
+          <t>⑤ S8-3</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr"/>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>テロップ　［52-60秒］</t>
+          <t>―　［70-75秒］</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr"/>
@@ -3549,16 +3549,24 @@
         <v>131</v>
       </c>
       <c r="B142" s="7" t="inlineStr"/>
-      <c r="C142" s="7" t="inlineStr"/>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>締め（⑧）</t>
+        </is>
+      </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-3</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr"/>
+          <t>⑧ S6-1</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>ロゴ　［52-60秒］</t>
+          <t>最後の一言。台本にない言葉を拾う　［52-60秒］</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr"/>
@@ -3568,29 +3576,17 @@
       <c r="A143" s="7" t="n">
         <v>132</v>
       </c>
-      <c r="B143" s="8" t="inlineStr">
-        <is>
-          <t>屋外・街</t>
-        </is>
-      </c>
-      <c r="C143" s="9" t="inlineStr">
-        <is>
-          <t>自宅の玄関まわり（①）</t>
-        </is>
-      </c>
+      <c r="B143" s="7" t="inlineStr"/>
+      <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>① S1-1</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>⑧ S6-2</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>玄関の中。全身が入る引き。出かける支度をしている　［0-5秒］</t>
+          <t>テロップ　［52-60秒］</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr"/>
@@ -3604,13 +3600,13 @@
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>① S1-2</t>
+          <t>⑧ S6-3</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>ドアの前に立つ（引き）。同じ画角に固定する　［0-5秒］</t>
+          <t>ロゴ　［52-60秒］</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr"/>
@@ -3620,17 +3616,29 @@
       <c r="A145" s="7" t="n">
         <v>134</v>
       </c>
-      <c r="B145" s="7" t="inlineStr"/>
-      <c r="C145" s="7" t="inlineStr"/>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>屋外・街</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>自宅の玄関まわり（①）</t>
+        </is>
+      </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>① S1-3</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr"/>
+          <t>① S1-1</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>ドアが開く。開いた瞬間、服も鞄も変わっている。同じ画角のまま。この一本の決まりごとを、いちばん最初に見せてしまう　［0-5秒］</t>
+          <t>玄関の中。全身が入る引き。出かける支度をしている　［0-5秒］</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr"/>
@@ -3644,13 +3652,13 @@
       <c r="C146" s="7" t="inlineStr"/>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>① S2-1</t>
+          <t>① S1-2</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr"/>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［5-9秒］</t>
+          <t>ドアの前に立つ（引き）。同じ画角に固定する　［0-5秒］</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr"/>
@@ -3664,13 +3672,13 @@
       <c r="C147" s="7" t="inlineStr"/>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>① S2-2</t>
+          <t>① S1-3</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr"/>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>同じ画角。歩いてくる全身（一色目）　［5-9秒］</t>
+          <t>ドアが開く。開いた瞬間、服も鞄も変わっている。同じ画角のまま。この一本の決まりごとを、いちばん最初に見せてしまう　［0-5秒］</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr"/>
@@ -3684,13 +3692,13 @@
       <c r="C148" s="7" t="inlineStr"/>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>① S2-3</t>
+          <t>① S2-1</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr"/>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>歩き出す全身（引き・ロー）。鞄が体の横で揺れる　［5-9秒］</t>
+          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［5-9秒］</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr"/>
@@ -3701,24 +3709,16 @@
         <v>138</v>
       </c>
       <c r="B149" s="7" t="inlineStr"/>
-      <c r="C149" s="9" t="inlineStr">
-        <is>
-          <t>街歩き・夕方の斜光（④）</t>
-        </is>
-      </c>
+      <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>④ S1-1</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>① S2-2</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
+          <t>同じ画角。歩いてくる全身（一色目）　［5-9秒］</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr"/>
@@ -3732,13 +3732,13 @@
       <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>④ S1-2</t>
+          <t>① S2-3</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
+          <t>歩き出す全身（引き・ロー）。鞄が体の横で揺れる　［5-9秒］</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr"/>
@@ -3749,16 +3749,24 @@
         <v>140</v>
       </c>
       <c r="B151" s="7" t="inlineStr"/>
-      <c r="C151" s="7" t="inlineStr"/>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>街歩き・夕方の斜光（④）</t>
+        </is>
+      </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>④ S1-3</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="inlineStr"/>
+          <t>④ S1-1</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
+          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr"/>
@@ -3772,13 +3780,13 @@
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>④ S2-1</t>
+          <t>④ S1-2</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
+          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr"/>
@@ -3792,13 +3800,13 @@
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>④ S2-2</t>
+          <t>④ S1-3</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
+          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr"/>
@@ -3812,13 +3820,13 @@
       <c r="C154" s="7" t="inlineStr"/>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>④ S2-3</t>
+          <t>④ S2-1</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr"/>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
+          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr"/>
@@ -3832,13 +3840,13 @@
       <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>④ S3-1</t>
+          <t>④ S2-2</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr"/>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
+          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr"/>
@@ -3852,13 +3860,13 @@
       <c r="C156" s="7" t="inlineStr"/>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>④ S3-2</t>
+          <t>④ S2-3</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr"/>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
+          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr"/>
@@ -3872,13 +3880,13 @@
       <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>④ S3-3</t>
+          <t>④ S3-1</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr"/>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
+          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr"/>
@@ -3892,13 +3900,13 @@
       <c r="C158" s="7" t="inlineStr"/>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>④ S4-1</t>
+          <t>④ S3-2</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr"/>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
+          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr"/>
@@ -3912,13 +3920,13 @@
       <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>④ S4-2</t>
+          <t>④ S3-3</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
+          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr"/>
@@ -3932,13 +3940,13 @@
       <c r="C160" s="7" t="inlineStr"/>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>④ S4-3</t>
+          <t>④ S4-1</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr"/>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
+          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
         </is>
       </c>
       <c r="G160" s="11" t="inlineStr"/>
@@ -3952,13 +3960,13 @@
       <c r="C161" s="7" t="inlineStr"/>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>④ S5-1</t>
+          <t>④ S4-2</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>手すりの前で立ち止まる　［24-30秒］</t>
+          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr"/>
@@ -3972,13 +3980,13 @@
       <c r="C162" s="7" t="inlineStr"/>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>④ S5-2</t>
+          <t>④ S4-3</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。保存袋・小物まで並べる　［24-30秒］</t>
+          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
         </is>
       </c>
       <c r="G162" s="11" t="inlineStr"/>
@@ -3992,13 +4000,13 @@
       <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>④ S5-3</t>
+          <t>④ S5-1</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
+          <t>手すりの前で立ち止まる　［24-30秒］</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr"/>
@@ -4009,24 +4017,16 @@
         <v>153</v>
       </c>
       <c r="B164" s="7" t="inlineStr"/>
-      <c r="C164" s="9" t="inlineStr">
-        <is>
-          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
-        </is>
-      </c>
+      <c r="C164" s="7" t="inlineStr"/>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>① S3-1</t>
-        </is>
-      </c>
-      <c r="E164" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>④ S5-2</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr"/>
       <c r="F164" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま服が変わっている。小物の色も変わる（二色目）　［9-14秒］</t>
+          <t>真俯瞰。保存袋・小物まで並べる　［24-30秒］</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr"/>
@@ -4040,13 +4040,13 @@
       <c r="C165" s="7" t="inlineStr"/>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>① S3-2</t>
+          <t>④ S5-3</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr"/>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>同じ道。三色目　［9-14秒］</t>
+          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr"/>
@@ -4057,16 +4057,24 @@
         <v>155</v>
       </c>
       <c r="B166" s="7" t="inlineStr"/>
-      <c r="C166" s="7" t="inlineStr"/>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
+        </is>
+      </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>① S3-3</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr"/>
+          <t>① S3-1</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>立ち止まって振り返る。手元の色が見える　［9-14秒］</t>
+          <t>同じ画角のまま服が変わっている。小物の色も変わる（二色目）　［9-14秒］</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr"/>
@@ -4080,13 +4088,13 @@
       <c r="C167" s="7" t="inlineStr"/>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>① S4-1</t>
+          <t>① S3-2</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr"/>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>手前を木の幹が横切る（前ボケ＝トランジション）　［14-18秒］</t>
+          <t>同じ道。三色目　［9-14秒］</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr"/>
@@ -4100,13 +4108,13 @@
       <c r="C168" s="7" t="inlineStr"/>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>① S4-2</t>
+          <t>① S3-3</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>抜けたら別の服・別の色になっている（四色目）　［14-18秒］</t>
+          <t>立ち止まって振り返る。手元の色が見える　［9-14秒］</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr"/>
@@ -4120,13 +4128,13 @@
       <c r="C169" s="7" t="inlineStr"/>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>① S4-3</t>
+          <t>① S4-1</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr"/>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>場所が変わる。駅の構内（引き）　［14-18秒］</t>
+          <t>手前を木の幹が横切る（前ボケ＝トランジション）　［14-18秒］</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr"/>
@@ -4140,13 +4148,13 @@
       <c r="C170" s="7" t="inlineStr"/>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>① S5-1</t>
+          <t>① S4-2</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>乗り場（引き）。同じ人・違う色　［18-22秒］</t>
+          <t>抜けたら別の服・別の色になっている（四色目）　［14-18秒］</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr"/>
@@ -4160,13 +4168,13 @@
       <c r="C171" s="7" t="inlineStr"/>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>① S5-2</t>
+          <t>① S4-3</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>通路を歩く。横移動で追う　［18-22秒］</t>
+          <t>場所が変わる。駅の構内（引き）　［14-18秒］</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr"/>
@@ -4180,13 +4188,13 @@
       <c r="C172" s="7" t="inlineStr"/>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>① S5-3</t>
+          <t>① S5-1</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="10" t="inlineStr">
         <is>
-          <t>会社の入口に着く　［18-22秒］</t>
+          <t>乗り場（引き）。同じ人・違う色　［18-22秒］</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr"/>
@@ -4200,13 +4208,13 @@
       <c r="C173" s="7" t="inlineStr"/>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>① S6-1</t>
+          <t>① S5-2</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr"/>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>ロビーに入る　［22-27秒］</t>
+          <t>通路を歩く。横移動で追う　［18-22秒］</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr"/>
@@ -4220,13 +4228,13 @@
       <c r="C174" s="7" t="inlineStr"/>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>① S6-2</t>
+          <t>① S5-3</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr"/>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>ロビーを歩く（引き）　［22-27秒］</t>
+          <t>会社の入口に着く　［18-22秒］</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr"/>
@@ -4240,13 +4248,13 @@
       <c r="C175" s="7" t="inlineStr"/>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>① S6-3</t>
+          <t>① S6-1</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr"/>
       <c r="F175" s="10" t="inlineStr">
         <is>
-          <t>立ち止まる。ここが到着点　［22-27秒］</t>
+          <t>ロビーに入る　［22-27秒］</t>
         </is>
       </c>
       <c r="G175" s="11" t="inlineStr"/>
@@ -4256,29 +4264,17 @@
       <c r="A176" s="7" t="n">
         <v>165</v>
       </c>
-      <c r="B176" s="8" t="inlineStr">
-        <is>
-          <t>締めカード</t>
-        </is>
-      </c>
-      <c r="C176" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。文字を組んで作る</t>
-        </is>
-      </c>
+      <c r="B176" s="7" t="inlineStr"/>
+      <c r="C176" s="7" t="inlineStr"/>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-1</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
+          <t>① S6-2</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr"/>
       <c r="F176" s="10" t="inlineStr">
         <is>
-          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
+          <t>ロビーを歩く（引き）　［22-27秒］</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr"/>
@@ -4292,13 +4288,13 @@
       <c r="C177" s="7" t="inlineStr"/>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-2</t>
+          <t>① S6-3</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr"/>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
+          <t>立ち止まる。ここが到着点　［22-27秒］</t>
         </is>
       </c>
       <c r="G177" s="11" t="inlineStr"/>
@@ -4308,24 +4304,76 @@
       <c r="A178" s="7" t="n">
         <v>167</v>
       </c>
-      <c r="B178" s="7" t="inlineStr"/>
-      <c r="C178" s="7" t="inlineStr"/>
+      <c r="B178" s="8" t="inlineStr">
+        <is>
+          <t>締めカード</t>
+        </is>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。文字を組んで作る</t>
+        </is>
+      </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-3</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr"/>
+          <t>⑥ S9-1</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
       <c r="F178" s="10" t="inlineStr">
         <is>
-          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
+          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
         </is>
       </c>
       <c r="G178" s="11" t="inlineStr"/>
       <c r="H178" s="11" t="inlineStr"/>
     </row>
+    <row r="179" ht="32" customHeight="1">
+      <c r="A179" s="7" t="n">
+        <v>168</v>
+      </c>
+      <c r="B179" s="7" t="inlineStr"/>
+      <c r="C179" s="7" t="inlineStr"/>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-2</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr"/>
+      <c r="F179" s="10" t="inlineStr">
+        <is>
+          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G179" s="11" t="inlineStr"/>
+      <c r="H179" s="11" t="inlineStr"/>
+    </row>
+    <row r="180" ht="32" customHeight="1">
+      <c r="A180" s="7" t="n">
+        <v>169</v>
+      </c>
+      <c r="B180" s="7" t="inlineStr"/>
+      <c r="C180" s="7" t="inlineStr"/>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-3</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr"/>
+      <c r="F180" s="10" t="inlineStr">
+        <is>
+          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G180" s="11" t="inlineStr"/>
+      <c r="H180" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A11:H178"/>
+  <autoFilter ref="A11:H180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -2354,7 +2354,7 @@
       <c r="E86" s="7" t="inlineStr"/>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>同じ構図のまま今の BROOKLYN MUSEUM 店舗へ。白黒からカラーに変わる　［6-20秒］</t>
+          <t>1979年の写真と同じ構図で、今の店舗へ。ショーウィンドウ越しに店内が見える。白黒からカラーに変わる　［6-20秒］</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr"/>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>BROOKLYN MUSEUM 店舗の外観　［52-63秒］</t>
+          <t>店内（引き）。ショーケースと棚が並ぶ。ロゴが入る位置まで見せる　［52-63秒］</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr"/>
@@ -3218,7 +3218,7 @@
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>店内。棚に並ぶ商品を、お客様が手に取る　［52-63秒］</t>
+          <t>棚から商品を手に取る（寄り）。お客様の手だけでもよい　［52-63秒］</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -2354,7 +2354,7 @@
       <c r="E86" s="7" t="inlineStr"/>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>1979年の写真と同じ構図で、今の店舗へ。ショーウィンドウ越しに店内が見える。白黒からカラーに変わる　［6-20秒］</t>
+          <t>1979年の写真と同じ構図で、今の店舗へ。店先を外から撮る。白黒からカラーに変わる　［6-20秒］</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr"/>
@@ -3218,7 +3218,7 @@
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>棚から商品を手に取る（寄り）。お客様の手だけでもよい　［52-63秒］</t>
+          <t>ショーウィンドウ越しに店内を見せる。外から見た店の顔。（棚から商品を手に取る寄りも撮っておく）　［52-63秒］</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -2314,7 +2314,7 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>1979年の創業。ヒストリーページの一枚目。年号テロップ「1979　東京千駄ヶ谷にて創業」を重ねる（画面上部の英字はサイト側の見出し。実際は年号テロップだけを載せる）　［6-20秒］</t>
+          <t>コラボの実績から入る。年号テロップを次々に重ねる（1980 SHIPS ／ 1982 BEAMS ／ 1984 To Boot New York ／ 1990 UNITED ARROWS ／ 1991 Paul Smith ／ 2011 RALPH LAUREN）　［6-20秒］</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr"/>
@@ -2334,7 +2334,7 @@
       <c r="E85" s="7" t="inlineStr"/>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>1984 To Boot New York。年号テロップを続けて重ねる（1980 SHIPS ／ 1982 BEAMS ／ 1984 To Boot New York）　［6-20秒］</t>
+          <t>昔の外観。実績を並べたあと、はじまりの店先に戻る。テロップ「1979　東京千駄ヶ谷にて創業」（画面上部の英字はサイト側の見出し。実際は年号テロップだけを載せる）　［6-20秒］</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr"/>
@@ -2354,7 +2354,7 @@
       <c r="E86" s="7" t="inlineStr"/>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>1979年の写真と同じ構図で、今の店舗へ。店先を外から撮る。白黒からカラーに変わる　［6-20秒］</t>
+          <t>同じ構図のまま、今の外観へ。昔の店先からそのまま移り変わる。白黒からカラーに変わる　［6-20秒］</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ショットリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-1</t>
+          <t>⑧ S3-1</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>バストショット。窓を背にして、手前に植物を置いてボカす。名前は出さず「使っている人」として自己紹介　［8-18秒］</t>
+          <t>バストショット。窓を背にして、手前に植物を置いてボカす。名前は出さず「使っている人」として自己紹介。話した言葉をそのままテロップで出す　［11-19秒］</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr"/>
@@ -1040,13 +1040,13 @@
       <c r="C29" s="7" t="inlineStr"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-2</t>
+          <t>⑧ S4-1</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr"/>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>同じ画角。カメラは一度も動かさない　［8-18秒］</t>
+          <t>インタビューに戻る。同じ画角。カメラは一度も動かさない　［19-28秒］</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr"/>
@@ -1060,13 +1060,13 @@
       <c r="C30" s="7" t="inlineStr"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-3</t>
+          <t>⑧ S6-1</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr"/>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>話した言葉をそのままテロップで出す（この参考動画の出し方をそのまま真似る）　［8-18秒］</t>
+          <t>インタビューに戻る。表情のアップ。買ってから変わったことを一言で　［38-50秒］</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr"/>
@@ -1076,17 +1076,29 @@
       <c r="A31" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B31" s="7" t="inlineStr"/>
-      <c r="C31" s="7" t="inlineStr"/>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>空撮・外観</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>工房の上空と外観（⑤⑥共通・晴天の午前）</t>
+        </is>
+      </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-1</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr"/>
+          <t>⑤ S1-1</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>ドローンまたは高所／カメラ</t>
+        </is>
+      </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>外に出る。空を入れて気分を変える　［42-52秒］</t>
+          <t>バードアイショット。東京の空から降り、向島の街と工房を見つける　［0-6秒］</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr"/>
@@ -1100,13 +1112,13 @@
       <c r="C32" s="7" t="inlineStr"/>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-2</t>
+          <t>⑤ S1-2</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>引きの画に人が入る。買ってから変わったことを語る　［42-52秒］</t>
+          <t>高度を下げ、建物に寄る。ここで永尾社長の声が先に入りはじめる（Jカット）　［0-6秒］</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr"/>
@@ -1120,13 +1132,13 @@
       <c r="C33" s="7" t="inlineStr"/>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-3</t>
+          <t>⑥ S1-1</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>インタビューの画に戻る。表情のアップ　［42-52秒］</t>
+          <t>バードアイショット。上から降りて、向島の工房を見つける　［0-10秒］</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr"/>
@@ -1136,29 +1148,17 @@
       <c r="A34" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>空撮・外観</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>工房の上空と外観（⑤⑥共通・晴天の午前）</t>
-        </is>
-      </c>
+      <c r="B34" s="7" t="inlineStr"/>
+      <c r="C34" s="7" t="inlineStr"/>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>⑤ S1-1</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>ドローンまたは高所／カメラ</t>
-        </is>
-      </c>
+          <t>⑥ S1-2</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr"/>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>バードアイショット。東京の空から降り、向島の街と工房を見つける　［0-6秒］</t>
+          <t>高度を下げ、建物の全景へ。街の音　［0-10秒］</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr"/>
@@ -1168,17 +1168,29 @@
       <c r="A35" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B35" s="7" t="inlineStr"/>
-      <c r="C35" s="7" t="inlineStr"/>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>工房・全体</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>工房の全景と通路（⑥）</t>
+        </is>
+      </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>⑤ S1-2</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr"/>
+          <t>⑥ S2-1</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／広角</t>
+        </is>
+      </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>高度を下げ、建物に寄る。ここで永尾社長の声が先に入りはじめる（Jカット）　［0-6秒］</t>
+          <t>入口を抜けて中へ。工房の全景（引き）。規模が分かる画角　［10-25秒］</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr"/>
@@ -1192,13 +1204,13 @@
       <c r="C36" s="7" t="inlineStr"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>⑥ S1-1</t>
+          <t>⑥ S2-2</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr"/>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>バードアイショット。上から降りて、向島の工房を見つける　［0-10秒］</t>
+          <t>機械と人が同じ画面に入る。台数と人数が分かる　［10-25秒］</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr"/>
@@ -1212,13 +1224,13 @@
       <c r="C37" s="7" t="inlineStr"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>⑥ S1-2</t>
+          <t>⑥ S2-3</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr"/>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>高度を下げ、建物の全景へ。街の音　［0-10秒］</t>
+          <t>Bロール：職人の顔。手を止めずに作業している横顔（寄り）　［10-25秒］</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr"/>
@@ -1230,27 +1242,27 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>工房・全体</t>
+          <t>工房・材料</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>工房の全景と通路（⑥）</t>
+          <t>原反と金型・型紙（⑥）</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>⑥ S2-1</t>
+          <t>⑥ S3-1</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>カメラ／三脚／広角</t>
+          <t>カメラ／三脚</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>入口を抜けて中へ。工房の全景（引き）。規模が分かる画角　［10-25秒］</t>
+          <t>棚に革が色ごとに並ぶ。扱える革の種類と量がそのまま伝わる　［25-42秒］</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr"/>
@@ -1264,13 +1276,13 @@
       <c r="C39" s="7" t="inlineStr"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>⑥ S2-2</t>
+          <t>⑥ S3-2</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr"/>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>機械と人が同じ画面に入る。台数と人数が分かる　［10-25秒］</t>
+          <t>金型・型紙が品番ごとに並ぶ。手が一つを抜き出す　［25-42秒］</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr"/>
@@ -1284,13 +1296,13 @@
       <c r="C40" s="7" t="inlineStr"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>⑥ S2-3</t>
+          <t>⑥ S3-3</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr"/>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の顔。手を止めずに作業している横顔（寄り）　［10-25秒］</t>
+          <t>革の上に型紙を置き、取り都合を決める（寄り）　［25-42秒］</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr"/>
@@ -1302,27 +1314,27 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>工房・材料</t>
+          <t>工房・裁つ</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>原反と金型・型紙（⑥）</t>
+          <t>作業台・真俯瞰と横（②）</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>⑥ S3-1</t>
+          <t>② S1-1</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>カメラ／三脚</t>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>原反が積まれている。扱える革の量を示す　［25-42秒］</t>
+          <t>超マクロ。刃が革に入る瞬間。何を見ているか分からない距離。「スッ」と抜ける一音だけ。BGMは鳴らさない　［0-5秒］</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr"/>
@@ -1336,13 +1348,13 @@
       <c r="C42" s="7" t="inlineStr"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>⑥ S3-2</t>
+          <t>② S1-2</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr"/>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>金型・型紙が品番ごとに並ぶ。手が一つを抜き出す　［25-42秒］</t>
+          <t>刃が進み、革の繊維が開いていく（同じ画角のまま）　［0-5秒］</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr"/>
@@ -1356,13 +1368,13 @@
       <c r="C43" s="7" t="inlineStr"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>⑥ S3-3</t>
+          <t>② S1-3</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>革の上に型紙を置き、取り都合を決める（寄り）　［25-42秒］</t>
+          <t>切り終わり。断面がまだ生成りのまま残っている　［0-5秒］</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr"/>
@@ -1372,29 +1384,17 @@
       <c r="A44" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>工房・裁つ</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>作業台・真俯瞰と横（②）</t>
-        </is>
-      </c>
+      <c r="B44" s="7" t="inlineStr"/>
+      <c r="C44" s="7" t="inlineStr"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>② S1-1</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
-        </is>
-      </c>
+          <t>② S2-1</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr"/>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>超マクロ。刃が革に入る瞬間。何を見ているか分からない距離　［0-3秒］</t>
+          <t>真俯瞰。金属定規を当てて直線を一気に引く　［5-11秒］</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr"/>
@@ -1408,13 +1408,13 @@
       <c r="C45" s="7" t="inlineStr"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>② S1-2</t>
+          <t>② S2-2</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr"/>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>刃が進み、革の繊維が開いていく（同じ画角のまま）　［0-3秒］</t>
+          <t>角を回して切る（横）　［5-11秒］</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr"/>
@@ -1428,13 +1428,13 @@
       <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>② S1-3</t>
+          <t>② S2-3</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr"/>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>「スッ」と抜ける一音だけ。BGMは鳴らさない　［0-3秒］</t>
+          <t>ヘリを落とす。断面の角が丸くなる（超マクロ）　［5-11秒］</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr"/>
@@ -1445,16 +1445,24 @@
         <v>36</v>
       </c>
       <c r="B47" s="7" t="inlineStr"/>
-      <c r="C47" s="7" t="inlineStr"/>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>裁断機と革包丁（⑥）</t>
+        </is>
+      </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>② S2-1</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr"/>
+          <t>⑥ S4-1</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。金属定規を当てて直線を一気に引く　［3-11秒］</t>
+          <t>金型が置かれ、裁断機が下りる。テロップ「金型裁断 Die Cutting」　［42-62秒］</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr"/>
@@ -1468,13 +1476,13 @@
       <c r="C48" s="7" t="inlineStr"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>② S2-2</t>
+          <t>⑥ S4-2</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr"/>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>角を回して切る（横）　［3-11秒］</t>
+          <t>革包丁で細部を切る。テロップ「手裁断 Hand Cutting」　［42-62秒］</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr"/>
@@ -1488,13 +1496,13 @@
       <c r="C49" s="7" t="inlineStr"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>② S2-3</t>
+          <t>⑥ S4-3</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr"/>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>切り終わり。断面がまだ生成りのまま残っている　［3-11秒］</t>
+          <t>裁ち上がったパーツが並ぶ。量産も少量も同じ場所でできる　［42-62秒］</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr"/>
@@ -1504,17 +1512,29 @@
       <c r="A50" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="B50" s="7" t="inlineStr"/>
-      <c r="C50" s="7" t="inlineStr"/>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>工房・下仕事</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>作業台・目打ちと菱目打ち（②）</t>
+        </is>
+      </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
           <t>② S3-1</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr"/>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+        </is>
+      </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>菱目打ちを槌で打つ。同じ音が三回続く（横）　［11-17秒］</t>
+          <t>目打ちで縫う位置に印をつける　［11-17秒］</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr"/>
@@ -1534,7 +1554,7 @@
       <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>等間隔に並んだ穴だけが画面に残る　［11-17秒］</t>
+          <t>菱目打ちを槌で打つ。同じ音が三回続く（横）　［11-17秒］</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr"/>
@@ -1554,7 +1574,7 @@
       <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>目打ちの超マクロ。革の断面と穴が同じ画面に入る　［11-17秒］</t>
+          <t>等間隔に並んだ穴だけが画面に残る　［11-17秒］</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr"/>
@@ -1567,22 +1587,22 @@
       <c r="B53" s="7" t="inlineStr"/>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>裁断機と革包丁（⑥）</t>
+          <t>作業台・金具と刻印（②）</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>⑥ S4-1</t>
+          <t>② S4-1</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>カメラ／三脚</t>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>金型が置かれ、裁断機が下りる。テロップ「金型裁断 Die Cutting」　［42-62秒］</t>
+          <t>ボール盤で金具用の穴をあける　［17-22秒］</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr"/>
@@ -1596,13 +1616,13 @@
       <c r="C54" s="7" t="inlineStr"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>⑥ S4-2</t>
+          <t>② S4-2</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr"/>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>革包丁で細部を切る。テロップ「手裁断 Hand Cutting」　［42-62秒］</t>
+          <t>カシメを打つ。金属が革に沈む一音　［17-22秒］</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr"/>
@@ -1616,13 +1636,13 @@
       <c r="C55" s="7" t="inlineStr"/>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>⑥ S4-3</t>
+          <t>② S4-3</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>裁ち上がったパーツが並ぶ。量産も少量も同じ場所でできる　［42-62秒］</t>
+          <t>刻印を押す。斜めから光を当てて、窪みに影を作る　［17-22秒］</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr"/>
@@ -1632,11 +1652,7 @@
       <c r="A56" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>工房・下仕事</t>
-        </is>
-      </c>
+      <c r="B56" s="7" t="inlineStr"/>
       <c r="C56" s="9" t="inlineStr">
         <is>
           <t>漉き・目打ち（⑥）</t>
@@ -1784,7 +1800,7 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>② S4-1</t>
+          <t>② S5-1</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -1794,7 +1810,7 @@
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>針が革を抜ける（寄り）　［17-24秒］</t>
+          <t>針が革を抜ける（寄り）　［22-28秒］</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr"/>
@@ -1808,13 +1824,13 @@
       <c r="C63" s="7" t="inlineStr"/>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>② S4-2</t>
+          <t>② S5-2</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr"/>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>二本の糸が交差して締まる（超マクロ）　［17-24秒］</t>
+          <t>二本の糸が交差して締まる（超マクロ）　［22-28秒］</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr"/>
@@ -1828,13 +1844,13 @@
       <c r="C64" s="7" t="inlineStr"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>② S4-3</t>
+          <t>② S5-3</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr"/>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>縫い目に沿って仕上げる。手の動きだけを見せる　［17-24秒］</t>
+          <t>縫い目に沿って仕上げる。手の動きだけを見せる　［22-28秒］</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr"/>
@@ -1851,12 +1867,12 @@
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>作業台・超マクロ（②の核）</t>
+          <t>作業台・超マクロ（②）</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>② S5-1</t>
+          <t>② S6-1</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
@@ -1866,7 +1882,7 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>塗り始め。道具の先が断面に触れる（超マクロ）　［24-33秒］</t>
+          <t>塗り始め。道具の先が断面に触れる（超マクロ）　［28-34秒］</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr"/>
@@ -1880,13 +1896,13 @@
       <c r="C66" s="7" t="inlineStr"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>② S5-2</t>
+          <t>② S6-2</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr"/>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>コバ塗り ★核。塗った側と塗っていない側が同じ画面に入る。長回し・カットを割らない　［24-33秒］</t>
+          <t>この一本の見せ場。塗った側と塗っていない側が同じ画面に入る。長回し・カットを割らない　［28-34秒］</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr"/>
@@ -1900,13 +1916,13 @@
       <c r="C67" s="7" t="inlineStr"/>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>② S5-3</t>
+          <t>② S6-3</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr"/>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>塗り終わり。同じ画角のまま断面の色が変わりきっている　［24-33秒］</t>
+          <t>塗り終わり。同じ画角のまま断面の色が変わりきっている　［28-34秒］</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr"/>
@@ -1920,13 +1936,13 @@
       <c r="C68" s="7" t="inlineStr"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>② S6-1</t>
+          <t>② S7-1</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr"/>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>超マクロ。コバを磨く。摩擦音　［33-40秒］</t>
+          <t>ヘラで仕上げ剤を薄く伸ばす　［34-38秒］</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr"/>
@@ -1940,13 +1956,13 @@
       <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>② S6-2</t>
+          <t>② S7-2</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>使われている場所に置かれる → テロップ → ロゴ　［33-40秒］</t>
+          <t>超マクロ。コバを磨く。摩擦音　［34-38秒］</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr"/>
@@ -1960,13 +1976,13 @@
       <c r="C70" s="7" t="inlineStr"/>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>② S6-3</t>
+          <t>② S7-3</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr"/>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>―　［33-40秒］</t>
+          <t>磨き終わった断面に、光が一本だけ走る　［34-38秒］</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr"/>
@@ -2242,7 +2258,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>革が色ごとに並ぶ。扱える色数がそのまま伝わる　［20-29秒］</t>
+          <t>机を囲んで話し合う。資料を広げ、二人以上が同じものを見ている。企画はここから始まる　［20-29秒］</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr"/>
@@ -2262,7 +2278,7 @@
       <c r="E82" s="7" t="inlineStr"/>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>色を選ぶ（寄り）　［20-29秒］</t>
+          <t>革を並べて色を決める。扱える色数がそのまま伝わる　［20-29秒］</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr"/>
@@ -3228,29 +3244,25 @@
       <c r="A128" s="7" t="n">
         <v>117</v>
       </c>
-      <c r="B128" s="8" t="inlineStr">
-        <is>
-          <t>お客様・開封</t>
-        </is>
-      </c>
+      <c r="B128" s="7" t="inlineStr"/>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>買った日の再現（⑧）</t>
+          <t>商品と空間（⑧のつかみ）</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-1</t>
+          <t>⑧ S2-1</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>カメラ／三脚／照明1灯</t>
+          <t>カメラ／三脚／マクロレンズ／照明1灯</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>商品の真俯瞰。声は続いたまま　［30-42秒］</t>
+          <t>商品の寄り。できあがった瞬間　［5-11秒］</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr"/>
@@ -3264,13 +3276,13 @@
       <c r="C129" s="7" t="inlineStr"/>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-2</t>
+          <t>⑧ S2-2</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr"/>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>売り場・棚の引き　［30-42秒］</t>
+          <t>商品の真俯瞰。並べて撮る　［5-11秒］</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr"/>
@@ -3284,13 +3296,13 @@
       <c r="C130" s="7" t="inlineStr"/>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-3</t>
+          <t>⑧ S2-3</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr"/>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>ディテールの寄り。良かった点を語っている場所に重ねる　［30-42秒］</t>
+          <t>空間。窓際と光。ここまで人の顔は出さない　［5-11秒］</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr"/>
@@ -3300,29 +3312,17 @@
       <c r="A131" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="B131" s="8" t="inlineStr">
-        <is>
-          <t>お客様・街</t>
-        </is>
-      </c>
-      <c r="C131" s="9" t="inlineStr">
-        <is>
-          <t>使用シーン（⑧）</t>
-        </is>
-      </c>
+      <c r="B131" s="7" t="inlineStr"/>
+      <c r="C131" s="7" t="inlineStr"/>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-1</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S3-2</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr"/>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>ここから画はBロールに変わるが、声はそのまま流し続ける　［18-30秒］</t>
+          <t>ここから画はBロールに変わるが、声はそのまま流し続ける（引き）　［11-19秒］</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr"/>
@@ -3336,13 +3336,13 @@
       <c r="C132" s="7" t="inlineStr"/>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-2</t>
+          <t>⑧ S3-3</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr"/>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>同じ場所を別の角度で。声に合わせて切り替える　［18-30秒］</t>
+          <t>商品の寄り。話している内容に合わせて切り替える　［11-19秒］</t>
         </is>
       </c>
       <c r="G132" s="11" t="inlineStr"/>
@@ -3356,13 +3356,13 @@
       <c r="C133" s="7" t="inlineStr"/>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-3</t>
+          <t>⑧ S4-2</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr"/>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>落ち着いた場所での一枚。間を作る　［18-30秒］</t>
+          <t>声の上にBロール。空間の引き　［19-28秒］</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr"/>
@@ -3373,24 +3373,16 @@
         <v>123</v>
       </c>
       <c r="B134" s="7" t="inlineStr"/>
-      <c r="C134" s="9" t="inlineStr">
-        <is>
-          <t>受け取りと使用（⑤⑧共通）</t>
-        </is>
-      </c>
+      <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-1</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S4-3</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr"/>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>会計。店員から手渡される瞬間　［63-70秒］</t>
+          <t>窓辺の一枚。間を作る　［19-28秒］</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr"/>
@@ -3401,16 +3393,24 @@
         <v>124</v>
       </c>
       <c r="B135" s="7" t="inlineStr"/>
-      <c r="C135" s="7" t="inlineStr"/>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>外観と作っているところ（⑧のつかみ）</t>
+        </is>
+      </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-2</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr"/>
+          <t>⑧ S1-1</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>受け取った人の笑顔　［63-70秒］</t>
+          <t>外観のロー。空を入れて見上げる。ロゴを重ねる　［0-5秒］</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr"/>
@@ -3424,13 +3424,13 @@
       <c r="C136" s="7" t="inlineStr"/>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-3</t>
+          <t>⑧ S1-2</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr"/>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>街で実際に使われている手元。ここで永尾社長の声がもう一度入りはじめる（Jカット）　［63-70秒］</t>
+          <t>外観の全景（引き）。入口に人が立つ　［0-5秒］</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr"/>
@@ -3444,13 +3444,13 @@
       <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-1</t>
+          <t>⑧ S1-3</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr"/>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>外観のロー。空を入れて見上げる。まだ人は出さない　［0-8秒］</t>
+          <t>作っているところ。手元だけ（寄り）　［0-5秒］</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr"/>
@@ -3461,16 +3461,24 @@
         <v>127</v>
       </c>
       <c r="B138" s="7" t="inlineStr"/>
-      <c r="C138" s="7" t="inlineStr"/>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>見送り（⑧の締め）</t>
+        </is>
+      </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-2</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr"/>
+          <t>⑧ S7-1</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>店舗／工房の全景（引き）。人が出入りする　［0-8秒］</t>
+          <t>店の前。スタッフが出てくる（引き）　［50-60秒］</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr"/>
@@ -3484,13 +3492,13 @@
       <c r="C139" s="7" t="inlineStr"/>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-3</t>
+          <t>⑧ S7-2</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr"/>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>窓辺と光。商品が置いてある（寄り）　［0-8秒］</t>
+          <t>手を振って見送る。カメラは動かさない　［50-60秒］</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr"/>
@@ -3501,24 +3509,16 @@
         <v>129</v>
       </c>
       <c r="B140" s="7" t="inlineStr"/>
-      <c r="C140" s="9" t="inlineStr">
-        <is>
-          <t>締め（⑤）</t>
-        </is>
-      </c>
+      <c r="C140" s="7" t="inlineStr"/>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-2</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S7-3</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr"/>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>声が終わり、音が引く。ロゴだけ。テロップは出さない　［70-75秒］</t>
+          <t>同じ引きの画面の中央に、ロゴが重なる　［50-60秒］</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr"/>
@@ -3528,17 +3528,29 @@
       <c r="A141" s="7" t="n">
         <v>130</v>
       </c>
-      <c r="B141" s="7" t="inlineStr"/>
-      <c r="C141" s="7" t="inlineStr"/>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>お客様・街</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>使っている場面（⑧）</t>
+        </is>
+      </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-3</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr"/>
+          <t>⑧ S5-1</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>―　［70-75秒］</t>
+          <t>別の場所へ移る（引き）　［28-38秒］</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr"/>
@@ -3549,24 +3561,16 @@
         <v>131</v>
       </c>
       <c r="B142" s="7" t="inlineStr"/>
-      <c r="C142" s="9" t="inlineStr">
-        <is>
-          <t>締め（⑧）</t>
-        </is>
-      </c>
+      <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-1</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S5-2</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr"/>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>最後の一言。台本にない言葉を拾う　［52-60秒］</t>
+          <t>落ち着いた場所での一枚　［28-38秒］</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr"/>
@@ -3580,13 +3584,13 @@
       <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-2</t>
+          <t>⑧ S5-3</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>テロップ　［52-60秒］</t>
+          <t>外に出る。空を入れて気分を変える　［28-38秒］</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr"/>
@@ -3600,13 +3604,13 @@
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-3</t>
+          <t>⑧ S6-2</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>ロゴ　［52-60秒］</t>
+          <t>外の引きに人が入る。声はそのまま続く　［38-50秒］</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr"/>
@@ -3616,29 +3620,17 @@
       <c r="A145" s="7" t="n">
         <v>134</v>
       </c>
-      <c r="B145" s="8" t="inlineStr">
-        <is>
-          <t>屋外・街</t>
-        </is>
-      </c>
-      <c r="C145" s="9" t="inlineStr">
-        <is>
-          <t>自宅の玄関まわり（①）</t>
-        </is>
-      </c>
+      <c r="B145" s="7" t="inlineStr"/>
+      <c r="C145" s="7" t="inlineStr"/>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>① S1-1</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>⑧ S6-3</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr"/>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>玄関の中。全身が入る引き。出かける支度をしている　［0-5秒］</t>
+          <t>窓辺に戻る。静かな一枚。台本にない一言を拾う　［38-50秒］</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr"/>
@@ -3649,16 +3641,24 @@
         <v>135</v>
       </c>
       <c r="B146" s="7" t="inlineStr"/>
-      <c r="C146" s="7" t="inlineStr"/>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>使われている場所（②の締め）</t>
+        </is>
+      </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>① S1-2</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr"/>
+          <t>② S8-1</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>ドアの前に立つ（引き）。同じ画角に固定する　［0-5秒］</t>
+          <t>作業机ではなく、使われている場所に置く → テロップ → ロゴ　［38-40秒］</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr"/>
@@ -3672,13 +3672,13 @@
       <c r="C147" s="7" t="inlineStr"/>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>① S1-3</t>
+          <t>② S8-2</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr"/>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>ドアが開く。開いた瞬間、服も鞄も変わっている。同じ画角のまま。この一本の決まりごとを、いちばん最初に見せてしまう　［0-5秒］</t>
+          <t>―　［38-40秒］</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr"/>
@@ -3692,13 +3692,13 @@
       <c r="C148" s="7" t="inlineStr"/>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>① S2-1</t>
+          <t>② S8-3</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr"/>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>通勤路を歩く（引き）。この画角を最後まで使い回す（基準カット）　［5-9秒］</t>
+          <t>―　［38-40秒］</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr"/>
@@ -3709,16 +3709,24 @@
         <v>138</v>
       </c>
       <c r="B149" s="7" t="inlineStr"/>
-      <c r="C149" s="7" t="inlineStr"/>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>受け取りと使用（⑤⑧共通）</t>
+        </is>
+      </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>① S2-2</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr"/>
+          <t>⑤ S7-1</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>同じ画角。歩いてくる全身（一色目）　［5-9秒］</t>
+          <t>会計。店員から手渡される瞬間　［63-70秒］</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr"/>
@@ -3732,13 +3740,13 @@
       <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>① S2-3</t>
+          <t>⑤ S7-2</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>歩き出す全身（引き・ロー）。鞄が体の横で揺れる　［5-9秒］</t>
+          <t>受け取った人の笑顔　［63-70秒］</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr"/>
@@ -3749,24 +3757,16 @@
         <v>140</v>
       </c>
       <c r="B151" s="7" t="inlineStr"/>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>街歩き・夕方の斜光（④）</t>
-        </is>
-      </c>
+      <c r="C151" s="7" t="inlineStr"/>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>④ S1-1</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>⑤ S7-3</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
+          <t>街で実際に使われている手元。ここで永尾社長の声がもう一度入りはじめる（Jカット）　［63-70秒］</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr"/>
@@ -3777,16 +3777,24 @@
         <v>141</v>
       </c>
       <c r="B152" s="7" t="inlineStr"/>
-      <c r="C152" s="7" t="inlineStr"/>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>締め（⑤）</t>
+        </is>
+      </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>④ S1-2</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="inlineStr"/>
+          <t>⑤ S8-2</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
+          <t>声が終わり、音が引く。ロゴだけ。テロップは出さない　［70-75秒］</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr"/>
@@ -3800,13 +3808,13 @@
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>④ S1-3</t>
+          <t>⑤ S8-3</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
+          <t>―　［70-75秒］</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr"/>
@@ -3816,17 +3824,29 @@
       <c r="A154" s="7" t="n">
         <v>143</v>
       </c>
-      <c r="B154" s="7" t="inlineStr"/>
-      <c r="C154" s="7" t="inlineStr"/>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>屋外・街</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>自宅の玄関まわり（①）</t>
+        </is>
+      </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>④ S2-1</t>
-        </is>
-      </c>
-      <c r="E154" s="7" t="inlineStr"/>
+          <t>① S1-1</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
+          <t>玄関の中。全身が入る引き。出かける支度をしている　［0-5秒］</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr"/>
@@ -3840,13 +3860,13 @@
       <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>④ S2-2</t>
+          <t>① S1-2</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr"/>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
+          <t>ドアの前に立つ（引き）　［0-5秒］</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr"/>
@@ -3860,13 +3880,13 @@
       <c r="C156" s="7" t="inlineStr"/>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>④ S2-3</t>
+          <t>① S1-3</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr"/>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
+          <t>ドアが開く。開いた瞬間、服も鞄も変わっている。表情も変わっている。「服が変われば、合う色も気分も変わる」という決まりごとを、ここで先に見せておく。あとのトランジションが全部これで読める　［0-5秒］</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr"/>
@@ -3880,13 +3900,13 @@
       <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>④ S3-1</t>
+          <t>① S2-1</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr"/>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
+          <t>通勤路を歩く（引き）。この場所をこのあとも使い回す　［5-9秒］</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr"/>
@@ -3900,13 +3920,13 @@
       <c r="C158" s="7" t="inlineStr"/>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>④ S3-2</t>
+          <t>① S2-2</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr"/>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
+          <t>歩いてくる全身（一色目）。すまし顔で　［5-9秒］</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr"/>
@@ -3920,13 +3940,13 @@
       <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>④ S3-3</t>
+          <t>① S2-3</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
+          <t>歩き出す全身（引き・ロー）。鞄が体の横で揺れる　［5-9秒］</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr"/>
@@ -3937,16 +3957,24 @@
         <v>149</v>
       </c>
       <c r="B160" s="7" t="inlineStr"/>
-      <c r="C160" s="7" t="inlineStr"/>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>街歩き・夕方の斜光（④）</t>
+        </is>
+      </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>④ S4-1</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr"/>
+          <t>④ S1-1</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
+          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
         </is>
       </c>
       <c r="G160" s="11" t="inlineStr"/>
@@ -3960,13 +3988,13 @@
       <c r="C161" s="7" t="inlineStr"/>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>④ S4-2</t>
+          <t>④ S1-2</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
+          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr"/>
@@ -3980,13 +4008,13 @@
       <c r="C162" s="7" t="inlineStr"/>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>④ S4-3</t>
+          <t>④ S1-3</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
+          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
         </is>
       </c>
       <c r="G162" s="11" t="inlineStr"/>
@@ -4000,13 +4028,13 @@
       <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>④ S5-1</t>
+          <t>④ S2-1</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>手すりの前で立ち止まる　［24-30秒］</t>
+          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr"/>
@@ -4020,13 +4048,13 @@
       <c r="C164" s="7" t="inlineStr"/>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>④ S5-2</t>
+          <t>④ S2-2</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr"/>
       <c r="F164" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。保存袋・小物まで並べる　［24-30秒］</t>
+          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr"/>
@@ -4040,13 +4068,13 @@
       <c r="C165" s="7" t="inlineStr"/>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>④ S5-3</t>
+          <t>④ S2-3</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr"/>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
+          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr"/>
@@ -4057,24 +4085,16 @@
         <v>155</v>
       </c>
       <c r="B166" s="7" t="inlineStr"/>
-      <c r="C166" s="9" t="inlineStr">
-        <is>
-          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
-        </is>
-      </c>
+      <c r="C166" s="7" t="inlineStr"/>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>① S3-1</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>④ S3-1</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr"/>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま服が変わっている。小物の色も変わる（二色目）　［9-14秒］</t>
+          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr"/>
@@ -4088,13 +4108,13 @@
       <c r="C167" s="7" t="inlineStr"/>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>① S3-2</t>
+          <t>④ S3-2</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr"/>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>同じ道。三色目　［9-14秒］</t>
+          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr"/>
@@ -4108,13 +4128,13 @@
       <c r="C168" s="7" t="inlineStr"/>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>① S3-3</t>
+          <t>④ S3-3</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>立ち止まって振り返る。手元の色が見える　［9-14秒］</t>
+          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr"/>
@@ -4128,13 +4148,13 @@
       <c r="C169" s="7" t="inlineStr"/>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>① S4-1</t>
+          <t>④ S4-1</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr"/>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>手前を木の幹が横切る（前ボケ＝トランジション）　［14-18秒］</t>
+          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr"/>
@@ -4148,13 +4168,13 @@
       <c r="C170" s="7" t="inlineStr"/>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>① S4-2</t>
+          <t>④ S4-2</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>抜けたら別の服・別の色になっている（四色目）　［14-18秒］</t>
+          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr"/>
@@ -4168,13 +4188,13 @@
       <c r="C171" s="7" t="inlineStr"/>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>① S4-3</t>
+          <t>④ S4-3</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>場所が変わる。駅の構内（引き）　［14-18秒］</t>
+          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr"/>
@@ -4188,13 +4208,13 @@
       <c r="C172" s="7" t="inlineStr"/>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>① S5-1</t>
+          <t>④ S5-1</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="10" t="inlineStr">
         <is>
-          <t>乗り場（引き）。同じ人・違う色　［18-22秒］</t>
+          <t>手すりの前で立ち止まる　［24-30秒］</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr"/>
@@ -4208,13 +4228,13 @@
       <c r="C173" s="7" t="inlineStr"/>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>① S5-2</t>
+          <t>④ S5-2</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr"/>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>通路を歩く。横移動で追う　［18-22秒］</t>
+          <t>真俯瞰。保存袋・小物まで並べる　［24-30秒］</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr"/>
@@ -4228,13 +4248,13 @@
       <c r="C174" s="7" t="inlineStr"/>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>① S5-3</t>
+          <t>④ S5-3</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr"/>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>会社の入口に着く　［18-22秒］</t>
+          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr"/>
@@ -4245,16 +4265,24 @@
         <v>164</v>
       </c>
       <c r="B175" s="7" t="inlineStr"/>
-      <c r="C175" s="7" t="inlineStr"/>
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
+        </is>
+      </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>① S6-1</t>
-        </is>
-      </c>
-      <c r="E175" s="7" t="inlineStr"/>
+          <t>① S3-1</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F175" s="10" t="inlineStr">
         <is>
-          <t>ロビーに入る　［22-27秒］</t>
+          <t>服が変わり、小物の色も変わる（二色目）。表情も一緒に変える　［9-14秒］</t>
         </is>
       </c>
       <c r="G175" s="11" t="inlineStr"/>
@@ -4268,13 +4296,13 @@
       <c r="C176" s="7" t="inlineStr"/>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>① S6-2</t>
+          <t>① S3-2</t>
         </is>
       </c>
       <c r="E176" s="7" t="inlineStr"/>
       <c r="F176" s="10" t="inlineStr">
         <is>
-          <t>ロビーを歩く（引き）　［22-27秒］</t>
+          <t>同じ道。三色目。ここは笑っている表情で　［9-14秒］</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr"/>
@@ -4288,13 +4316,13 @@
       <c r="C177" s="7" t="inlineStr"/>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>① S6-3</t>
+          <t>① S3-3</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr"/>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>立ち止まる。ここが到着点　［22-27秒］</t>
+          <t>立ち止まって振り返る。服装ごとに気分が違うことを見せる　［9-14秒］</t>
         </is>
       </c>
       <c r="G177" s="11" t="inlineStr"/>
@@ -4304,29 +4332,17 @@
       <c r="A178" s="7" t="n">
         <v>167</v>
       </c>
-      <c r="B178" s="8" t="inlineStr">
-        <is>
-          <t>締めカード</t>
-        </is>
-      </c>
-      <c r="C178" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。文字を組んで作る</t>
-        </is>
-      </c>
+      <c r="B178" s="7" t="inlineStr"/>
+      <c r="C178" s="7" t="inlineStr"/>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-1</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
+          <t>① S4-1</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr"/>
       <c r="F178" s="10" t="inlineStr">
         <is>
-          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
+          <t>手前を木の幹が横切る（前ボケ＝トランジション）　［14-18秒］</t>
         </is>
       </c>
       <c r="G178" s="11" t="inlineStr"/>
@@ -4340,13 +4356,13 @@
       <c r="C179" s="7" t="inlineStr"/>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-2</t>
+          <t>① S4-2</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr"/>
       <c r="F179" s="10" t="inlineStr">
         <is>
-          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
+          <t>抜けたら別の服・別の色になっている（四色目）　［14-18秒］</t>
         </is>
       </c>
       <c r="G179" s="11" t="inlineStr"/>
@@ -4360,20 +4376,280 @@
       <c r="C180" s="7" t="inlineStr"/>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-3</t>
+          <t>① S4-3</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr"/>
       <c r="F180" s="10" t="inlineStr">
         <is>
-          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
+          <t>場所が変わる。駅の構内（引き）　［14-18秒］</t>
         </is>
       </c>
       <c r="G180" s="11" t="inlineStr"/>
       <c r="H180" s="11" t="inlineStr"/>
     </row>
+    <row r="181" ht="32" customHeight="1">
+      <c r="A181" s="7" t="n">
+        <v>170</v>
+      </c>
+      <c r="B181" s="7" t="inlineStr"/>
+      <c r="C181" s="7" t="inlineStr"/>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>① S5-1</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr"/>
+      <c r="F181" s="10" t="inlineStr">
+        <is>
+          <t>乗り場（引き）。同じ人・違う色　［18-22秒］</t>
+        </is>
+      </c>
+      <c r="G181" s="11" t="inlineStr"/>
+      <c r="H181" s="11" t="inlineStr"/>
+    </row>
+    <row r="182" ht="32" customHeight="1">
+      <c r="A182" s="7" t="n">
+        <v>171</v>
+      </c>
+      <c r="B182" s="7" t="inlineStr"/>
+      <c r="C182" s="7" t="inlineStr"/>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>① S5-2</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr"/>
+      <c r="F182" s="10" t="inlineStr">
+        <is>
+          <t>通路を歩く。横移動で追う　［18-22秒］</t>
+        </is>
+      </c>
+      <c r="G182" s="11" t="inlineStr"/>
+      <c r="H182" s="11" t="inlineStr"/>
+    </row>
+    <row r="183" ht="32" customHeight="1">
+      <c r="A183" s="7" t="n">
+        <v>172</v>
+      </c>
+      <c r="B183" s="7" t="inlineStr"/>
+      <c r="C183" s="7" t="inlineStr"/>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>① S5-3</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr"/>
+      <c r="F183" s="10" t="inlineStr">
+        <is>
+          <t>会社の入口に着く　［18-22秒］</t>
+        </is>
+      </c>
+      <c r="G183" s="11" t="inlineStr"/>
+      <c r="H183" s="11" t="inlineStr"/>
+    </row>
+    <row r="184" ht="32" customHeight="1">
+      <c r="A184" s="7" t="n">
+        <v>173</v>
+      </c>
+      <c r="B184" s="7" t="inlineStr"/>
+      <c r="C184" s="7" t="inlineStr"/>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>① S6-1</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr"/>
+      <c r="F184" s="10" t="inlineStr">
+        <is>
+          <t>ロビーに入る　［22-27秒］</t>
+        </is>
+      </c>
+      <c r="G184" s="11" t="inlineStr"/>
+      <c r="H184" s="11" t="inlineStr"/>
+    </row>
+    <row r="185" ht="32" customHeight="1">
+      <c r="A185" s="7" t="n">
+        <v>174</v>
+      </c>
+      <c r="B185" s="7" t="inlineStr"/>
+      <c r="C185" s="7" t="inlineStr"/>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>① S6-2</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr"/>
+      <c r="F185" s="10" t="inlineStr">
+        <is>
+          <t>ロビーを歩く（引き）　［22-27秒］</t>
+        </is>
+      </c>
+      <c r="G185" s="11" t="inlineStr"/>
+      <c r="H185" s="11" t="inlineStr"/>
+    </row>
+    <row r="186" ht="32" customHeight="1">
+      <c r="A186" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="B186" s="7" t="inlineStr"/>
+      <c r="C186" s="7" t="inlineStr"/>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>① S6-3</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr"/>
+      <c r="F186" s="10" t="inlineStr">
+        <is>
+          <t>立ち止まる。ここが到着点　［22-27秒］</t>
+        </is>
+      </c>
+      <c r="G186" s="11" t="inlineStr"/>
+      <c r="H186" s="11" t="inlineStr"/>
+    </row>
+    <row r="187" ht="32" customHeight="1">
+      <c r="A187" s="7" t="n">
+        <v>176</v>
+      </c>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>締めカード</t>
+        </is>
+      </c>
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。文字を組んで作る</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-1</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
+      <c r="F187" s="10" t="inlineStr">
+        <is>
+          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G187" s="11" t="inlineStr"/>
+      <c r="H187" s="11" t="inlineStr"/>
+    </row>
+    <row r="188" ht="32" customHeight="1">
+      <c r="A188" s="7" t="n">
+        <v>177</v>
+      </c>
+      <c r="B188" s="7" t="inlineStr"/>
+      <c r="C188" s="7" t="inlineStr"/>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-2</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr"/>
+      <c r="F188" s="10" t="inlineStr">
+        <is>
+          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G188" s="11" t="inlineStr"/>
+      <c r="H188" s="11" t="inlineStr"/>
+    </row>
+    <row r="189" ht="32" customHeight="1">
+      <c r="A189" s="7" t="n">
+        <v>178</v>
+      </c>
+      <c r="B189" s="7" t="inlineStr"/>
+      <c r="C189" s="7" t="inlineStr"/>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>⑥ S9-3</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr"/>
+      <c r="F189" s="10" t="inlineStr">
+        <is>
+          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
+        </is>
+      </c>
+      <c r="G189" s="11" t="inlineStr"/>
+      <c r="H189" s="11" t="inlineStr"/>
+    </row>
+    <row r="190" ht="32" customHeight="1">
+      <c r="A190" s="7" t="n">
+        <v>179</v>
+      </c>
+      <c r="B190" s="7" t="inlineStr"/>
+      <c r="C190" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。白に抜いてロゴだけ</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>⑧ S8-1</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
+      <c r="F190" s="10" t="inlineStr">
+        <is>
+          <t>映像が白に抜けて、ロゴだけが残る。ここで音も切る　［60秒］</t>
+        </is>
+      </c>
+      <c r="G190" s="11" t="inlineStr"/>
+      <c r="H190" s="11" t="inlineStr"/>
+    </row>
+    <row r="191" ht="32" customHeight="1">
+      <c r="A191" s="7" t="n">
+        <v>180</v>
+      </c>
+      <c r="B191" s="7" t="inlineStr"/>
+      <c r="C191" s="7" t="inlineStr"/>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>⑧ S8-2</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr"/>
+      <c r="F191" s="10" t="inlineStr">
+        <is>
+          <t>―　［60秒］</t>
+        </is>
+      </c>
+      <c r="G191" s="11" t="inlineStr"/>
+      <c r="H191" s="11" t="inlineStr"/>
+    </row>
+    <row r="192" ht="32" customHeight="1">
+      <c r="A192" s="7" t="n">
+        <v>181</v>
+      </c>
+      <c r="B192" s="7" t="inlineStr"/>
+      <c r="C192" s="7" t="inlineStr"/>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>⑧ S8-3</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr"/>
+      <c r="F192" s="10" t="inlineStr">
+        <is>
+          <t>―　［60秒］</t>
+        </is>
+      </c>
+      <c r="G192" s="11" t="inlineStr"/>
+      <c r="H192" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A11:H180"/>
+  <autoFilter ref="A11:H192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -2462,7 +2462,7 @@
       <c r="E90" s="7" t="inlineStr"/>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>道具と染料が並ぶ。手がその前に入る　［4-8秒］</t>
+          <t>作業台に革を置く。奥に染料と道具が並ぶ　［4-8秒］</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
       <c r="E91" s="7" t="inlineStr"/>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>革を持ち上げる。腕時計・指輪は外す　［4-8秒］</t>
+          <t>二枚を合わせて位置を決める。腕時計・指輪は外す　［4-8秒］</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr"/>
@@ -2502,7 +2502,7 @@
       <c r="E92" s="7" t="inlineStr"/>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>暗がりで革を手に取る。ここから作りはじめる　［4-8秒］</t>
+          <t>合わせた革を押さえる。ここから形になっていく　［4-8秒］</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -2258,7 +2258,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>机を囲んで話し合う。資料を広げ、二人以上が同じものを見ている。企画はここから始まる　［20-29秒］</t>
+          <t>色見本を見ながら打ち合わせる。二人で同じものを覗き込む（俯瞰気味）。企画はここから始まる　［20-29秒］</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr"/>
@@ -2298,7 +2298,7 @@
       <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>工房に革が吊るされている（引き）　［20-29秒］</t>
+          <t>机いっぱいに色見本と資料が広がる。手が動いて話している（引き）　［20-29秒］</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -2014,7 +2014,7 @@
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>原反が積まれている（引き）　［38-52秒］</t>
+          <t>大型の機械が動いている（引き）。設備の規模がそのまま伝わる　［38-52秒］</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -3162,7 +3162,7 @@
       <c r="E124" s="7" t="inlineStr"/>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>テロップ「急がば、定位置。」　［21-25秒］</t>
+          <t>テロップ「支度も、仕事も、スマートに。」　［21-25秒］</t>
         </is>
       </c>
       <c r="G124" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -3726,7 +3726,7 @@
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>会計。店員から手渡される瞬間　［63-70秒］</t>
+          <t>会計。カウンターで店員が応対する。二人が同じ画面に入る　［63-70秒］</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr"/>
@@ -3746,7 +3746,7 @@
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>受け取った人の笑顔　［63-70秒］</t>
+          <t>手渡される瞬間と、受け取った人の笑顔。渡す側と受け取る側を一つの画に入れる　［63-70秒］</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>街で実際に使われている手元。ここで永尾社長の声がもう一度入りはじめる（Jカット）　［63-70秒］</t>
+          <t>実際に使われている手元。ノートPCを入れる。ここで永尾社長の声がもう一度入りはじめる（Jカット）　［63-70秒］</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -2138,7 +2138,7 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>不織布で包み、角を折る（真俯瞰）。紙の音　［122-133秒］</t>
+          <t>白手袋で包む。手元の寄り。不織布の角を折る。紙の音　［122-133秒］</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
       <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>箱に納め、テープで閉じる → 出荷を待つ箱が積まれている。テロップ「梱包 Packing」　［122-133秒］</t>
+          <t>箱に納め、テープで閉じる。梱包場の引き。奥にも人が写る。テロップ「梱包 Packing」　［122-133秒］</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ショットリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
       <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>漉き・仕上げの仕事について一言。顔出しが難しければ手元だけのバージョンも撮る</t>
+          <t>店舗での接客と、店に並ぶまでの話を一言。顔出しが難しければ手元だけのバージョンも撮る</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
       <c r="B56" s="7" t="inlineStr"/>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>漉き・目打ち（⑥）</t>
+          <t>折り目つけ・貼り合わせ・コバ塗り（⑥）</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>革を漉いて厚みを揃える（寄り）。テロップ「漉き Skiving」　［62-82秒］</t>
+          <t>へらで折り目をつけ、縁を折り返す（寄り）。テロップ「折り目つけ Creasing」　［62-82秒］</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
       <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>目打ち・接着。縫う前の下ごしらえ（マクロ）　［62-82秒］</t>
+          <t>革の裏にスプレーを吹き、貼り合わせる。テロップ「貼り合わせ Bonding」　［62-82秒］</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr"/>
@@ -1710,7 +1710,7 @@
       <c r="E58" s="7" t="inlineStr"/>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の顔。手元から顔へパンし、目線だけを見せる　［62-82秒］</t>
+          <t>断面に塗料をのせる（超マクロ）。塗った側と塗っていない側が同じ画面に入る。テロップ「コバ塗り Edge Painting」　［62-82秒］</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr"/>
@@ -1720,29 +1720,17 @@
       <c r="A59" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>工房・縫う</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>ミシンと手縫い（⑥）</t>
-        </is>
-      </c>
+      <c r="B59" s="7" t="inlineStr"/>
+      <c r="C59" s="7" t="inlineStr"/>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>⑥ S6-1</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑥ S5-4</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr"/>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>ミシンで縫う（横）。テロップ「機械縫製 Machine Stitching」　［82-102秒］</t>
+          <t>Bロール：職人の目だけの超マクロ。手元を見ている目に寄る。テロップは出さない　［62-82秒］</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr"/>
@@ -1752,17 +1740,29 @@
       <c r="A60" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B60" s="7" t="inlineStr"/>
-      <c r="C60" s="7" t="inlineStr"/>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>工房・縫う</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>ミシンと手縫い（⑥）</t>
+        </is>
+      </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>⑥ S6-2</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr"/>
+          <t>⑥ S6-1</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>手縫い。二本の針が交差する（マクロ）。テロップ「手縫い Hand Stitching」　［82-102秒］</t>
+          <t>縫う部品を手に取り、ミシンへ向かう。縫い目と糸端が見える（寄り・背景ボケ）　［82-102秒］</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr"/>
@@ -1776,13 +1776,13 @@
       <c r="C61" s="7" t="inlineStr"/>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>⑥ S6-3</t>
+          <t>⑥ S6-2</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr"/>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>目止め → コバ磨き（超マクロ）。ここが全工程の四割　［82-102秒］</t>
+          <t>ミシンの針が革に落ちる（超マクロ）。押さえ金と革だけ。テロップ「機械縫製 Machine Stitching」　［82-102秒］</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr"/>
@@ -1793,24 +1793,16 @@
         <v>51</v>
       </c>
       <c r="B62" s="7" t="inlineStr"/>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>作業台・真俯瞰と横（②）</t>
-        </is>
-      </c>
+      <c r="C62" s="7" t="inlineStr"/>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>② S5-1</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
-        </is>
-      </c>
+          <t>⑥ S6-3</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr"/>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>針が革を抜ける（寄り）　［22-28秒］</t>
+          <t>両手が生地を送り、縫い進める（引き寄り）。手の動きと機械の音が同時に入る　［82-102秒］</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr"/>
@@ -1821,16 +1813,24 @@
         <v>52</v>
       </c>
       <c r="B63" s="7" t="inlineStr"/>
-      <c r="C63" s="7" t="inlineStr"/>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>作業台・真俯瞰と横（②）</t>
+        </is>
+      </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>② S5-2</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr"/>
+          <t>② S5-1</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+        </is>
+      </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>二本の糸が交差して締まる（超マクロ）　［22-28秒］</t>
+          <t>針が革を抜ける（寄り）　［22-28秒］</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr"/>
@@ -1844,13 +1844,13 @@
       <c r="C64" s="7" t="inlineStr"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>② S5-3</t>
+          <t>② S5-2</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr"/>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>縫い目に沿って仕上げる。手の動きだけを見せる　［22-28秒］</t>
+          <t>二本の糸が交差して締まる（超マクロ）　［22-28秒］</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr"/>
@@ -1860,29 +1860,17 @@
       <c r="A65" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>工房・コバ</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>作業台・超マクロ（②）</t>
-        </is>
-      </c>
+      <c r="B65" s="7" t="inlineStr"/>
+      <c r="C65" s="7" t="inlineStr"/>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>② S6-1</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
-        </is>
-      </c>
+          <t>② S5-3</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr"/>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>塗り始め。道具の先が断面に触れる（超マクロ）　［28-34秒］</t>
+          <t>縫い目に沿って仕上げる。手の動きだけを見せる　［22-28秒］</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr"/>
@@ -1892,17 +1880,29 @@
       <c r="A66" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="B66" s="7" t="inlineStr"/>
-      <c r="C66" s="7" t="inlineStr"/>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>工房・コバ</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>作業台・超マクロ（②）</t>
+        </is>
+      </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>② S6-2</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr"/>
+          <t>② S6-1</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／スマホ（音の別録り）</t>
+        </is>
+      </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>この一本の見せ場。塗った側と塗っていない側が同じ画面に入る。長回し・カットを割らない　［28-34秒］</t>
+          <t>塗り始め。道具の先が断面に触れる（超マクロ）　［28-34秒］</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr"/>
@@ -1916,13 +1916,13 @@
       <c r="C67" s="7" t="inlineStr"/>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>② S6-3</t>
+          <t>② S6-2</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr"/>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>塗り終わり。同じ画角のまま断面の色が変わりきっている　［28-34秒］</t>
+          <t>この一本の見せ場。塗った側と塗っていない側が同じ画面に入る。長回し・カットを割らない　［28-34秒］</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr"/>
@@ -1936,13 +1936,13 @@
       <c r="C68" s="7" t="inlineStr"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>② S7-1</t>
+          <t>② S6-3</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr"/>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>ヘラで仕上げ剤を薄く伸ばす　［34-38秒］</t>
+          <t>塗り終わり。同じ画角のまま断面の色が変わりきっている　［28-34秒］</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr"/>
@@ -1956,13 +1956,13 @@
       <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>② S7-2</t>
+          <t>② S7-1</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>超マクロ。コバを磨く。摩擦音　［34-38秒］</t>
+          <t>ヘラで仕上げ剤を薄く伸ばす　［34-38秒］</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr"/>
@@ -1976,13 +1976,13 @@
       <c r="C70" s="7" t="inlineStr"/>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>② S7-3</t>
+          <t>② S7-2</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr"/>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>磨き終わった断面に、光が一本だけ走る　［34-38秒］</t>
+          <t>超マクロ。コバを磨く。摩擦音　［34-38秒］</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr"/>
@@ -1992,29 +1992,17 @@
       <c r="A71" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>工房・全工程</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>一工程一カットで流す（⑤は簡潔に）</t>
-        </is>
-      </c>
+      <c r="B71" s="7" t="inlineStr"/>
+      <c r="C71" s="7" t="inlineStr"/>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>⑤ S5-2</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>② S7-3</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr"/>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>大型の機械が動いている（引き）。設備の規模がそのまま伝わる　［38-52秒］</t>
+          <t>磨き終わった断面に、光が一本だけ走る　［34-38秒］</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr"/>
@@ -2024,17 +2012,29 @@
       <c r="A72" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="B72" s="7" t="inlineStr"/>
-      <c r="C72" s="7" t="inlineStr"/>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>工房・全工程</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>一工程一カットで流す（⑤は簡潔に）</t>
+        </is>
+      </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>⑤ S5-3</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr"/>
+          <t>⑤ S5-2</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>裁つ・縫う・磨く。一工程一カット。説明はしない。ここでくさがやさんの声が先に入りはじめる（Jカット）　［38-52秒］</t>
+          <t>大型の機械が動いている（引き）。設備の規模がそのまま伝わる　［38-52秒］</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr"/>
@@ -2044,29 +2044,17 @@
       <c r="A73" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>工房・検品</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>検品台（⑥・最重要）</t>
-        </is>
-      </c>
+      <c r="B73" s="7" t="inlineStr"/>
+      <c r="C73" s="7" t="inlineStr"/>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>⑥ S7-1</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑤ S5-3</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr"/>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>一点を手に取り、光にかざす。作業音が消える　［102-122秒］</t>
+          <t>裁つ・縫う・磨く。一工程一カット。説明はしない。ここでくさがやさんの声が先に入りはじめる（Jカット）　［38-52秒］</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr"/>
@@ -2076,17 +2064,29 @@
       <c r="A74" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="B74" s="7" t="inlineStr"/>
-      <c r="C74" s="7" t="inlineStr"/>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>工房・検品</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>検品台（⑥・最重要）</t>
+        </is>
+      </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>⑥ S7-2</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr"/>
+          <t>⑥ S7-1</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>寸法と縫い目を目で確かめる（寄り）　［102-122秒］</t>
+          <t>一点を手に取り、光にかざす。作業音が消える　［102-122秒］</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr"/>
@@ -2100,13 +2100,13 @@
       <c r="C75" s="7" t="inlineStr"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>⑥ S7-3</t>
+          <t>⑥ S7-2</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の顔。確かめ終えて顔を上げる一瞬。テロップ「検品 Inspection」　［102-122秒］</t>
+          <t>手に取って開き、内側と縫い目まで確かめる（寄り）。片方の手で押さえ、もう片方でめくる　［102-122秒］</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr"/>
@@ -2116,29 +2116,17 @@
       <c r="A76" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>梱包</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>梱包場（⑥）</t>
-        </is>
-      </c>
+      <c r="B76" s="7" t="inlineStr"/>
+      <c r="C76" s="7" t="inlineStr"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>⑥ S8-1</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑥ S7-3</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr"/>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>白手袋で包む。手元の寄り。不織布の角を折る。紙の音　［122-133秒］</t>
+          <t>Bロール：職人の顔。確かめ終えて顔を上げる一瞬。テロップ「検品 Inspection」　［102-122秒］</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr"/>
@@ -2148,17 +2136,29 @@
       <c r="A77" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B77" s="7" t="inlineStr"/>
-      <c r="C77" s="7" t="inlineStr"/>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>梱包</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>梱包場（⑥）</t>
+        </is>
+      </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>⑥ S8-2</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr"/>
+          <t>⑥ S8-1</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>箱に納め、テープで閉じる。梱包場の引き。奥にも人が写る。テロップ「梱包 Packing」　［122-133秒］</t>
+          <t>白手袋で包む。手元の寄り。不織布の角を折る。紙の音　［122-133秒］</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr"/>
@@ -2168,29 +2168,17 @@
       <c r="A78" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>企画・設計</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>机まわり・図面と数値（⑤⑥共通）</t>
-        </is>
-      </c>
+      <c r="B78" s="7" t="inlineStr"/>
+      <c r="C78" s="7" t="inlineStr"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>⑤ S4-1</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑥ S8-2</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr"/>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>手が図面をなぞる（寄り）　［29-38秒］</t>
+          <t>箱に納め、テープで閉じる。梱包場の引き。奥にも人が写る。テロップ「梱包 Packing」　［122-133秒］</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr"/>
@@ -2200,17 +2188,29 @@
       <c r="A79" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="B79" s="7" t="inlineStr"/>
-      <c r="C79" s="7" t="inlineStr"/>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>企画・設計</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>机まわり・図面と数値（⑤⑥共通）</t>
+        </is>
+      </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>⑤ S4-2</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr"/>
+          <t>⑤ S4-1</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>型紙・図面の俯瞰　［29-38秒］</t>
+          <t>手が図面をなぞる（寄り）　［29-38秒］</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr"/>
@@ -2224,13 +2224,13 @@
       <c r="C80" s="7" t="inlineStr"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>⑤ S4-3</t>
+          <t>⑤ S4-2</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr"/>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>机で数値を決める。ここで佐藤さんの声が先に入りはじめる（Jカット）　［29-38秒］</t>
+          <t>型紙・図面の俯瞰　［29-38秒］</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr"/>
@@ -2241,24 +2241,16 @@
         <v>70</v>
       </c>
       <c r="B81" s="7" t="inlineStr"/>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>革を選ぶ・色を決める（⑤）</t>
-        </is>
-      </c>
+      <c r="C81" s="7" t="inlineStr"/>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>⑤ S3-1</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯</t>
-        </is>
-      </c>
+          <t>⑤ S4-3</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>色見本を見ながら打ち合わせる。二人で同じものを覗き込む（俯瞰気味）。企画はここから始まる　［20-29秒］</t>
+          <t>机で数値を決める。ここで佐藤さんの声が先に入りはじめる（Jカット）　［29-38秒］</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr"/>
@@ -2269,16 +2261,24 @@
         <v>71</v>
       </c>
       <c r="B82" s="7" t="inlineStr"/>
-      <c r="C82" s="7" t="inlineStr"/>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>革を選ぶ・色を決める（⑤）</t>
+        </is>
+      </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>⑤ S3-2</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr"/>
+          <t>⑤ S3-1</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯</t>
+        </is>
+      </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>革を並べて色を決める。扱える色数がそのまま伝わる　［20-29秒］</t>
+          <t>色見本を見ながら打ち合わせる。二人で同じものを覗き込む（俯瞰気味）。企画はここから始まる　［20-29秒］</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr"/>
@@ -2292,13 +2292,13 @@
       <c r="C83" s="7" t="inlineStr"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>⑤ S3-3</t>
+          <t>⑤ S3-2</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>机いっぱいに色見本と資料が広がる。手が動いて話している（引き）　［20-29秒］</t>
+          <t>革を並べて色を決める。扱える色数がそのまま伝わる　［20-29秒］</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr"/>
@@ -2308,29 +2308,17 @@
       <c r="A84" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>複写・資料</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>沿革の写真を複写する（⑤）</t>
-        </is>
-      </c>
+      <c r="B84" s="7" t="inlineStr"/>
+      <c r="C84" s="7" t="inlineStr"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>⑤ S2-1</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／自然光</t>
-        </is>
-      </c>
+          <t>⑤ S3-3</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr"/>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>コラボの実績から入る。年号テロップを次々に重ねる（1980 SHIPS ／ 1982 BEAMS ／ 1984 To Boot New York ／ 1990 UNITED ARROWS ／ 1991 Paul Smith ／ 2011 RALPH LAUREN）　［6-20秒］</t>
+          <t>机いっぱいに色見本と資料が広がる。手が動いて話している（引き）　［20-29秒］</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr"/>
@@ -2340,17 +2328,29 @@
       <c r="A85" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="B85" s="7" t="inlineStr"/>
-      <c r="C85" s="7" t="inlineStr"/>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>複写・資料</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>沿革の写真を複写する（⑤）</t>
+        </is>
+      </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>⑤ S2-2</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr"/>
+          <t>⑤ S2-1</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／自然光</t>
+        </is>
+      </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>昔の外観。実績を並べたあと、はじまりの店先に戻る。テロップ「1979　東京千駄ヶ谷にて創業」（画面上部の英字はサイト側の見出し。実際は年号テロップだけを載せる）　［6-20秒］</t>
+          <t>コラボの実績から入る。年号テロップを次々に重ねる（1980 SHIPS ／ 1982 BEAMS ／ 1984 To Boot New York ／ 1990 UNITED ARROWS ／ 1991 Paul Smith ／ 2011 RALPH LAUREN）　［6-20秒］</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr"/>
@@ -2364,13 +2364,13 @@
       <c r="C86" s="7" t="inlineStr"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>⑤ S2-3</t>
+          <t>⑤ S2-2</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr"/>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>同じ構図のまま、今の外観へ。昔の店先からそのまま移り変わる。白黒からカラーに変わる　［6-20秒］</t>
+          <t>昔の外観。実績を並べたあと、はじまりの店先に戻る。テロップ「1979　東京千駄ヶ谷にて創業」（画面上部の英字はサイト側の見出し。実際は年号テロップだけを載せる）　［6-20秒］</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr"/>
@@ -2380,29 +2380,17 @@
       <c r="A87" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>黒バック撮影</t>
-        </is>
-      </c>
-      <c r="C87" s="9" t="inlineStr">
-        <is>
-          <t>黒スチレンボード＋一灯（③専用・別日）</t>
-        </is>
-      </c>
+      <c r="B87" s="7" t="inlineStr"/>
+      <c r="C87" s="7" t="inlineStr"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>③ S1-1</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／マクロレンズ／三脚／照明1灯／黒スチレンボード／アクリル板／白手袋</t>
-        </is>
-      </c>
+          <t>⑤ S2-3</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr"/>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>真っ黒。細い光の帯が一本だけ立つ　［0-4秒］</t>
+          <t>同じ構図のまま、今の外観へ。昔の店先からそのまま移り変わる。白黒からカラーに変わる　［6-20秒］</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr"/>
@@ -2412,17 +2400,29 @@
       <c r="A88" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="B88" s="7" t="inlineStr"/>
-      <c r="C88" s="7" t="inlineStr"/>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>黒バック撮影</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>黒スチレンボード＋一灯（③専用・別日）</t>
+        </is>
+      </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>③ S1-2</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr"/>
+          <t>③ S1-1</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／マクロレンズ／三脚／照明1灯／黒スチレンボード／アクリル板／白手袋</t>
+        </is>
+      </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>光の帯がゆっくり動く。無音から低いBGMが立ち上がる　［0-4秒］</t>
+          <t>真っ黒。細い光の帯が一本だけ立つ　［0-4秒］</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr"/>
@@ -2436,13 +2436,13 @@
       <c r="C89" s="7" t="inlineStr"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>③ S1-3</t>
+          <t>③ S1-2</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr"/>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>―　［0-4秒］</t>
+          <t>光の帯がゆっくり動く。無音から低いBGMが立ち上がる　［0-4秒］</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr"/>
@@ -2456,13 +2456,13 @@
       <c r="C90" s="7" t="inlineStr"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>③ S2-1</t>
+          <t>③ S1-3</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr"/>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>作業台に革を置く。奥に染料と道具が並ぶ　［4-8秒］</t>
+          <t>―　［0-4秒］</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr"/>
@@ -2476,13 +2476,13 @@
       <c r="C91" s="7" t="inlineStr"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>③ S2-2</t>
+          <t>③ S2-1</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr"/>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>二枚を合わせて位置を決める。腕時計・指輪は外す　［4-8秒］</t>
+          <t>作業台に革を置く。奥に染料と道具が並ぶ　［4-8秒］</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr"/>
@@ -2496,13 +2496,13 @@
       <c r="C92" s="7" t="inlineStr"/>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>③ S2-3</t>
+          <t>③ S2-2</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr"/>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>合わせた革を押さえる。ここから形になっていく　［4-8秒］</t>
+          <t>二枚を合わせて位置を決める。腕時計・指輪は外す　［4-8秒］</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr"/>
@@ -2516,13 +2516,13 @@
       <c r="C93" s="7" t="inlineStr"/>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>③ S3-1</t>
+          <t>③ S2-3</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>手だけ。革を折る　［8-15秒］</t>
+          <t>合わせた革を押さえる。ここから形になっていく　［4-8秒］</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr"/>
@@ -2536,13 +2536,13 @@
       <c r="C94" s="7" t="inlineStr"/>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>③ S3-2</t>
+          <t>③ S3-1</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr"/>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>縁を押さえる（超マクロ）　［8-15秒］</t>
+          <t>手だけ。革を折る　［8-15秒］</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
       <c r="C95" s="7" t="inlineStr"/>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>③ S3-3</t>
+          <t>③ S3-2</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr"/>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>角が立ち上がる。顔と工房は一切映さない　［8-15秒］</t>
+          <t>縁を押さえる（超マクロ）　［8-15秒］</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr"/>
@@ -2576,13 +2576,13 @@
       <c r="C96" s="7" t="inlineStr"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>③ S4-1</t>
+          <t>③ S3-3</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr"/>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>白手袋で金具を持つ。金属が触れる音　［15-19秒］</t>
+          <t>角が立ち上がる。顔と工房は一切映さない　［8-15秒］</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr"/>
@@ -2596,13 +2596,13 @@
       <c r="C97" s="7" t="inlineStr"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>③ S4-2</t>
+          <t>③ S4-1</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr"/>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>金具を取り付ける（超マクロ）。カチリと一音　［15-19秒］</t>
+          <t>白手袋で金具を持つ。金属が触れる音　［15-19秒］</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr"/>
@@ -2616,13 +2616,13 @@
       <c r="C98" s="7" t="inlineStr"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>③ S4-3</t>
+          <t>③ S4-2</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr"/>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>指が金具の縁をなぞる　［15-19秒］</t>
+          <t>金具を取り付ける（超マクロ）。カチリと一音　［15-19秒］</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr"/>
@@ -2636,13 +2636,13 @@
       <c r="C99" s="7" t="inlineStr"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>③ S5-1</t>
+          <t>③ S4-3</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr"/>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>コバに染料を入れる（超マクロ）　※参考動画にこの工程は映っていない。2本目の参考動画（コバ塗り）を見て画角を決める　［19-25秒］</t>
+          <t>指が金具の縁をなぞる　［15-19秒］</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr"/>
@@ -2656,13 +2656,13 @@
       <c r="C100" s="7" t="inlineStr"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>③ S5-2</t>
+          <t>③ S5-1</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr"/>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>磨く。光が断面に反射する角度を探す（超マクロ）　［19-25秒］</t>
+          <t>完成品を持ち上げる　［19-28秒］</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr"/>
@@ -2676,13 +2676,13 @@
       <c r="C101" s="7" t="inlineStr"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>③ S5-3</t>
+          <t>③ S5-2</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr"/>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>磨き終わった断面に、光が一本だけ走る　［19-25秒］</t>
+          <t>道具の前に置く。上から一灯だけ　［19-28秒］</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr"/>
@@ -2696,13 +2696,13 @@
       <c r="C102" s="7" t="inlineStr"/>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>③ S6-1</t>
+          <t>③ S5-3</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr"/>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>完成品を持ち上げる　［25-28秒］</t>
+          <t>金具のマクロ → BGMが止まる → ロゴのみ。テロップは出さない　［19-28秒］</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr"/>
@@ -2712,17 +2712,29 @@
       <c r="A103" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="B103" s="7" t="inlineStr"/>
-      <c r="C103" s="7" t="inlineStr"/>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>白台・物撮り</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>五色を並べる（①の締め）</t>
+        </is>
+      </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>③ S6-2</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr"/>
+          <t>① S8-1</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯／白台</t>
+        </is>
+      </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>道具の前に置く。上から一灯だけ　［25-28秒］</t>
+          <t>人がフレームから出る。置かれた小物だけが残る　［25-30秒］</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr"/>
@@ -2736,13 +2748,13 @@
       <c r="C104" s="7" t="inlineStr"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>③ S6-3</t>
+          <t>① S8-2</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr"/>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>金具のマクロ → BGMが止まる → ロゴのみ。テロップは出さない　［25-28秒］</t>
+          <t>五色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る　［25-30秒］</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr"/>
@@ -2752,29 +2764,17 @@
       <c r="A105" s="7" t="n">
         <v>94</v>
       </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>白台・物撮り</t>
-        </is>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>四色を並べる（①の締め）</t>
-        </is>
-      </c>
+      <c r="B105" s="7" t="inlineStr"/>
+      <c r="C105" s="7" t="inlineStr"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>① S7-1</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯／白台</t>
-        </is>
-      </c>
+          <t>① S8-3</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr"/>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>人がフレームから出る。置かれた小物だけが残る　［27-30秒］</t>
+          <t>そのままロゴ。締めのテロップは出さない　［25-30秒］</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr"/>
@@ -2785,16 +2785,24 @@
         <v>95</v>
       </c>
       <c r="B106" s="7" t="inlineStr"/>
-      <c r="C106" s="7" t="inlineStr"/>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>白い台・正面固定（⑦専用・三品番を同じ画角で）</t>
+        </is>
+      </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>① S7-2</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr"/>
+          <t>⑦ S1-1</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／マクロレンズ／照明1灯／白台／レフ板</t>
+        </is>
+      </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>四色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る　［27-30秒］</t>
+          <t>机に鞄が一つ置いてある。正面固定の引き。手前に入れるものが並べてある　［0-4秒］</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr"/>
@@ -2808,13 +2816,13 @@
       <c r="C107" s="7" t="inlineStr"/>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>① S7-3</t>
+          <t>⑦ S1-2</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr"/>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>そのままロゴ。締めのテロップは出さない　［27-30秒］</t>
+          <t>ここから最後までこの画角のまま。三品番とも同じ位置に置く　［0-4秒］</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr"/>
@@ -2825,24 +2833,16 @@
         <v>97</v>
       </c>
       <c r="B108" s="7" t="inlineStr"/>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>白い台・正面固定（⑦専用・三品番を同じ画角で）</t>
-        </is>
-      </c>
+      <c r="C108" s="7" t="inlineStr"/>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>⑦ S1-1</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／マクロレンズ／照明1灯／白台／レフ板</t>
-        </is>
-      </c>
+          <t>⑦ S1-3</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr"/>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>超マクロ・モノクロ。ファスナーの歯　［0-4秒］</t>
+          <t>人が入ってきて、鞄の口を開ける。中は空。顔は入れない　［0-4秒］</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr"/>
@@ -2856,13 +2856,13 @@
       <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>⑦ S1-2</t>
+          <t>⑦ S2-1</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr"/>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>ストラップと縫い目（モノクロのまま）　［0-4秒］</t>
+          <t>A4書類とノートPCを入れる　［4-10秒］</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr"/>
@@ -2876,13 +2876,13 @@
       <c r="C110" s="7" t="inlineStr"/>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>⑦ S1-3</t>
+          <t>⑦ S2-2</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr"/>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>金具の質感（モノクロのまま）　［0-4秒］</t>
+          <t>ノートPCが底まで収まる。入れる音を拾う　［4-10秒］</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr"/>
@@ -2896,13 +2896,13 @@
       <c r="C111" s="7" t="inlineStr"/>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>⑦ S2-1</t>
+          <t>⑦ S2-3</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr"/>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>引く。カラーに変わる。白い台に鞄が一つ　［4-7秒］</t>
+          <t>手帳・鍵・サングラス　［4-10秒］</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr"/>
@@ -2916,13 +2916,13 @@
       <c r="C112" s="7" t="inlineStr"/>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>⑦ S2-2</t>
+          <t>⑦ S3-1</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr"/>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>正面固定。ここから最後までこの画角のまま　［4-7秒］</t>
+          <t>ペン・小物。入れる音を一つずつ拾う　［10-15秒］</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr"/>
@@ -2936,13 +2936,13 @@
       <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>⑦ S2-3</t>
+          <t>⑦ S3-2</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>鞄を開ける。中は空　［4-7秒］</t>
+          <t>傘・水筒まで入れる。それでもまだ閉まる　［10-15秒］</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr"/>
@@ -2956,13 +2956,13 @@
       <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>⑦ S3-1</t>
+          <t>⑦ S3-3</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr"/>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>A4書類とノートPCを入れる　［7-13秒］</t>
+          <t>最後の一つを入れる。ここで手が止まる　［10-15秒］</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr"/>
@@ -2976,13 +2976,13 @@
       <c r="C115" s="7" t="inlineStr"/>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>⑦ S3-2</t>
+          <t>⑦ S4-1</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>入りきる。上端にまだ余りがあるのを見せる　［7-13秒］</t>
+          <t>持ち手をまとめて持ち上げる　［15-20秒］</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr"/>
@@ -2996,13 +2996,13 @@
       <c r="C116" s="7" t="inlineStr"/>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>⑦ S3-3</t>
+          <t>⑦ S4-2</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr"/>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>手帳・鍵・サングラス。顔は入れない　［7-13秒］</t>
+          <t>肩に掛けて、そのままフレームの外へ出ていく。台は動かさない　［15-20秒］</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr"/>
@@ -3016,13 +3016,13 @@
       <c r="C117" s="7" t="inlineStr"/>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>⑦ S4-1</t>
+          <t>⑦ S5-1</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr"/>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>ペン・小物。入れる音を一つずつ拾う　［13-17秒］</t>
+          <t>人も鞄もフレームから出て、何も乗っていない机だけが残る。参考動画と同じ終わり方　［20-25秒］</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr"/>
@@ -3036,13 +3036,13 @@
       <c r="C118" s="7" t="inlineStr"/>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>⑦ S4-2</t>
+          <t>⑦ S5-2</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr"/>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>傘・水筒まで入れる。それでもまだ閉まる　［13-17秒］</t>
+          <t>その画にテロップを重ねる「支度も、仕事も、スマートに。」　［20-25秒］</t>
         </is>
       </c>
       <c r="G118" s="11" t="inlineStr"/>
@@ -3056,13 +3056,13 @@
       <c r="C119" s="7" t="inlineStr"/>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>⑦ S4-3</t>
+          <t>⑦ S5-3</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr"/>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>最後の一つを入れる。ここで手が止まる　［13-17秒］</t>
+          <t>ロゴ。三品番とも同じ終わり方にする　［20-25秒］</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr"/>
@@ -3072,17 +3072,29 @@
       <c r="A120" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="B120" s="7" t="inlineStr"/>
-      <c r="C120" s="7" t="inlineStr"/>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>店舗</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>BROOKLYN MUSEUM 店舗（⑤⑧共通）</t>
+        </is>
+      </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>⑦ S5-1</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr"/>
+          <t>⑤ S6-2</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／ガンマイク</t>
+        </is>
+      </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>片手で持ち上げる。軽さを動作で見せる　［17-21秒］</t>
+          <t>店内（引き）。ショーケースと棚が並ぶ。ロゴが入る位置まで見せる　［52-63秒］</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr"/>
@@ -3096,13 +3108,13 @@
       <c r="C121" s="7" t="inlineStr"/>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>⑦ S5-2</t>
+          <t>⑤ S6-3</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr"/>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>肩にかける。台は動かさない　［17-21秒］</t>
+          <t>棚から商品を手に取る（寄り）。店員の手だけ。参考になる映像がないので写真は入れていない　［52-63秒］</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr"/>
@@ -3113,16 +3125,24 @@
         <v>111</v>
       </c>
       <c r="B122" s="7" t="inlineStr"/>
-      <c r="C122" s="7" t="inlineStr"/>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>商品と空間（⑧のつかみ）</t>
+        </is>
+      </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>⑦ S5-3</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr"/>
+          <t>⑧ S2-1</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／マクロレンズ／照明1灯</t>
+        </is>
+      </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>数字を小さくテロップで添える（千百六十グラム）　［17-21秒］</t>
+          <t>商品の寄り。できあがった瞬間　［5-11秒］</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr"/>
@@ -3136,13 +3156,13 @@
       <c r="C123" s="7" t="inlineStr"/>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>⑦ S6-1</t>
+          <t>⑧ S2-2</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr"/>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>人がフレームから出る。鞄だけが残る　［21-25秒］</t>
+          <t>商品の真俯瞰。並べて撮る　［5-11秒］</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr"/>
@@ -3156,13 +3176,13 @@
       <c r="C124" s="7" t="inlineStr"/>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>⑦ S6-2</t>
+          <t>⑧ S2-3</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr"/>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>テロップ「支度も、仕事も、スマートに。」　［21-25秒］</t>
+          <t>空間。窓際と光。ここまで人の顔は出さない　［5-11秒］</t>
         </is>
       </c>
       <c r="G124" s="11" t="inlineStr"/>
@@ -3176,13 +3196,13 @@
       <c r="C125" s="7" t="inlineStr"/>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>⑦ S6-3</t>
+          <t>⑧ S3-2</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr"/>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>ロゴ。三品番とも同じ終わり方にする　［21-25秒］</t>
+          <t>ここから画はBロールに変わるが、声はそのまま流し続ける（引き）　［11-19秒］</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr"/>
@@ -3192,29 +3212,17 @@
       <c r="A126" s="7" t="n">
         <v>115</v>
       </c>
-      <c r="B126" s="8" t="inlineStr">
-        <is>
-          <t>店舗</t>
-        </is>
-      </c>
-      <c r="C126" s="9" t="inlineStr">
-        <is>
-          <t>BROOKLYN MUSEUM 店舗（⑤⑧共通）</t>
-        </is>
-      </c>
+      <c r="B126" s="7" t="inlineStr"/>
+      <c r="C126" s="7" t="inlineStr"/>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>⑤ S6-2</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／ガンマイク</t>
-        </is>
-      </c>
+          <t>⑧ S3-3</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr"/>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>店内（引き）。ショーケースと棚が並ぶ。ロゴが入る位置まで見せる　［52-63秒］</t>
+          <t>商品の寄り。話している内容に合わせて切り替える　［11-19秒］</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr"/>
@@ -3228,13 +3236,13 @@
       <c r="C127" s="7" t="inlineStr"/>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>⑤ S6-3</t>
+          <t>⑧ S4-2</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>ショーウィンドウ越しに店内を見せる。外から見た店の顔。（棚から商品を手に取る寄りも撮っておく）　［52-63秒］</t>
+          <t>声の上にBロール。空間の引き　［19-28秒］</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr"/>
@@ -3245,24 +3253,16 @@
         <v>117</v>
       </c>
       <c r="B128" s="7" t="inlineStr"/>
-      <c r="C128" s="9" t="inlineStr">
-        <is>
-          <t>商品と空間（⑧のつかみ）</t>
-        </is>
-      </c>
+      <c r="C128" s="7" t="inlineStr"/>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-1</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／マクロレンズ／照明1灯</t>
-        </is>
-      </c>
+          <t>⑧ S4-3</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr"/>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>商品の寄り。できあがった瞬間　［5-11秒］</t>
+          <t>窓辺の一枚。間を作る　［19-28秒］</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr"/>
@@ -3273,16 +3273,24 @@
         <v>118</v>
       </c>
       <c r="B129" s="7" t="inlineStr"/>
-      <c r="C129" s="7" t="inlineStr"/>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>外観と作っているところ（⑧のつかみ）</t>
+        </is>
+      </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-2</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr"/>
+          <t>⑧ S1-1</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>商品の真俯瞰。並べて撮る　［5-11秒］</t>
+          <t>外観のロー。空を入れて見上げる。ロゴを重ねる　［0-5秒］</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr"/>
@@ -3296,13 +3304,13 @@
       <c r="C130" s="7" t="inlineStr"/>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-3</t>
+          <t>⑧ S1-2</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr"/>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>空間。窓際と光。ここまで人の顔は出さない　［5-11秒］</t>
+          <t>外観の全景（引き）。入口に人が立つ　［0-5秒］</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr"/>
@@ -3316,13 +3324,13 @@
       <c r="C131" s="7" t="inlineStr"/>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-2</t>
+          <t>⑧ S1-3</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr"/>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>ここから画はBロールに変わるが、声はそのまま流し続ける（引き）　［11-19秒］</t>
+          <t>作っているところ。手元だけ（寄り）　［0-5秒］</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr"/>
@@ -3333,16 +3341,24 @@
         <v>121</v>
       </c>
       <c r="B132" s="7" t="inlineStr"/>
-      <c r="C132" s="7" t="inlineStr"/>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>見送り（⑧の締め）</t>
+        </is>
+      </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-3</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr"/>
+          <t>⑧ S7-1</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>商品の寄り。話している内容に合わせて切り替える　［11-19秒］</t>
+          <t>店の前。スタッフが出てくる（引き）　［50-60秒］</t>
         </is>
       </c>
       <c r="G132" s="11" t="inlineStr"/>
@@ -3356,13 +3372,13 @@
       <c r="C133" s="7" t="inlineStr"/>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-2</t>
+          <t>⑧ S7-2</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr"/>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>声の上にBロール。空間の引き　［19-28秒］</t>
+          <t>手を振って見送る。カメラは動かさない　［50-60秒］</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr"/>
@@ -3376,13 +3392,13 @@
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-3</t>
+          <t>⑧ S7-3</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr"/>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>窓辺の一枚。間を作る　［19-28秒］</t>
+          <t>同じ引きの画面の中央に、ロゴが重なる　［50-60秒］</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr"/>
@@ -3392,25 +3408,29 @@
       <c r="A135" s="7" t="n">
         <v>124</v>
       </c>
-      <c r="B135" s="7" t="inlineStr"/>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>お客様・街</t>
+        </is>
+      </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>外観と作っているところ（⑧のつかみ）</t>
+          <t>使っている場面（⑧）</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-1</t>
+          <t>⑧ S5-1</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>カメラ／三脚／レフ板</t>
+          <t>カメラ／三脚</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>外観のロー。空を入れて見上げる。ロゴを重ねる　［0-5秒］</t>
+          <t>別の場所へ移る（引き）　［28-38秒］</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr"/>
@@ -3424,13 +3444,13 @@
       <c r="C136" s="7" t="inlineStr"/>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-2</t>
+          <t>⑧ S5-2</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr"/>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>外観の全景（引き）。入口に人が立つ　［0-5秒］</t>
+          <t>落ち着いた場所での一枚　［28-38秒］</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr"/>
@@ -3444,13 +3464,13 @@
       <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-3</t>
+          <t>⑧ S5-3</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr"/>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>作っているところ。手元だけ（寄り）　［0-5秒］</t>
+          <t>外に出る。空を入れて気分を変える　［28-38秒］</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr"/>
@@ -3461,24 +3481,16 @@
         <v>127</v>
       </c>
       <c r="B138" s="7" t="inlineStr"/>
-      <c r="C138" s="9" t="inlineStr">
-        <is>
-          <t>見送り（⑧の締め）</t>
-        </is>
-      </c>
+      <c r="C138" s="7" t="inlineStr"/>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>⑧ S7-1</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>⑧ S6-2</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr"/>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>店の前。スタッフが出てくる（引き）　［50-60秒］</t>
+          <t>外の引きに人が入る。声はそのまま続く　［38-50秒］</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr"/>
@@ -3492,13 +3504,13 @@
       <c r="C139" s="7" t="inlineStr"/>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>⑧ S7-2</t>
+          <t>⑧ S6-3</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr"/>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>手を振って見送る。カメラは動かさない　［50-60秒］</t>
+          <t>窓辺に戻る。静かな一枚。台本にない一言を拾う　［38-50秒］</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr"/>
@@ -3509,16 +3521,24 @@
         <v>129</v>
       </c>
       <c r="B140" s="7" t="inlineStr"/>
-      <c r="C140" s="7" t="inlineStr"/>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>使われている場所（②の締め）</t>
+        </is>
+      </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>⑧ S7-3</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr"/>
+          <t>② S8-1</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>同じ引きの画面の中央に、ロゴが重なる　［50-60秒］</t>
+          <t>作業机ではなく、使われている場所に置く → テロップ → ロゴ　［38-40秒］</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr"/>
@@ -3528,29 +3548,17 @@
       <c r="A141" s="7" t="n">
         <v>130</v>
       </c>
-      <c r="B141" s="8" t="inlineStr">
-        <is>
-          <t>お客様・街</t>
-        </is>
-      </c>
-      <c r="C141" s="9" t="inlineStr">
-        <is>
-          <t>使っている場面（⑧）</t>
-        </is>
-      </c>
+      <c r="B141" s="7" t="inlineStr"/>
+      <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-1</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>② S8-2</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr"/>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>別の場所へ移る（引き）　［28-38秒］</t>
+          <t>―　［38-40秒］</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr"/>
@@ -3564,13 +3572,13 @@
       <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-2</t>
+          <t>② S8-3</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr"/>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>落ち着いた場所での一枚　［28-38秒］</t>
+          <t>―　［38-40秒］</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr"/>
@@ -3581,16 +3589,24 @@
         <v>132</v>
       </c>
       <c r="B143" s="7" t="inlineStr"/>
-      <c r="C143" s="7" t="inlineStr"/>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>受け取りと使用（⑤⑧共通）</t>
+        </is>
+      </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-3</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr"/>
+          <t>⑤ S7-1</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>外に出る。空を入れて気分を変える　［28-38秒］</t>
+          <t>会計。カウンターで店員が応対する。二人が同じ画面に入る　［63-70秒］</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr"/>
@@ -3604,13 +3620,13 @@
       <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-2</t>
+          <t>⑤ S7-2</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>外の引きに人が入る。声はそのまま続く　［38-50秒］</t>
+          <t>手渡される瞬間と、受け取った人の笑顔。渡す側と受け取る側を一つの画に入れる　［63-70秒］</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr"/>
@@ -3624,13 +3640,13 @@
       <c r="C145" s="7" t="inlineStr"/>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-3</t>
+          <t>⑤ S7-3</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr"/>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>窓辺に戻る。静かな一枚。台本にない一言を拾う　［38-50秒］</t>
+          <t>実際に使われている手元。ノートPCを入れる。ここで永尾社長の声がもう一度入りはじめる（Jカット）　［63-70秒］</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr"/>
@@ -3643,12 +3659,12 @@
       <c r="B146" s="7" t="inlineStr"/>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>使われている場所（②の締め）</t>
+          <t>締め（⑤）</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>② S8-1</t>
+          <t>⑤ S8-2</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
@@ -3658,7 +3674,7 @@
       </c>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>作業机ではなく、使われている場所に置く → テロップ → ロゴ　［38-40秒］</t>
+          <t>声が終わり、音が引く。ロゴだけ。テロップは出さない　［70-75秒］</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr"/>
@@ -3672,13 +3688,13 @@
       <c r="C147" s="7" t="inlineStr"/>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>② S8-2</t>
+          <t>⑤ S8-3</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr"/>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>―　［38-40秒］</t>
+          <t>―　［70-75秒］</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr"/>
@@ -3688,17 +3704,29 @@
       <c r="A148" s="7" t="n">
         <v>137</v>
       </c>
-      <c r="B148" s="7" t="inlineStr"/>
-      <c r="C148" s="7" t="inlineStr"/>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>屋外・街</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>会社のロビー（①の到着点）</t>
+        </is>
+      </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>② S8-3</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="inlineStr"/>
+          <t>① S7-1</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>―　［38-40秒］</t>
+          <t>全体。柱が抜けるとロビー。立ち止まる。ここが到着点　［21-25秒　｜　切り替わり＝手前をロビーの柱が横切る］</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr"/>
@@ -3709,24 +3737,16 @@
         <v>138</v>
       </c>
       <c r="B149" s="7" t="inlineStr"/>
-      <c r="C149" s="9" t="inlineStr">
-        <is>
-          <t>受け取りと使用（⑤⑧共通）</t>
-        </is>
-      </c>
+      <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-1</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>① S7-2</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>会計。カウンターで店員が応対する。二人が同じ画面に入る　［63-70秒］</t>
+          <t>腰より上。肩の鞄を掛け直して笑う。三十秒でいちばん明るい表情　［21-25秒　｜　切り替わり＝手前をロビーの柱が横切る］</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr"/>
@@ -3737,16 +3757,24 @@
         <v>139</v>
       </c>
       <c r="B150" s="7" t="inlineStr"/>
-      <c r="C150" s="7" t="inlineStr"/>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>自宅の玄関まわり（①）</t>
+        </is>
+      </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-2</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr"/>
+          <t>① S1-1</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>手渡される瞬間と、受け取った人の笑顔。渡す側と受け取る側を一つの画に入れる　［63-70秒］</t>
+          <t>キーケースの寄りで始まる。初めはピントを外しておく。そこへ手が入って取り上げ、ピントが合う　［0-5秒］</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr"/>
@@ -3760,13 +3788,13 @@
       <c r="C151" s="7" t="inlineStr"/>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-3</t>
+          <t>① S1-2</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>実際に使われている手元。ノートPCを入れる。ここで永尾社長の声がもう一度入りはじめる（Jカット）　［63-70秒］</t>
+          <t>鏡の前。鞄を肩に当てて合わせる。身支度をしているところ　［0-5秒］</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr"/>
@@ -3777,24 +3805,16 @@
         <v>141</v>
       </c>
       <c r="B152" s="7" t="inlineStr"/>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>締め（⑤）</t>
-        </is>
-      </c>
+      <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-2</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>① S1-3</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>声が終わり、音が引く。ロゴだけ。テロップは出さない　［70-75秒］</t>
+          <t>玄関のドアに手をかけて開ける（後ろ姿・逆光）　［0-5秒］</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr"/>
@@ -3808,13 +3828,13 @@
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-3</t>
+          <t>① S1-4</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>―　［70-75秒］</t>
+          <t>ドアが開くと、もう別の服になっている。同じ玄関、違う人・違う色。この一本の決まりごとを、いちばん最初に見せてしまう　［0-5秒］</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr"/>
@@ -3824,19 +3844,15 @@
       <c r="A154" s="7" t="n">
         <v>143</v>
       </c>
-      <c r="B154" s="8" t="inlineStr">
-        <is>
-          <t>屋外・街</t>
-        </is>
-      </c>
+      <c r="B154" s="7" t="inlineStr"/>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>自宅の玄関まわり（①）</t>
+          <t>街歩き・夕方の斜光（④）</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>① S1-1</t>
+          <t>④ S1-1</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
@@ -3846,7 +3862,7 @@
       </c>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>玄関の中。全身が入る引き。出かける支度をしている　［0-5秒］</t>
+          <t>フェンスに掛ける（引き・三脚で固定）。カメラは止めたまま、背景の街だけが動く　［0-6秒］</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr"/>
@@ -3860,13 +3876,13 @@
       <c r="C155" s="7" t="inlineStr"/>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>① S1-2</t>
+          <t>④ S1-2</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr"/>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>ドアの前に立つ（引き）　［0-5秒］</t>
+          <t>柱の前。鞄を持って立つ（引き）　［0-6秒］</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr"/>
@@ -3880,13 +3896,13 @@
       <c r="C156" s="7" t="inlineStr"/>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>① S1-3</t>
+          <t>④ S1-3</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr"/>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>ドアが開く。開いた瞬間、服も鞄も変わっている。表情も変わっている。「服が変われば、合う色も気分も変わる」という決まりごとを、ここで先に見せておく。あとのトランジションが全部これで読める　［0-5秒］</t>
+          <t>全身の引き。顔は主役にしない　［0-6秒］</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr"/>
@@ -3900,13 +3916,13 @@
       <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>① S2-1</t>
+          <t>④ S2-1</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr"/>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>通勤路を歩く（引き）。この場所をこのあとも使い回す　［5-9秒］</t>
+          <t>真俯瞰。鞄の口を開ける　［6-12秒］</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr"/>
@@ -3920,13 +3936,13 @@
       <c r="C158" s="7" t="inlineStr"/>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>① S2-2</t>
+          <t>④ S2-2</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr"/>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>歩いてくる全身（一色目）。すまし顔で　［5-9秒］</t>
+          <t>真俯瞰。中身を整える手（寄り）　［6-12秒］</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr"/>
@@ -3940,13 +3956,13 @@
       <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>① S2-3</t>
+          <t>④ S2-3</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>歩き出す全身（引き・ロー）。鞄が体の横で揺れる　［5-9秒］</t>
+          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［6-12秒］</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr"/>
@@ -3957,24 +3973,16 @@
         <v>149</v>
       </c>
       <c r="B160" s="7" t="inlineStr"/>
-      <c r="C160" s="9" t="inlineStr">
-        <is>
-          <t>街歩き・夕方の斜光（④）</t>
-        </is>
-      </c>
+      <c r="C160" s="7" t="inlineStr"/>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>④ S1-1</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>④ S3-1</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr"/>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>フェンスに掛ける（引き・三脚で固定）。背景に街が流れる　［0-6秒］</t>
+          <t>高い場所を歩く（引き・映画的）　［12-18秒］</t>
         </is>
       </c>
       <c r="G160" s="11" t="inlineStr"/>
@@ -3988,13 +3996,13 @@
       <c r="C161" s="7" t="inlineStr"/>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>④ S1-2</t>
+          <t>④ S3-2</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>同じ画角のまま、背景を車が横切る　［0-6秒］</t>
+          <t>肩に掛かった鞄に寄る　［12-18秒］</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr"/>
@@ -4008,13 +4016,13 @@
       <c r="C162" s="7" t="inlineStr"/>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>④ S1-3</t>
+          <t>④ S3-3</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>鞄だけに寄る。革の面と持ち手　［0-6秒］</t>
+          <t>鞄と脚だけ（歩く）　［12-18秒］</t>
         </is>
       </c>
       <c r="G162" s="11" t="inlineStr"/>
@@ -4028,13 +4036,13 @@
       <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>④ S2-1</t>
+          <t>④ S4-1</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>建物の柱の前。鞄を持って立つ（引き）　［6-11秒］</t>
+          <t>手すりの前で立ち止まる　［18-24秒］</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr"/>
@@ -4048,13 +4056,13 @@
       <c r="C164" s="7" t="inlineStr"/>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>④ S2-2</t>
+          <t>④ S4-2</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr"/>
       <c r="F164" s="10" t="inlineStr">
         <is>
-          <t>全身の引き。顔は主役にしない　［6-11秒］</t>
+          <t>白い服が画面を横切る（つなぎ）　［18-24秒］</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr"/>
@@ -4068,13 +4076,13 @@
       <c r="C165" s="7" t="inlineStr"/>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>④ S2-3</t>
+          <t>④ S4-3</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr"/>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>肩に掛かった鞄だけに寄る　［6-11秒］</t>
+          <t>真俯瞰。鞄と持ち物・靴を並べる置き画　［18-24秒］</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr"/>
@@ -4088,13 +4096,13 @@
       <c r="C166" s="7" t="inlineStr"/>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>④ S3-1</t>
+          <t>④ S5-1</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr"/>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄の口を開ける　［11-18秒］</t>
+          <t>最初と同じフェンスの画角に戻る。一周して戻ってきたことが分かる　［24-30秒］</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr"/>
@@ -4108,13 +4116,13 @@
       <c r="C167" s="7" t="inlineStr"/>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>④ S3-2</t>
+          <t>④ S5-2</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr"/>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。中身を整える手（寄り）　［11-18秒］</t>
+          <t>背景の街だけが動いている　［24-30秒］</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr"/>
@@ -4128,13 +4136,13 @@
       <c r="C168" s="7" t="inlineStr"/>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>④ S3-3</t>
+          <t>④ S5-3</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄と持ち物を並べた置き画　［11-18秒］</t>
+          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr"/>
@@ -4145,16 +4153,24 @@
         <v>158</v>
       </c>
       <c r="B169" s="7" t="inlineStr"/>
-      <c r="C169" s="7" t="inlineStr"/>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>通勤路の並木道（①・同じ画角を使い回す）</t>
+        </is>
+      </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>④ S4-1</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="inlineStr"/>
+          <t>① S2-1</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［18-24秒］</t>
+          <t>全体。ドアが開くと、もう別の服になっている。並木道を歩いてくる全身の引き（濃いグレー）。すまし顔　［5-8秒　｜　切り替わり＝玄関のドアが開く］</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr"/>
@@ -4168,13 +4184,13 @@
       <c r="C170" s="7" t="inlineStr"/>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>④ S4-2</t>
+          <t>① S2-2</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>高い場所を歩く（引き・映画的）　［18-24秒］</t>
+          <t>腰より上。同じ人に寄る。鞄の色と表情が一度に見える　［5-8秒　｜　切り替わり＝玄関のドアが開く］</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr"/>
@@ -4188,13 +4204,13 @@
       <c r="C171" s="7" t="inlineStr"/>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>④ S4-3</t>
+          <t>① S3-1</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>鞄と脚だけ（寄り・歩く）　［18-24秒］</t>
+          <t>全体。車が抜けると服も鞄の色も変わっている（白・ブルー）　［8-11秒　｜　切り替わり＝手前を車が横切る］</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr"/>
@@ -4208,13 +4224,13 @@
       <c r="C172" s="7" t="inlineStr"/>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>④ S5-1</t>
+          <t>① S3-2</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="10" t="inlineStr">
         <is>
-          <t>手すりの前で立ち止まる　［24-30秒］</t>
+          <t>腰より上。サングラスを直す。ここは笑っている表情で　［8-11秒　｜　切り替わり＝手前を車が横切る］</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr"/>
@@ -4228,13 +4244,13 @@
       <c r="C173" s="7" t="inlineStr"/>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>④ S5-2</t>
+          <t>① S4-1</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr"/>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。保存袋・小物まで並べる　［24-30秒］</t>
+          <t>全体。木の幹が抜けると三色目。同じ並木道を奥から歩いてくる　［11-14秒　｜　切り替わり＝手前を木の幹が横切る（前ボケ）］</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr"/>
@@ -4248,13 +4264,13 @@
       <c r="C174" s="7" t="inlineStr"/>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>④ S5-3</t>
+          <t>① S4-2</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr"/>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
+          <t>腰より上。立ち止まって振り返る。帽子を押さえる仕草を入れる　［11-14秒　｜　切り替わり＝手前を木の幹が横切る（前ボケ）］</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr"/>
@@ -4267,12 +4283,12 @@
       <c r="B175" s="7" t="inlineStr"/>
       <c r="C175" s="9" t="inlineStr">
         <is>
-          <t>通勤路・駅・会社前（①・同じ画角を使い回す）</t>
+          <t>駅の構内（①）</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>① S3-1</t>
+          <t>① S5-1</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr">
@@ -4282,7 +4298,7 @@
       </c>
       <c r="F175" s="10" t="inlineStr">
         <is>
-          <t>服が変わり、小物の色も変わる（二色目）。表情も一緒に変える　［9-14秒］</t>
+          <t>全体。柱が抜けると場所が駅に変わり、四色目になっている（ブルー）　［14-18秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
         </is>
       </c>
       <c r="G175" s="11" t="inlineStr"/>
@@ -4296,13 +4312,13 @@
       <c r="C176" s="7" t="inlineStr"/>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>① S3-2</t>
+          <t>① S5-2</t>
         </is>
       </c>
       <c r="E176" s="7" t="inlineStr"/>
       <c r="F176" s="10" t="inlineStr">
         <is>
-          <t>同じ道。三色目。ここは笑っている表情で　［9-14秒］</t>
+          <t>腰より上。構内を歩く。少し急ぎ足の表情　［14-18秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr"/>
@@ -4316,13 +4332,13 @@
       <c r="C177" s="7" t="inlineStr"/>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>① S3-3</t>
+          <t>① S6-1</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr"/>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>立ち止まって振り返る。服装ごとに気分が違うことを見せる　［9-14秒］</t>
+          <t>全体。人が抜けると五色目（ピンク）。通路を横移動で追う　［18-21秒　｜　切り替わり＝手前を人が横切る］</t>
         </is>
       </c>
       <c r="G177" s="11" t="inlineStr"/>
@@ -4336,13 +4352,13 @@
       <c r="C178" s="7" t="inlineStr"/>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>① S4-1</t>
+          <t>① S6-2</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr"/>
       <c r="F178" s="10" t="inlineStr">
         <is>
-          <t>手前を木の幹が横切る（前ボケ＝トランジション）　［14-18秒］</t>
+          <t>腰より上。入口に着く。顔を上げる　［18-21秒　｜　切り替わり＝手前を人が横切る］</t>
         </is>
       </c>
       <c r="G178" s="11" t="inlineStr"/>
@@ -4352,17 +4368,29 @@
       <c r="A179" s="7" t="n">
         <v>168</v>
       </c>
-      <c r="B179" s="7" t="inlineStr"/>
-      <c r="C179" s="7" t="inlineStr"/>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>締めカード</t>
+        </is>
+      </c>
+      <c r="C179" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。文字を組んで作る</t>
+        </is>
+      </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>① S4-2</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr"/>
+          <t>⑥ S9-1</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
       <c r="F179" s="10" t="inlineStr">
         <is>
-          <t>抜けたら別の服・別の色になっている（四色目）　［14-18秒］</t>
+          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
         </is>
       </c>
       <c r="G179" s="11" t="inlineStr"/>
@@ -4376,13 +4404,13 @@
       <c r="C180" s="7" t="inlineStr"/>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>① S4-3</t>
+          <t>⑥ S9-2</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr"/>
       <c r="F180" s="10" t="inlineStr">
         <is>
-          <t>場所が変わる。駅の構内（引き）　［14-18秒］</t>
+          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
         </is>
       </c>
       <c r="G180" s="11" t="inlineStr"/>
@@ -4396,13 +4424,13 @@
       <c r="C181" s="7" t="inlineStr"/>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>① S5-1</t>
+          <t>⑥ S9-3</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr"/>
       <c r="F181" s="10" t="inlineStr">
         <is>
-          <t>乗り場（引き）。同じ人・違う色　［18-22秒］</t>
+          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
         </is>
       </c>
       <c r="G181" s="11" t="inlineStr"/>
@@ -4413,16 +4441,24 @@
         <v>171</v>
       </c>
       <c r="B182" s="7" t="inlineStr"/>
-      <c r="C182" s="7" t="inlineStr"/>
+      <c r="C182" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。白に抜いてロゴだけ</t>
+        </is>
+      </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>① S5-2</t>
-        </is>
-      </c>
-      <c r="E182" s="7" t="inlineStr"/>
+          <t>⑧ S8-1</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
       <c r="F182" s="10" t="inlineStr">
         <is>
-          <t>通路を歩く。横移動で追う　［18-22秒］</t>
+          <t>映像が白に抜けて、ロゴだけが残る。ここで音も切る　［60秒］</t>
         </is>
       </c>
       <c r="G182" s="11" t="inlineStr"/>
@@ -4436,13 +4472,13 @@
       <c r="C183" s="7" t="inlineStr"/>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>① S5-3</t>
+          <t>⑧ S8-2</t>
         </is>
       </c>
       <c r="E183" s="7" t="inlineStr"/>
       <c r="F183" s="10" t="inlineStr">
         <is>
-          <t>会社の入口に着く　［18-22秒］</t>
+          <t>―　［60秒］</t>
         </is>
       </c>
       <c r="G183" s="11" t="inlineStr"/>
@@ -4456,200 +4492,20 @@
       <c r="C184" s="7" t="inlineStr"/>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>① S6-1</t>
+          <t>⑧ S8-3</t>
         </is>
       </c>
       <c r="E184" s="7" t="inlineStr"/>
       <c r="F184" s="10" t="inlineStr">
         <is>
-          <t>ロビーに入る　［22-27秒］</t>
+          <t>―　［60秒］</t>
         </is>
       </c>
       <c r="G184" s="11" t="inlineStr"/>
       <c r="H184" s="11" t="inlineStr"/>
     </row>
-    <row r="185" ht="32" customHeight="1">
-      <c r="A185" s="7" t="n">
-        <v>174</v>
-      </c>
-      <c r="B185" s="7" t="inlineStr"/>
-      <c r="C185" s="7" t="inlineStr"/>
-      <c r="D185" s="7" t="inlineStr">
-        <is>
-          <t>① S6-2</t>
-        </is>
-      </c>
-      <c r="E185" s="7" t="inlineStr"/>
-      <c r="F185" s="10" t="inlineStr">
-        <is>
-          <t>ロビーを歩く（引き）　［22-27秒］</t>
-        </is>
-      </c>
-      <c r="G185" s="11" t="inlineStr"/>
-      <c r="H185" s="11" t="inlineStr"/>
-    </row>
-    <row r="186" ht="32" customHeight="1">
-      <c r="A186" s="7" t="n">
-        <v>175</v>
-      </c>
-      <c r="B186" s="7" t="inlineStr"/>
-      <c r="C186" s="7" t="inlineStr"/>
-      <c r="D186" s="7" t="inlineStr">
-        <is>
-          <t>① S6-3</t>
-        </is>
-      </c>
-      <c r="E186" s="7" t="inlineStr"/>
-      <c r="F186" s="10" t="inlineStr">
-        <is>
-          <t>立ち止まる。ここが到着点　［22-27秒］</t>
-        </is>
-      </c>
-      <c r="G186" s="11" t="inlineStr"/>
-      <c r="H186" s="11" t="inlineStr"/>
-    </row>
-    <row r="187" ht="32" customHeight="1">
-      <c r="A187" s="7" t="n">
-        <v>176</v>
-      </c>
-      <c r="B187" s="8" t="inlineStr">
-        <is>
-          <t>締めカード</t>
-        </is>
-      </c>
-      <c r="C187" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。文字を組んで作る</t>
-        </is>
-      </c>
-      <c r="D187" s="7" t="inlineStr">
-        <is>
-          <t>⑥ S9-1</t>
-        </is>
-      </c>
-      <c r="E187" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
-      <c r="F187" s="10" t="inlineStr">
-        <is>
-          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
-        </is>
-      </c>
-      <c r="G187" s="11" t="inlineStr"/>
-      <c r="H187" s="11" t="inlineStr"/>
-    </row>
-    <row r="188" ht="32" customHeight="1">
-      <c r="A188" s="7" t="n">
-        <v>177</v>
-      </c>
-      <c r="B188" s="7" t="inlineStr"/>
-      <c r="C188" s="7" t="inlineStr"/>
-      <c r="D188" s="7" t="inlineStr">
-        <is>
-          <t>⑥ S9-2</t>
-        </is>
-      </c>
-      <c r="E188" s="7" t="inlineStr"/>
-      <c r="F188" s="10" t="inlineStr">
-        <is>
-          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
-        </is>
-      </c>
-      <c r="G188" s="11" t="inlineStr"/>
-      <c r="H188" s="11" t="inlineStr"/>
-    </row>
-    <row r="189" ht="32" customHeight="1">
-      <c r="A189" s="7" t="n">
-        <v>178</v>
-      </c>
-      <c r="B189" s="7" t="inlineStr"/>
-      <c r="C189" s="7" t="inlineStr"/>
-      <c r="D189" s="7" t="inlineStr">
-        <is>
-          <t>⑥ S9-3</t>
-        </is>
-      </c>
-      <c r="E189" s="7" t="inlineStr"/>
-      <c r="F189" s="10" t="inlineStr">
-        <is>
-          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
-        </is>
-      </c>
-      <c r="G189" s="11" t="inlineStr"/>
-      <c r="H189" s="11" t="inlineStr"/>
-    </row>
-    <row r="190" ht="32" customHeight="1">
-      <c r="A190" s="7" t="n">
-        <v>179</v>
-      </c>
-      <c r="B190" s="7" t="inlineStr"/>
-      <c r="C190" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。白に抜いてロゴだけ</t>
-        </is>
-      </c>
-      <c r="D190" s="7" t="inlineStr">
-        <is>
-          <t>⑧ S8-1</t>
-        </is>
-      </c>
-      <c r="E190" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
-      <c r="F190" s="10" t="inlineStr">
-        <is>
-          <t>映像が白に抜けて、ロゴだけが残る。ここで音も切る　［60秒］</t>
-        </is>
-      </c>
-      <c r="G190" s="11" t="inlineStr"/>
-      <c r="H190" s="11" t="inlineStr"/>
-    </row>
-    <row r="191" ht="32" customHeight="1">
-      <c r="A191" s="7" t="n">
-        <v>180</v>
-      </c>
-      <c r="B191" s="7" t="inlineStr"/>
-      <c r="C191" s="7" t="inlineStr"/>
-      <c r="D191" s="7" t="inlineStr">
-        <is>
-          <t>⑧ S8-2</t>
-        </is>
-      </c>
-      <c r="E191" s="7" t="inlineStr"/>
-      <c r="F191" s="10" t="inlineStr">
-        <is>
-          <t>―　［60秒］</t>
-        </is>
-      </c>
-      <c r="G191" s="11" t="inlineStr"/>
-      <c r="H191" s="11" t="inlineStr"/>
-    </row>
-    <row r="192" ht="32" customHeight="1">
-      <c r="A192" s="7" t="n">
-        <v>181</v>
-      </c>
-      <c r="B192" s="7" t="inlineStr"/>
-      <c r="C192" s="7" t="inlineStr"/>
-      <c r="D192" s="7" t="inlineStr">
-        <is>
-          <t>⑧ S8-3</t>
-        </is>
-      </c>
-      <c r="E192" s="7" t="inlineStr"/>
-      <c r="F192" s="10" t="inlineStr">
-        <is>
-          <t>―　［60秒］</t>
-        </is>
-      </c>
-      <c r="G192" s="11" t="inlineStr"/>
-      <c r="H192" s="11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A11:H192"/>
+  <autoFilter ref="A11:H184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ショットリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2126,7 +2126,7 @@
       <c r="E76" s="7" t="inlineStr"/>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の顔。確かめ終えて顔を上げる一瞬。テロップ「検品 Inspection」　［102-122秒］</t>
+          <t>Bロール：職人の顔。確かめ終えて顔を上げる一瞬。S2と同じ画角・同じ人で撮る。テロップ「検品 Inspection」　［102-122秒］</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr"/>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>フェンスに掛ける（引き・三脚で固定）。カメラは止めたまま、背景の街だけが動く　［0-6秒］</t>
+          <t>フェンスに掛ける（引き・三脚で固定）。カメラは止めたまま、背景の街だけが動く　［0-8秒］</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr"/>
@@ -3882,7 +3882,7 @@
       <c r="E155" s="7" t="inlineStr"/>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>柱の前。鞄を持って立つ（引き）　［0-6秒］</t>
+          <t>鞄を肩に掛けて立つ（横・引き）　［0-8秒］</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr"/>
@@ -3902,7 +3902,7 @@
       <c r="E156" s="7" t="inlineStr"/>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>全身の引き。顔は主役にしない　［0-6秒］</t>
+          <t>石壁の前。全身の引き。顔は主役にしない　［0-8秒］</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       <c r="E157" s="7" t="inlineStr"/>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄の口を開ける　［6-12秒］</t>
+          <t>真俯瞰。鞄の口を開ける　［8-15秒］</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr"/>
@@ -3942,7 +3942,7 @@
       <c r="E158" s="7" t="inlineStr"/>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。中身を整える手（寄り）　［6-12秒］</t>
+          <t>真俯瞰。中身を整える手（寄り）　［8-15秒］</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr"/>
@@ -3962,7 +3962,7 @@
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>手前に手すり。奥を歩く（前ボケでつなぐ）　［6-12秒］</t>
+          <t>次の画へ横にスライドしてつなぐ。参考動画のつなぎ方はこれ一つだけ。同じ画を細かく割らない　［8-15秒］</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr"/>
@@ -3982,7 +3982,7 @@
       <c r="E160" s="7" t="inlineStr"/>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>高い場所を歩く（引き・映画的）　［12-18秒］</t>
+          <t>高い通路を歩く（引き・映画的）　［15-22秒］</t>
         </is>
       </c>
       <c r="G160" s="11" t="inlineStr"/>
@@ -4002,7 +4002,7 @@
       <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>肩に掛かった鞄に寄る　［12-18秒］</t>
+          <t>肩に掛かった鞄に寄る　［15-22秒］</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr"/>
@@ -4022,7 +4022,7 @@
       <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>鞄と脚だけ（歩く）　［12-18秒］</t>
+          <t>鞄と脚だけ（歩く）　［15-22秒］</t>
         </is>
       </c>
       <c r="G162" s="11" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
       <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>手すりの前で立ち止まる　［18-24秒］</t>
+          <t>フェンスの前で立ち止まる　［22-30秒］</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr"/>
@@ -4062,7 +4062,7 @@
       <c r="E164" s="7" t="inlineStr"/>
       <c r="F164" s="10" t="inlineStr">
         <is>
-          <t>白い服が画面を横切る（つなぎ）　［18-24秒］</t>
+          <t>真俯瞰。鞄と持ち物・靴を並べる置き画。この画で終わる。参考動画に写っている他社の布袋と金具はぼかしてあります　［22-30秒］</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr"/>
@@ -4082,7 +4082,7 @@
       <c r="E165" s="7" t="inlineStr"/>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄と持ち物・靴を並べる置き画　［18-24秒］</t>
+          <t>そのままロゴだけ。テロップは出さない　［22-30秒］</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr"/>
@@ -4093,16 +4093,24 @@
         <v>155</v>
       </c>
       <c r="B166" s="7" t="inlineStr"/>
-      <c r="C166" s="7" t="inlineStr"/>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>通勤路の並木道（①・同じ画角を使い回す）</t>
+        </is>
+      </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>④ S5-1</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr"/>
+          <t>① S2-1</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>最初と同じフェンスの画角に戻る。一周して戻ってきたことが分かる　［24-30秒］</t>
+          <t>全体。ドアが開くと、もう別の服になっている。並木道を歩いてくる全身の引き（濃いグレー）。すまし顔　［5-8秒　｜　切り替わり＝玄関のドアが開く］</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr"/>
@@ -4116,13 +4124,13 @@
       <c r="C167" s="7" t="inlineStr"/>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>④ S5-2</t>
+          <t>① S2-2</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr"/>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>背景の街だけが動いている　［24-30秒］</t>
+          <t>腰より上。同じ人に寄る。鞄の色と表情が一度に見える　［5-8秒　｜　切り替わり＝玄関のドアが開く］</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr"/>
@@ -4136,13 +4144,13 @@
       <c r="C168" s="7" t="inlineStr"/>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>④ S5-3</t>
+          <t>① S3-1</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>ロゴのみ。テロップは出さない　［24-30秒］</t>
+          <t>全体。車が抜けると服も鞄の色も変わっている（白・ブルー）　［8-11秒　｜　切り替わり＝手前を車が横切る］</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr"/>
@@ -4153,24 +4161,16 @@
         <v>158</v>
       </c>
       <c r="B169" s="7" t="inlineStr"/>
-      <c r="C169" s="9" t="inlineStr">
-        <is>
-          <t>通勤路の並木道（①・同じ画角を使い回す）</t>
-        </is>
-      </c>
+      <c r="C169" s="7" t="inlineStr"/>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>① S2-1</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>① S3-2</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr"/>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>全体。ドアが開くと、もう別の服になっている。並木道を歩いてくる全身の引き（濃いグレー）。すまし顔　［5-8秒　｜　切り替わり＝玄関のドアが開く］</t>
+          <t>腰より上。サングラスを直す。ここは笑っている表情で　［8-11秒　｜　切り替わり＝手前を車が横切る］</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr"/>
@@ -4184,13 +4184,13 @@
       <c r="C170" s="7" t="inlineStr"/>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>① S2-2</t>
+          <t>① S4-1</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>腰より上。同じ人に寄る。鞄の色と表情が一度に見える　［5-8秒　｜　切り替わり＝玄関のドアが開く］</t>
+          <t>全体。木の幹が抜けると三色目。同じ並木道を奥から歩いてくる　［11-14秒　｜　切り替わり＝手前を木の幹が横切る（前ボケ）］</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr"/>
@@ -4204,13 +4204,13 @@
       <c r="C171" s="7" t="inlineStr"/>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>① S3-1</t>
+          <t>① S4-2</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>全体。車が抜けると服も鞄の色も変わっている（白・ブルー）　［8-11秒　｜　切り替わり＝手前を車が横切る］</t>
+          <t>腰より上。立ち止まって振り返る。帽子を押さえる仕草を入れる　［11-14秒　｜　切り替わり＝手前を木の幹が横切る（前ボケ）］</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr"/>
@@ -4221,16 +4221,24 @@
         <v>161</v>
       </c>
       <c r="B172" s="7" t="inlineStr"/>
-      <c r="C172" s="7" t="inlineStr"/>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>駅の構内（①）</t>
+        </is>
+      </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>① S3-2</t>
-        </is>
-      </c>
-      <c r="E172" s="7" t="inlineStr"/>
+          <t>① S5-1</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F172" s="10" t="inlineStr">
         <is>
-          <t>腰より上。サングラスを直す。ここは笑っている表情で　［8-11秒　｜　切り替わり＝手前を車が横切る］</t>
+          <t>全体。柱が抜けると場所が駅に変わり、四色目になっている（ブルー）　［14-18秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr"/>
@@ -4244,13 +4252,13 @@
       <c r="C173" s="7" t="inlineStr"/>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>① S4-1</t>
+          <t>① S5-2</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr"/>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>全体。木の幹が抜けると三色目。同じ並木道を奥から歩いてくる　［11-14秒　｜　切り替わり＝手前を木の幹が横切る（前ボケ）］</t>
+          <t>腰より上。構内を歩く。少し急ぎ足の表情　［14-18秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr"/>
@@ -4264,13 +4272,13 @@
       <c r="C174" s="7" t="inlineStr"/>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>① S4-2</t>
+          <t>① S6-1</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr"/>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>腰より上。立ち止まって振り返る。帽子を押さえる仕草を入れる　［11-14秒　｜　切り替わり＝手前を木の幹が横切る（前ボケ）］</t>
+          <t>全体。人が抜けると五色目（ピンク）。通路を横移動で追う　［18-21秒　｜　切り替わり＝手前を人が横切る］</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr"/>
@@ -4281,24 +4289,16 @@
         <v>164</v>
       </c>
       <c r="B175" s="7" t="inlineStr"/>
-      <c r="C175" s="9" t="inlineStr">
-        <is>
-          <t>駅の構内（①）</t>
-        </is>
-      </c>
+      <c r="C175" s="7" t="inlineStr"/>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>① S5-1</t>
-        </is>
-      </c>
-      <c r="E175" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>① S6-2</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr"/>
       <c r="F175" s="10" t="inlineStr">
         <is>
-          <t>全体。柱が抜けると場所が駅に変わり、四色目になっている（ブルー）　［14-18秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
+          <t>腰より上。入口に着く。顔を上げる　［18-21秒　｜　切り替わり＝手前を人が横切る］</t>
         </is>
       </c>
       <c r="G175" s="11" t="inlineStr"/>
@@ -4308,17 +4308,29 @@
       <c r="A176" s="7" t="n">
         <v>165</v>
       </c>
-      <c r="B176" s="7" t="inlineStr"/>
-      <c r="C176" s="7" t="inlineStr"/>
+      <c r="B176" s="8" t="inlineStr">
+        <is>
+          <t>締めカード</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。文字を組んで作る</t>
+        </is>
+      </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>① S5-2</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr"/>
+          <t>⑥ S9-1</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
       <c r="F176" s="10" t="inlineStr">
         <is>
-          <t>腰より上。構内を歩く。少し急ぎ足の表情　［14-18秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
+          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr"/>
@@ -4332,13 +4344,13 @@
       <c r="C177" s="7" t="inlineStr"/>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>① S6-1</t>
+          <t>⑥ S9-2</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr"/>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>全体。人が抜けると五色目（ピンク）。通路を横移動で追う　［18-21秒　｜　切り替わり＝手前を人が横切る］</t>
+          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
         </is>
       </c>
       <c r="G177" s="11" t="inlineStr"/>
@@ -4352,13 +4364,13 @@
       <c r="C178" s="7" t="inlineStr"/>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>① S6-2</t>
+          <t>⑥ S9-3</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr"/>
       <c r="F178" s="10" t="inlineStr">
         <is>
-          <t>腰より上。入口に着く。顔を上げる　［18-21秒　｜　切り替わり＝手前を人が横切る］</t>
+          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
         </is>
       </c>
       <c r="G178" s="11" t="inlineStr"/>
@@ -4368,19 +4380,15 @@
       <c r="A179" s="7" t="n">
         <v>168</v>
       </c>
-      <c r="B179" s="8" t="inlineStr">
-        <is>
-          <t>締めカード</t>
-        </is>
-      </c>
+      <c r="B179" s="7" t="inlineStr"/>
       <c r="C179" s="9" t="inlineStr">
         <is>
-          <t>撮影不要。文字を組んで作る</t>
+          <t>撮影不要。白に抜いてロゴだけ</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-1</t>
+          <t>⑧ S8-1</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr">
@@ -4390,7 +4398,7 @@
       </c>
       <c r="F179" s="10" t="inlineStr">
         <is>
-          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
+          <t>映像が白に抜けて、ロゴだけが残る。ここで音も切る　［60秒］</t>
         </is>
       </c>
       <c r="G179" s="11" t="inlineStr"/>
@@ -4404,13 +4412,13 @@
       <c r="C180" s="7" t="inlineStr"/>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-2</t>
+          <t>⑧ S8-2</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr"/>
       <c r="F180" s="10" t="inlineStr">
         <is>
-          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
+          <t>―　［60秒］</t>
         </is>
       </c>
       <c r="G180" s="11" t="inlineStr"/>
@@ -4424,88 +4432,20 @@
       <c r="C181" s="7" t="inlineStr"/>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-3</t>
+          <t>⑧ S8-3</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr"/>
       <c r="F181" s="10" t="inlineStr">
         <is>
-          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
+          <t>―　［60秒］</t>
         </is>
       </c>
       <c r="G181" s="11" t="inlineStr"/>
       <c r="H181" s="11" t="inlineStr"/>
     </row>
-    <row r="182" ht="32" customHeight="1">
-      <c r="A182" s="7" t="n">
-        <v>171</v>
-      </c>
-      <c r="B182" s="7" t="inlineStr"/>
-      <c r="C182" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。白に抜いてロゴだけ</t>
-        </is>
-      </c>
-      <c r="D182" s="7" t="inlineStr">
-        <is>
-          <t>⑧ S8-1</t>
-        </is>
-      </c>
-      <c r="E182" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
-      <c r="F182" s="10" t="inlineStr">
-        <is>
-          <t>映像が白に抜けて、ロゴだけが残る。ここで音も切る　［60秒］</t>
-        </is>
-      </c>
-      <c r="G182" s="11" t="inlineStr"/>
-      <c r="H182" s="11" t="inlineStr"/>
-    </row>
-    <row r="183" ht="32" customHeight="1">
-      <c r="A183" s="7" t="n">
-        <v>172</v>
-      </c>
-      <c r="B183" s="7" t="inlineStr"/>
-      <c r="C183" s="7" t="inlineStr"/>
-      <c r="D183" s="7" t="inlineStr">
-        <is>
-          <t>⑧ S8-2</t>
-        </is>
-      </c>
-      <c r="E183" s="7" t="inlineStr"/>
-      <c r="F183" s="10" t="inlineStr">
-        <is>
-          <t>―　［60秒］</t>
-        </is>
-      </c>
-      <c r="G183" s="11" t="inlineStr"/>
-      <c r="H183" s="11" t="inlineStr"/>
-    </row>
-    <row r="184" ht="32" customHeight="1">
-      <c r="A184" s="7" t="n">
-        <v>173</v>
-      </c>
-      <c r="B184" s="7" t="inlineStr"/>
-      <c r="C184" s="7" t="inlineStr"/>
-      <c r="D184" s="7" t="inlineStr">
-        <is>
-          <t>⑧ S8-3</t>
-        </is>
-      </c>
-      <c r="E184" s="7" t="inlineStr"/>
-      <c r="F184" s="10" t="inlineStr">
-        <is>
-          <t>―　［60秒］</t>
-        </is>
-      </c>
-      <c r="G184" s="11" t="inlineStr"/>
-      <c r="H184" s="11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A11:H184"/>
+  <autoFilter ref="A11:H181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -3114,7 +3114,7 @@
       <c r="E121" s="7" t="inlineStr"/>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>棚から商品を手に取る（寄り）。店員の手だけ。参考になる映像がないので写真は入れていない　［52-63秒］</t>
+          <t>ショーウィンドウ越しに店内を見せる。外から見た店の顔。S2の「今の外観」と同じ写真です（画角の参考として同じものを当てています）。棚から商品を手に取る寄りも撮っておく　［52-63秒］</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ショットリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -666,7 +666,7 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>くさがやさん。この一カットだけ画に映る。横顔、空いた側に見出しテロップ。声は次のカットにかぶったまま続く　［52-63秒］</t>
+          <t>くさがやさん。この一カットだけ画に映る。横顔、空いた側に見出しテロップ。声は次のカットにかぶったまま続く。　［52-63秒］</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr"/>
@@ -762,7 +762,7 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>佐藤さん。この一カットだけ画に映る。引き、背景に工房。声は次のカットにかぶったまま続く　［38-52秒］</t>
+          <t>佐藤さん。この一カットだけ画に映る。引き、背景に工房。声は次のカットにかぶったまま続く。　［38-52秒］</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr"/>
@@ -830,7 +830,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>佐藤さん。工房案内のはじまり。引き、背景に工房。ここから最後まで、佐藤さんの声が画の上に流れ続ける　［0-10秒］</t>
+          <t>佐藤さん。工房案内のはじまり。引き、背景に工房。ここから最後まで、佐藤さんの声が画の上に流れ続ける。　［0-10秒］</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr"/>
@@ -850,7 +850,7 @@
       <c r="E20" s="7" t="inlineStr"/>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>佐藤さん。話し終わる瞬間。バストショットに寄る。言い終えて口を閉じるところまで残す　［122-133秒］</t>
+          <t>佐藤さん。話し終わる瞬間。バストショットに寄る。言い終えて口を閉じるところまで残す。　［122-133秒］</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr"/>
@@ -918,7 +918,7 @@
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>永尾社長。この一カットだけ画に映る。バストショット、顔の下に役職テロップ。声は次のシーンにかぶったまま続く　［0-6秒］</t>
+          <t>永尾社長。この一カットだけ画に映る。バストショット、顔の下に役職テロップ。声は次のシーンにかぶったまま続く。　［0-6秒］</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr"/>
@@ -938,7 +938,7 @@
       <c r="E24" s="7" t="inlineStr"/>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>永尾社長。締めの一言。冒頭と同じ画角に戻し、頭と終わりで挟む。この一本で言いたいことを、本人の言葉で置く　［70-75秒］</t>
+          <t>永尾社長。締めの一言。冒頭と同じ画角に戻し、頭と終わりで挟む。この一本で言いたいことを、本人の言葉で置く。　［70-75秒］</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>バストショット。窓を背にして、手前に植物を置いてボカす。名前は出さず「使っている人」として自己紹介。話した言葉をそのままテロップで出す　［11-19秒］</t>
+          <t>バストショット。窓を背にして、手前に植物を置いてボカす。名前は出さず「使っている人」として自己紹介。話した言葉をそのままテロップで出す。　［11-19秒］</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr"/>
@@ -1046,7 +1046,7 @@
       <c r="E29" s="7" t="inlineStr"/>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>インタビューに戻る。同じ画角。カメラは一度も動かさない　［19-28秒］</t>
+          <t>インタビューに戻る。同じ画角。カメラは一度も動かさない。　［19-28秒］</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       <c r="E30" s="7" t="inlineStr"/>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>インタビューに戻る。表情のアップ。買ってから変わったことを一言で　［38-50秒］</t>
+          <t>インタビューに戻る。表情のアップ。買ってから変わったことを一言で。　［38-50秒］</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>バードアイショット。東京の空から降り、向島の街と工房を見つける　［0-6秒］</t>
+          <t>バードアイショット。東京の空から降り、向島の街と工房を見つける。　［0-6秒］</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr"/>
@@ -1138,7 +1138,7 @@
       <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>バードアイショット。上から降りて、向島の工房を見つける　［0-10秒］</t>
+          <t>バードアイショット。上から降りて、向島の工房を見つける。　［0-10秒］</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
       <c r="E34" s="7" t="inlineStr"/>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>高度を下げ、建物の全景へ。街の音　［0-10秒］</t>
+          <t>高度を下げ、建物の全景へ。街の音。　［0-10秒］</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr"/>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>入口を抜けて中へ。工房の全景（引き）。規模が分かる画角　［10-25秒］</t>
+          <t>入口を抜けて中へ。工房の全景（引き）。規模が分かる画角。　［10-25秒］</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
       <c r="E36" s="7" t="inlineStr"/>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>機械と人が同じ画面に入る。台数と人数が分かる　［10-25秒］</t>
+          <t>機械と人が同じ画面に入る。台数と人数が分かる。　［10-25秒］</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>棚に革が色ごとに並ぶ。扱える革の種類と量がそのまま伝わる　［25-42秒］</t>
+          <t>棚に革が色ごとに並ぶ。扱える革の種類と量がそのまま伝わる。　［25-42秒］</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr"/>
@@ -1282,7 +1282,7 @@
       <c r="E39" s="7" t="inlineStr"/>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>金型・型紙が品番ごとに並ぶ。手が一つを抜き出す　［25-42秒］</t>
+          <t>金型・型紙が品番ごとに並ぶ。手が一つを抜き出す。　［25-42秒］</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>超マクロ。刃が革に入る瞬間。何を見ているか分からない距離。「スッ」と抜ける一音だけ。BGMは鳴らさない　［0-5秒］</t>
+          <t>超マクロ。刃が革に入る瞬間。何を見ているか分からない距離。「スッ」と抜ける一音だけ。BGMは鳴らさない。　［0-5秒］</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
       <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>切り終わり。断面がまだ生成りのまま残っている　［0-5秒］</t>
+          <t>切り終わり。断面がまだ生成りのまま残っている。　［0-5秒］</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
       <c r="E44" s="7" t="inlineStr"/>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。金属定規を当てて直線を一気に引く　［5-11秒］</t>
+          <t>真俯瞰。金属定規を当てて直線を一気に引く。　［5-11秒］</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       <c r="E49" s="7" t="inlineStr"/>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>裁ち上がったパーツが並ぶ。量産も少量も同じ場所でできる　［42-62秒］</t>
+          <t>裁ち上がったパーツが並ぶ。量産も少量も同じ場所でできる。　［42-62秒］</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>目打ちで縫う位置に印をつける　［11-17秒］</t>
+          <t>目打ちで縫う位置に印をつける。　［11-17秒］</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>等間隔に並んだ穴だけが画面に残る　［11-17秒］</t>
+          <t>等間隔に並んだ穴だけが画面に残る。　［11-17秒］</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>ボール盤で金具用の穴をあける　［17-22秒］</t>
+          <t>ボール盤で金具用の穴をあける。　［17-22秒］</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr"/>
@@ -1622,7 +1622,7 @@
       <c r="E54" s="7" t="inlineStr"/>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>カシメを打つ。金属が革に沈む一音　［17-22秒］</t>
+          <t>カシメを打つ。金属が革に沈む一音。　［17-22秒］</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>刻印を押す。斜めから光を当てて、窪みに影を作る　［17-22秒］</t>
+          <t>刻印を押す。斜めから光を当てて、窪みに影を作る。　［17-22秒］</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr"/>
@@ -1730,7 +1730,7 @@
       <c r="E59" s="7" t="inlineStr"/>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>Bロール：職人の目だけの超マクロ。手元を見ている目に寄る。テロップは出さない　［62-82秒］</t>
+          <t>Bロール：職人の目だけの超マクロ。手元を見ている目に寄る。テロップは出さない。　［62-82秒］</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr"/>
@@ -1802,7 +1802,7 @@
       <c r="E62" s="7" t="inlineStr"/>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>両手が生地を送り、縫い進める（引き寄り）。手の動きと機械の音が同時に入る　［82-102秒］</t>
+          <t>両手が生地を送り、縫い進める（引き寄り）。手の動きと機械の音が同時に入る。　［82-102秒］</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
       <c r="E65" s="7" t="inlineStr"/>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>縫い目に沿って仕上げる。手の動きだけを見せる　［22-28秒］</t>
+          <t>縫い目に沿って仕上げる。手の動きだけを見せる。　［22-28秒］</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr"/>
@@ -1922,7 +1922,7 @@
       <c r="E67" s="7" t="inlineStr"/>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>この一本の見せ場。塗った側と塗っていない側が同じ画面に入る。長回し・カットを割らない　［28-34秒］</t>
+          <t>この一本の見せ場。塗った側と塗っていない側が同じ画面に入る。長回し・カットを割らない。　［28-34秒］</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
       <c r="E68" s="7" t="inlineStr"/>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>塗り終わり。同じ画角のまま断面の色が変わりきっている　［28-34秒］</t>
+          <t>塗り終わり。同じ画角のまま断面の色が変わりきっている。　［28-34秒］</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr"/>
@@ -1962,7 +1962,7 @@
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>ヘラで仕上げ剤を薄く伸ばす　［34-38秒］</t>
+          <t>ヘラで仕上げ剤を薄く伸ばす。　［34-38秒］</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr"/>
@@ -1982,7 +1982,7 @@
       <c r="E70" s="7" t="inlineStr"/>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>超マクロ。コバを磨く。摩擦音　［34-38秒］</t>
+          <t>超マクロ。コバを磨く。摩擦音。　［34-38秒］</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
       <c r="E71" s="7" t="inlineStr"/>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>磨き終わった断面に、光が一本だけ走る　［34-38秒］</t>
+          <t>磨き終わった断面に、光が一本だけ走る。　［34-38秒］</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr"/>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>大型の機械が動いている（引き）。設備の規模がそのまま伝わる　［38-52秒］</t>
+          <t>大型の機械が動いている（引き）。設備の規模がそのまま伝わる。　［38-52秒］</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr"/>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>一点を手に取り、光にかざす。作業音が消える　［102-122秒］</t>
+          <t>一点を手に取り、光にかざす。作業音が消える。　［102-122秒］</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr"/>
@@ -2106,7 +2106,7 @@
       <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>手に取って開き、内側と縫い目まで確かめる（寄り）。片方の手で押さえ、もう片方でめくる　［102-122秒］</t>
+          <t>手に取って開き、内側と縫い目まで確かめる（寄り）。片方の手で押さえ、もう片方でめくる。　［102-122秒］</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>白手袋で包む。手元の寄り。不織布の角を折る。紙の音　［122-133秒］</t>
+          <t>白手袋で包む。手元の寄り。不織布の角を折る。紙の音。　［122-133秒］</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr"/>
@@ -2230,7 +2230,7 @@
       <c r="E80" s="7" t="inlineStr"/>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>型紙・図面の俯瞰　［29-38秒］</t>
+          <t>型紙・図面の俯瞰。　［29-38秒］</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr"/>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>色見本を見ながら打ち合わせる。二人で同じものを覗き込む（俯瞰気味）。企画はここから始まる　［20-29秒］</t>
+          <t>色見本を見ながら打ち合わせる。二人で同じものを覗き込む（俯瞰気味）。企画はここから始まる。　［20-29秒］</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr"/>
@@ -2298,7 +2298,7 @@
       <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>革を並べて色を決める。扱える色数がそのまま伝わる　［20-29秒］</t>
+          <t>革を並べて色を決める。扱える色数がそのまま伝わる。　［20-29秒］</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr"/>
@@ -2390,7 +2390,7 @@
       <c r="E87" s="7" t="inlineStr"/>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>同じ構図のまま、今の外観へ。昔の店先からそのまま移り変わる。白黒からカラーに変わる　［6-20秒］</t>
+          <t>同じ構図のまま、今の外観へ。昔の店先からそのまま移り変わる。白黒からカラーに変わる。　［6-20秒］</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr"/>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>真っ黒。細い光の帯が一本だけ立つ　［0-4秒］</t>
+          <t>真っ黒。細い光の帯が一本だけ立つ。　［0-4秒］</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr"/>
@@ -2442,7 +2442,7 @@
       <c r="E89" s="7" t="inlineStr"/>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>光の帯がゆっくり動く。無音から低いBGMが立ち上がる　［0-4秒］</t>
+          <t>光の帯がゆっくり動く。無音から低いBGMが立ち上がる。　［0-4秒］</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
       <c r="E91" s="7" t="inlineStr"/>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>作業台に革を置く。奥に染料と道具が並ぶ　［4-8秒］</t>
+          <t>作業台に革を置く。奥に染料と道具が並ぶ。　［4-8秒］</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr"/>
@@ -2502,7 +2502,7 @@
       <c r="E92" s="7" t="inlineStr"/>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>二枚を合わせて位置を決める。腕時計・指輪は外す　［4-8秒］</t>
+          <t>二枚を合わせて位置を決める。腕時計・指輪は外す。　［4-8秒］</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr"/>
@@ -2522,7 +2522,7 @@
       <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>合わせた革を押さえる。ここから形になっていく　［4-8秒］</t>
+          <t>合わせた革を押さえる。ここから形になっていく。　［4-8秒］</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr"/>
@@ -2542,7 +2542,7 @@
       <c r="E94" s="7" t="inlineStr"/>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>手だけ。革を折る　［8-15秒］</t>
+          <t>手だけ。革を折る。　［8-15秒］</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr"/>
@@ -2582,7 +2582,7 @@
       <c r="E96" s="7" t="inlineStr"/>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>角が立ち上がる。顔と工房は一切映さない　［8-15秒］</t>
+          <t>角が立ち上がる。顔と工房は一切映さない。　［8-15秒］</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr"/>
@@ -2602,7 +2602,7 @@
       <c r="E97" s="7" t="inlineStr"/>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>白手袋で金具を持つ。金属が触れる音　［15-19秒］</t>
+          <t>白手袋で金具を持つ。金属が触れる音。　［15-19秒］</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
       <c r="E98" s="7" t="inlineStr"/>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>金具を取り付ける（超マクロ）。カチリと一音　［15-19秒］</t>
+          <t>金具を取り付ける（超マクロ）。カチリと一音。　［15-19秒］</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr"/>
@@ -2642,7 +2642,7 @@
       <c r="E99" s="7" t="inlineStr"/>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>指が金具の縁をなぞる　［15-19秒］</t>
+          <t>指が金具の縁をなぞる。　［15-19秒］</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       <c r="E100" s="7" t="inlineStr"/>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>完成品を持ち上げる　［19-28秒］</t>
+          <t>完成品を持ち上げる。　［19-28秒］</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr"/>
@@ -2682,7 +2682,7 @@
       <c r="E101" s="7" t="inlineStr"/>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>道具の前に置く。上から一灯だけ　［19-28秒］</t>
+          <t>道具の前に置く。上から一灯だけ。　［19-28秒］</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr"/>
@@ -2702,7 +2702,7 @@
       <c r="E102" s="7" t="inlineStr"/>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>金具のマクロ → BGMが止まる → ロゴのみ。テロップは出さない　［19-28秒］</t>
+          <t>金具のマクロ → BGMが止まる → ロゴのみ。テロップは出さない。　［19-28秒］</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr"/>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>① S8-1</t>
+          <t>① S7-1</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>人がフレームから出る。置かれた小物だけが残る　［25-30秒］</t>
+          <t>人がフレームから出る。置かれた小物だけが残る。　［25-30秒］</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr"/>
@@ -2748,13 +2748,13 @@
       <c r="C104" s="7" t="inlineStr"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>① S8-2</t>
+          <t>① S7-2</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr"/>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>五色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る　［25-30秒］</t>
+          <t>五色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る。　［25-30秒］</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr"/>
@@ -2768,13 +2768,13 @@
       <c r="C105" s="7" t="inlineStr"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>① S8-3</t>
+          <t>① S7-3</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr"/>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>そのままロゴ。締めのテロップは出さない　［25-30秒］</t>
+          <t>そのままロゴ。締めのテロップは出さない。　［25-30秒］</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr"/>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>机に鞄が一つ置いてある。正面固定の引き。手前に入れるものが並べてある　［0-4秒］</t>
+          <t>机に鞄が一つ置いてある。正面固定の引き。手前に入れるものが並べてある。　［0-4秒］</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
       <c r="E107" s="7" t="inlineStr"/>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>ここから最後までこの画角のまま。三品番とも同じ位置に置く　［0-4秒］</t>
+          <t>ここから最後までこの画角のまま。三品番とも同じ位置に置く。　［0-4秒］</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr"/>
@@ -2842,7 +2842,7 @@
       <c r="E108" s="7" t="inlineStr"/>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>人が入ってきて、鞄の口を開ける。中は空。顔は入れない　［0-4秒］</t>
+          <t>人が入ってきて、鞄の口を開ける。中は空。顔は入れない。　［0-4秒］</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr"/>
@@ -2862,7 +2862,7 @@
       <c r="E109" s="7" t="inlineStr"/>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>A4書類とノートPCを入れる　［4-10秒］</t>
+          <t>A4書類とノートPCを入れる。　［4-10秒］</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr"/>
@@ -2882,7 +2882,7 @@
       <c r="E110" s="7" t="inlineStr"/>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>ノートPCが底まで収まる。入れる音を拾う　［4-10秒］</t>
+          <t>ノートPCが底まで収まる。入れる音を拾う。　［4-10秒］</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr"/>
@@ -2902,7 +2902,7 @@
       <c r="E111" s="7" t="inlineStr"/>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>手帳・鍵・サングラス　［4-10秒］</t>
+          <t>手帳・鍵・サングラス。　［4-10秒］</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
       <c r="E112" s="7" t="inlineStr"/>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>ペン・小物。入れる音を一つずつ拾う　［10-15秒］</t>
+          <t>ペン・小物。入れる音を一つずつ拾う。　［10-15秒］</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr"/>
@@ -2942,7 +2942,7 @@
       <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>傘・水筒まで入れる。それでもまだ閉まる　［10-15秒］</t>
+          <t>傘・水筒まで入れる。それでもまだ閉まる。　［10-15秒］</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
       <c r="E114" s="7" t="inlineStr"/>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>最後の一つを入れる。ここで手が止まる　［10-15秒］</t>
+          <t>最後の一つを入れる。ここで手が止まる。　［10-15秒］</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr"/>
@@ -2982,7 +2982,7 @@
       <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>持ち手をまとめて持ち上げる　［15-20秒］</t>
+          <t>持ち手をまとめて持ち上げる。　［15-20秒］</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr"/>
@@ -3002,7 +3002,7 @@
       <c r="E116" s="7" t="inlineStr"/>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>肩に掛けて、そのままフレームの外へ出ていく。台は動かさない　［15-20秒］</t>
+          <t>肩に掛けて、そのままフレームの外へ出ていく。台は動かさない。　［15-20秒］</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr"/>
@@ -3022,7 +3022,7 @@
       <c r="E117" s="7" t="inlineStr"/>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>人も鞄もフレームから出て、何も乗っていない机だけが残る。参考動画と同じ終わり方　［20-25秒］</t>
+          <t>人も鞄もフレームから出て、何も乗っていない机だけが残る。参考動画と同じ終わり方。　［20-25秒］</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr"/>
@@ -3062,7 +3062,7 @@
       <c r="E119" s="7" t="inlineStr"/>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>ロゴ。三品番とも同じ終わり方にする　［20-25秒］</t>
+          <t>ロゴ。三品番とも同じ終わり方にする。　［20-25秒］</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr"/>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>店内（引き）。ショーケースと棚が並ぶ。ロゴが入る位置まで見せる　［52-63秒］</t>
+          <t>店内（引き）。ショーケースと棚が並ぶ。ロゴが入る位置まで見せる。　［52-63秒］</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr"/>
@@ -3114,7 +3114,7 @@
       <c r="E121" s="7" t="inlineStr"/>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>ショーウィンドウ越しに店内を見せる。外から見た店の顔。S2の「今の外観」と同じ写真です（画角の参考として同じものを当てています）。棚から商品を手に取る寄りも撮っておく　［52-63秒］</t>
+          <t>ショーウィンドウ越しに店内を見せる。外から見た店の顔。S2の「今の外観」と同じ写真です（画角の参考として同じものを当てています）。棚から商品を手に取る寄りも撮っておく。　［52-63秒］</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr"/>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>商品の寄り。できあがった瞬間　［5-11秒］</t>
+          <t>商品の寄り。できあがった瞬間。　［5-11秒］</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr"/>
@@ -3162,7 +3162,7 @@
       <c r="E123" s="7" t="inlineStr"/>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>商品の真俯瞰。並べて撮る　［5-11秒］</t>
+          <t>商品の真俯瞰。並べて撮る。　［5-11秒］</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr"/>
@@ -3182,7 +3182,7 @@
       <c r="E124" s="7" t="inlineStr"/>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>空間。窓際と光。ここまで人の顔は出さない　［5-11秒］</t>
+          <t>空間。窓際と光。ここまで人の顔は出さない。　［5-11秒］</t>
         </is>
       </c>
       <c r="G124" s="11" t="inlineStr"/>
@@ -3222,7 +3222,7 @@
       <c r="E126" s="7" t="inlineStr"/>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>商品の寄り。話している内容に合わせて切り替える　［11-19秒］</t>
+          <t>商品の寄り。話している内容に合わせて切り替える。　［11-19秒］</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr"/>
@@ -3242,7 +3242,7 @@
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>声の上にBロール。空間の引き　［19-28秒］</t>
+          <t>声の上にBロール。空間の引き。　［19-28秒］</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr"/>
@@ -3262,7 +3262,7 @@
       <c r="E128" s="7" t="inlineStr"/>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>窓辺の一枚。間を作る　［19-28秒］</t>
+          <t>窓辺の一枚。間を作る。　［19-28秒］</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr"/>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>外観のロー。空を入れて見上げる。ロゴを重ねる　［0-5秒］</t>
+          <t>外観のロー。空を入れて見上げる。ロゴを重ねる。　［0-5秒］</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr"/>
@@ -3310,7 +3310,7 @@
       <c r="E130" s="7" t="inlineStr"/>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>外観の全景（引き）。入口に人が立つ　［0-5秒］</t>
+          <t>外観の全景（引き）。入口に人が立つ。　［0-5秒］</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr"/>
@@ -3378,7 +3378,7 @@
       <c r="E133" s="7" t="inlineStr"/>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>手を振って見送る。カメラは動かさない　［50-60秒］</t>
+          <t>手を振って見送る。カメラは動かさない。　［50-60秒］</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr"/>
@@ -3398,7 +3398,7 @@
       <c r="E134" s="7" t="inlineStr"/>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>同じ引きの画面の中央に、ロゴが重なる　［50-60秒］</t>
+          <t>同じ引きの画面の中央に、ロゴが重なる。　［50-60秒］</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr"/>
@@ -3450,7 +3450,7 @@
       <c r="E136" s="7" t="inlineStr"/>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>落ち着いた場所での一枚　［28-38秒］</t>
+          <t>落ち着いた場所での一枚。　［28-38秒］</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr"/>
@@ -3470,7 +3470,7 @@
       <c r="E137" s="7" t="inlineStr"/>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>外に出る。空を入れて気分を変える　［28-38秒］</t>
+          <t>外に出る。空を入れて気分を変える。　［28-38秒］</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr"/>
@@ -3490,7 +3490,7 @@
       <c r="E138" s="7" t="inlineStr"/>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>外の引きに人が入る。声はそのまま続く　［38-50秒］</t>
+          <t>外の引きに人が入る。声はそのまま続く。　［38-50秒］</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr"/>
@@ -3510,7 +3510,7 @@
       <c r="E139" s="7" t="inlineStr"/>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>窓辺に戻る。静かな一枚。台本にない一言を拾う　［38-50秒］</t>
+          <t>窓辺に戻る。静かな一枚。台本にない一言を拾う。　［38-50秒］</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr"/>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>作業机ではなく、使われている場所に置く → テロップ → ロゴ　［38-40秒］</t>
+          <t>作業机ではなく、使われている場所に置く → テロップ → ロゴ。　［38-40秒］</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr"/>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>会計。カウンターで店員が応対する。二人が同じ画面に入る　［63-70秒］</t>
+          <t>会計。カウンターで店員が応対する。二人が同じ画面に入る。　［63-70秒］</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr"/>
@@ -3626,7 +3626,7 @@
       <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>手渡される瞬間と、受け取った人の笑顔。渡す側と受け取る側を一つの画に入れる　［63-70秒］</t>
+          <t>手渡される瞬間と、受け取った人の笑顔。渡す側と受け取る側を一つの画に入れる。　［63-70秒］</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr"/>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>声が終わり、音が引く。ロゴだけ。テロップは出さない　［70-75秒］</t>
+          <t>声が終わり、音が引く。ロゴだけ。テロップは出さない。　［70-75秒］</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr"/>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>① S7-1</t>
+          <t>① S6-1</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>全体。柱が抜けるとロビー。立ち止まる。ここが到着点　［21-25秒　｜　切り替わり＝手前をロビーの柱が横切る］</t>
+          <t>全体。柱が抜けるとロビー。立ち止まる。ここが到着点。　［21-25秒　｜　切り替わり＝手前をロビーの柱が横切る］</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
       <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>① S7-2</t>
+          <t>① S6-2</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>腰より上。肩の鞄を掛け直して笑う。三十秒でいちばん明るい表情　［21-25秒　｜　切り替わり＝手前をロビーの柱が横切る］</t>
+          <t>腰より上。肩の鞄を掛け直して笑う。三十秒でいちばん明るい表情。　［21-25秒　｜　切り替わり＝手前をロビーの柱が横切る］</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr"/>
@@ -3759,7 +3759,7 @@
       <c r="B150" s="7" t="inlineStr"/>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>自宅の玄関まわり（①）</t>
+          <t>自宅の玄関まわり（①・一色目）</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>キーケースの寄りで始まる。初めはピントを外しておく。そこへ手が入って取り上げ、ピントが合う　［0-5秒］</t>
+          <t>キーケースの寄りで始まる。初めはピントを外しておく。そこへ手が入って取り上げ、ピントが合う。　［0-5秒］</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>鏡の前。鞄を肩に当てて合わせる。身支度をしているところ　［0-5秒］</t>
+          <t>鏡の前。鞄を肩に当てて合わせる。身支度をしているところ。　［0-5秒］</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr"/>
@@ -3814,7 +3814,7 @@
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>玄関のドアに手をかけて開ける（後ろ姿・逆光）　［0-5秒］</t>
+          <t>玄関のドアに手をかけて開ける（後ろ姿・逆光）。　［0-5秒］</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr"/>
@@ -3834,7 +3834,7 @@
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>ドアが開くと、もう別の服になっている。同じ玄関、違う人・違う色。この一本の決まりごとを、いちばん最初に見せてしまう　［0-5秒］</t>
+          <t>ドアが開くと、もう別の服になっている。同じ玄関、違う人。この一本の決まりごとを、いちばん最初に見せてしまう。　［0-5秒］</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr"/>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>フェンスに掛ける（引き・三脚で固定）。カメラは止めたまま、背景の街だけが動く　［0-8秒］</t>
+          <t>フェンスに掛ける（引き・三脚で固定）。カメラは止めたまま、背景の街だけが動く。　［0-8秒］</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr"/>
@@ -3902,7 +3902,7 @@
       <c r="E156" s="7" t="inlineStr"/>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>石壁の前。全身の引き。顔は主役にしない　［0-8秒］</t>
+          <t>石壁の前。全身の引き。顔は主役にしない。　［0-8秒］</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       <c r="E157" s="7" t="inlineStr"/>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄の口を開ける　［8-15秒］</t>
+          <t>真俯瞰。鞄の口を開ける。　［8-15秒］</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr"/>
@@ -3962,7 +3962,7 @@
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>次の画へ横にスライドしてつなぐ。参考動画のつなぎ方はこれ一つだけ。同じ画を細かく割らない　［8-15秒］</t>
+          <t>次の画へ横にスライドしてつなぐ。参考動画のつなぎ方はこれ一つだけ。同じ画を細かく割らない。　［8-15秒］</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr"/>
@@ -4002,7 +4002,7 @@
       <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>肩に掛かった鞄に寄る　［15-22秒］</t>
+          <t>肩に掛かった鞄に寄る。　［15-22秒］</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
       <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>フェンスの前で立ち止まる　［22-30秒］</t>
+          <t>フェンスの前で立ち止まる。　［22-30秒］</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr"/>
@@ -4062,7 +4062,7 @@
       <c r="E164" s="7" t="inlineStr"/>
       <c r="F164" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄と持ち物・靴を並べる置き画。この画で終わる。参考動画に写っている他社の布袋と金具はぼかしてあります　［22-30秒］</t>
+          <t>真俯瞰。鞄と持ち物・靴を並べる置き画。この画で終わる。参考動画に写っている他社の布袋と金具はぼかしてあります。　［22-30秒］</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr"/>
@@ -4082,7 +4082,7 @@
       <c r="E165" s="7" t="inlineStr"/>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>そのままロゴだけ。テロップは出さない　［22-30秒］</t>
+          <t>そのままロゴだけ。テロップは出さない。　［22-30秒］</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr"/>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>全体。ドアが開くと、もう別の服になっている。並木道を歩いてくる全身の引き（濃いグレー）。すまし顔　［5-8秒　｜　切り替わり＝玄関のドアが開く］</t>
+          <t>全体。そのまま通勤路へ。並木道を歩いてくる全身の引き。すまし顔。　［5-9秒　｜　切り替わり＝玄関のドアが開く］</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
       <c r="E167" s="7" t="inlineStr"/>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>腰より上。同じ人に寄る。鞄の色と表情が一度に見える　［5-8秒　｜　切り替わり＝玄関のドアが開く］</t>
+          <t>腰より上。同じ人に寄る。鞄の色と表情が一度に見える。　［5-9秒　｜　切り替わり＝玄関のドアが開く］</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr"/>
@@ -4150,7 +4150,7 @@
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>全体。車が抜けると服も鞄の色も変わっている（白・ブルー）　［8-11秒　｜　切り替わり＝手前を車が横切る］</t>
+          <t>全体。車が抜けると、服も鞄の色も変わっている。　［9-13秒　｜　切り替わり＝手前を車が横切る］</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr"/>
@@ -4170,7 +4170,7 @@
       <c r="E169" s="7" t="inlineStr"/>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>腰より上。サングラスを直す。ここは笑っている表情で　［8-11秒　｜　切り替わり＝手前を車が横切る］</t>
+          <t>腰より上。サングラスを直す。ここは笑っている表情で。　［9-13秒　｜　切り替わり＝手前を車が横切る］</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr"/>
@@ -4181,16 +4181,24 @@
         <v>159</v>
       </c>
       <c r="B170" s="7" t="inlineStr"/>
-      <c r="C170" s="7" t="inlineStr"/>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>駅の構内（①）</t>
+        </is>
+      </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
           <t>① S4-1</t>
         </is>
       </c>
-      <c r="E170" s="7" t="inlineStr"/>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>全体。木の幹が抜けると三色目。同じ並木道を奥から歩いてくる　［11-14秒　｜　切り替わり＝手前を木の幹が横切る（前ボケ）］</t>
+          <t>全体。柱が抜けると、場所が駅に変わっている。　［13-17秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr"/>
@@ -4210,7 +4218,7 @@
       <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>腰より上。立ち止まって振り返る。帽子を押さえる仕草を入れる　［11-14秒　｜　切り替わり＝手前を木の幹が横切る（前ボケ）］</t>
+          <t>腰より上。構内を歩く。少し急ぎ足の表情。　［13-17秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr"/>
@@ -4221,24 +4229,16 @@
         <v>161</v>
       </c>
       <c r="B172" s="7" t="inlineStr"/>
-      <c r="C172" s="9" t="inlineStr">
-        <is>
-          <t>駅の構内（①）</t>
-        </is>
-      </c>
+      <c r="C172" s="7" t="inlineStr"/>
       <c r="D172" s="7" t="inlineStr">
         <is>
           <t>① S5-1</t>
         </is>
       </c>
-      <c r="E172" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+      <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="10" t="inlineStr">
         <is>
-          <t>全体。柱が抜けると場所が駅に変わり、四色目になっている（ブルー）　［14-18秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
+          <t>全体。人が抜けると五色目。通路を横移動で追う。　［17-21秒　｜　切り替わり＝手前を人が横切る］</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr"/>
@@ -4258,7 +4258,7 @@
       <c r="E173" s="7" t="inlineStr"/>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>腰より上。構内を歩く。少し急ぎ足の表情　［14-18秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
+          <t>腰より上。入口に着く。顔を上げる。　［17-21秒　｜　切り替わり＝手前を人が横切る］</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr"/>
@@ -4268,17 +4268,29 @@
       <c r="A174" s="7" t="n">
         <v>163</v>
       </c>
-      <c r="B174" s="7" t="inlineStr"/>
-      <c r="C174" s="7" t="inlineStr"/>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>締めカード</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。文字を組んで作る</t>
+        </is>
+      </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>① S6-1</t>
-        </is>
-      </c>
-      <c r="E174" s="7" t="inlineStr"/>
+          <t>⑥ S9-1</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>全体。人が抜けると五色目（ピンク）。通路を横移動で追う　［18-21秒　｜　切り替わり＝手前を人が横切る］</t>
+          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr"/>
@@ -4292,13 +4304,13 @@
       <c r="C175" s="7" t="inlineStr"/>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>① S6-2</t>
+          <t>⑥ S9-2</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr"/>
       <c r="F175" s="10" t="inlineStr">
         <is>
-          <t>腰より上。入口に着く。顔を上げる　［18-21秒　｜　切り替わり＝手前を人が横切る］</t>
+          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え。　［133-140秒］</t>
         </is>
       </c>
       <c r="G175" s="11" t="inlineStr"/>
@@ -4308,29 +4320,17 @@
       <c r="A176" s="7" t="n">
         <v>165</v>
       </c>
-      <c r="B176" s="8" t="inlineStr">
-        <is>
-          <t>締めカード</t>
-        </is>
-      </c>
-      <c r="C176" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。文字を組んで作る</t>
-        </is>
-      </c>
+      <c r="B176" s="7" t="inlineStr"/>
+      <c r="C176" s="7" t="inlineStr"/>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-1</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
+          <t>⑥ S9-3</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr"/>
       <c r="F176" s="10" t="inlineStr">
         <is>
-          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
+          <t>白に反転してロゴだけ。無音版はここでBGMも切る。　［133-140秒］</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr"/>
@@ -4341,16 +4341,24 @@
         <v>166</v>
       </c>
       <c r="B177" s="7" t="inlineStr"/>
-      <c r="C177" s="7" t="inlineStr"/>
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。白に抜いてロゴだけ</t>
+        </is>
+      </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-2</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="inlineStr"/>
+          <t>⑧ S8-1</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え　［133-140秒］</t>
+          <t>映像が白に抜けて、ロゴだけが残る。ここで音も切る。　［60秒］</t>
         </is>
       </c>
       <c r="G177" s="11" t="inlineStr"/>
@@ -4364,13 +4372,13 @@
       <c r="C178" s="7" t="inlineStr"/>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-3</t>
+          <t>⑧ S8-2</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr"/>
       <c r="F178" s="10" t="inlineStr">
         <is>
-          <t>白に反転してロゴだけ。無音版はここでBGMも切る　［133-140秒］</t>
+          <t>―　［60秒］</t>
         </is>
       </c>
       <c r="G178" s="11" t="inlineStr"/>
@@ -4381,71 +4389,23 @@
         <v>168</v>
       </c>
       <c r="B179" s="7" t="inlineStr"/>
-      <c r="C179" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。白に抜いてロゴだけ</t>
-        </is>
-      </c>
+      <c r="C179" s="7" t="inlineStr"/>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>⑧ S8-1</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
+          <t>⑧ S8-3</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr"/>
       <c r="F179" s="10" t="inlineStr">
         <is>
-          <t>映像が白に抜けて、ロゴだけが残る。ここで音も切る　［60秒］</t>
+          <t>―　［60秒］</t>
         </is>
       </c>
       <c r="G179" s="11" t="inlineStr"/>
       <c r="H179" s="11" t="inlineStr"/>
     </row>
-    <row r="180" ht="32" customHeight="1">
-      <c r="A180" s="7" t="n">
-        <v>169</v>
-      </c>
-      <c r="B180" s="7" t="inlineStr"/>
-      <c r="C180" s="7" t="inlineStr"/>
-      <c r="D180" s="7" t="inlineStr">
-        <is>
-          <t>⑧ S8-2</t>
-        </is>
-      </c>
-      <c r="E180" s="7" t="inlineStr"/>
-      <c r="F180" s="10" t="inlineStr">
-        <is>
-          <t>―　［60秒］</t>
-        </is>
-      </c>
-      <c r="G180" s="11" t="inlineStr"/>
-      <c r="H180" s="11" t="inlineStr"/>
-    </row>
-    <row r="181" ht="32" customHeight="1">
-      <c r="A181" s="7" t="n">
-        <v>170</v>
-      </c>
-      <c r="B181" s="7" t="inlineStr"/>
-      <c r="C181" s="7" t="inlineStr"/>
-      <c r="D181" s="7" t="inlineStr">
-        <is>
-          <t>⑧ S8-3</t>
-        </is>
-      </c>
-      <c r="E181" s="7" t="inlineStr"/>
-      <c r="F181" s="10" t="inlineStr">
-        <is>
-          <t>―　［60秒］</t>
-        </is>
-      </c>
-      <c r="G181" s="11" t="inlineStr"/>
-      <c r="H181" s="11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A11:H181"/>
+  <autoFilter ref="A11:H179"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>超マクロ。刃が革に入る瞬間。何を見ているか分からない距離。「スッ」と抜ける一音だけ。BGMは鳴らさない。　［0-5秒］</t>
+          <t>マクロ。刃が革に入る瞬間。「スッ」と抜ける一音だけ。BGM小さく。　［0-5秒］</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>等間隔に並んだ穴だけが画面に残る。　［11-17秒］</t>
+          <t>アップにして再度穴を開ける。　［11-17秒］</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr"/>
@@ -1622,7 +1622,7 @@
       <c r="E54" s="7" t="inlineStr"/>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>カシメを打つ。金属が革に沈む一音。　［17-22秒］</t>
+          <t>ラインを引く。金属が革に沈む一音。　［17-22秒］</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
       <c r="E65" s="7" t="inlineStr"/>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>縫い目に沿って仕上げる。手の動きだけを見せる。　［22-28秒］</t>
+          <t>焼く。糸の端を焼いて留める。　［22-28秒］</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr"/>
@@ -2602,7 +2602,7 @@
       <c r="E97" s="7" t="inlineStr"/>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>白手袋で金具を持つ。金属が触れる音。　［15-19秒］</t>
+          <t>白手袋で金具を革に取り付ける。金属が触れる音。　［15-19秒］</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
       <c r="E98" s="7" t="inlineStr"/>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>金具を取り付ける（超マクロ）。カチリと一音。　［15-19秒］</t>
+          <t>取り付いた金具を手に取って確かめる（超マクロ）。カチリと一音。　［15-19秒］</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       <c r="E100" s="7" t="inlineStr"/>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>完成品を持ち上げる。　［19-28秒］</t>
+          <t>工房の奥、道具の前で完成品を持ち上げる。ここだけ背景に道具が入る。　［19-28秒］</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr"/>
@@ -2682,7 +2682,7 @@
       <c r="E101" s="7" t="inlineStr"/>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>道具の前に置く。上から一灯だけ。　［19-28秒］</t>
+          <t>黒い背景に戻り、完成品を両手で持つ。上から一灯だけ。　［19-28秒］</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr"/>
@@ -2702,7 +2702,7 @@
       <c r="E102" s="7" t="inlineStr"/>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>金具のマクロ → BGMが止まる → ロゴのみ。テロップは出さない。　［19-28秒］</t>
+          <t>BGMが止まる → ロゴのみ。テロップは出さない。　［19-28秒］</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>人がフレームから出る。置かれた小物だけが残る。　［25-30秒］</t>
+          <t>バッグのアップショット。　［25-30秒］</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr"/>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>全体。柱が抜けるとロビー。立ち止まる。ここが到着点。　［21-25秒　｜　切り替わり＝手前をロビーの柱が横切る］</t>
+          <t>全体。柱が抜けるとロビー。立ち止まる。ここが到着点。最初のファッションに戻る。　［21-25秒　｜　切り替わり＝手前をロビーの柱が横切る］</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr"/>
@@ -3962,7 +3962,7 @@
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>次の画へ横にスライドしてつなぐ。参考動画のつなぎ方はこれ一つだけ。同じ画を細かく割らない。　［8-15秒］</t>
+          <t>次の画へ横にスライドしてつなぐ。参考動画のつなぎ方はこれ一つだけ。　［8-15秒］</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr"/>

--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ショットリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ショットリスト'!$A$11:$H$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>コラボの実績から入る。年号テロップを次々に重ねる（1980 SHIPS ／ 1982 BEAMS ／ 1984 To Boot New York ／ 1990 UNITED ARROWS ／ 1991 Paul Smith ／ 2011 RALPH LAUREN）　［6-20秒］</t>
+          <t>コラボの実績から入る。年号テロップを画面の右端に次々に重ねる（1980 SHIPS ／ 1982 BEAMS ／ 1984 To Boot New York ／ 1990 UNITED ARROWS ／ 1991 Paul Smith ／ 2011 RALPH LAUREN）　［6-20秒］</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr"/>
@@ -2370,7 +2370,7 @@
       <c r="E86" s="7" t="inlineStr"/>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>昔の外観。実績を並べたあと、はじまりの店先に戻る。テロップ「1979　東京千駄ヶ谷にて創業」（画面上部の英字はサイト側の見出し。実際は年号テロップだけを載せる）　［6-20秒］</t>
+          <t>昔の外観。実績を並べたあと、はじまりの店先に戻る。テロップ「1979　東京千駄ヶ谷にて創業」を右端に出す。（画面上部の英字はサイト側の見出し。実際は年号テロップだけを載せる）　［6-20秒］</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr"/>
@@ -2542,7 +2542,7 @@
       <c r="E94" s="7" t="inlineStr"/>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>手だけ。革を折る。　［8-15秒］</t>
+          <t>手だけ。革を折り上げる。暗がりに革の面だけが浮く。　［8-15秒］</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr"/>
@@ -2582,7 +2582,7 @@
       <c r="E96" s="7" t="inlineStr"/>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>角が立ち上がる。顔と工房は一切映さない。　［8-15秒］</t>
+          <t>角が立ち上がる。ここまで顔は一切映さない。　［8-15秒］</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr"/>
@@ -2642,7 +2642,7 @@
       <c r="E99" s="7" t="inlineStr"/>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>指が金具の縁をなぞる。　［15-19秒］</t>
+          <t>取り付いた金具の寄り。ここだけ光が回った明るい画にする。　［15-19秒］</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr"/>
@@ -2702,7 +2702,7 @@
       <c r="E102" s="7" t="inlineStr"/>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>BGMが止まる → ロゴのみ。テロップは出さない。　［19-28秒］</t>
+          <t>完成品が工房の作業台に立つ。道具に囲まれた引き。ここが着地点。　［19-28秒］</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr"/>
@@ -2712,29 +2712,17 @@
       <c r="A103" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>白台・物撮り</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>五色を並べる（①の締め）</t>
-        </is>
-      </c>
+      <c r="B103" s="7" t="inlineStr"/>
+      <c r="C103" s="7" t="inlineStr"/>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>① S7-1</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／照明1灯／白台</t>
-        </is>
-      </c>
+          <t>③ S5-4</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr"/>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>バッグのアップショット。　［25-30秒］</t>
+          <t>BGMが止まる → ロゴのみ。テロップは出さない。　［19-28秒］</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr"/>
@@ -2744,17 +2732,29 @@
       <c r="A104" s="7" t="n">
         <v>93</v>
       </c>
-      <c r="B104" s="7" t="inlineStr"/>
-      <c r="C104" s="7" t="inlineStr"/>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>白台・物撮り</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>五色を並べる（①の締め）</t>
+        </is>
+      </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>① S7-2</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr"/>
+          <t>① S7-1</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／照明1灯／白台</t>
+        </is>
+      </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>五色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る。　［25-30秒］</t>
+          <t>バッグのアップショット。　［25-30秒］</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr"/>
@@ -2768,13 +2768,13 @@
       <c r="C105" s="7" t="inlineStr"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>① S7-3</t>
+          <t>① S7-2</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr"/>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>そのままロゴ。締めのテロップは出さない。　［25-30秒］</t>
+          <t>五色が並ぶ。この画にテロップ「同じ道を、違う私で。」を重ね、ナレーション「毎日をカラフルに」が一言だけ入る。　［25-30秒］</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr"/>
@@ -2785,24 +2785,16 @@
         <v>95</v>
       </c>
       <c r="B106" s="7" t="inlineStr"/>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>白い台・正面固定（⑦専用・三品番を同じ画角で）</t>
-        </is>
-      </c>
+      <c r="C106" s="7" t="inlineStr"/>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>⑦ S1-1</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／マクロレンズ／照明1灯／白台／レフ板</t>
-        </is>
-      </c>
+          <t>① S7-3</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr"/>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>机に鞄が一つ置いてある。正面固定の引き。手前に入れるものが並べてある。　［0-4秒］</t>
+          <t>そのままロゴ。締めのテロップは出さない。　［25-30秒］</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr"/>
@@ -2813,16 +2805,24 @@
         <v>96</v>
       </c>
       <c r="B107" s="7" t="inlineStr"/>
-      <c r="C107" s="7" t="inlineStr"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>白い台・正面固定（⑦専用・三品番を同じ画角で）</t>
+        </is>
+      </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>⑦ S1-2</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr"/>
+          <t>⑦ S1-1</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／マクロレンズ／照明1灯／白台／レフ板</t>
+        </is>
+      </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>ここから最後までこの画角のまま。三品番とも同じ位置に置く。　［0-4秒］</t>
+          <t>机に鞄が一つ置いてある。正面固定の引き。手前に入れるものが並べてある。　［0-4秒］</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr"/>
@@ -2836,13 +2836,13 @@
       <c r="C108" s="7" t="inlineStr"/>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>⑦ S1-3</t>
+          <t>⑦ S1-2</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr"/>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>人が入ってきて、鞄の口を開ける。中は空。顔は入れない。　［0-4秒］</t>
+          <t>ここから最後までこの画角のまま。三品番とも同じ位置に置く。　［0-4秒］</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr"/>
@@ -2856,13 +2856,13 @@
       <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>⑦ S2-1</t>
+          <t>⑦ S1-3</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr"/>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>A4書類とノートPCを入れる。　［4-10秒］</t>
+          <t>人が入ってきて、鞄の口を開ける。中は空。顔は入れない。　［0-4秒］</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr"/>
@@ -2876,13 +2876,13 @@
       <c r="C110" s="7" t="inlineStr"/>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>⑦ S2-2</t>
+          <t>⑦ S2-1</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr"/>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>ノートPCが底まで収まる。入れる音を拾う。　［4-10秒］</t>
+          <t>A4書類とノートPCを入れる。　［4-10秒］</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr"/>
@@ -2896,13 +2896,13 @@
       <c r="C111" s="7" t="inlineStr"/>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>⑦ S2-3</t>
+          <t>⑦ S2-2</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr"/>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>手帳・鍵・サングラス。　［4-10秒］</t>
+          <t>ノートPCが底まで収まる。入れる音を拾う。　［4-10秒］</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr"/>
@@ -2916,13 +2916,13 @@
       <c r="C112" s="7" t="inlineStr"/>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>⑦ S3-1</t>
+          <t>⑦ S2-3</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr"/>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>ペン・小物。入れる音を一つずつ拾う。　［10-15秒］</t>
+          <t>手帳・鍵・サングラス。　［4-10秒］</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr"/>
@@ -2936,13 +2936,13 @@
       <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>⑦ S3-2</t>
+          <t>⑦ S3-1</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>傘・水筒まで入れる。それでもまだ閉まる。　［10-15秒］</t>
+          <t>ペン・小物。入れる音を一つずつ拾う。　［10-15秒］</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr"/>
@@ -2956,13 +2956,13 @@
       <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>⑦ S3-3</t>
+          <t>⑦ S3-2</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr"/>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>最後の一つを入れる。ここで手が止まる。　［10-15秒］</t>
+          <t>傘・水筒まで入れる。それでもまだ閉まる。　［10-15秒］</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr"/>
@@ -2976,13 +2976,13 @@
       <c r="C115" s="7" t="inlineStr"/>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>⑦ S4-1</t>
+          <t>⑦ S3-3</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>持ち手をまとめて持ち上げる。　［15-20秒］</t>
+          <t>最後の一つを入れる。ここで手が止まる。　［10-15秒］</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr"/>
@@ -2996,13 +2996,13 @@
       <c r="C116" s="7" t="inlineStr"/>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>⑦ S4-2</t>
+          <t>⑦ S4-1</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr"/>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>肩に掛けて、そのままフレームの外へ出ていく。台は動かさない。　［15-20秒］</t>
+          <t>持ち手をまとめて持ち上げる。　［15-20秒］</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr"/>
@@ -3016,13 +3016,13 @@
       <c r="C117" s="7" t="inlineStr"/>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>⑦ S5-1</t>
+          <t>⑦ S4-2</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr"/>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>人も鞄もフレームから出て、何も乗っていない机だけが残る。参考動画と同じ終わり方。　［20-25秒］</t>
+          <t>肩に掛けて、そのままフレームの外へ出ていく。台は動かさない。　［15-20秒］</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr"/>
@@ -3036,13 +3036,13 @@
       <c r="C118" s="7" t="inlineStr"/>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>⑦ S5-2</t>
+          <t>⑦ S5-1</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr"/>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>その画にテロップを重ねる「支度も、仕事も、スマートに。」　［20-25秒］</t>
+          <t>人も鞄もフレームから出て、何も乗っていない机だけが残る。参考動画と同じ終わり方。　［20-25秒］</t>
         </is>
       </c>
       <c r="G118" s="11" t="inlineStr"/>
@@ -3056,13 +3056,13 @@
       <c r="C119" s="7" t="inlineStr"/>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>⑦ S5-3</t>
+          <t>⑦ S5-2</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr"/>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>ロゴ。三品番とも同じ終わり方にする。　［20-25秒］</t>
+          <t>その画にテロップを重ねる「支度も、仕事も、スマートに。」　［20-25秒］</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr"/>
@@ -3072,29 +3072,17 @@
       <c r="A120" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>店舗</t>
-        </is>
-      </c>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>BROOKLYN MUSEUM 店舗（⑤⑧共通）</t>
-        </is>
-      </c>
+      <c r="B120" s="7" t="inlineStr"/>
+      <c r="C120" s="7" t="inlineStr"/>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>⑤ S6-2</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／ガンマイク</t>
-        </is>
-      </c>
+          <t>⑦ S5-3</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr"/>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>店内（引き）。ショーケースと棚が並ぶ。ロゴが入る位置まで見せる。　［52-63秒］</t>
+          <t>ロゴ。三品番とも同じ終わり方にする。　［20-25秒］</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr"/>
@@ -3104,17 +3092,29 @@
       <c r="A121" s="7" t="n">
         <v>110</v>
       </c>
-      <c r="B121" s="7" t="inlineStr"/>
-      <c r="C121" s="7" t="inlineStr"/>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>店舗</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>BROOKLYN MUSEUM 店舗（⑤⑧共通）</t>
+        </is>
+      </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>⑤ S6-3</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr"/>
+          <t>⑤ S6-2</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／ガンマイク</t>
+        </is>
+      </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>ショーウィンドウ越しに店内を見せる。外から見た店の顔。S2の「今の外観」と同じ写真です（画角の参考として同じものを当てています）。棚から商品を手に取る寄りも撮っておく。　［52-63秒］</t>
+          <t>店内（引き）。ショーケースと棚が並ぶ。ロゴが入る位置まで見せる。　［52-63秒］</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr"/>
@@ -3125,24 +3125,16 @@
         <v>111</v>
       </c>
       <c r="B122" s="7" t="inlineStr"/>
-      <c r="C122" s="9" t="inlineStr">
-        <is>
-          <t>商品と空間（⑧のつかみ）</t>
-        </is>
-      </c>
+      <c r="C122" s="7" t="inlineStr"/>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-1</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／マクロレンズ／照明1灯</t>
-        </is>
-      </c>
+          <t>⑤ S6-3</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr"/>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>商品の寄り。できあがった瞬間。　［5-11秒］</t>
+          <t>ショーウィンドウ越しに店内を見せる。外から見た店の顔。S2の「今の外観」と同じ写真です（画角の参考として同じものを当てています）。棚から商品を手に取る寄りも撮っておく。　［52-63秒］</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr"/>
@@ -3153,16 +3145,24 @@
         <v>112</v>
       </c>
       <c r="B123" s="7" t="inlineStr"/>
-      <c r="C123" s="7" t="inlineStr"/>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>商品と空間（⑧のつかみ）</t>
+        </is>
+      </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-2</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr"/>
+          <t>⑧ S2-1</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／マクロレンズ／照明1灯</t>
+        </is>
+      </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>商品の真俯瞰。並べて撮る。　［5-11秒］</t>
+          <t>商品の寄り。できあがった瞬間。　［5-11秒］</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr"/>
@@ -3176,13 +3176,13 @@
       <c r="C124" s="7" t="inlineStr"/>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>⑧ S2-3</t>
+          <t>⑧ S2-2</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr"/>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>空間。窓際と光。ここまで人の顔は出さない。　［5-11秒］</t>
+          <t>商品の真俯瞰。並べて撮る。　［5-11秒］</t>
         </is>
       </c>
       <c r="G124" s="11" t="inlineStr"/>
@@ -3196,13 +3196,13 @@
       <c r="C125" s="7" t="inlineStr"/>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-2</t>
+          <t>⑧ S2-3</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr"/>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>ここから画はBロールに変わるが、声はそのまま流し続ける（引き）　［11-19秒］</t>
+          <t>空間。窓際と光。ここまで人の顔は出さない。　［5-11秒］</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr"/>
@@ -3216,13 +3216,13 @@
       <c r="C126" s="7" t="inlineStr"/>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>⑧ S3-3</t>
+          <t>⑧ S3-2</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr"/>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>商品の寄り。話している内容に合わせて切り替える。　［11-19秒］</t>
+          <t>ここから画はBロールに変わるが、声はそのまま流し続ける（引き）　［11-19秒］</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr"/>
@@ -3236,13 +3236,13 @@
       <c r="C127" s="7" t="inlineStr"/>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-2</t>
+          <t>⑧ S3-3</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>声の上にBロール。空間の引き。　［19-28秒］</t>
+          <t>商品の寄り。話している内容に合わせて切り替える。　［11-19秒］</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr"/>
@@ -3256,13 +3256,13 @@
       <c r="C128" s="7" t="inlineStr"/>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>⑧ S4-3</t>
+          <t>⑧ S4-2</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr"/>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>窓辺の一枚。間を作る。　［19-28秒］</t>
+          <t>声の上にBロール。空間の引き。　［19-28秒］</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr"/>
@@ -3273,24 +3273,16 @@
         <v>118</v>
       </c>
       <c r="B129" s="7" t="inlineStr"/>
-      <c r="C129" s="9" t="inlineStr">
-        <is>
-          <t>外観と作っているところ（⑧のつかみ）</t>
-        </is>
-      </c>
+      <c r="C129" s="7" t="inlineStr"/>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-1</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>⑧ S4-3</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr"/>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>外観のロー。空を入れて見上げる。ロゴを重ねる。　［0-5秒］</t>
+          <t>窓辺の一枚。間を作る。　［19-28秒］</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr"/>
@@ -3301,16 +3293,24 @@
         <v>119</v>
       </c>
       <c r="B130" s="7" t="inlineStr"/>
-      <c r="C130" s="7" t="inlineStr"/>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>外観と作っているところ（⑧のつかみ）</t>
+        </is>
+      </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-2</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="inlineStr"/>
+          <t>⑧ S1-1</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>外観の全景（引き）。入口に人が立つ。　［0-5秒］</t>
+          <t>外観のロー。空を入れて見上げる。ロゴを重ねる。　［0-5秒］</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr"/>
@@ -3324,13 +3324,13 @@
       <c r="C131" s="7" t="inlineStr"/>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>⑧ S1-3</t>
+          <t>⑧ S1-2</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr"/>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>作っているところ。手元だけ（寄り）　［0-5秒］</t>
+          <t>外観の全景（引き）。入口に人が立つ。　［0-5秒］</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr"/>
@@ -3341,24 +3341,16 @@
         <v>121</v>
       </c>
       <c r="B132" s="7" t="inlineStr"/>
-      <c r="C132" s="9" t="inlineStr">
-        <is>
-          <t>見送り（⑧の締め）</t>
-        </is>
-      </c>
+      <c r="C132" s="7" t="inlineStr"/>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>⑧ S7-1</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>⑧ S1-3</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr"/>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>店の前。スタッフが出てくる（引き）　［50-60秒］</t>
+          <t>作っているところ。手元だけ（寄り）　［0-5秒］</t>
         </is>
       </c>
       <c r="G132" s="11" t="inlineStr"/>
@@ -3369,16 +3361,24 @@
         <v>122</v>
       </c>
       <c r="B133" s="7" t="inlineStr"/>
-      <c r="C133" s="7" t="inlineStr"/>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>見送り（⑧の締め）</t>
+        </is>
+      </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>⑧ S7-2</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="inlineStr"/>
+          <t>⑧ S7-1</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>手を振って見送る。カメラは動かさない。　［50-60秒］</t>
+          <t>店の前。スタッフが出てくる（引き）　［50-60秒］</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr"/>
@@ -3392,13 +3392,13 @@
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>⑧ S7-3</t>
+          <t>⑧ S7-2</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr"/>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>同じ引きの画面の中央に、ロゴが重なる。　［50-60秒］</t>
+          <t>手を振って見送る。カメラは動かさない。　［50-60秒］</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr"/>
@@ -3408,29 +3408,17 @@
       <c r="A135" s="7" t="n">
         <v>124</v>
       </c>
-      <c r="B135" s="8" t="inlineStr">
-        <is>
-          <t>お客様・街</t>
-        </is>
-      </c>
-      <c r="C135" s="9" t="inlineStr">
-        <is>
-          <t>使っている場面（⑧）</t>
-        </is>
-      </c>
+      <c r="B135" s="7" t="inlineStr"/>
+      <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-1</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S7-3</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr"/>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>別の場所へ移る（引き）　［28-38秒］</t>
+          <t>同じ引きの画面の中央に、ロゴが重なる。　［50-60秒］</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr"/>
@@ -3440,17 +3428,29 @@
       <c r="A136" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="B136" s="7" t="inlineStr"/>
-      <c r="C136" s="7" t="inlineStr"/>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>お客様・街</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>使っている場面（⑧）</t>
+        </is>
+      </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-2</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr"/>
+          <t>⑧ S5-1</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>落ち着いた場所での一枚。　［28-38秒］</t>
+          <t>別の場所へ移る（引き）　［28-38秒］</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr"/>
@@ -3464,13 +3464,13 @@
       <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>⑧ S5-3</t>
+          <t>⑧ S5-2</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr"/>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>外に出る。空を入れて気分を変える。　［28-38秒］</t>
+          <t>落ち着いた場所での一枚。　［28-38秒］</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr"/>
@@ -3484,13 +3484,13 @@
       <c r="C138" s="7" t="inlineStr"/>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-2</t>
+          <t>⑧ S5-3</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr"/>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>外の引きに人が入る。声はそのまま続く。　［38-50秒］</t>
+          <t>外に出る。空を入れて気分を変える。　［28-38秒］</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr"/>
@@ -3504,13 +3504,13 @@
       <c r="C139" s="7" t="inlineStr"/>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>⑧ S6-3</t>
+          <t>⑧ S6-2</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr"/>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>窓辺に戻る。静かな一枚。台本にない一言を拾う。　［38-50秒］</t>
+          <t>外の引きに人が入る。声はそのまま続く。　［38-50秒］</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr"/>
@@ -3521,24 +3521,16 @@
         <v>129</v>
       </c>
       <c r="B140" s="7" t="inlineStr"/>
-      <c r="C140" s="9" t="inlineStr">
-        <is>
-          <t>使われている場所（②の締め）</t>
-        </is>
-      </c>
+      <c r="C140" s="7" t="inlineStr"/>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>② S8-1</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑧ S6-3</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr"/>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>作業机ではなく、使われている場所に置く → テロップ → ロゴ。　［38-40秒］</t>
+          <t>窓辺に戻る。静かな一枚。台本にない一言を拾う。　［38-50秒］</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr"/>
@@ -3549,16 +3541,24 @@
         <v>130</v>
       </c>
       <c r="B141" s="7" t="inlineStr"/>
-      <c r="C141" s="7" t="inlineStr"/>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>使われている場所（②の締め）</t>
+        </is>
+      </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>② S8-2</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr"/>
+          <t>② S8-1</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>―　［38-40秒］</t>
+          <t>作業机ではなく、使われている場所に置く → テロップ → ロゴ。　［38-40秒］</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr"/>
@@ -3572,7 +3572,7 @@
       <c r="C142" s="7" t="inlineStr"/>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>② S8-3</t>
+          <t>② S8-2</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr"/>
@@ -3589,24 +3589,16 @@
         <v>132</v>
       </c>
       <c r="B143" s="7" t="inlineStr"/>
-      <c r="C143" s="9" t="inlineStr">
-        <is>
-          <t>受け取りと使用（⑤⑧共通）</t>
-        </is>
-      </c>
+      <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-1</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>② S8-3</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>会計。カウンターで店員が応対する。二人が同じ画面に入る。　［63-70秒］</t>
+          <t>―　［38-40秒］</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr"/>
@@ -3617,16 +3609,24 @@
         <v>133</v>
       </c>
       <c r="B144" s="7" t="inlineStr"/>
-      <c r="C144" s="7" t="inlineStr"/>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>受け取りと使用（⑤⑧共通）</t>
+        </is>
+      </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-2</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="inlineStr"/>
+          <t>⑤ S7-1</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>手渡される瞬間と、受け取った人の笑顔。渡す側と受け取る側を一つの画に入れる。　［63-70秒］</t>
+          <t>会計。カウンターで店員が応対する。二人が同じ画面に入る。　［63-70秒］</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr"/>
@@ -3640,13 +3640,13 @@
       <c r="C145" s="7" t="inlineStr"/>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>⑤ S7-3</t>
+          <t>⑤ S7-2</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr"/>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>実際に使われている手元。ノートPCを入れる。ここで永尾社長の声がもう一度入りはじめる（Jカット）　［63-70秒］</t>
+          <t>手渡される瞬間と、受け取った人の笑顔。渡す側と受け取る側を一つの画に入れる。　［63-70秒］</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr"/>
@@ -3657,24 +3657,16 @@
         <v>135</v>
       </c>
       <c r="B146" s="7" t="inlineStr"/>
-      <c r="C146" s="9" t="inlineStr">
-        <is>
-          <t>締め（⑤）</t>
-        </is>
-      </c>
+      <c r="C146" s="7" t="inlineStr"/>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-2</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚</t>
-        </is>
-      </c>
+          <t>⑤ S7-3</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr"/>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>声が終わり、音が引く。ロゴだけ。テロップは出さない。　［70-75秒］</t>
+          <t>実際に使われている手元。ノートPCを入れる。ここで永尾社長の声がもう一度入りはじめる（Jカット）　［63-70秒］</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr"/>
@@ -3685,16 +3677,24 @@
         <v>136</v>
       </c>
       <c r="B147" s="7" t="inlineStr"/>
-      <c r="C147" s="7" t="inlineStr"/>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>締め（⑤）</t>
+        </is>
+      </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>⑤ S8-3</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="inlineStr"/>
+          <t>⑤ S8-2</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚</t>
+        </is>
+      </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>―　［70-75秒］</t>
+          <t>声が終わり、音が引く。ロゴだけ。テロップは出さない。　［70-75秒］</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr"/>
@@ -3704,29 +3704,17 @@
       <c r="A148" s="7" t="n">
         <v>137</v>
       </c>
-      <c r="B148" s="8" t="inlineStr">
-        <is>
-          <t>屋外・街</t>
-        </is>
-      </c>
-      <c r="C148" s="9" t="inlineStr">
-        <is>
-          <t>会社のロビー（①の到着点）</t>
-        </is>
-      </c>
+      <c r="B148" s="7" t="inlineStr"/>
+      <c r="C148" s="7" t="inlineStr"/>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>① S6-1</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>⑤ S8-3</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr"/>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>全体。柱が抜けるとロビー。立ち止まる。ここが到着点。最初のファッションに戻る。　［21-25秒　｜　切り替わり＝手前をロビーの柱が横切る］</t>
+          <t>―　［70-75秒］</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr"/>
@@ -3736,17 +3724,29 @@
       <c r="A149" s="7" t="n">
         <v>138</v>
       </c>
-      <c r="B149" s="7" t="inlineStr"/>
-      <c r="C149" s="7" t="inlineStr"/>
+      <c r="B149" s="8" t="inlineStr">
+        <is>
+          <t>屋外・街</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>会社のロビー（①の到着点）</t>
+        </is>
+      </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>① S6-2</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr"/>
+          <t>① S6-1</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>腰より上。肩の鞄を掛け直して笑う。三十秒でいちばん明るい表情。　［21-25秒　｜　切り替わり＝手前をロビーの柱が横切る］</t>
+          <t>全体。柱が抜けるとロビー。立ち止まる。ここが到着点。最初のファッションに戻る。　［21-25秒　｜　切り替わり＝手前をロビーの柱が横切る］</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr"/>
@@ -3757,24 +3757,16 @@
         <v>139</v>
       </c>
       <c r="B150" s="7" t="inlineStr"/>
-      <c r="C150" s="9" t="inlineStr">
-        <is>
-          <t>自宅の玄関まわり（①・一色目）</t>
-        </is>
-      </c>
+      <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>① S1-1</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>① S6-2</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t>キーケースの寄りで始まる。初めはピントを外しておく。そこへ手が入って取り上げ、ピントが合う。　［0-5秒］</t>
+          <t>腰より上。肩の鞄を掛け直して笑う。三十秒でいちばん明るい表情。　［21-25秒　｜　切り替わり＝手前をロビーの柱が横切る］</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr"/>
@@ -3785,16 +3777,24 @@
         <v>140</v>
       </c>
       <c r="B151" s="7" t="inlineStr"/>
-      <c r="C151" s="7" t="inlineStr"/>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>自宅の玄関まわり（①・一色目）</t>
+        </is>
+      </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>① S1-2</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="inlineStr"/>
+          <t>① S1-1</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t>鏡の前。鞄を肩に当てて合わせる。身支度をしているところ。　［0-5秒］</t>
+          <t>キーケースの寄りで始まる。初めはピントを外しておく。そこへ手が入って取り上げ、ピントが合う。　［0-5秒］</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr"/>
@@ -3808,13 +3808,13 @@
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>① S1-3</t>
+          <t>① S1-2</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>玄関のドアに手をかけて開ける（後ろ姿・逆光）。　［0-5秒］</t>
+          <t>鏡の前。鞄を肩に当てて合わせる。身支度をしているところ。　［0-5秒］</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr"/>
@@ -3828,13 +3828,13 @@
       <c r="C153" s="7" t="inlineStr"/>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>① S1-4</t>
+          <t>① S1-3</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>ドアが開くと、もう別の服になっている。同じ玄関、違う人。この一本の決まりごとを、いちばん最初に見せてしまう。　［0-5秒］</t>
+          <t>玄関のドアに手をかけて開ける（後ろ姿・逆光）。　［0-5秒］</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr"/>
@@ -3845,24 +3845,16 @@
         <v>143</v>
       </c>
       <c r="B154" s="7" t="inlineStr"/>
-      <c r="C154" s="9" t="inlineStr">
-        <is>
-          <t>街歩き・夕方の斜光（④）</t>
-        </is>
-      </c>
+      <c r="C154" s="7" t="inlineStr"/>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>④ S1-1</t>
-        </is>
-      </c>
-      <c r="E154" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>① S1-4</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr"/>
       <c r="F154" s="10" t="inlineStr">
         <is>
-          <t>フェンスに掛ける（引き・三脚で固定）。カメラは止めたまま、背景の街だけが動く。　［0-8秒］</t>
+          <t>ドアが開くと、もう別の服になっている。同じ玄関、違う人。この一本の決まりごとを、いちばん最初に見せてしまう。　［0-5秒］</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr"/>
@@ -3873,16 +3865,24 @@
         <v>144</v>
       </c>
       <c r="B155" s="7" t="inlineStr"/>
-      <c r="C155" s="7" t="inlineStr"/>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>街歩き・夕方の斜光（④）</t>
+        </is>
+      </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>④ S1-2</t>
-        </is>
-      </c>
-      <c r="E155" s="7" t="inlineStr"/>
+          <t>④ S1-1</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F155" s="10" t="inlineStr">
         <is>
-          <t>鞄を肩に掛けて立つ（横・引き）　［0-8秒］</t>
+          <t>フェンスに掛ける（引き・三脚で固定）。カメラは止めたまま、背景の街だけが動く。　［0-8秒］</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr"/>
@@ -3896,13 +3896,13 @@
       <c r="C156" s="7" t="inlineStr"/>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>④ S1-3</t>
+          <t>④ S1-2</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr"/>
       <c r="F156" s="10" t="inlineStr">
         <is>
-          <t>石壁の前。全身の引き。顔は主役にしない。　［0-8秒］</t>
+          <t>鞄を肩に掛けて立つ（横・引き）　［0-8秒］</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr"/>
@@ -3916,13 +3916,13 @@
       <c r="C157" s="7" t="inlineStr"/>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>④ S2-1</t>
+          <t>④ S1-3</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr"/>
       <c r="F157" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄の口を開ける。　［8-15秒］</t>
+          <t>石壁の前。全身の引き。顔は主役にしない。　［0-8秒］</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr"/>
@@ -3936,13 +3936,13 @@
       <c r="C158" s="7" t="inlineStr"/>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>④ S2-2</t>
+          <t>④ S2-1</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr"/>
       <c r="F158" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。中身を整える手（寄り）　［8-15秒］</t>
+          <t>真俯瞰。鞄の口を開ける。　［8-15秒］</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr"/>
@@ -3956,13 +3956,13 @@
       <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>④ S2-3</t>
+          <t>④ S2-2</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="10" t="inlineStr">
         <is>
-          <t>次の画へ横にスライドしてつなぐ。参考動画のつなぎ方はこれ一つだけ。　［8-15秒］</t>
+          <t>真俯瞰。中身を整える手（寄り）　［8-15秒］</t>
         </is>
       </c>
       <c r="G159" s="11" t="inlineStr"/>
@@ -3976,13 +3976,13 @@
       <c r="C160" s="7" t="inlineStr"/>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>④ S3-1</t>
+          <t>④ S2-3</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr"/>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>高い通路を歩く（引き・映画的）　［15-22秒］</t>
+          <t>次の画へ横にスライドしてつなぐ。参考動画のつなぎ方はこれ一つだけ。　［8-15秒］</t>
         </is>
       </c>
       <c r="G160" s="11" t="inlineStr"/>
@@ -3996,13 +3996,13 @@
       <c r="C161" s="7" t="inlineStr"/>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>④ S3-2</t>
+          <t>④ S3-1</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>肩に掛かった鞄に寄る。　［15-22秒］</t>
+          <t>高い通路を歩く（引き・映画的）　［15-22秒］</t>
         </is>
       </c>
       <c r="G161" s="11" t="inlineStr"/>
@@ -4016,13 +4016,13 @@
       <c r="C162" s="7" t="inlineStr"/>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>④ S3-3</t>
+          <t>④ S3-2</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="10" t="inlineStr">
         <is>
-          <t>鞄と脚だけ（歩く）　［15-22秒］</t>
+          <t>肩に掛かった鞄に寄る。　［15-22秒］</t>
         </is>
       </c>
       <c r="G162" s="11" t="inlineStr"/>
@@ -4036,13 +4036,13 @@
       <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>④ S4-1</t>
+          <t>④ S3-3</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>フェンスの前で立ち止まる。　［22-30秒］</t>
+          <t>鞄と脚だけ（歩く）　［15-22秒］</t>
         </is>
       </c>
       <c r="G163" s="11" t="inlineStr"/>
@@ -4056,13 +4056,13 @@
       <c r="C164" s="7" t="inlineStr"/>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>④ S4-2</t>
+          <t>④ S4-1</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr"/>
       <c r="F164" s="10" t="inlineStr">
         <is>
-          <t>真俯瞰。鞄と持ち物・靴を並べる置き画。この画で終わる。参考動画に写っている他社の布袋と金具はぼかしてあります。　［22-30秒］</t>
+          <t>フェンスの前で立ち止まる。　［22-30秒］</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr"/>
@@ -4076,13 +4076,13 @@
       <c r="C165" s="7" t="inlineStr"/>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>④ S4-3</t>
+          <t>④ S4-2</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr"/>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>そのままロゴだけ。テロップは出さない。　［22-30秒］</t>
+          <t>真俯瞰。鞄と持ち物・靴を並べる置き画。この画で終わる。参考動画に写っている他社の布袋と金具はぼかしてあります。　［22-30秒］</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr"/>
@@ -4093,24 +4093,16 @@
         <v>155</v>
       </c>
       <c r="B166" s="7" t="inlineStr"/>
-      <c r="C166" s="9" t="inlineStr">
-        <is>
-          <t>通勤路の並木道（①・同じ画角を使い回す）</t>
-        </is>
-      </c>
+      <c r="C166" s="7" t="inlineStr"/>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>① S2-1</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>④ S4-3</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr"/>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>全体。そのまま通勤路へ。並木道を歩いてくる全身の引き。すまし顔。　［5-9秒　｜　切り替わり＝玄関のドアが開く］</t>
+          <t>そのままロゴだけ。テロップは出さない。　［22-30秒］</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr"/>
@@ -4121,16 +4113,24 @@
         <v>156</v>
       </c>
       <c r="B167" s="7" t="inlineStr"/>
-      <c r="C167" s="7" t="inlineStr"/>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>通勤路の並木道（①・同じ画角を使い回す）</t>
+        </is>
+      </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>① S2-2</t>
-        </is>
-      </c>
-      <c r="E167" s="7" t="inlineStr"/>
+          <t>① S2-1</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F167" s="10" t="inlineStr">
         <is>
-          <t>腰より上。同じ人に寄る。鞄の色と表情が一度に見える。　［5-9秒　｜　切り替わり＝玄関のドアが開く］</t>
+          <t>全体。そのまま通勤路へ。並木道を歩いてくる全身の引き。すまし顔。　［5-9秒　｜　切り替わり＝玄関のドアが開く］</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr"/>
@@ -4144,13 +4144,13 @@
       <c r="C168" s="7" t="inlineStr"/>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>① S3-1</t>
+          <t>① S2-2</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>全体。車が抜けると、服も鞄の色も変わっている。　［9-13秒　｜　切り替わり＝手前を車が横切る］</t>
+          <t>腰より上。同じ人に寄る。鞄の色と表情が一度に見える。　［5-9秒　｜　切り替わり＝玄関のドアが開く］</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr"/>
@@ -4164,13 +4164,13 @@
       <c r="C169" s="7" t="inlineStr"/>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>① S3-2</t>
+          <t>① S3-1</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr"/>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>腰より上。サングラスを直す。ここは笑っている表情で。　［9-13秒　｜　切り替わり＝手前を車が横切る］</t>
+          <t>全体。車が抜けると、服も鞄の色も変わっている。　［9-13秒　｜　切り替わり＝手前を車が横切る］</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr"/>
@@ -4181,24 +4181,16 @@
         <v>159</v>
       </c>
       <c r="B170" s="7" t="inlineStr"/>
-      <c r="C170" s="9" t="inlineStr">
-        <is>
-          <t>駅の構内（①）</t>
-        </is>
-      </c>
+      <c r="C170" s="7" t="inlineStr"/>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>① S4-1</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr">
-        <is>
-          <t>カメラ／三脚／レフ板</t>
-        </is>
-      </c>
+          <t>① S3-2</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="10" t="inlineStr">
         <is>
-          <t>全体。柱が抜けると、場所が駅に変わっている。　［13-17秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
+          <t>腰より上。サングラスを直す。ここは笑っている表情で。　［9-13秒　｜　切り替わり＝手前を車が横切る］</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr"/>
@@ -4209,16 +4201,24 @@
         <v>160</v>
       </c>
       <c r="B171" s="7" t="inlineStr"/>
-      <c r="C171" s="7" t="inlineStr"/>
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>駅の構内（①）</t>
+        </is>
+      </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>① S4-2</t>
-        </is>
-      </c>
-      <c r="E171" s="7" t="inlineStr"/>
+          <t>① S4-1</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>カメラ／三脚／レフ板</t>
+        </is>
+      </c>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>腰より上。構内を歩く。少し急ぎ足の表情。　［13-17秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
+          <t>全体。柱が抜けると、場所が駅に変わっている。　［13-17秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr"/>
@@ -4232,13 +4232,13 @@
       <c r="C172" s="7" t="inlineStr"/>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>① S5-1</t>
+          <t>① S4-2</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="10" t="inlineStr">
         <is>
-          <t>全体。人が抜けると五色目。通路を横移動で追う。　［17-21秒　｜　切り替わり＝手前を人が横切る］</t>
+          <t>腰より上。構内を歩く。少し急ぎ足の表情。　［13-17秒　｜　切り替わり＝手前を駅の柱が横切る］</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr"/>
@@ -4252,13 +4252,13 @@
       <c r="C173" s="7" t="inlineStr"/>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>① S5-2</t>
+          <t>① S5-1</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr"/>
       <c r="F173" s="10" t="inlineStr">
         <is>
-          <t>腰より上。入口に着く。顔を上げる。　［17-21秒　｜　切り替わり＝手前を人が横切る］</t>
+          <t>全体。人が抜けると五色目。通路を横移動で追う。　［17-21秒　｜　切り替わり＝手前を人が横切る］</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr"/>
@@ -4268,29 +4268,17 @@
       <c r="A174" s="7" t="n">
         <v>163</v>
       </c>
-      <c r="B174" s="8" t="inlineStr">
-        <is>
-          <t>締めカード</t>
-        </is>
-      </c>
-      <c r="C174" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。文字を組んで作る</t>
-        </is>
-      </c>
+      <c r="B174" s="7" t="inlineStr"/>
+      <c r="C174" s="7" t="inlineStr"/>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-1</t>
-        </is>
-      </c>
-      <c r="E174" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
+          <t>① S5-2</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr"/>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
+          <t>腰より上。入口に着く。顔を上げる。　［17-21秒　｜　切り替わり＝手前を人が横切る］</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr"/>
@@ -4300,17 +4288,29 @@
       <c r="A175" s="7" t="n">
         <v>164</v>
       </c>
-      <c r="B175" s="7" t="inlineStr"/>
-      <c r="C175" s="7" t="inlineStr"/>
+      <c r="B175" s="8" t="inlineStr">
+        <is>
+          <t>締めカード</t>
+        </is>
+      </c>
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。文字を組んで作る</t>
+        </is>
+      </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-2</t>
-        </is>
-      </c>
-      <c r="E175" s="7" t="inlineStr"/>
+          <t>⑥ S9-1</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
       <c r="F175" s="10" t="inlineStr">
         <is>
-          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え。　［133-140秒］</t>
+          <t>対応技法の一覧（この見本のとおり文字で出す）。黒地に工程名を日英で三列。下段に「小ロットから量産まで」　［133-140秒］</t>
         </is>
       </c>
       <c r="G175" s="11" t="inlineStr"/>
@@ -4324,13 +4324,13 @@
       <c r="C176" s="7" t="inlineStr"/>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>⑥ S9-3</t>
+          <t>⑥ S9-2</t>
         </is>
       </c>
       <c r="E176" s="7" t="inlineStr"/>
       <c r="F176" s="10" t="inlineStr">
         <is>
-          <t>白に反転してロゴだけ。無音版はここでBGMも切る。　［133-140秒］</t>
+          <t>問い合わせ先とURL。社名・住所・TEL・メール・WEBを一画面。連絡先は確定したものに差し替え。　［133-140秒］</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr"/>
@@ -4341,24 +4341,16 @@
         <v>166</v>
       </c>
       <c r="B177" s="7" t="inlineStr"/>
-      <c r="C177" s="9" t="inlineStr">
-        <is>
-          <t>撮影不要。白に抜いてロゴだけ</t>
-        </is>
-      </c>
+      <c r="C177" s="7" t="inlineStr"/>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>⑧ S8-1</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="inlineStr">
-        <is>
-          <t>撮影不要</t>
-        </is>
-      </c>
+          <t>⑥ S9-3</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr"/>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>映像が白に抜けて、ロゴだけが残る。ここで音も切る。　［60秒］</t>
+          <t>白に反転してロゴだけ。無音版はここでBGMも切る。　［133-140秒］</t>
         </is>
       </c>
       <c r="G177" s="11" t="inlineStr"/>
@@ -4369,16 +4361,24 @@
         <v>167</v>
       </c>
       <c r="B178" s="7" t="inlineStr"/>
-      <c r="C178" s="7" t="inlineStr"/>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>撮影不要。白に抜いてロゴだけ</t>
+        </is>
+      </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>⑧ S8-2</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr"/>
+          <t>⑧ S8-1</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>撮影不要</t>
+        </is>
+      </c>
       <c r="F178" s="10" t="inlineStr">
         <is>
-          <t>―　［60秒］</t>
+          <t>映像が白に抜けて、ロゴだけが残る。ここで音も切る。　［60秒］</t>
         </is>
       </c>
       <c r="G178" s="11" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
       <c r="C179" s="7" t="inlineStr"/>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>⑧ S8-3</t>
+          <t>⑧ S8-2</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr"/>
@@ -4404,8 +4404,28 @@
       <c r="G179" s="11" t="inlineStr"/>
       <c r="H179" s="11" t="inlineStr"/>
     </row>
+    <row r="180" ht="32" customHeight="1">
+      <c r="A180" s="7" t="n">
+        <v>169</v>
+      </c>
+      <c r="B180" s="7" t="inlineStr"/>
+      <c r="C180" s="7" t="inlineStr"/>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>⑧ S8-3</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr"/>
+      <c r="F180" s="10" t="inlineStr">
+        <is>
+          <t>―　［60秒］</t>
+        </is>
+      </c>
+      <c r="G180" s="11" t="inlineStr"/>
+      <c r="H180" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A11:H179"/>
+  <autoFilter ref="A11:H180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf/02_場面別ショットリスト.xlsx
+++ b/pdf/02_場面別ショットリスト.xlsx
@@ -2842,7 +2842,7 @@
       <c r="E108" s="7" t="inlineStr"/>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>ここから最後までこの画角のまま。三品番とも同じ位置に置く。　［0-4秒］</t>
+          <t>ここから最後までこの画角のまま。　［0-4秒］</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
       <c r="E120" s="7" t="inlineStr"/>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>ロゴ。三品番とも同じ終わり方にする。　［20-25秒］</t>
+          <t>ロゴ。　［20-25秒］</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr"/>
